--- a/output/tlclighting_all.xlsx
+++ b/output/tlclighting_all.xlsx
@@ -606,7 +606,7 @@
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>{"cong_suat": "10W", "anh_sang": "Ba màu", "nhiet_do_mau": "3000k/6500K", "kich_thuoc": "ø120x30mm", "lo_khoet": "ø90mm", "chip_led": "OSRAM", "hieu_suat_quang": "900 Lm", "chi_so_hoan_mau": "CRI ≥ 85", "dien_ap": "150-265V", "thuong_hieu": "TLC LIGHTING", "chi_so_chong_choi_ugr": "~19-20 (Giảm tới 40%)", "bao_hanh": "24 tháng", "dien_ap_ac": "150 – 265V", "do_hoan_mau": "CRI≥85", "duong_kinh_lo_khoet": "Ø90mm", "kich_thuoc_den": "120x30mm", "chi_so_chong_am": "IP 54", "chip_led_xuat_xu": "OSRAM – CHLB Đức"}</t>
+          <t>{"cong_suat": "10W", "anh_sang": "Ba màu", "nhiet_do_mau": "3000k/6500K", "kich_thuoc_den": "120x30mm", "lo_khoet": "ø90mm", "chip_led": "OSRAM", "hieu_suat_quang": "900 Lm", "chi_so_hoan_mau": "CRI ≥ 85", "dien_ap": "150-265V", "thuong_hieu": "TLC LIGHTING", "chi_so_chong_choi_ugr": "~19-20 (Giảm tới 40%)", "bao_hanh": "24 tháng", "dien_ap_ac": "150 – 265V", "do_hoan_mau": "CRI≥85", "chi_so_chong_am": "IP 54"}</t>
         </is>
       </c>
       <c r="J2" t="n">
@@ -699,7 +699,7 @@
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>{"cong_suat": "10W", "anh_sang": "Đơn sắc", "nhiet_do_mau": "3000k/6500K", "kich_thuoc": "ø120x30mm", "lo_khoet": "ø90mm", "chip_led": "OSRAM", "hieu_suat_quang": "900 Lm", "chi_so_hoan_mau": "CRI ≥ 85", "dien_ap": "150-265V", "thuong_hieu": "TLC LIGHTING", "chi_so_chong_choi_ugr": "~19-20 (Giảm tới 40%)", "bao_hanh": "24 tháng", "dien_ap_ac": "150 – 265V", "do_hoan_mau": "CRI≥85", "duong_kinh_lo_khoet": "Ø90mm", "kich_thuoc_den": "120x30mm", "chi_so_chong_am": "IP 54", "chip_led_chlb_duc": "OSRAM – CHLB Đức"}</t>
+          <t>{"cong_suat": "10W", "anh_sang": "Đơn sắc", "nhiet_do_mau": "3000k/6500K", "kich_thuoc": "ø120x30mm", "lo_khoet": "ø90mm", "chip_led": "OSRAM", "hieu_suat_quang": "900 Lm", "chi_so_hoan_mau": "CRI ≥ 85", "dien_ap": "150-265V", "thuong_hieu": "TLC LIGHTING", "chi_so_chong_choi_ugr": "~19-20 (Giảm tới 40%)", "bao_hanh": "24 tháng", "dien_ap_ac": "150 – 265V", "kich_thuoc_den": "120x30mm", "chi_so_chong_am": "IP 54"}</t>
         </is>
       </c>
       <c r="J3" t="n">
@@ -885,7 +885,7 @@
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>{"cong_suat": "10W", "anh_sang": "Trắng", "nhiet_do_mau": "3000k/6500K", "kich_thuoc": "ø120x30mm", "lo_khoet": "ø90mm", "chip_led": "OSRAM", "hieu_suat_quang": "900 Lm", "chi_so_hoan_mau": "CRI ≥ 85", "dien_ap": "150-265V", "thuong_hieu": "TLC LIGHTING", "chi_so_chong_choi_ugr": "~19-20 (Giảm tới 40%)", "bao_hanh": "24 tháng", "dien_ap_ac": "150 – 265V", "do_hoan_mau": "CRI≥85", "kich_thuoc_den": "120x30mm", "chi_so_chong_am": "IP 54"}</t>
+          <t>{"cong_suat": "10W", "anh_sang": "Trắng, Vàng, Trung Tính", "nhiet_do_mau": "3000k/6500K", "kich_thuoc": "ø120x30mm", "lo_khoet": "ø90mm", "chip_led": "OSRAM", "hieu_suat_quang": "900 Lm", "chi_so_hoan_mau": "CRI ≥ 85", "dien_ap": "150-265V", "thuong_hieu": "TLC LIGHTING", "chi_so_chong_choi_UGR": "~19-20 (Giảm tới 40%)", "bao_hanh": "24 tháng", "dien_ap_AC": "150 – 265V", "do_hoan_mau": "CRI≥85", "kich_thuoc_den": "120x30mm", "chi_so_chong_am": "IP 54"}</t>
         </is>
       </c>
       <c r="J5" t="n">
@@ -1339,7 +1339,7 @@
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>{"cong_suat": "8W", "anh_sang": "Ba màu", "nhiet_do_mau": "3000k/6500K", "kich_thuoc": "ø120x30mm", "lo_khoet": "ø90mm", "chip_led": "OSRAM", "hieu_suat_quang": "720 Lm", "chi_so_hoan_mau": "CRI ≥ 85", "dien_ap": "150-265V", "thuong_hieu": "TLC LIGHTING", "chi_so_chong_choi_UGR": "~19-20 (Giảm tới 40%)", "bao_hanh": "24 tháng", "dien_ap_AC": "150 – 265V", "do_hoan_mau": "CRI≥85", "duong_kinh_lo_khoet": "Ø90mm", "kich_thuoc_den": "120x30mm", "chi_so_chong_am": "IP 54"}</t>
+          <t>{"cong_suat": "8W", "anh_sang": "Ba màu", "nhiet_do_mau": "3000k/6500K", "kich_thuoc": "ø120x30mm", "lo_khoet": "ø90mm", "chip_led": "OSRAM", "hieu_suat_quang": "720 Lm", "chi_so_hoan_mau": "CRI ≥ 85", "dien_ap": "150-265V", "thuong_hieu": "TLC LIGHTING", "chi_so_chong_choi_ugr": "~19-20 (Giảm tới 40%)", "bao_hanh": "24 tháng", "dien_ap_ac": "150 – 265V", "do_hoan_mau": "CRI≥85", "duong_kinh_lo_khoet": "Ø90mm", "kich_thuoc_den": "120x30mm", "chi_so_chong_am": "IP 54", "chip_led_chlb_duc": "OSRAM – CHLB Đức"}</t>
         </is>
       </c>
       <c r="J10" t="n">
@@ -1432,7 +1432,7 @@
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>{"cong_suat": "8W", "anh_sang": "Trắng | Vàng | Trung Tính", "nhiet_do_mau": "3000k/6500K", "kich_thuoc": "ø120x30mm", "lo_khoet": "ø90mm", "chip_led": "OSRAM", "hieu_suat_quang": "720 Lm", "chi_so_hoan_mau": "CRI ≥ 85", "dien_ap": "150-265V", "thuong_hieu": "TLC LIGHTING", "chi_so_chong_choi_ugr": "~19-20 (Giảm tới 40%)", "bao_hanh": "24 tháng", "dien_ap_ac": "150 – 265V", "do_hoan_mau": "CRI≥85", "duong_kinh_lo_khoet": "Ø90mm", "kich_thuoc_den": "120x30mm", "chi_so_chong_am": "IP 54", "chip_led_chlb_duc": "OSRAM – CHLB Đức"}</t>
+          <t>{"cong_suat": "8W", "anh_sang": "Trắng | Vàng | Trung Tính", "nhiet_do_mau": "3000k/6500K", "kich_thuoc": "ø120x30mm", "lo_khoet": "ø90mm", "chip_led": "OSRAM", "hieu_suat_quang": "720 Lm", "chi_so_hoan_mau": "CRI ≥ 85", "dien_ap": "150-265V", "thuong_hieu": "TLC LIGHTING", "chi_so_chong_choi_ugr": "~19-20 (Giảm tới 40%)", "bao_hanh": "24 tháng", "dien_ap_ac": "150 – 265V", "do_hoan_mau": "CRI≥85", "kich_thuoc_den": "120x30mm", "chi_so_chong_am": "IP 54", "chip_led_chlb_duc": "OSRAM – CHLB Đức"}</t>
         </is>
       </c>
       <c r="J11" t="n">
@@ -1525,7 +1525,7 @@
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>{"cong_suat": "8W", "anh_sang": "Ba màu", "nhiet_do_mau": "3000k/6500K", "kich_thuoc": "ø120x30mm", "lo_khoet": "ø90mm", "chip_led": "OSRAM", "hieu_suat_quang": "720 Lm", "chi_so_hoan_mau": "CRI ≥ 85", "dien_ap": "150-265V", "thuong_hieu": "TLC LIGHTING", "chi_so_chong_choi_ugr": "~19-20 (Giảm tới 40%)", "bao_hanh": "24 tháng", "dien_ap_ac": "150 – 265V", "do_hoan_mau": "CRI≥85", "kich_thuoc_den": "120x30mm", "chi_so_chong_am": "IP 54"}</t>
+          <t>{"cong_suat": "8W", "anh_sang": "Ba màu", "nhiet_do_mau": "3000k/6500K", "kich_thuoc": "ø120x30mm", "lo_khoet": "ø90mm", "chip_led": "OSRAM", "hieu_suat_quang": "720 Lm", "chi_so_hoan_mau": "CRI ≥ 85", "dien_ap": "150-265V", "thuong_hieu": "TLC LIGHTING", "chi_so_chong_choi_ugr": "~19-20 (Giảm tới 40%)", "bao_hanh": "24 tháng", "dien_ap_ac": "150 – 265V", "do_hoan_mau": "CRI≥85", "duong_kinh_lo_khoet": "Ø90mm", "kich_thuoc_den": "120x30mm", "chi_so_chong_am": "IP 54", "chip_led_xuat_xu": "OSRAM – CHLB Đức"}</t>
         </is>
       </c>
       <c r="J12" t="n">
@@ -1618,7 +1618,7 @@
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>{"cong_suat": "8W", "anh_sang": "Trắng", "nhiet_do_mau": "3000k/6500K", "kich_thuoc": "ø120x30mm", "lo_khoet": "ø90mm", "chip_led": "OSRAM", "hieu_suat_quang": "720 Lm", "chi_so_hoan_mau": "CRI ≥ 85", "dien_ap": "150-265V", "thuong_hieu": "TLC LIGHTING", "chi_so_chong_choi_ugr": "~19-20 (Giảm tới 40%)", "bao_hanh": "24 tháng", "dien_ap_ac": "150 – 265V", "do_hoan_mau": "CRI≥85", "duong_kinh_lo_khoet": "Ø90mm", "kich_thuoc_den": "120x30mm", "chi_so_chong_am": "IP 54"}</t>
+          <t>{"cong_suat": "8W", "anh_sang": "Trắng, Vàng, Trung Tính", "nhiet_do_mau": "3000k/6500K", "kich_thuoc": "ø120x30mm", "lo_khoet": "ø90mm", "chip_led": "OSRAM", "hieu_suat_quang": "720 Lm", "chi_so_hoan_mau": "CRI ≥ 85", "dien_ap": "150-265V", "thuong_hieu": "TLC LIGHTING", "chi_so_chong_choi_ugr": "~19-20 (Giảm tới 40%)", "bao_hanh": "24 tháng", "dien_ap_ac": "150 – 265V", "do_hoan_mau": "CRI≥85", "duong_kinh_lo_khoet": "Ø90mm", "kich_thuoc_den": "120x30mm", "chi_so_chong_am": "IP 54", "chip_led_chi_lb_duc": "OSRAM – CHLB Đức"}</t>
         </is>
       </c>
       <c r="J13" t="n">
@@ -1809,7 +1809,7 @@
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>{"cong_suat": "5W", "anh_sang": "Trắng/ Vàng, Trắng, Vàng", "nhiet_do_mau": "3500K/6500K", "kich_thuoc": "ø110x35mm, 110x35mm", "chip_led": "OSRAM, Chip OSRAM", "hieu_suat_quang": "110-120 Lm/w, 110~120Lm/w", "chi_so_hoan_mau": "CRI≥85", "dien_ap": "85-265V", "thuong_hieu": "TLC LIGHTING", "tuoi_tho": "40.000h", "bao_hanh": "30 tháng", "quang_thong": "575Lm", "do_hoan_mau": "&gt;85", "dien_ap_ac": "85-265V", "lo_khoet": "Ø72", "tuoi_tho_chip_led": "40.000 giờ"}</t>
+          <t>{"cong_suat": "5W", "anh_sang": "Trắng/ Vàng", "nhiet_do_mau": "3500K/6500K", "kich_thuoc": "ø110x35mm", "chip_led": "OSRAM", "hieu_suat_quang": "110-120 Lm/w", "chi_so_hoan_mau": "CRI≥85", "dien_ap": "85-265V", "thuong_hieu": "TLC LIGHTING", "tuoi_tho": "40.000h", "bao_hanh": "30 tháng", "quang_thong": "575Lm", "do_hoan_mau": "&gt;85", "dien_ap_ac": "85-265V", "lo_khoet": "Ø72", "tuoi_tho_chip_led": "40.000 giờ"}</t>
         </is>
       </c>
       <c r="J15" t="n">
@@ -2014,7 +2014,7 @@
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>{"cong_suat": "7W", "anh_sang": "Trắng/ Vàng", "nhiet_do_mau": "3500K/6500K", "kich_thuoc": "ø120x38mm", "chip_led": "OSRAM", "hieu_suat_quang": "110-120 Lm/w", "chi_so_hoan_mau": "CRI≥85", "dien_ap": "85-265V", "thuong_hieu": "TLC LIGHTING", "tuoi_tho": "40.000h", "bao_hanh": "30 tháng", "quang_thong": "805Lm", "dien_ap_ac": "85-265V", "tuoi_tho_chip_led": "40.000 giờ"}</t>
+          <t>{"cong_suat": "7W", "anh_sang": "Trắng/ Vàng", "nhiet_do_mau": "3500K/6500K", "kich_thuoc": "ø120x38mm", "chip_led": "OSRAM", "hieu_suat_quang": "110-120 Lm/w", "chi_so_hoan_mau": "CRI≥85", "dien_ap": "85-265V", "thuong_hieu": "TLC LIGHTING", "tuoi_tho": "40.000h", "bao_hanh": "30 tháng", "quang_thong": "805Lm", "do_hoan_mau": "&gt;85", "dien_ap_ac": "85-265V", "tuoi_tho_chip_led": "40.000 giờ"}</t>
         </is>
       </c>
       <c r="J17" t="n">
@@ -2115,7 +2115,7 @@
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>{"cong_suat": "9W", "anh_sang": "Ba màu", "nhiet_do_mau": "3500K/6500K", "kich_thuoc": "ø145x39mm", "chip_led": "OSRAM", "hieu_suat_quang": "110-120 Lm/w", "chi_so_hoan_mau": "CRI≥85", "dien_ap": "85-265V", "thuong_hieu": "TLC LIGHTING", "tuoi_tho": "40.000h", "bao_hanh": "30 tháng", "quang_thong": "1035Lm", "do_hoan_mau": "&gt;85", "lo_khoet": "ø102", "tuoi_tho_chip_led": "40.000 giờ"}</t>
+          <t>{"cong_suat": "9W", "anh_sang": "Ba màu", "nhiet_do_mau": "3500K/6500K", "kich_thuoc": "ø145x39mm", "chip_led": "OSRAM", "hieu_suat_quang": "110-120 Lm/w", "chi_so_hoan_mau": "CRI≥85", "dien_ap": "85-265V", "thuong_hieu": "TLC LIGHTING", "tuoi_tho": "40.000h", "bao_hanh": "30 tháng", "quang_thong": "1035Lm", "do_hoan_mau": "&gt;85", "dien_ap_ac": "85-265V", "lo_khoet": "ø102", "tuoi_tho_chip_led": "40.000 giờ"}</t>
         </is>
       </c>
       <c r="J18" t="n">
@@ -2217,7 +2217,7 @@
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>{"cong_suat": "9W", "anh_sang": "Trắng/ Vàng", "nhiet_do_mau": "3500K/6500K", "kich_thuoc": "ø145x39mm", "chip_led": "OSRAM", "hieu_suat_quang": "110-120 Lm/w", "chi_so_hoan_mau": "CRI≥85", "dien_ap": "85-265V", "thuong_hieu": "TLC LIGHTING", "tuoi_tho": "40.000h", "bao_hanh": "30 tháng", "quang_thong": "1035Lm", "do_hoan_mau": "&gt;85", "dien_ap_ac": "85-265V", "lo_khoet": "ø102", "tuoi_tho_chip_led": "40.000 giờ"}</t>
+          <t>{"cong_suat": "9W", "anh_sang": "Trắng/ Vàng, Trắng, Vàng", "nhiet_do_mau": "3500K/6500K", "kich_thuoc": "ø145x39mm, 145x39mm", "chip_led": "OSRAM, Chip OSRAM", "hieu_suat_quang": "110-120 Lm/w, 110~120Lm/w", "chi_so_hoan_mau": "CRI≥85, &gt;85", "dien_ap": "85-265V", "thuong_hieu": "TLC LIGHTING", "tuoi_tho": "40.000h, 40.000 giờ", "bao_hanh": "30 tháng", "quang_thong": "1035Lm", "dien_ap_ac": "85-265V", "lo_khoet": "ø102"}</t>
         </is>
       </c>
       <c r="J19" t="n">
@@ -2424,7 +2424,7 @@
       </c>
       <c r="I21" t="inlineStr">
         <is>
-          <t>{"cong_suat": "5W", "anh_sang": "Trắng/ Vàng", "nhiet_do_mau": "3500K/6500K", "kich_thuoc": "ø110x35mm", "chip_led": "OSRAM", "hieu_suat_quang": "110-120 Lm/w", "chi_so_hoan_mau": "CRI≥85", "dien_ap": "85-265V", "thuong_hieu": "TLC LIGHTING", "tuoi_tho": "40.000h", "bao_hanh": "30 tháng", "quang_thong": "575Lm", "do_hoan_mau": "&gt;85", "dien_ap_ac": "85-265V", "lo_khoet": "ø72", "tuoi_tho_chip_led": "40.000 giờ"}</t>
+          <t>{"cong_suat": "5W", "anh_sang": "Trắng, Vàng", "nhiet_do_mau": "3500K/6500K", "kich_thuoc": "ø110x35mm", "chip_led": "OSRAM", "hieu_suat_quang": "110-120 Lm/w", "chi_so_hoan_mau": "CRI≥85", "dien_ap": "85-265V", "thuong_hieu": "TLC LIGHTING", "tuoi_tho": "40.000h", "bao_hanh": "30 tháng", "quang_thong": "575Lm", "do_hoan_mau": "&gt;85", "dien_ap_ac": "85-265V", "lo_khoet": "ø72", "tuoi_tho_chip_led": "40.000 giờ"}</t>
         </is>
       </c>
       <c r="J21" t="n">
@@ -2635,7 +2635,7 @@
       </c>
       <c r="I23" t="inlineStr">
         <is>
-          <t>{"cong_suat": "7W", "anh_sang": "Trắng/ Vàng, Trắng, Vàng", "nhiet_do_mau": "3500K/6500K", "kich_thuoc": "ø120x38mm, 120x38mm", "chip_led": "OSRAM, Chip OSRAM", "hieu_suat_quang": "110-120 Lm/w, 110~120Lm/w", "chi_so_hoan_mau": "CRI≥85, &gt;85", "dien_ap": "85-265V, 85-265V", "thuong_hieu": "TLC LIGHTING", "tuoi_tho": "40.000h", "bao_hanh": "30 tháng", "quang_thong": "805Lm", "lo_khoet": "ø82", "tuoi_tho_chip_led": "40.000 giờ"}</t>
+          <t>{"cong_suat": "7W", "anh_sang": "Trắng/ Vàng", "nhiet_do_mau": "3500K/6500K", "kich_thuoc": "ø120x38mm", "chip_led": "OSRAM", "hieu_suat_quang": "110-120 Lm/w", "chi_so_hoan_mau": "CRI≥85", "dien_ap": "85-265V", "thuong_hieu": "TLC LIGHTING", "tuoi_tho": "40.000h", "bao_hanh": "30 tháng", "quang_thong": "805Lm", "do_hoan_mau": "&gt;85", "dien_ap_ac": "85-265V", "lo_khoet": "ø82", "tuoi_tho_chip_led": "40.000 giờ"}</t>
         </is>
       </c>
       <c r="J23" t="n">
@@ -2740,7 +2740,7 @@
       </c>
       <c r="I24" t="inlineStr">
         <is>
-          <t>{"cong_suat": "9W", "anh_sang": "Ba màu", "nhiet_do_mau": "3500K/6500K", "kich_thuoc": "ø145x39mm", "chip_led": "OSRAM", "hieu_suat_quang": "110-120 Lm/w", "chi_so_hoan_mau": "CRI≥85", "dien_ap": "85-265V", "thuong_hieu": "TLC LIGHTING", "tuoi_tho": "40.000h", "bao_hanh": "30 tháng", "quang_thong": "1035Lm", "do_hoan_mau": "&gt;85", "dien_ap_ac": "85-265V", "lo_khoet": "102", "tuoi_tho_chip_led": "40.000 giờ"}</t>
+          <t>{"cong_suat": "9W", "anh_sang": "Ba màu", "nhiet_do_mau": "3500K/6500K", "kich_thuoc": "ø145x39mm", "chip_led": "OSRAM", "hieu_suat_quang": "110-120 Lm/w", "chi_so_hoan_mau": "CRI≥85", "dien_ap": "85-265V", "thuong_hieu": "TLC LIGHTING", "tuoi_tho": "40.000h", "bao_hanh": "30 tháng", "quang_thong": "1035Lm", "do_hoan_mau": "&gt;85", "dien_ap_ac": "85-265V", "lo_khoet": "102", "tuoi_tho_chip_LED": "40.000 giờ"}</t>
         </is>
       </c>
       <c r="J24" t="n">
@@ -3150,7 +3150,7 @@
       </c>
       <c r="I28" t="inlineStr">
         <is>
-          <t>{"cong_suat": "7W", "anh_sang": "Ba màu", "nhiet_do_mau": "3500K/6500K", "kich_thuoc": "ø120x38mm, 120x38mm", "chip_led": "OSRAM", "hieu_suat_quang": "110-120 Lm/w, 110~120Lm/w", "chi_so_hoan_mau": "CRI≥85", "dien_ap": "85-265V", "thuong_hieu": "TLC LIGHTING", "tuoi_tho": "40.000h", "bao_hanh": "24 tháng, 30 tháng", "quang_thong": "805Lm", "do_hoan_mau": "&gt;85", "dien_ap_ac": "85-265V", "lo_khoet": "ø82", "chip_led_thuong_hieu": "Chip OSRAM", "tuoi_tho_chip_led": "40.000 giờ"}</t>
+          <t>{"cong_suat": "7W", "anh_sang": "Ba màu", "nhiet_do_mau": "3500K/6500K", "kich_thuoc": "ø120x38mm", "chip_led": "OSRAM", "hieu_suat_quang": "110-120 Lm/w", "chi_so_hoan_mau": "CRI≥85", "dien_ap": "85-265V", "thuong_hieu": "TLC LIGHTING", "tuoi_tho": "40.000h", "bao_hanh": "24 tháng", "quang_thong": "805Lm", "do_hoan_mau": "&gt;85", "dien_ap_ac": "85-265V", "lo_khoet": "ø82", "tuoi_tho_chip_led": "40.000 giờ"}</t>
         </is>
       </c>
       <c r="J28" t="n">
@@ -3256,7 +3256,7 @@
       </c>
       <c r="I29" t="inlineStr">
         <is>
-          <t>{"cong_suat": "7W", "anh_sang": "Trắng/vàng/trung tính", "nhiet_do_mau": "3500K/6500K", "kich_thuoc": "ø120x38mm", "chip_led": "OSRAM", "hieu_suat_quang": "110-120 Lm/w", "chi_so_hoan_mau": "CRI≥85", "dien_ap": "85-265V", "thuong_hieu": "TLC LIGHTING", "tuoi_tho": "40.000h", "bao_hanh": "24 tháng", "quang_thong": "805Lm", "do_hoan_mau": "&gt;85", "dien_ap_ac": "85-265V", "lo_khoet": "ø82", "tuoi_tho_chip_led": "40.000 giờ"}</t>
+          <t>{"cong_suat": "7W", "anh_sang": "Trắng/vàng/trung tính", "nhiet_do_mau": "3500K/6500K", "kich_thuoc": "ø120x38mm", "chip_led": "OSRAM", "hieu_suat_quang": "110-120 Lm/w", "chi_so_hoan_mau": "CRI≥85", "dien_ap": "85-265V", "thuong_hieu": "TLC LIGHTING", "tuoi_tho": "40.000h", "bao_hanh": "24 tháng, 30 tháng", "quang_thong": "805Lm", "do_hoan_mau": "&gt;85", "dien_ap_ac": "85-265V", "lo_khoet": "ø82", "tuoi_tho_chip_led": "40.000 giờ"}</t>
         </is>
       </c>
       <c r="J29" t="n">
@@ -3362,7 +3362,7 @@
       </c>
       <c r="I30" t="inlineStr">
         <is>
-          <t>{"cong_suat": "9W", "anh_sang": "Ba màu", "nhiet_do_mau": "3500K/6500K", "kich_thuoc": "ø145x39mm, 145x39mm", "chip_led": "OSRAM, Chip OSRAM", "hieu_suat_quang": "110-120 Lm/w, 110~120Lm/w", "chi_so_hoan_mau": "CRI≥85", "dien_ap": "85-265V", "thuong_hieu": "TLC LIGHTING", "tuoi_tho": "40.000h", "bao_hanh": "24 tháng, 30 tháng", "quang_thong": "1035Lm", "do_hoan_mau": "&gt;85", "dien_ap_ac": "85-265V", "lo_khoet": "ø102", "tuoi_tho_chip_led": "40.000 giờ"}</t>
+          <t>{"cong_suat": "9W", "anh_sang": "Ba màu", "nhiet_do_mau": "3500K/6500K", "kich_thuoc": "ø145x39mm", "chip_led": "OSRAM", "hieu_suat_quang": "110-120 Lm/w", "chi_so_hoan_mau": "CRI≥85", "dien_ap": "85-265V", "thuong_hieu": "TLC LIGHTING", "tuoi_tho": "40.000h", "bao_hanh": "30 tháng", "quang_thong": "1035Lm", "do_hoan_mau": "&gt;85", "dien_ap_ac": "85-265V", "lo_khoet": "ø102", "tuoi_tho_chip_led": "40.000 giờ"}</t>
         </is>
       </c>
       <c r="J30" t="n">
@@ -3803,7 +3803,7 @@
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>{"cong_suat": "18W", "anh_sang": "Ba màu", "nhiet_do_mau": "3500K/6500K", "kich_thuoc": "220x220x25", "lo_khoet": "205×205", "hieu_suat_quang": "110-120 Lm/w", "chi_so_hoan_mau": "CRI≥85", "dien_ap": "85-265V", "thuong_hieu": "TLC LIGHTING", "tuoi_tho": "40.000h", "bao_hanh": "24 tháng"}</t>
+          <t>{"cong_suat": "18W", "anh_sang": "Ba màu", "nhiet_do_mau": "3500K/6500K", "kich_thuoc": "220x220x25", "hieu_suat_quang": "110-120 Lm/w, ~110Lm/w", "chi_so_hoan_mau": "CRI≥85", "dien_ap": "85-265V", "thuong_hieu": "TLC LIGHTING", "tuoi_tho": "40.000h, 40.000 giờ", "bao_hanh": "24 tháng", "do_hoan_mau": "&gt;90Ra", "che_do_anh_sang": "Chống chói", "quang_thong": "1440", "chat_lieu": "Hợp kim nhôm sơn tĩnh điện"}</t>
         </is>
       </c>
       <c r="J3" t="n">
@@ -3886,7 +3886,7 @@
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>{"cong_suat": "6W", "anh_sang": "Ba màu", "nhiet_do_mau": "3500K/6500K", "kich_thuoc": "115x115x25", "hieu_suat_quang": "110-120 Lm/w, 90-100 Lm/w", "chi_so_hoan_mau": "CRI≥85", "dien_ap": "85-265V", "thuong_hieu": "TLC LIGHTING", "tuoi_tho": "40.000h, 40.000 giờ", "bao_hanh": "24 tháng", "dien_ap_ac": "85-265V", "do_hoan_mau": "&gt;80 Ra", "che_do_anh_sang": "Chống chói", "duong_kinh_lo_khoet": "106×106", "quang_thong": "480 Lm", "chat_lieu": "Hợp kim nhôm sơn tĩnh điện"}</t>
+          <t>{"cong_suat": "6W", "anh_sang": "Ba màu", "nhiet_do_mau": "3500K/6500K", "kich_thuoc": "115x115x25", "hieu_suat_quang": "110-120 Lm/w, 90-100 Lm/w", "chi_so_hoan_mau": "CRI≥85", "dien_ap": "85-265V", "thuong_hieu": "TLC LIGHTING, TLC Lighting", "tuoi_tho": "40.000h, 40.000 giờ", "bao_hanh": "24 tháng", "dien_ap_ac": "85-265V", "do_hoan_mau": "&gt;80 Ra", "che_do_anh_sang": "Chống chói", "quang_thong": "480 Lm", "chat_lieu": "Hợp kim nhôm sơn tĩnh điện"}</t>
         </is>
       </c>
       <c r="J4" t="n">
@@ -3969,7 +3969,7 @@
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>{"cong_suat": "12W", "anh_sang": "trắng/vàng", "nhiet_do_mau": "3500K/6500K", "kich_thuoc": "168x168x25", "lo_khoet": "155×155", "hieu_suat_quang": "90-100 Lm/w", "chi_so_hoan_mau": "CRI≥85", "dien_ap": "85-265V", "thuong_hieu": "TLC LIGHTING", "tuoi_tho": "40.000h", "bao_hanh": "24 tháng", "dien_ap_ac": "85-265V", "quang_thong": "90-100 Lm/w, 960", "do_hoan_mau": "&gt;90Ra", "che_do_anh_sang": "Chống chói", "duong_kinh_lo_khoet": "155×155", "chat_lieu": "Hợp kim nhôm sơn tĩnh điện"}</t>
+          <t>{"cong_suat": "12W", "anh_sang": "trắng/vàng", "nhiet_do_mau": "3500K/6500K", "kich_thuoc": "168x168x25", "lo_khoet": "155×155", "hieu_suat_quang": "90-100 Lm/w", "chi_so_hoan_mau": "CRI≥85", "dien_ap": "85-265V", "thuong_hieu": "TLC LIGHTING", "tuoi_tho": "40.000h", "bao_hanh": "24 tháng", "dien_ap_ac": "85-265V", "quang_thong": "90-100 Lm/w, 960", "do_hoan_mau": "&gt;90Ra", "che_do_anh_sang": "Chống chói", "duong_kinh_lo_khoet": "155×155", "chat_lieu": "Hợp kim nhôm sơn tĩnh điện", "tuoi_tho_gio": "40.000 giờ"}</t>
         </is>
       </c>
       <c r="J5" t="n">
@@ -4159,7 +4159,7 @@
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>{"cong_suat": "6W", "anh_sang": "Ba màu", "nhiet_do_mau": "3500K/6500K", "kich_thuoc": "ø120x25mm", "lo_khoet": "Φ105", "hieu_suat_quang": "110-120 Lm/w", "chi_so_hoan_mau": "CRI≥85", "dien_ap": "85-265V", "thuong_hieu": "TLC LIGHTING", "tuoi_tho": "40.000h", "bao_hanh": "24 tháng", "dien_ap_ac": "85-265V", "hieu_suat_quang_2": "~110Lm/w", "do_hoan_mau": "&gt;90Ra", "che_do_anh_sang": "Chống chói", "duong_kinh_lo_khoet": "D105mm", "duong_kinh_mat": "D120mm", "chieu_day": "25mm", "chat_lieu": "Hợp kim nhôm sơn tĩnh điện", "tuoi_tho_2": "40.000 giờ"}</t>
+          <t>{"cong_suat": "6W", "anh_sang": "Ba màu", "nhiet_do_mau": "3500K/6500K", "kich_thuoc": "ø120x25mm", "lo_khoet": "Φ105", "hieu_suat_quang": "110-120 Lm/w", "chi_so_hoan_mau": "CRI≥85", "dien_ap": "85-265V", "thuong_hieu": "TLC LIGHTING", "tuoi_tho": "40.000h", "bao_hanh": "24 tháng", "dien_ap_ac": "85-265V", "do_hoan_mau": "&gt;90Ra", "che_do_anh_sang": "Chống chói", "duong_kinh_lo_khoet": "D105mm", "duong_kinh_mat": "D120mm", "chieu_day": "25mm", "chat_lieu": "Hợp kim nhôm sơn tĩnh điện", "tuoi_tho_gio": "40.000 giờ", "bao_hanh_nam": "2 năm"}</t>
         </is>
       </c>
       <c r="J7" t="n">
@@ -4257,7 +4257,7 @@
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>{"cong_suat": "9W", "anh_sang": "Ba màu", "nhiet_do_mau": "3500K/6500K", "kich_thuoc": "ø145x25mm", "lo_khoet": "Φ120", "hieu_suat_quang": "110-120 Lm/w", "chi_so_hoan_mau": "CRI≥85", "dien_ap": "85-265V", "thuong_hieu": "TLC LIGHTING", "tuoi_tho": "40.000h", "bao_hanh": "24 tháng", "dien_ap_ac": "85-265V", "hieu_suat_quang_2": "~110Lm/w", "do_hoan_mau": "&gt;90Ra", "che_do_anh_sang": "Chống chói", "duong_kinh_lo_khoet": "D120mm", "duong_kinh_mat": "D145mm", "chieu_day": "25mm", "chat_lieu": "Hợp kim nhôm sơn tĩnh điện", "tuoi_tho_2": "40.000 giờ"}</t>
+          <t>{"cong_suat": "9W", "anh_sang": "Ba màu", "nhiet_do_mau": "3500K/6500K", "kich_thuoc": "ø145x25mm", "lo_khoet": "Φ120", "hieu_suat_quang": "110-120 Lm/w, ~110Lm/w", "chi_so_hoan_mau": "CRI≥85", "dien_ap": "85-265V", "thuong_hieu": "TLC LIGHTING", "tuoi_tho": "40.000h, 40.000 giờ", "bao_hanh": "24 tháng, 2 năm", "dien_ap_ac": "85-265V", "do_hoan_mau": "&gt;90Ra", "che_do_anh_sang": "Chống chói", "duong_kinh_lo_khoet": "D120mm", "duong_kinh_mat": "D145mm", "chieu_day": "25mm", "chat_lieu": "Hợp kim nhôm sơn tĩnh điện"}</t>
         </is>
       </c>
       <c r="J8" t="n">
@@ -4352,7 +4352,7 @@
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>{"cong_suat": "9W", "anh_sang": "trắng/vàng", "nhiet_do_mau": "3500K/6500K", "kich_thuoc": "ø145x25mm", "lo_khoet": "Φ120", "hieu_suat_quang": "110-120 Lm/w", "chi_so_hoan_mau": "CRI≥85", "dien_ap": "85-265V", "thuong_hieu": "TLC LIGHTING", "tuoi_tho": "40.000h", "bao_hanh": "24 tháng", "dien_ap_ac": "85-265V", "hieu_suat_quang_2": "~110Lm/w", "do_hoan_mau": "&gt;90Ra", "che_do_anh_sang": "Chống chói", "duong_kinh_lo_khoet": "D120mm", "duong_kinh_mat": "D145mm", "chieu_day": "25mm", "chat_lieu": "Hợp kim nhôm sơn tĩnh điện", "tuoi_tho_2": "40.000 giờ", "bao_hanh_2": "2 năm"}</t>
+          <t>{"cong_suat": "9W", "anh_sang": "trắng/vàng", "nhiet_do_mau": "3500K/6500K", "kich_thuoc": "ø145x25mm", "lo_khoet": "Φ120", "hieu_suat_quang": "110-120 Lm/w", "chi_so_hoan_mau": "CRI≥85", "dien_ap": "85-265V", "thuong_hieu": "TLC LIGHTING", "tuoi_tho": "40.000h", "bao_hanh": "24 tháng", "dien_ap_ac": "85-265V", "hieu_suat_quang_2": "~110Lm/w", "do_hoan_mau": "&gt;90Ra", "che_do_anh_sang": "Chống chói", "duong_kinh_lo_khoet": "D120mm", "duong_kinh_mat": "D145mm", "chieu_day": "25mm", "chat_lieu": "Hợp kim nhôm sơn tĩnh điện", "tuoi_tho_2": "40.000 giờ"}</t>
         </is>
       </c>
       <c r="J9" t="n">
@@ -4550,7 +4550,7 @@
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>{"cong_suat": "12W", "anh_sang": "ba màu", "nhiet_do_mau": "3500K/6500K", "kich_thuoc": "ø168x25mm", "lo_khoet": "Φ155", "hieu_suat_quang": "110-120 Lm/w", "chi_so_hoan_mau": "CRI≥85", "dien_ap": "85-265V", "thuong_hieu": "TLC LIGHTING", "tuoi_tho": "40.000h", "bao_hanh": "24 tháng", "dien_ap_ac": "85-265V", "do_hoan_mau": "&gt;90Ra", "che_do_anh_sang": "Chống chói", "duong_kinh_lo_khoet": "D155mm", "duong_kinh_mat": "D168mm", "chieu_day": "25mm", "chat_lieu": "Hợp kim nhôm sơn tĩnh điện", "tuoi_tho_gio": "40.000 giờ"}</t>
+          <t>{"cong_suat": "12W", "anh_sang": "ba màu", "nhiet_do_mau": "3500K/6500K", "kich_thuoc": "ø168x25mm", "lo_khoet": "Φ155", "hieu_suat_quang": "110-120 Lm/w", "chi_so_hoan_mau": "CRI≥85", "dien_ap": "85-265V", "thuong_hieu": "TLC LIGHTING", "tuoi_tho": "40.000h", "bao_hanh": "24 tháng", "dien_ap_ac": "85-265V", "hieu_suat_quang_2": "~110Lm/w", "do_hoan_mau": "&gt;90Ra", "che_do_anh_sang": "Chống chói", "duong_kinh_lo_khoet": "D155mm", "duong_kinh_mat": "D168mm", "chieu_day": "25mm", "chat_lieu": "Hợp kim nhôm sơn tĩnh điện", "tuoi_tho_2": "40.000 giờ", "bao_hanh_2": "2 năm"}</t>
         </is>
       </c>
       <c r="J11" t="n">
@@ -4642,7 +4642,7 @@
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>{"cong_suat": "12W", "anh_sang": "Trắng/vàng", "nhiet_do_mau": "3500K/6500K", "kich_thuoc": "ø168x25mm", "lo_khoet": "Φ155", "hieu_suat_quang": "110-120 Lm/w, ~110Lm/w", "chi_so_hoan_mau": "CRI≥85", "dien_ap": "85-265V", "thuong_hieu": "TLC LIGHTING", "tuoi_tho": "40.000h, 40.000 giờ", "bao_hanh": "24 tháng, 2 năm", "dien_ap_ac": "85-265V", "do_hoan_mau": "&gt;90Ra", "che_do_anh_sang": "Chống chói", "duong_kinh_lo_khoet": "D155mm", "duong_kinh_mat": "D168mm", "chieu_day": "25mm", "chat_lieu": "Hợp kim nhôm sơn tĩnh điện"}</t>
+          <t>{"cong_suat": "12W", "anh_sang": "Trắng/vàng", "nhiet_do_mau": "3500K/6500K", "kich_thuoc": "ø168x25mm", "lo_khoet": "Φ155", "hieu_suat_quang": "110-120 Lm/w", "chi_so_hoan_mau": "CRI≥85", "dien_ap": "85-265V", "thuong_hieu": "TLC LIGHTING", "tuoi_tho": "40.000h", "bao_hanh": "24 tháng", "dien_ap_ac": "85-265V", "hieu_suat_quang_2": "~110Lm/w", "do_hoan_mau": "&gt;90Ra", "che_do_anh_sang": "Chống chói", "duong_kinh_lo_khoet": "D155mm", "duong_kinh_mat": "D168mm", "chieu_day": "25mm", "chat_lieu": "Hợp kim nhôm sơn tĩnh điện", "tuoi_tho_2": "40.000 giờ", "bao_hanh_2": "2 năm"}</t>
         </is>
       </c>
       <c r="J12" t="n">
@@ -4839,7 +4839,7 @@
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>{"cong_suat": "18W", "anh_sang": "trắng/vàng", "nhiet_do_mau": "3500K/6500K", "kich_thuoc": "ø220x25mm", "lo_khoet": "Φ205", "hieu_suat_quang": "110-120 Lm/w", "chi_so_hoan_mau": "CRI≥85", "dien_ap": "85-265V", "thuong_hieu": "TLC LIGHTING", "tuoi_tho": "40.000h", "bao_hanh": "24 tháng", "dien_ap_ac": "85-265V", "hieu_suat_quang_2": "~110Lm/w", "do_hoan_mau": "&gt;80Ra", "che_do_anh_sang": "Chống chói", "duong_kinh_lo_khoet": "D205mm", "duong_kinh_mat": "D220mm", "chieu_day": "25mm", "chat_lieu": "Hợp kim nhôm sơn tĩnh điện"}</t>
+          <t>{"cong_suat": "18W", "anh_sang": "trắng/vàng", "nhiet_do_mau": "3500K/6500K", "kich_thuoc": "ø220x25mm", "lo_khoet": "Φ205", "hieu_suat_quang": "110-120 Lm/w", "chi_so_hoan_mau": "CRI≥85", "dien_ap": "85-265V", "thuong_hieu": "TLC LIGHTING", "tuoi_tho": "40.000h", "bao_hanh": "24 tháng", "dien_ap_ac": "85-265V", "do_hoan_mau": "&gt;80Ra", "che_do_anh_sang": "Chống chói", "duong_kinh_lo_khoet": "D205mm", "duong_kinh_mat": "D220mm", "chieu_day": "25mm", "chat_lieu": "Hợp kim nhôm sơn tĩnh điện", "tuoi_tho_gio": "40.000 giờ", "bao_hanh_nam": "2 năm"}</t>
         </is>
       </c>
       <c r="J14" t="n">
@@ -5097,7 +5097,12 @@
       </c>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Thông tin liên hệ</t>
+          <t>âm trần
+Mặt đèn được đúc từ đồng nguyên khối dày dặn, chắc chắn, chống chịu được những tác động của ngoại lực do quá trình vận chuyển, lắp đặt.
+Tuổi thọ cao: 50.000 giờ
+Chip Led Citizen giúp ánh sáng trắng/ vàng của đèn ổn định.
+Tản nhiệt nhôm nguyên khối, kích thước nhỏ gọn, dễ dàng lắp đặt.
+Sản phẩm sau khi được khách hàng lắp đặt và sử dụng nếu gặp bất kỳ sự cố nào do nhà sản xuất sẽ được đổi mới trong vòng 3 năm và bảo hành trực tiếp tại dự án trong 2 năm.</t>
         </is>
       </c>
       <c r="Q2" t="inlineStr">
@@ -5131,8 +5136,7 @@
       </c>
       <c r="T2" t="inlineStr">
         <is>
-          <t>Ưu điểm
-Đèn
+          <t>Đèn
 âm trần
 cổ điển 18K
 có thiết kế sang trọng, hơn cả một sản phẩm để chiếu sáng, thì đây là một yếu tố giúp khẳng định đẳng cấp công trình của bạn.
@@ -5140,16 +5144,7 @@
 Tuổi thọ cao: 50.000 giờ
 Chip Led Citizen giúp ánh sáng trắng/ vàng của đèn ổn định.
 Tản nhiệt nhôm nguyên khối, kích thước nhỏ gọn, dễ dàng lắp đặt.
-Sản phẩm sau khi được khách hàng lắp đặt và sử dụng nếu gặp bất kỳ sự cố nào do nhà sản xuất sẽ được đổi mới trong vòng 3 năm và bảo hành trực tiếp tại dự án trong 2 năm.
-***Mọi thông tin chi tiết xin vui lòng liên hệ: 18006192
-Thông tin liên hệ:
-CÔNG TY CỔ PHẦN ĐÈN CHIẾU SÁNG THIÊN LỘC
-VPGD: Tầng 7, tòa nhà Nam Cường Building, đường Tố Hữu, Q. Hà Đông, TP Hà Nội
-NMSX: Lô CN8.1, đường D4, KCN Châu Sơn, TP. Phủ Lý, tỉnh Hà Nam.
-CN: số 82, đường số 3, khu phố 6, Bình Hưng Hòa, Bình Tân, TP. HCM
-Hotline: 1800.6192
-Website: www.tlclighting.com.vn
-Email: info@tlclighting.com.vn</t>
+Sản phẩm sau khi được khách hàng lắp đặt và sử dụng nếu gặp bất kỳ sự cố nào do nhà sản xuất sẽ được đổi mới trong vòng 3 năm và bảo hành trực tiếp tại dự án trong 2 năm.</t>
         </is>
       </c>
     </row>
@@ -5179,7 +5174,7 @@
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>{"cong_suat": "10W", "anh_sang": "Trắng/ Vàng, Trắng, Vàng", "nhiet_do_mau": "3500K/6500K", "kich_thuoc": "ø108x70mm, 108x70mm", "lo_khoet": "ø76mm", "chip_led": "Citizen, Chip Citizen", "hieu_suat_quang": "150Lm/w", "chi_so_hoan_mau": "CRI=85", "dien_ap": "100-275V", "thuong_hieu": "TLC LIGHTING", "tuoi_tho": "40.000h", "bao_hanh": "24 tháng", "quang_thong": "1450Lm", "do_hoan_mau": "=85", "dien_ap_ac": "100-275V", "tuoi_tho_chip_led": "40.000 giờ"}</t>
+          <t>{"cong_suat": "10W", "anh_sang": "Trắng/ Vàng", "nhiet_do_mau": "3500K/6500K", "kich_thuoc": "ø108x70mm", "lo_khoet": "ø76mm", "chip_led": "Citizen", "hieu_suat_quang": "150Lm/w", "chi_so_hoan_mau": "CRI=85", "dien_ap": "100-275V", "thuong_hieu": "TLC LIGHTING", "tuoi_tho": "40.000h", "bao_hanh": "24 tháng", "quang_thong": "1450Lm", "do_hoan_mau": "=85", "dien_ap_ac": "100-275V", "tuoi_tho_chip_led": "40.000 giờ"}</t>
         </is>
       </c>
       <c r="J3" t="n">
@@ -5410,7 +5405,7 @@
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>{"cong_suat": "7W", "anh_sang": "Ba màu", "nhiet_do_mau": "3500K/6500K", "kich_thuoc": "ø120x38mm", "lo_khoet": "ø82mm", "chip_led": "Chip COB", "hieu_suat_quang": "110-120 Lm/w", "chi_so_hoan_mau": "CRI≥85", "dien_ap": "85-265V", "thuong_hieu": "TLC LIGHTING", "tuoi_tho": "40.000h", "bao_hanh": "24 tháng", "quang_thong": "770Lm", "dien_ap_ac": "85-265V", "tuoi_tho_chip_led": "40.000 giờ"}</t>
+          <t>{"cong_suat": "7W", "anh_sang": "Ba màu", "nhiet_do_mau": "3500K/6500K", "kich_thuoc": "ø120x38mm", "chip_led": "Chip COB", "hieu_suat_quang": "110-120 Lm/w", "chi_so_hoan_mau": "CRI≥85", "dien_ap": "85-265V", "thuong_hieu": "TLC LIGHTING", "tuoi_tho": "40.000h", "bao_hanh": "24 tháng", "quang_thong": "770Lm", "do_hoan_mau": "&gt;85", "dien_ap_ac": "85-265V", "lo_khoet": "82", "tuoi_tho_chip_led": "40.000 giờ"}</t>
         </is>
       </c>
       <c r="J2" t="n">
@@ -5424,6 +5419,17 @@
       <c r="M2" t="inlineStr">
         <is>
           <t>https://tlclighting.com.vn/wp-content/uploads/2019/08/den-led-am-tran-cob-plast.png</t>
+        </is>
+      </c>
+      <c r="P2" t="inlineStr">
+        <is>
+          <t>Đèn sử dụng chip LED COB với khả năng chiếu sáng vượt trội. Hiệu suất quang lên tới 110 – 120 Lm/w.
+Ánh sáng đèn giúp bảo vệ mắt hiệu quả theo tiêu chuẩn Châu Âu với Ra &gt; 85.
+Công nghệ sơn Plast bền màu với chính sách bảo hành màu sắc 5 năm.
+Thiết kế: mặt cong mềm mại cong bo ôm sát trần với viền bạch kim tạo điểm nhấn sang trọng cho thiết kế không gian.
+Tản nhiệt của đèn được đúc từ nhôm nguyên khối với cấu tạo đa chiều cho hiệu quả tản nhiệt hiệu quả.
+Tuổi thọ của đèn lên đến 40.000 giờ chiếu sáng, giúp tiết kiệm chi phí bảo trì, bảo dưỡng hay thay mới.
+Chóa đèn được làm từ kính thủy tinh với lớp chóa sần mờ tránh ánh sáng trực tiếp, cho ánh sáng đồng đều, tốt cho mắt.</t>
         </is>
       </c>
       <c r="Q2" t="inlineStr">
@@ -5446,6 +5452,19 @@
 3 màu: Tham khảo tại đây</t>
         </is>
       </c>
+      <c r="T2" t="inlineStr">
+        <is>
+          <t>Những ưu điểm của đèn âm trần COB Plast ba màu
+Đèn LED âm trần COB Plast
+Đèn sử dụng chip LED COB với khả năng chiếu sáng vượt trội. Hiệu suất quang lên tới 110 – 120 Lm/w.
+Ánh sáng đèn giúp bảo vệ mắt hiệu quả theo tiêu chuẩn Châu Âu với Ra &gt; 85.
+Công nghệ sơn Plast bền màu với chính sách bảo hành màu sắc 5 năm.
+Thiết kế: mặt cong mềm mại cong bo ôm sát trần với viền bạch kim tạo điểm nhấn sang trọng cho thiết kế không gian.
+Tản nhiệt của đèn được đúc từ nhôm nguyên khối với cấu tạo đa chiều cho hiệu quả tản nhiệt hiệu quả.
+Tuổi thọ của đèn lên đến 40.000 giờ chiếu sáng, giúp tiết kiệm chi phí bảo trì, bảo dưỡng hay thay mới.
+Chóa đèn được làm từ kính thủy tinh với lớp chóa sần mờ tránh ánh sáng trực tiếp, cho ánh sáng đồng đều, tốt cho mắt.</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -5473,7 +5492,7 @@
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>{"cong_suat": "7W", "anh_sang": "Trắng/ Vàng, Trắng, Vàng", "nhiet_do_mau": "3500K/6500K", "kich_thuoc": "ø120x38mm, 120x38mm", "lo_khoet": "ø82mm, 82, Φ82", "chip_led": "Chip COB", "hieu_suat_quang": "110-120 Lm/w, 110~120Lm/w", "chi_so_hoan_mau": "CRI≥85", "dien_ap": "85-265V", "thuong_hieu": "TLC LIGHTING", "tuoi_tho": "40.000h", "bao_hanh": "24 tháng", "quang_thong": "770Lm", "do_hoan_mau": "&gt;85", "dien_ap_ac": "85-265V", "tuoi_tho_chip_led": "40.000 giờ"}</t>
+          <t>{"cong_suat": "7W", "anh_sang": "Trắng/ Vàng", "nhiet_do_mau": "3500K/6500K", "kich_thuoc": "ø120x38mm", "lo_khoet": "ø82mm", "chip_led": "Chip COB", "hieu_suat_quang": "110-120 Lm/w", "chi_so_hoan_mau": "CRI≥85", "dien_ap": "85-265V", "thuong_hieu": "TLC LIGHTING", "tuoi_tho": "40.000h", "bao_hanh": "24 tháng", "quang_thong": "770Lm", "do_hoan_mau": "&gt;85", "dien_ap_ac": "85-265V", "lo_khoet_phi": "82", "tuoi_tho_chip_led": "40.000 giờ"}</t>
         </is>
       </c>
       <c r="J3" t="n">
@@ -5487,6 +5506,17 @@
       <c r="M3" t="inlineStr">
         <is>
           <t>https://tlclighting.com.vn/wp-content/uploads/2019/08/den-led-am-tran-cob-plast.png</t>
+        </is>
+      </c>
+      <c r="P3" t="inlineStr">
+        <is>
+          <t>Đèn sử dụng chip LED COB với khả năng chiếu sáng vượt trội. Hiệu suất quang lên tới 110 – 120 Lm/w.
+Ánh sáng đèn giúp bảo vệ mắt hiệu quả theo tiêu chuẩn Châu Âu với Ra &gt; 85.
+Công nghệ sơn Plast bền màu với chính sách bảo hành màu sắc 5 năm.
+Thiết kế: mặt cong mềm mại cong bo ôm sát trần với viền bạch kim tạo điểm nhấn sang trọng cho thiết kế không gian.
+Tản nhiệt của đèn được đúc từ nhôm nguyên khối với cấu tạo đa chiều cho hiệu quả tản nhiệt hiệu quả.
+Tuổi thọ của đèn lên đến 40.000 giờ chiếu sáng, giúp tiết kiệm chi phí bảo trì, bảo dưỡng hay thay mới.
+Chóa đèn được làm từ kính thủy tinh với lớp chóa sần mờ tránh ánh sáng trực tiếp, cho ánh sáng đồng đều, tốt cho mắt.</t>
         </is>
       </c>
       <c r="Q3" t="inlineStr">
@@ -5522,6 +5552,19 @@
 3 màu: Tham khảo tại đây</t>
         </is>
       </c>
+      <c r="T3" t="inlineStr">
+        <is>
+          <t>Những ưu điểm của đèn âm trần COB Plast đơn sắc
+Đèn LED âm trần COB Plast
+Đèn sử dụng chip LED COB với khả năng chiếu sáng vượt trội. Hiệu suất quang lên tới 110 – 120 Lm/w.
+Ánh sáng đèn giúp bảo vệ mắt hiệu quả theo tiêu chuẩn Châu Âu với Ra &gt; 85.
+Công nghệ sơn Plast bền màu với chính sách bảo hành màu sắc 5 năm.
+Thiết kế: mặt cong mềm mại cong bo ôm sát trần với viền bạch kim tạo điểm nhấn sang trọng cho thiết kế không gian.
+Tản nhiệt của đèn được đúc từ nhôm nguyên khối với cấu tạo đa chiều cho hiệu quả tản nhiệt hiệu quả.
+Tuổi thọ của đèn lên đến 40.000 giờ chiếu sáng, giúp tiết kiệm chi phí bảo trì, bảo dưỡng hay thay mới.
+Chóa đèn được làm từ kính thủy tinh với lớp chóa sần mờ tránh ánh sáng trực tiếp, cho ánh sáng đồng đều, tốt cho mắt.</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -5549,7 +5592,7 @@
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>{"thuong_hieu": "TLC LIGHTING", "cong_suat": "14W", "kich_thuoc": "225x120x75", "hieu_suat_quang": "110~120Lm/w", "quang_thong": "770Lm", "do_hoan_mau": "&gt;80", "anh_sang": "Trắng/Vàng", "dien_ap_AC": "85-265V", "lo_khoet": "90×180", "chip_LED": "Chip COB", "tuoi_tho_chip_LED": "40.000 giờ", "bao_hanh": "24 tháng", "dien_ap": "85 ~265 V", "tuoi_tho": "&gt; 50.000 giờ"}</t>
+          <t>{"thuong_hieu": "TLC LIGHTING", "cong_suat": "14W", "kich_thuoc": "225x120x75", "hieu_suat_quang": "110~120Lm/w", "quang_thong": "770Lm", "do_hoan_mau": "&gt;80", "anh_sang": "Trắng/Vàng", "dien_ap_ac": "85-265V", "lo_khoet": "90×180", "chip_led": "Chip COB", "tuoi_tho_chip_led": "40.000 giờ", "bao_hanh": "24 tháng"}</t>
         </is>
       </c>
       <c r="J4" t="n">
@@ -5563,6 +5606,18 @@
       <c r="M4" t="inlineStr">
         <is>
           <t>https://tlclighting.com.vn/wp-content/uploads/2019/10/IMG_2407-min.jpg</t>
+        </is>
+      </c>
+      <c r="P4" t="inlineStr">
+        <is>
+          <t>Đèn hoạt động tốt trong dải điện áp rộng 85 ~265 V mà không bị hỏng và thay đổi cường độ sáng.
+Không nhấp nháy gây hại cho mắt người sử dụng.
+Hệ số hoàn màu cao: Ra &gt; 85
+Tuổi thọ cao: &gt; 50.000 giờ
+Đèn âm trần đôi COB 14w sử dụng 14 chíp led công suất 1w tạo quang thông lớn, các chíp led được bộ trí đối xứng tạo hiệu ứng ánh sáng.
+Bộ tản nhiệt của đèn LED âm trần và vỏ được chế tạo bằng hợp kim nhôm giúp tản nhiệt tốt, góc chiếu của bộ đèn có thể điều chỉnh được.
+Đèn LED tiết kiệm điện,thân thiện môi trường,ánh sáng không chói tốt cho mắt là sự lựa chọn tuyệt vời cho chiếu sáng
+Bộ phận tản nhiệt của đèn được thiết kế đặc biệt giúp đèn chiếu sáng hiệu quả và tuổi thọ cao giảm chi phí thay lắp, bảo dưỡng.</t>
         </is>
       </c>
       <c r="Q4" t="inlineStr">
@@ -5585,6 +5640,20 @@
 3 màu: Tham khảo tại đây</t>
         </is>
       </c>
+      <c r="T4" t="inlineStr">
+        <is>
+          <t>Đặc điểm của đèn LED âm trần đôi COB 2×7
+Đèn led âm trần đôi 2×7 mang thương hiệu TLC Lighting được thiết kế và sản xuất theo tiêu chuẩn của châu Âu nên sản phẩm không những có tính thẩm mỹ cao mà còn có độ bền vượt trội.
+Đèn hoạt động tốt trong dải điện áp rộng 85 ~265 V mà không bị hỏng và thay đổi cường độ sáng.
+Không nhấp nháy gây hại cho mắt người sử dụng.
+Hệ số hoàn màu cao: Ra &gt; 85
+Tuổi thọ cao: &gt; 50.000 giờ
+Đèn âm trần đôi COB 14w sử dụng 14 chíp led công suất 1w tạo quang thông lớn, các chíp led được bộ trí đối xứng tạo hiệu ứng ánh sáng.
+Bộ tản nhiệt của đèn LED âm trần và vỏ được chế tạo bằng hợp kim nhôm giúp tản nhiệt tốt, góc chiếu của bộ đèn có thể điều chỉnh được.
+Đèn LED tiết kiệm điện,thân thiện môi trường,ánh sáng không chói tốt cho mắt là sự lựa chọn tuyệt vời cho chiếu sáng
+Bộ phận tản nhiệt của đèn được thiết kế đặc biệt giúp đèn chiếu sáng hiệu quả và tuổi thọ cao giảm chi phí thay lắp, bảo dưỡng.</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -5626,6 +5695,18 @@
       <c r="M5" t="inlineStr">
         <is>
           <t>https://tlclighting.com.vn/wp-content/uploads/2019/10/IMG_2407-min.jpg</t>
+        </is>
+      </c>
+      <c r="P5" t="inlineStr">
+        <is>
+          <t>Đèn hoạt động tốt trong dải điện áp rộng 85 ~265 V mà không bị hỏng và thay đổi cường độ sáng.
+Không nhấp nháy gây hại cho mắt người sử dụng.
+Hệ số hoàn màu cao: Ra &gt; 85
+Tuổi thọ cao: &gt; 50.000 giờ
+Đèn âm trần đôi COB 14w sử dụng 14 chíp led công suất 1w tạo quang thông lớn, các chíp led được bộ trí đối xứng tạo hiệu ứng ánh sáng.
+Bộ tản nhiệt của đèn LED âm trần và vỏ được chế tạo bằng hợp kim nhôm giúp tản nhiệt tốt, góc chiếu của bộ đèn có thể điều chỉnh được.
+Đèn LED tiết kiệm điện,thân thiện môi trường,ánh sáng không chói tốt cho mắt là sự lựa chọn tuyệt vời cho chiếu sáng
+Bộ phận tản nhiệt của đèn được thiết kế đặc biệt giúp đèn chiếu sáng hiệu quả và tuổi thọ cao giảm chi phí thay lắp, bảo dưỡng.</t>
         </is>
       </c>
       <c r="Q5" t="inlineStr">
@@ -5660,6 +5741,20 @@
 3 màu: Tham khảo tại đây</t>
         </is>
       </c>
+      <c r="T5" t="inlineStr">
+        <is>
+          <t>Đặc điểm của đèn LED âm trần đôi COB 2×7
+Đèn led âm trần đôi 2×7 mang thương hiệu TLC Lighting được thiết kế và sản xuất theo tiêu chuẩn của châu Âu nên sản phẩm không những có tính thẩm mỹ cao mà còn có độ bền vượt trội.
+Đèn hoạt động tốt trong dải điện áp rộng 85 ~265 V mà không bị hỏng và thay đổi cường độ sáng.
+Không nhấp nháy gây hại cho mắt người sử dụng.
+Hệ số hoàn màu cao: Ra &gt; 85
+Tuổi thọ cao: &gt; 50.000 giờ
+Đèn âm trần đôi COB 14w sử dụng 14 chíp led công suất 1w tạo quang thông lớn, các chíp led được bộ trí đối xứng tạo hiệu ứng ánh sáng.
+Bộ tản nhiệt của đèn LED âm trần và vỏ được chế tạo bằng hợp kim nhôm giúp tản nhiệt tốt, góc chiếu của bộ đèn có thể điều chỉnh được.
+Đèn LED tiết kiệm điện,thân thiện môi trường,ánh sáng không chói tốt cho mắt là sự lựa chọn tuyệt vời cho chiếu sáng
+Bộ phận tản nhiệt của đèn được thiết kế đặc biệt giúp đèn chiếu sáng hiệu quả và tuổi thọ cao giảm chi phí thay lắp, bảo dưỡng.</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -5687,7 +5782,7 @@
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>{"cong_suat": "7W", "anh_sang": "Trắng/Vàng", "nhiet_do_mau": "3500K/6500K", "kich_thuoc": "ø107x66mm", "chip_LED": "Chip COB", "hieu_suat_quang": "110-120 Lm/w", "chi_so_hoan_mau": "CRI&gt;80", "dien_ap": "85-265V", "thuong_hieu": "TLC LIGHTING", "tuoi_tho": "40.000h", "bao_hanh": "24 tháng", "quang_thong": "770Lm", "do_hoan_mau": "&gt;80", "dien_ap_AC": "85-265V", "lo_khoet": "ø90", "tuoi_tho_chip_LED": "40.000 giờ"}</t>
+          <t>{"cong_suat": "7W", "anh_sang": "Trắng/Vàng", "nhiet_do_mau": "3500K/6500K", "kich_thuoc": "ø107x66mm", "chip_led": "Chip COB", "hieu_suat_quang": "110-120 Lm/w", "chi_so_hoan_mau": "CRI&gt;80", "dien_ap": "85-265V", "thuong_hieu": "TLC LIGHTING", "tuoi_tho": "40.000h", "bao_hanh": "24 tháng", "quang_thong": "770Lm", "do_hoan_mau": "&gt;80", "dien_ap_ac": "85-265V", "lo_khoet": "ø90", "tuoi_tho_chip_led": "40.000 giờ"}</t>
         </is>
       </c>
       <c r="J6" t="n">
@@ -5701,6 +5796,16 @@
       <c r="M6" t="inlineStr">
         <is>
           <t>https://tlclighting.com.vn/wp-content/uploads/2019/10/IMG_2383-min.jpg</t>
+        </is>
+      </c>
+      <c r="P6" t="inlineStr">
+        <is>
+          <t>Thân đèn và tản nhiệt làm bằng hợp kim nhôm cao cấp: khả năng chống va đập vượt trội, đèn có tuổi thọ cao, hạn chế chi phí bảo trì, bảo dưỡng, thay thế, đổi mới.
+Công suất 7w siêu sáng, siêu tiết kiệm, tương đương với 12w compact và 40w đèn sợi đốt: Đèn sử dụng chip LED COB với khả năng chiếu sáng vượt trội. Hiệu suất quang của đèn đạt 110-120  lm/w. Do vậy, đèn tiết kiệm 80% điện năng tiêu thụ so với đèn sợ đốt, 50% điện năng so với đèn huỳnh quang. Nhờ vậy, người sử dụng có thể tiết kiệm phần lớn chi phí cho điện năng tiêu thụ trong gia đình.
+Tản nhiệt nhôm dày, tăng tuổi thọ và độ bền màu: Tản nhiệt của đèn chính là bộ phận giải phóng nhiệt năng, duy trì cho bóng hoạt động tốt ở các điều kiện khác nhau. Đây chính là bộ phận có ảnh hưởng lớn tới tuổi thọ của bóng đèn.
+Ứng dụng công nghệ LED chất lượng cao. Chỉ số hoàn màu của đèn đạt Ra&gt; 85 cho hiệu quả chiếu sáng tốt, ánh sáng trung thực, tốt cho mắt, chống lóa – mỏi mắt, bảo vệ mắt theo tiêu chuẩn Châu Âu
+Tuổi thọ bóng: 40,000 giờ, Bảo hành 24 tháng trên toàn quốc
+Kết cấu tháo lắp đơn giản, tiện lợi, chắc chắn.</t>
         </is>
       </c>
       <c r="Q6" t="inlineStr">
@@ -5735,6 +5840,18 @@
 3 màu: Tham khảo tại đây</t>
         </is>
       </c>
+      <c r="T6" t="inlineStr">
+        <is>
+          <t>Đặc điểm đèn LED âm trần đơn COB 7W
+Thân đèn và tản nhiệt làm bằng hợp kim nhôm cao cấp: khả năng chống va đập vượt trội, đèn có tuổi thọ cao, hạn chế chi phí bảo trì, bảo dưỡng, thay thế, đổi mới.
+Công suất 7w siêu sáng, siêu tiết kiệm, tương đương với 12w compact và 40w đèn sợi đốt: Đèn sử dụng chip LED COB với khả năng chiếu sáng vượt trội. Hiệu suất quang của đèn đạt 110-120  lm/w. Do vậy, đèn tiết kiệm 80% điện năng tiêu thụ so với đèn sợ đốt, 50% điện năng so với đèn huỳnh quang. Nhờ vậy, người sử dụng có thể tiết kiệm phần lớn chi phí cho điện năng tiêu thụ trong gia đình.
+Tản nhiệt nhôm dày, tăng tuổi thọ và độ bền màu: Tản nhiệt của đèn chính là bộ phận giải phóng nhiệt năng, duy trì cho bóng hoạt động tốt ở các điều kiện khác nhau. Đây chính là bộ phận có ảnh hưởng lớn tới tuổi thọ của bóng đèn.
+Ứng dụng công nghệ LED chất lượng cao. Chỉ số hoàn màu của đèn đạt Ra&gt; 85 cho hiệu quả chiếu sáng tốt, ánh sáng trung thực, tốt cho mắt, chống lóa – mỏi mắt, bảo vệ mắt theo tiêu chuẩn Châu Âu
+Tuổi thọ bóng: 40,000 giờ,
+Bảo hành 24 tháng trên toàn quốc
+Kết cấu tháo lắp đơn giản, tiện lợi, chắc chắn.</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -5776,6 +5893,16 @@
       <c r="M7" t="inlineStr">
         <is>
           <t>https://tlclighting.com.vn/wp-content/uploads/2019/10/IMG_2383-min.jpg</t>
+        </is>
+      </c>
+      <c r="P7" t="inlineStr">
+        <is>
+          <t>Thân đèn và tản nhiệt làm bằng hợp kim nhôm cao cấp: khả năng chống va đập vượt trội, đèn có tuổi thọ cao, hạn chế chi phí bảo trì, bảo dưỡng, thay thế, đổi mới.
+Công suất 7w siêu sáng, siêu tiết kiệm, tương đương với 12w compact và 40w đèn sợi đốt: Đèn sử dụng chip LED COB với khả năng chiếu sáng vượt trội. Hiệu suất quang của đèn đạt 110-120  lm/w. Do vậy, đèn tiết kiệm 80% điện năng tiêu thụ so với đèn sợ đốt, 50% điện năng so với đèn huỳnh quang. Nhờ vậy, người sử dụng có thể tiết kiệm phần lớn chi phí cho điện năng tiêu thụ trong gia đình.
+Tản nhiệt nhôm dày, tăng tuổi thọ và độ bền màu: Tản nhiệt của đèn chính là bộ phận giải phóng nhiệt năng, duy trì cho bóng hoạt động tốt ở các điều kiện khác nhau. Đây chính là bộ phận có ảnh hưởng lớn tới tuổi thọ của bóng đèn.
+Ứng dụng công nghệ LED chất lượng cao. Chỉ số hoàn màu của đèn đạt Ra&gt; 85 cho hiệu quả chiếu sáng tốt, ánh sáng trung thực, tốt cho mắt, chống lóa – mỏi mắt, bảo vệ mắt theo tiêu chuẩn Châu Âu
+Tuổi thọ bóng: 40,000 giờ, Bảo hành 24 tháng trên toàn quốc
+Kết cấu tháo lắp đơn giản, tiện lợi, chắc chắn.</t>
         </is>
       </c>
       <c r="Q7" t="inlineStr">
@@ -5796,6 +5923,18 @@
 3 màu: Tham khảo tại đây
 3 màu: Tham khảo tại đây
 3 màu: Tham khảo tại đây</t>
+        </is>
+      </c>
+      <c r="T7" t="inlineStr">
+        <is>
+          <t>Đặc điểm đèn LED âm trần đơn COB 7W
+Thân đèn và tản nhiệt làm bằng hợp kim nhôm cao cấp: khả năng chống va đập vượt trội, đèn có tuổi thọ cao, hạn chế chi phí bảo trì, bảo dưỡng, thay thế, đổi mới.
+Công suất 7w siêu sáng, siêu tiết kiệm, tương đương với 12w compact và 40w đèn sợi đốt: Đèn sử dụng chip LED COB với khả năng chiếu sáng vượt trội. Hiệu suất quang của đèn đạt 110-120  lm/w. Do vậy, đèn tiết kiệm 80% điện năng tiêu thụ so với đèn sợ đốt, 50% điện năng so với đèn huỳnh quang. Nhờ vậy, người sử dụng có thể tiết kiệm phần lớn chi phí cho điện năng tiêu thụ trong gia đình.
+Tản nhiệt nhôm dày, tăng tuổi thọ và độ bền màu: Tản nhiệt của đèn chính là bộ phận giải phóng nhiệt năng, duy trì cho bóng hoạt động tốt ở các điều kiện khác nhau. Đây chính là bộ phận có ảnh hưởng lớn tới tuổi thọ của bóng đèn.
+Ứng dụng công nghệ LED chất lượng cao. Chỉ số hoàn màu của đèn đạt Ra&gt; 85 cho hiệu quả chiếu sáng tốt, ánh sáng trung thực, tốt cho mắt, chống lóa – mỏi mắt, bảo vệ mắt theo tiêu chuẩn Châu Âu
+Tuổi thọ bóng: 40,000 giờ,
+Bảo hành 24 tháng trên toàn quốc
+Kết cấu tháo lắp đơn giản, tiện lợi, chắc chắn.</t>
         </is>
       </c>
     </row>
@@ -5875,6 +6014,50 @@
 3 màu: Tham khảo tại đây</t>
         </is>
       </c>
+      <c r="T8" t="inlineStr">
+        <is>
+          <t>Thông số kỹ thuật:
+Mã sản phẩm
+TLC-NCO-VV-7W
+Hãng sản xuất
+TLC LIGHTING
+Xuất xứ
+Việt Nam
+Công suất
+7W
+Kích thước
+120x38mm
+Hiệu suất quang
+110~120Lm/w
+Quang thông
+770Lm
+Độ hoàn màu:
+&gt;85
+Ánh sáng
+Ba màu
+Điện áp (AC)
+85-265V
+Lỗ khoét
+82
+Chip LED
+Chip COB
+Tuổi thọ chip LED
+40.000 giờ
+Bảo hành
+24 tháng
+Sản phẩm tương tự:
+Màu
+Ghi chú
+TLC-NCO-VP-7W
+Trắng/Vàng
+Tham khảo tại đây
+3 màu
+TLC-PCO-VT-7W
+TLC-ACO-TT-7W
+TLC-ACO-TT-14W
+14W</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -5902,7 +6085,7 @@
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>{"cong_suat": "7W", "anh_sang": "Trắng/ Vàng", "nhiet_do_mau": "3500K/6500K", "kich_thuoc": "ø120x38mm", "lo_khoet": "82", "chip_led": "Chip COB", "hieu_suat_quang": "110-120 Lm/w", "chi_so_hoan_mau": "CRI≥85", "dien_ap": "85-265V", "thuong_hieu": "TLC LIGHTING", "tuoi_tho": "40.000h", "bao_hanh": "24 tháng", "quang_thong": "770Lm", "do_hoan_mau": "&gt;85", "dien_ap_ac": "85-265V", "tuoi_tho_chip_led": "40.000 giờ"}</t>
+          <t>{"cong_suat": "7W", "anh_sang": "Trắng/ Vàng", "nhiet_do_mau": "3500K/6500K", "kich_thuoc": "ø120x38mm", "lo_khoet": "ø82mm", "chip_led": "Chip COB", "hieu_suat_quang": "110-120 Lm/w", "chi_so_hoan_mau": "CRI≥85", "dien_ap": "85-265V", "thuong_hieu": "TLC LIGHTING", "tuoi_tho": "40.000h", "bao_hanh": "24 tháng", "quang_thong": "770Lm", "do_hoan_mau": "&gt;85", "dien_ap_ac": "85-265V", "lo_khoet_phi": "82", "tuoi_tho_chip_led": "40.000 giờ"}</t>
         </is>
       </c>
       <c r="J9" t="n">
@@ -5916,6 +6099,14 @@
       <c r="M9" t="inlineStr">
         <is>
           <t>https://tlclighting.com.vn/wp-content/uploads/2019/08/den-led-am-tran-nano-cob-gold.png</t>
+        </is>
+      </c>
+      <c r="P9" t="inlineStr">
+        <is>
+          <t>Đèn LED âm trần mặt cong Nano có cấu tạo và thiết kế tương tự như dòng đèn LED âm trần Nano. Tuy nhiên, chip LED được sử dụng là dòng chip LED COB. Lợi ích của dòng chip này là khả năng chiếu rọi tốt, tăng cường hiệu suất phát quang của chip mà vẫn bảo vệ mắt hiệu quả theo tiêu chuẩn Châu Âu với chỉ số hoàn màu Ra &gt; 85.
+Mặt đèn được ứng dụng công nghệ sơn Nano cao cấp với khả năng bảo vệ màu sắc mặt đèn vượt trội. Chính sách bảo hành màu sắc mặt đèn lên tới 10 năm của TLC Lighting là ưu điểm giúp chiếc đèn chiếm được thiện cảm với khách hàng.
+Tản nhiệt của đèn được thiết kế từ nhôm nguyên khối với cánh tản nhiệt đa chiều cho chất lượng tản nhiệt hiệu quả. Bộ phận tản nhiệt chính là một trong số những yếu tố quan trọng ảnh hưởng đến tuổi thọ của đèn.
+Mặt đèn được thiết kế mặt kính có lớp phủ sần chống chói, cho ánh sáng đồng đều, bảo vệ mắt hiệu quả.</t>
         </is>
       </c>
       <c r="Q9" t="inlineStr">
@@ -5951,6 +6142,20 @@
 3 màu: Tham khảo tại đây</t>
         </is>
       </c>
+      <c r="T9" t="inlineStr">
+        <is>
+          <t>Cấu tạo của đèn LED âm trần Nano COB Gold đơn sắc
+Dòng
+âm trần Nano COB Gold đơn sắc
+với màu vàng sang trọng, tinh tế, mang lại không gian đẳng cấp cho công trình nhà ở, khách sạn, nhà hàng, chung cư, trung tâm thương mại cao cấp… có cấu tạo:
+Đèn LED âm trần mặt cong Nano có cấu tạo và thiết kế tương tự như dòng đèn LED âm trần Nano. Tuy nhiên, chip LED được sử dụng là dòng chip LED COB. Lợi ích của dòng chip này là khả năng chiếu rọi tốt, tăng cường hiệu suất phát quang của chip mà vẫn bảo vệ mắt hiệu quả theo tiêu chuẩn Châu Âu với chỉ số hoàn màu Ra &gt; 85.
+Đèn LED âm trần Nano COB Gold
+Mặt đèn được ứng dụng công nghệ sơn Nano cao cấp với khả năng bảo vệ màu sắc mặt đèn vượt trội. Chính sách bảo hành màu sắc mặt đèn lên tới 10 năm của TLC Lighting là ưu điểm giúp chiếc đèn chiếm được thiện cảm với khách hàng.
+Tản nhiệt của đèn được thiết kế từ nhôm nguyên khối với cánh tản nhiệt đa chiều cho chất lượng tản nhiệt hiệu quả. Bộ phận tản nhiệt chính là một trong số những yếu tố quan trọng ảnh hưởng đến tuổi thọ của đèn.
+Mặt đèn được thiết kế mặt kính có lớp phủ sần chống chói, cho ánh sáng đồng đều, bảo vệ mắt hiệu quả.
+Ngoài ra, với tuổi thọ đèn lên đến 40.000 giờ chiếu sáng cùng đa dạng các loại ánh sáng: trắng, vàng sẽ giúp khách hàng có sự lựa chọn phù hợp với căn phòng của mình.</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -5978,7 +6183,7 @@
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>{"cong_suat": "7W", "anh_sang": "Ba màu", "nhiet_do_mau": "3500K/6500K", "kich_thuoc": "ø120x38mm, 120x38mm", "lo_khoet": "ø82mm, 82", "chip_led": "Chip COB", "hieu_suat_quang": "110-120 Lm/w, 110~120Lm/w, 110 Lm/w", "chi_so_hoan_mau": "CRI≥85", "dien_ap": "85-265V, 85-265V", "thuong_hieu": "TLC LIGHTING", "tuoi_tho": "40.000h", "bao_hanh": "24 tháng", "quang_thong": "770Lm", "do_hoan_mau": "&gt;85", "dien_ap_ac": "85-265V", "tuoi_tho_chip_led": "40.000 giờ"}</t>
+          <t>{"cong_suat": "7W", "anh_sang": "Ba màu", "nhiet_do_mau": "3500K/6500K", "kich_thuoc": "ø120x38mm", "lo_khoet": "ø82mm", "chip_led": "Chip COB", "hieu_suat_quang": "110-120 Lm/w", "chi_so_hoan_mau": "CRI≥85", "dien_ap": "85-265V", "thuong_hieu": "TLC LIGHTING", "tuoi_tho": "40.000h", "bao_hanh": "24 tháng", "quang_thong": "770Lm", "do_hoan_mau": "&gt;85", "dien_ap_ac": "85-265V", "lo_khoet_mm": "82", "tuoi_tho_chip_led": "40.000 giờ"}</t>
         </is>
       </c>
       <c r="J10" t="n">
@@ -5992,6 +6197,14 @@
       <c r="M10" t="inlineStr">
         <is>
           <t>https://tlclighting.com.vn/wp-content/uploads/2019/08/den-led-em-tran-nano-cob-platinum.png</t>
+        </is>
+      </c>
+      <c r="P10" t="inlineStr">
+        <is>
+          <t>Đèn sử dụng chip LED COB cao cấp với khả năng chiếu sáng cao. Hiệu suất phát quang của đèn lên tới 110 Lm/w. Ánh sáng chất lượng tốt, chống lóa, mỏi mắt, bảo vệ mắt theo tiêu chuẩn Châu Âu với chỉ số hoàn màu Ra &gt; 85.
+Thiết kế đầy thẩm mỹ với mặt cong mềm mại, ôm bo sát trần. Tích hợp công nghệ sơn Nano siêu bền màu giúp khả năng lưu lại màu sắc cao. Bên cạnh đó, TLC Lighting có chính sách bảo hành màu sắc mặt đèn đến 10 năm.
+Tuổi thọ đèn lên tới 40.000 giờ chiếu sáng, phụ thuộc vào tuổi thọ của nguồn, tuổi thọ của chip và khả năng tản nhiệt của đèn. Chip LED thuộc dòng chip LED cao cấp. Nguồn được cấu thành từ những linh kiện chất lượng, đảm bảo đèn hoạt động ổn định trong mọi hoàn cảnh. Và tản nhiệt của đèn được cấu tạo từ nhôm nguyên khối với cánh tản nhiệt đa chiều, cho khả năng tản nhiệt hiệu quả.
+Đèn được bảo hành 24 tháng đổi mới trên toàn quốc.</t>
         </is>
       </c>
       <c r="Q10" t="inlineStr">
@@ -6027,6 +6240,20 @@
 3 màu: Tham khảo tại đây</t>
         </is>
       </c>
+      <c r="T10" t="inlineStr">
+        <is>
+          <t>Đặc điểm
+Đèn Led
+âm trần nano COB Platinum ba màu
+thừa hưởng đầy đủ những đặc tính tốt của dòng âm trần mặt cong Nano, đèn LED âm trần Nano COB đã thêm những lựa chọn phù hợp với đa dạng các mục đích chiếu sáng người tiêu dùng.
+Điểm mạnh của dòng sản phẩm này là khả năng chiếu sáng vượt trội cùng thiết kế sản phẩm đầy ấn tượng: thiết mặt cong ôm bo sát trần với màu sắc bạch kim đầy sang trọng và đẳng cấp.
+Đèn LED âm trần Nano COB Platinum
+Đèn sử dụng chip LED COB cao cấp với khả năng chiếu sáng cao. Hiệu suất phát quang của đèn lên tới 110 Lm/w. Ánh sáng chất lượng tốt, chống lóa, mỏi mắt, bảo vệ mắt theo tiêu chuẩn Châu Âu với chỉ số hoàn màu Ra &gt; 85.
+Thiết kế đầy thẩm mỹ với mặt cong mềm mại, ôm bo sát trần. Tích hợp công nghệ sơn Nano siêu bền màu giúp khả năng lưu lại màu sắc cao. Bên cạnh đó, TLC Lighting có chính sách bảo hành màu sắc mặt đèn đến 10 năm.
+Tuổi thọ đèn lên tới 40.000 giờ chiếu sáng, phụ thuộc vào tuổi thọ của nguồn, tuổi thọ của chip và khả năng tản nhiệt của đèn. Chip LED thuộc dòng chip LED cao cấp. Nguồn được cấu thành từ những linh kiện chất lượng, đảm bảo đèn hoạt động ổn định trong mọi hoàn cảnh. Và tản nhiệt của đèn được cấu tạo từ nhôm nguyên khối với cánh tản nhiệt đa chiều, cho khả năng tản nhiệt hiệu quả.
+Đèn được bảo hành 24 tháng đổi mới trên toàn quốc.</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
@@ -6054,7 +6281,7 @@
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>{"cong_suat": "7W", "anh_sang": "Trắng/ Vàng", "nhiet_do_mau": "3500K/6500K", "kich_thuoc": "ø120x38mm", "lo_khoet": "ø82mm", "chip_led": "Chip COB", "hieu_suat_quang": "110-120 Lm/w", "chi_so_hoan_mau": "CRI≥85", "dien_ap": "85-265V", "thuong_hieu": "TLC LIGHTING", "tuoi_tho": "40.000h", "bao_hanh": "24 tháng", "quang_thong": "770Lm", "do_hoan_mau": "&gt;85", "dien_ap_ac": "85-265V", "tuoi_tho_chip_led": "40.000 giờ"}</t>
+          <t>{"cong_suat": "7W", "anh_sang": "Trắng/ Vàng, Trắng, Vàng", "nhiet_do_mau": "3500K/6500K", "kich_thuoc": "ø120x38mm, 120x38mm", "lo_khoet": "ø82mm, 82", "chip_led": "Chip COB", "hieu_suat_quang": "110-120 Lm/w, 110~120Lm/w", "chi_so_hoan_mau": "CRI≥85", "dien_ap": "85-265V", "thuong_hieu": "TLC LIGHTING", "tuoi_tho": "40.000h", "bao_hanh": "24 tháng", "quang_thong": "770Lm", "do_hoan_mau": "&gt;85", "dien_ap_ac": "85-265V", "tuoi_tho_chip_led": "40.000 giờ"}</t>
         </is>
       </c>
       <c r="J11" t="n">
@@ -6068,6 +6295,14 @@
       <c r="M11" t="inlineStr">
         <is>
           <t>https://tlclighting.com.vn/wp-content/uploads/2019/08/den-led-em-tran-nano-cob-platinum.png</t>
+        </is>
+      </c>
+      <c r="P11" t="inlineStr">
+        <is>
+          <t>Đèn sử dụng chip LED COB cao cấp với khả năng chiếu sáng cao. Hiệu suất phát quang của đèn lên tới 110 Lm/w. Ánh sáng chất lượng tốt, chống lóa, mỏi mắt, bảo vệ mắt theo tiêu chuẩn Châu Âu với chỉ số hoàn màu Ra &gt; 85.
+Thiết kế đầy thẩm mỹ với mặt cong mềm mại, ôm bo sát trần. Tích hợp công nghệ sơn Nano siêu bền màu giúp khả năng lưu lại màu sắc cao. Bên cạnh đó, TLC Lighting có chính sách bảo hành màu sắc mặt đèn đến 10 năm.
+Tuổi thọ đèn lên tới 40.000 giờ chiếu sáng, phụ thuộc vào tuổi thọ của nguồn, tuổi thọ của chip và khả năng tản nhiệt của đèn. Chip LED thuộc dòng chip LED cao cấp. Nguồn được cấu thành từ những linh kiện chất lượng, đảm bảo đèn hoạt động ổn định trong mọi hoàn cảnh. Và tản nhiệt của đèn được cấu tạo từ nhôm nguyên khối với cánh tản nhiệt đa chiều, cho khả năng tản nhiệt hiệu quả.
+Đèn được bảo hành 24 tháng đổi mới trên toàn quốc.</t>
         </is>
       </c>
       <c r="Q11" t="inlineStr">
@@ -6101,6 +6336,20 @@
 3 màu: Tham khảo tại đây
 3 màu: Tham khảo tại đây
 3 màu: Tham khảo tại đây</t>
+        </is>
+      </c>
+      <c r="T11" t="inlineStr">
+        <is>
+          <t>Đặc điểm
+Đèn Led
+âm trần nano COB Platinum đơn sắc
+thừa hưởng đầy đủ những đặc tính tốt của dòng âm trần mặt cong Nano, đèn LED âm trần Nano COB đã thêm những lựa chọn phù hợp với đa dạng các mục đích chiếu sáng người tiêu dùng.
+Điểm mạnh của dòng sản phẩm này là khả năng chiếu sáng vượt trội cùng thiết kế sản phẩm đầy ấn tượng: thiết mặt cong ôm bo sát trần với màu sắc bạch kim đầy sang trọng và đẳng cấp.
+Đèn LED âm trần Nano COB Platinum
+Đèn sử dụng chip LED COB cao cấp với khả năng chiếu sáng cao. Hiệu suất phát quang của đèn lên tới 110 Lm/w. Ánh sáng chất lượng tốt, chống lóa, mỏi mắt, bảo vệ mắt theo tiêu chuẩn Châu Âu với chỉ số hoàn màu Ra &gt; 85.
+Thiết kế đầy thẩm mỹ với mặt cong mềm mại, ôm bo sát trần. Tích hợp công nghệ sơn Nano siêu bền màu giúp khả năng lưu lại màu sắc cao. Bên cạnh đó, TLC Lighting có chính sách bảo hành màu sắc mặt đèn đến 10 năm.
+Tuổi thọ đèn lên tới 40.000 giờ chiếu sáng, phụ thuộc vào tuổi thọ của nguồn, tuổi thọ của chip và khả năng tản nhiệt của đèn. Chip LED thuộc dòng chip LED cao cấp. Nguồn được cấu thành từ những linh kiện chất lượng, đảm bảo đèn hoạt động ổn định trong mọi hoàn cảnh. Và tản nhiệt của đèn được cấu tạo từ nhôm nguyên khối với cánh tản nhiệt đa chiều, cho khả năng tản nhiệt hiệu quả.
+Đèn được bảo hành 24 tháng đổi mới trên toàn quốc.</t>
         </is>
       </c>
     </row>
@@ -6268,7 +6517,7 @@
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>{"kich_thuoc": "ø125x485mm", "cong_suat": "6W", "do_roi": "700Lux", "hieu_suat_quang": "100Lm/W", "dien_ap": "AC 85-265V", "loai_dui": "E27", "thuong_hieu": "TLC LIGHTING", "chip_led": "OSRAM", "chi_so_hoan_mau": "Ra &gt;85", "khong_nhap_nhay": "Flicker free", "do_ben_sang_cao": "L70 50.000H", "han_che_choi_mat": "UGR 19", "tuoi_tho": "15000 giờ"}</t>
+          <t>{"kich_thuoc": "ø125x485mm", "cong_suat": "6W", "do_roi": "700Lux", "hieu_suat_quang": "100Lm/W", "dien_ap": "AC 85-265V", "loai_dui": "E27", "thuong_hieu": "TLC LIGHTING", "chip_led": "OSRAM", "chi_so_hoan_mau": "Ra &gt;85", "khong_nhap_nhay": "Flicker free", "do_ben_sang_cao": "L70 50.000H", "han_che_choi_mat": "UGR 19", "chieu_dai_day_phich_cam": "1m"}</t>
         </is>
       </c>
       <c r="L2" t="inlineStr">
@@ -6593,7 +6842,7 @@
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>{"thuong_hieu": "TLC LIGHTING", "cong_tam_suat_pin": "25W/5V", "kich_thuoc_den": "450x180x73 mm", "anh_sang": "Trắng", "pin_sac": "LIFEPO4 – 3.2V", "dung_luong_pin": "30Ah", "chong_nuoc_khang_bui": "IP65", "cong_suat": "300W", "chip_led": "5730", "pin": "LiFePO4 3.2V", "tam_pin_monocrystalline": "25W/5V", "kich_thuoc_tam_pin": "510x390x17 mm", "thoi_gian_sac": "4-6 giờ", "ip": "65", "thoi_gian_sang_lien_tuc": "&gt;12h", "mau_sac": "Trắng", "bao_hanh": "24 tháng", "quang_thong": "2200 Lm"}</t>
+          <t>{"thuong_hieu": "TLC LIGHTING", "cong_tam_suat_pin": "25W/5V", "kich_thuoc_den": "450x180x73 mm", "anh_sang": "Trắng", "pin_sac": "LIFEPO4 – 3.2V", "dung_luong_pin": "30., 000 mAh", "chong_nuoc_khang_bui": "IP65", "cong_suat": "300W", "chip_LED": "5730", "pin": "LiFePO4 3.2V", "dung_luong_pin_2": "30Ah", "tam_pin_Monocrystalline": "25W/5V", "kich_thuoc_tam_Pin": "510x390x17 mm", "thoi_gian_sac": "4-6 giờ", "IP": "65", "thoi_gian_sang_lien_tuc": "&gt;12h", "mau_sac": "Trắng", "bao_hanh": "24 tháng", "quang_thong": "2200 Lm", "thoi_gian_hoat_dong_pin": "12 giờ"}</t>
         </is>
       </c>
       <c r="J2" t="n">
@@ -6780,7 +7029,7 @@
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>{"cong_suat": "90W", "anh_sang": "Trắng", "pin_sac": "Lithium 18650-4.2", "dung_luong_pin": "20.000mAh", "tieu_chuan": "IP67", "thuong_hieu": "TLC LIGHTING", "bao_hanh": "24 tháng", "thoi_gian_sac_pin": "6-8h", "thoi_gian_sang_lien_tuc": "12-15h"}</t>
+          <t>{"cong_suat": "90W", "anh_sang": "Trắng", "pin_sac": "Lithium 18650-4.2", "dung_luong_pin": "20.000mAh", "tieu_chuan": "IP67", "bao_hanh": "24 tháng", "thuong_hieu": "TLC LIGHTING", "thoi_gian_sac_pin": "6-8h", "thoi_gian_sang_lien_tuc": "12-15h"}</t>
         </is>
       </c>
       <c r="J4" t="n">
@@ -6858,7 +7107,7 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>TLC-ĐMS-100W</t>
+          <t>TLC-ĐMS-100w</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
@@ -6868,7 +7117,7 @@
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>{"cong_suat": "100W", "anh_sang": "Trắng", "pin_sac": "Lithium 18650-4.2, Li-ion 21700 Panasonic", "dung_luong_pin": "20.000mAh", "tieu_chuan": "IP67", "thuong_hieu": "TLC LIGHTING", "bao_hanh": "24 tháng", "thoi_gian_sac_pin": "6-8h", "thoi_gian_sang_lien_tuc": "12-15h"}</t>
+          <t>{"cong_suat": "100W", "anh_sang": "Trắng", "pin_sac": "Li-ion 21700 Panasonic", "dung_luong_pin": "20.000mAh", "tieu_chuan": "IP67", "bao_hanh": "24 tháng", "thuong_hieu": "TLC LIGHTING", "thoi_gian_sac_pin": "6-8h", "thoi_gian_sang_lien_tuc": "12-15h"}</t>
         </is>
       </c>
       <c r="J5" t="n">
@@ -6949,7 +7198,7 @@
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>{"cong_suat": "150W", "anh_sang": "Trắng", "pin_sac": "Lithium 18650-4.2, Li-ion 21700 Panasonic", "dung_luong_pin": "20.000mAh, 30.000mAh", "tieu_chuan": "IP67", "bao_hanh": "24 tháng", "thuong_hieu": "TLC LIGHTING", "thoi_gian_sac_pin": "6-8h", "thoi_gian_sang_lien_tuc": "12-15h"}</t>
+          <t>{"cong_suat": "150W", "anh_sang": "Trắng", "pin_sac": "Li-ion 21700 Panasonic", "dung_luong_pin": "30.000mAh", "tieu_chuan": "IP67", "thoi_gian_sac_pin": "6-8h", "thoi_gian_sang_lien_tuc": "12-15h", "bao_hanh": "24 tháng", "thuong_hieu": "TLC LIGHTING"}</t>
         </is>
       </c>
       <c r="J6" t="n">
@@ -7023,7 +7272,7 @@
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>{"cong_suat": "50W", "anh_sang": "Trắng", "dung_luong_pin": "15.000mAh", "tieu_chuan": "IP67", "bao_hanh": "24 tháng", "thuong_hieu": "TLC LIGHTING", "thoi_gian_sac_pin": "6-8h", "thoi_gian_sang_lien_tuc": "12-15h"}</t>
+          <t>{"cong_suat": "50W", "anh_sang": "Trắng", "pin_sac": "Lithium 18650-4.2", "dung_luong_pin": "15.000mAh", "tieu_chuan": "IP67", "bao_hanh": "24 tháng", "thuong_hieu": "TLC LIGHTING", "thoi_gian_sac_pin": "6-8h", "thoi_gian_sang_lien_tuc": "12-15h"}</t>
         </is>
       </c>
       <c r="J7" t="n">
@@ -7109,7 +7358,7 @@
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>{"cong_suat": "100W", "chip_led": "5730", "kich_thuoc": "275x240x56 mm", "pin": "LiFePO 3.2V", "thuong_hieu": "TLC LIGHTING", "tuoi_tho": "40.000h", "bao_hanh": "24 tháng", "kich_thuoc_den": "275x240x56mm", "dung_luong_pin": "10Ah", "tam_pin_monocrystalline": "12W/5V", "ip": "65", "chi_so_hoan_mau": "Ra=85", "thoi_gian_sang_lien_tuc": "&gt;12h", "mau_sac": "Trắng"}</t>
+          <t>{"cong_suat": "100W", "chip_led": "5730", "kich_thuoc": "275x240x56 mm", "pin": "LiFePO4 3.2V", "thuong_hieu": "TLC LIGHTING", "tuoi_tho": "40.000h", "bao_hanh": "24 tháng", "kich_thuoc_den": "275x240x56mm", "dung_luong_pin": "10Ah", "tam_pin_monocrystalline": "12W/5V", "ip": "65", "chi_so_hoan_mau": "Ra=85", "thoi_gian_sang_lien_tuc": "&gt;12h", "mau_sac": "Trắng"}</t>
         </is>
       </c>
       <c r="J8" t="n">
@@ -7199,7 +7448,7 @@
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>{"thuong_hieu": "TLC LIGHTING", "cong_suat": "100W", "kich_thuoc_den": "294x199x45 mm", "kich_thuoc_tam_pin": "600x350x17 mm", "anh_sang": "Trắng", "pin_sac": "Lithium 18650-4.2, LIFEPO 4 3.2V", "dung_luong_pin": "25.000 mAh", "chong_nuoc_khang_bui": "IP66", "thoi_gian_chieu_sang": "12H liên tục", "bao_hanh": "24 tháng", "chip_LED": "Espistar", "thoi_gian_sac_pin": "6-8h", "thoi_gian_sac_lien_tuc": "&gt;12H"}</t>
+          <t>{"thuong_hieu": "TLC LIGHTING", "cong_suat": "100W", "kich_thuoc_den": "294x199x45 mm", "kich_thuoc_tam_pin": "600x350x17 mm", "anh_sang": "Trắng", "pin_sac": "Lithium 18650-4.2, LIFEPO 4 3.2V", "dung_luong_pin": "25.000 mAh", "chong_nuoc_khang_bui": "IP66", "thoi_gian_chieu_sang": "12H liên tục", "bao_hanh": "24 tháng", "chip_led": "Espistar", "thoi_gian_sac_pin": "6-8h", "thoi_gian_sac_lien_tuc": "&gt;12H"}</t>
         </is>
       </c>
       <c r="J9" t="n">
@@ -7306,7 +7555,7 @@
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>{"thuong_hieu": "TLC LIGHTING", "cong_suat": "50W", "kich_thuoc_den": "240x175x45 mm", "kich_thuoc_tam_pin": "450x350x17 mm", "anh_sang": "Trắng", "pin_sac": "LIFEPO 4 3.2V", "dung_luong_pin": "20.000 mAh", "chong_nuoc_khang_bui": "IP66", "thoi_gian_chieu_sang": "12H liên tục", "bao_hanh": "24 tháng", "chip_led": "Espistar", "thoi_gian_sac_pin": "6-8h", "thoi_gian_sac_lien_tuc": "&gt;12H"}</t>
+          <t>{"thuong_hieu": "TLC LIGHTING", "cong_suat": "50W", "kich_thuoc_den": "240x175x45 mm", "kich_thuoc_tam_pin": "450x350x17 mm", "anh_sang": "Trắng", "pin_sac": "LIFEPO 4 3.2V", "dung_luong_pin": "20.000 mAh", "chong_nuoc_khang_bui": "IP66", "thoi_gian_chieu_sang": "12H liên tục", "bao_hanh": "24 tháng", "chip_led": "Espistar", "thoi_gian_sac_pin": "6-8h"}</t>
         </is>
       </c>
       <c r="J10" t="n">
@@ -7568,7 +7817,7 @@
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>{"cong_suat": "120W", "anh_sang": "Trắng", "pin_sac": "Litthium sắt phosphate, Lithium 18650-4.2", "dung_luong_pin": "20.000mAh, 15.000mAh", "tieu_chuan": "IP66", "thoi_gian_sac_pin": "6h – 8h, 6-8h", "bao_hanh": "24 tháng, 2 năm", "thuong_hieu": "TLC LIGHTING", "thoi_gian_sang_lien_tuc": "12-14h"}</t>
+          <t>{"cong_suat": "120W", "anh_sang": "Trắng", "pin_sac": "Litthium sắt phosphate, Lithium 18650-4.2", "dung_luong_pin": "20.000mAh, 15.000mAh", "tieu_chuan": "IP66", "thoi_gian_sac_pin": "6h – 8h, 6-8h", "bao_hanh": "24 tháng", "thuong_hieu": "TLC LIGHTING", "thoi_gian_sang_lien_tuc": "12-14h"}</t>
         </is>
       </c>
       <c r="J13" t="n">
@@ -7656,7 +7905,7 @@
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>{"cong_suat": "90W", "anh_sang": "Trắng", "pin_sac": "Litthium sắt phosphate, Litthium sắt phosphate 3.2V15A", "dung_luong_pin": "15.000mAh", "tieu_chuan": "IP66", "thoi_gian_sac_pin": "6h – 8h, 6-8h", "bao_hanh": "24 tháng", "thuong_hieu": "TLC LIGHTING", "thoi_gian_sang_lien_tuc": "12-14h"}</t>
+          <t>{"cong_suat": "90W", "anh_sang": "Trắng", "pin_sac": "Litthium sắt phosphate", "dung_luong_pin": "15.000mAh", "tieu_chuan": "IP66", "thoi_gian_sac_pin": "6h – 8h", "bao_hanh": "24 tháng", "thuong_hieu": "TLC LIGHTING", "thoi_gian_sang_lien_tuc": "12-14h"}</t>
         </is>
       </c>
       <c r="J14" t="n">
@@ -7670,6 +7919,15 @@
       <c r="M14" t="inlineStr">
         <is>
           <t>https://tlclighting.com.vn/wp-content/uploads/2021/01/T-NLTM-Friendly-90w-KT.jpg</t>
+        </is>
+      </c>
+      <c r="P14" t="inlineStr">
+        <is>
+          <t>Tiết kiệm chi phí: Đèn năng lượng mặt trời trong nhà Max Eco Friendly 90W
+Dễ dàng lắp đặt
+An toàn và thân thiện với môi trường
+Tiện lợi và linh động: Đèn năng lượng mặt trời trong nhà
+Tính ứng dụng cao</t>
         </is>
       </c>
       <c r="Q14" t="inlineStr">
@@ -7694,6 +7952,26 @@
 Bảo hành: 24 tháng</t>
         </is>
       </c>
+      <c r="T14" t="inlineStr">
+        <is>
+          <t>Lợi ích của đèn năng lượng mặt trời trong nhà Max Eco Friendly 90W
+Tiết kiệm chi phí: Đèn năng lượng mặt trời trong nhà Max Eco Friendly 90W
+là một giải pháp tiết kiệm điện năng hoàn hảo. Với việc sử dụng 100% năng lượng mặt trời, không cần phụ thuộc vào mạng lưới điện dân dụng,
+đèn năng lượng mặt trời lắp trong nhà
+giúp giảm đáng kể hóa đơn tiền điện cho gia đình. Người tiêu dùng sẽ không phải lo lắng về việc mất tiền dây điện và thời gian tắt bật như khi sử dụng đèn truyền thống.
+Dễ dàng lắp đặt:
+Với kiểu dáng hiện đại và kích thước nhỏ gọn, đèn này có thể được lắp đặt ở khắp mọi nơi mà bạn muốn. Để đảm bảo hiệu suất nạp điện tối ưu, hãy đặt tấm pin ở vị trí có nhiều ánh sáng mặt trời nhất trong suốt thời gian ban ngày và tránh đặt nơi có bóng râm.
+An toàn và thân thiện với môi trường:
+T
+hân thiện với môi trường, an toàn cho trẻ nhỏ và không gây ảnh hưởng đến môi trường.
+Tiện lợi và linh động: Đèn năng lượng mặt trời trong nhà
+MAX ECO FRIENDLY 90W
+cũng mang đến tính tiện lợi và linh hoạt cho người dùng. Với chế độ tự động bật tắt khi sạc pin, bạn không cần phải lo lắng về việc quên tắt hoặc lãng phí năng lượng. Đèn còn được trang bị chế độ cảm biến thông minh, giúp phát hiện chuyển động và điều chỉnh chiếu sáng phù hợp, tiết kiệm năng lượng và đảm bảo an ninh.
+Tính ứng dụng cao:
+Sản phẩm
+phù hợp cho nhiều không gian khác nhau. Bạn có thể di chuyển và lắp đặt đèn ở sân vườn, nhà xưởng, trang trại, đường đi, trường học, bệnh viện và nhiều địa điểm khác, mang lại sự thuận tiện và hiệu quả cho việc chiếu sáng trong các không gian này.</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
@@ -7721,7 +7999,7 @@
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>{"thuong_hieu": "TLC LIGHTING", "cong_suat_tam_suat_pin": "25W/5V", "kich_thuoc_den": "360x300x46 mm", "anh_sang": "Trắng", "pin_sac": "LIFEPO4 – 3.2V", "dung_luong_pin": "25 Ah", "chong_nuoc_khang_bui": "IP65", "cong_suat": "250W", "chip_led": "Espistar", "thoi_gian_sac_pin": "4-6h", "thoi_gian_sang_lien_tuc": "&gt;12H", "bao_hanh": "24 tháng"}</t>
+          <t>{"thuong_hieu": "TLC LIGHTING", "cong_suat": "250W", "kich_thuoc_den": "360x300x46 mm", "chip_led": "Espistar", "pin_sac": "LIFEPO4 – 3.2V", "dung_luong_pin": "25Ah", "chong_nuoc_khang_bui": "IP65", "anh_sang": "Trắng", "thoi_gian_sac_pin": "4-6h", "thoi_gian_sang_lien_tuc": "&gt;12H", "bao_hanh": "24 tháng", "cong_tam_suat_pin": "25W/5V", "dung_luong_pin_ket_cau": "10.000 mAh"}</t>
         </is>
       </c>
       <c r="J15" t="n">
@@ -7808,7 +8086,7 @@
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>{"thuong_hieu": "TLC LIGHTING", "cong_suat_tam_pin": "15W/5V", "kich_thuoc_den": "310x256x46 mm", "anh_sang": "Trắng", "pin_sac": "LIFEPO4 – 3.2V", "dung_luong_pin": "15. 000 mAh", "chong_nuoc_khang_bui": "IP65", "cong_suat": "150W", "kich_thuoc_tam_pin": "390x230x17 mm", "chip_led": "Espistar", "thoi_gian_sac_pin": "4-6h", "thoi_gian_sang_lien_tuc": "&gt;12H", "bao_hanh": "24 tháng"}</t>
+          <t>{"thuong_hieu": "TLC LIGHTING", "cong_suat": "150W", "kich_thuoc_den": "310x256x46 mm", "kich_thuoc_tam_pin": "390x230x17 mm", "chip_led": "Espistar", "pin_sac": "LIFEPO4 – 3.2V", "dung_luong_pin": "15.000 mAh", "chong_nuoc_khang_bui": "IP65", "anh_sang": "Trắng", "thoi_gian_sac_pin": "4-6h", "thoi_gian_sang_lien_tuc": "&gt;12H", "bao_hanh": "24 tháng", "cong_tam_suat_pin": "15W/5V"}</t>
         </is>
       </c>
       <c r="J16" t="n">
@@ -7900,7 +8178,7 @@
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>{"cong_suat_pin": "10W/5V", "kich_thuoc_den": "256x211x45 mm", "anh_sang": "Trắng", "pin_sac": "LIFEPO4 – 3.2V", "dung_luong_pin": "10.000 mAh", "chong_nuoc_khang_bui": "IP65", "cong_suat": "100W", "kich_thuoc_tam_pin": "295x210x17 mm", "chip_led": "Espistar", "thoi_gian_sac_pin": "4-6h", "thoi_gian_sang_lien_tuc": "&gt;12H", "bao_hanh": "24 tháng"}</t>
+          <t>{"thuong_hieu": "TLC LIGHTING", "cong_suat_pin": "10W/5V", "kich_thuoc_den": "256x211x45 mm", "anh_sang": "Trắng", "pin_sac": "LIFEPO4 – 3.2V", "dung_luong_pin": "10.000 mAh", "chong_nuoc_khang_bui": "IP65", "cong_suat": "100W", "kich_thuoc_tam_pin": "295x210x17 mm", "chip_LED": "Espistar", "thoi_gian_sac_pin": "4-6h", "thoi_gian_sang_lien_tuc": "&gt;12H", "bao_hanh": "24 tháng"}</t>
         </is>
       </c>
       <c r="J17" t="n">
@@ -7991,7 +8269,7 @@
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>{"cong_suat": "100W", "anh_sang": "Trắng", "pin_sac": "Lithium 18650-4.2", "dung_luong_pin": "30.000mAh", "tieu_chuan": "IP67", "thoi_gian_sac_pin": "6-8h", "bao_hanh": "24 tháng", "thoi_gian_sac_lien_tuc": "12 – 15h"}</t>
+          <t>{"cong_suat": "100W", "anh_sang": "Trắng", "pin_sac": "Lithium 18650-4.2", "dung_luong_pin": "30.000mAh", "tieu_chuan": "IP67", "thoi_gian_sac_pin": "6-8h", "bao_hanh": "24 tháng", "cong_nghe_sieu_chong_nuoc": "IP67", "thoi_gian_sac_lien_tuc": "12 – 15h"}</t>
         </is>
       </c>
       <c r="J18" t="n">
@@ -8069,7 +8347,7 @@
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>{"cong_suat": "150W", "anh_sang": "Trắng", "pin_sac": "Lithium 18650-4.2, Li-ion 21700 Panasonic", "dung_luong_pin": "40.000mAh", "tieu_chuan": "IP67", "thoi_gian_sac_pin": "6-8h", "bao_hanh": "24 tháng", "cong_nghe_sieu_chong_nuoc": "IP67", "thoi_gian_sac_lien_tuc": "12 – 15h"}</t>
+          <t>{"cong_suat": "150W", "anh_sang": "Trắng", "pin_sac": "Lithium 18650-4.2, Li-ion 21700 Panasonic", "dung_luong_pin": "40.000mAh", "tieu_chuan": "IP67", "thoi_gian_sac_pin": "6-8h", "bao_hanh": "24 tháng", "thoi_gian_sac_lien_tuc": "12 – 15h"}</t>
         </is>
       </c>
       <c r="J19" t="n">
@@ -8311,7 +8589,7 @@
       </c>
       <c r="I22" t="inlineStr">
         <is>
-          <t>{"cong_suat": "50W", "anh_sang": "Trắng", "pin_sac": "Lithium 18650-4.2", "dung_luong_pin": "20.000mAh", "tieu_chuan": "IP67", "thoi_gian_sac_pin": "6-8h", "bao_hanh": "24 tháng", "thoi_gian_sac_lien_tuc": "12 – 15h"}</t>
+          <t>{"cong_suat": "50W", "anh_sang": "Trắng", "pin_sac": "Lithium 18650-4.2", "dung_luong_pin": "20.000mAh", "tieu_chuan": "IP67", "thoi_gian_sac_pin": "6-8h", "bao_hanh": "24 tháng", "thuong_hieu": "TLC LIGHTING", "thoi_gian_sac_lien_tuc": "12 – 15h", "cong_nghe": "IP67"}</t>
         </is>
       </c>
       <c r="J22" t="n">
@@ -8393,7 +8671,7 @@
       </c>
       <c r="I23" t="inlineStr">
         <is>
-          <t>{"thuong_hieu": "TLC LIGHTING", "cong_suat_pin": "2W/6V", "kich_thuoc_den": "200x200x260 mm", "anh_sang": "Trắng, Trắng, Vàng", "pin_sac": "lithium 18650-4.2, Lithium", "dung_luong_pin": "2000 mAh", "chong_nuoc_khang_bui": "IP67", "thoi_gian_sac_pin": "6-8h", "thoi_gian_sac_lien_tuc": "&gt;12H", "bao_hanh": "24 tháng", "cong_suat": "3W", "chip_led": "DOB (Driver on Board)", "dui_den": "E27", "thoi_gian_sang_lien_tuc": "10 giờ"}</t>
+          <t>{"thuong_hieu": "TLC LIGHTING", "cong_suat_pin": "2W/6V", "kich_thuoc_den": "200x200x260 mm", "anh_sang": "Trắng, vàng", "pin_sac": "lithium 18650-4.2, Lithium", "dung_luong_pin": "2000 mAh", "chong_nuoc_khang_bui": "IP67", "thoi_gian_sac_pin": "6-8h", "thoi_gian_sac_lien_tuc": "&gt;12H", "bao_hanh": "24 tháng", "cong_suat": "3W"}</t>
         </is>
       </c>
       <c r="J23" t="n">
@@ -8608,7 +8886,7 @@
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>{"cong_suat": "110W", "nhiet_do_mau": "6500K, 5700–6500K", "kich_thuoc_den": "528x300x78mm", "chip_led": "Bridgelux SMD 5054 148PCS", "hieu_suat_quang": "21000 Lm/W", "chi_so_hoan_mau": "CRI &gt;70Ra", "dien_ap": "DC 54V, DC 48V", "thuong_hieu": "TLC LIGHTING", "bao_hanh": "2-5 năm", "chi_so_chong_am": "IP 65", "thong_so_tam_pin_solar_panel": "36V 240W (2*120W), Kích thước: 1180*670, Sạc 7H", "thong_so_pin_luu_tru_battery": "32700 lithium iron Phosphate (25.6V/36AH) 921WH)", "bo_dieu_khien_nguon_controller": "MPPT 24V automatic ON/OFF", "goc_chieu": "70°*140°", "vat_lieu": "Die-casting Aluminium"}</t>
+          <t>{"cong_suat": "110W", "nhiet_do_mau": "6500K, 5700–6500K", "kich_thuoc_den": "528x300x78mm", "chip_led": "Bridgelux SMD 5054 148PCS", "hieu_suat_quang": "21000 Lm/W", "chi_so_hoan_mau": "CRI &gt;70Ra", "dien_ap": "DC 54V", "thuong_hieu": "TLC LIGHTING", "bao_hanh": "2-5 năm", "dien_ap_ac": "DC 48V", "kich_thuoc": "528x300x78mm", "chi_so_chong_am": "IP 65", "thong_so_tam_pin_solar_panel": "36V 240W (2*120W)", "kich_thuoc_tam_pin": "1180*670", "sac": "7H", "thong_so_pin_luu_tru_battery": "32700 lithium iron Phosphate (25.6V/36AH) 921WH)", "bo_dieu_khien_nguon_controller": "MPPT 24V automatic ON/OFF", "goc_chieu": "70°*140°", "vat_lieu": "Die-casting Aluminium"}</t>
         </is>
       </c>
       <c r="L2" t="inlineStr">
@@ -8640,6 +8918,27 @@
 Bảo hành: 2-5 năm</t>
         </is>
       </c>
+      <c r="T2" t="inlineStr">
+        <is>
+          <t>Đặc điểm nổi bật của đèn đường LED năng lượng mặt trời TLC 110W
+Chip LED
+Đèn đường LED năng lượng mặt trời TLC 110W
+sử dụng chip LED với hiệu suất quang cao: 21000 Lm/W,
+hiệu quả chiếu sáng vượt trồi
+, tiết kiệm năng lượng, giải pháp hoàn hảo cho chiếu sáng khu vực đi lại của khu độ thị mới, khu công nghiệp, nội khu nhà máy.
+Được trang bị thấu kính đi kèm mỗi hạt Chip LED, giúp tăng diện tích chiếu sáng, đảm bảo độ sáng đồng đều, khu vực chiếu sáng rộng, tiết kiệm điện năng và hiệu quả sử dụng
+Chi tiết đ
+èn đường LED năng lượng mặt trời TLC 110W
+Tấm pin
+Đèn đường LED năng lượng mặt trời TLC 110W sử dụng tấm pin Mono 36V/ 240W cao cấp, cho hiệu suất chuyển đổi năng lượng vượt trội so với tâm pin poly thông thường. Tối ưu hóa khả năng hấp thụ ánh sáng, giúp đèn vận hành ổn định trong mọi điều kiện thời tiết kể cả tại những vùng ít nắng, những ngày mưa bão hay trời âm u, nhiều mây.
+Pin lưu trữ
+Pin Lithium cao cấp của đèn đường LED năng lượng mặt trời TLC 110W sở hữu hiệu suất nạp xả cực cao, cho độ bền vượt trội lên đến 10 năm mà không cần thay mới.
+Dung lượng pin lớn và chất lượng pin ưu việt, giúp đèn có thể sáng liên tục đến 14 tiếng, đảm bảo an toàn cho khu vực nội khu đô thị, khu công nghiệp.
+Với thiết kế thông minh, hạn chế hoàn toàn việc xâm nhập nước, hơi ẩm làm giảm tuổi thọ của pin.
+Thân đèn
+Thân đèn làm bằng nhôm đúc giúp tản nhiệt hiệu quả, giảm tác động của nhiệt đến các linh kiện điện tử khác, tăng tuổi thọ của đèn.. Thước thuỷ kế giúp đảm bảo độ cân bằng chính xác, dễ dàng căn chỉnh thân đèn theo phương nằm ngang hoàn hảo trong quá trình thi công, tránh tình trạng đèn bị nghiêng hoặc lệch góc.</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -8662,7 +8961,7 @@
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>{"cong_suat": "75W", "nhiet_do_mau": "6500K, 5700–6500K", "kich_thuoc_den": "450 x300x78mm", "chip_led": "Bridgelux SMD 5054 100PCS", "hieu_suat_quang": "14200 Lm/W", "chi_so_hoan_mau": "CRI &gt;70Ra", "dien_ap": "DC 54V", "thuong_hieu": "TLC LIGHTING", "bao_hanh": "2-5 năm", "kich_thuoc": "450x300x78mm", "chi_so_chong_am": "IP 65", "thong_so_tam_pin": "36V 150W, Kích thước: 1480*670, Sạc 7H", "thong_so_pin_luu_tru": "(25.6V/24AH) 614WH / Lithium iron Phosphate battery", "bo_dieu_khien_nguon": "MPPT 24V automatic ON/OFF", "goc_chieu": "70°*140°", "vat_lieu": "Die-casting Aluminium"}</t>
+          <t>{"cong_suat": "75W", "nhiet_do_mau": "6500K, 5700–6500K", "kich_thuoc_den": "450 x300x78mm", "chip_led": "Bridgelux SMD 5054 100PCS", "hieu_suat_quang": "14200 Lm/W", "chi_so_hoan_mau": "CRI &gt;70Ra", "dien_ap": "DC 54V", "thuong_hieu": "TLC LIGHTING", "bao_hanh": "2-5 năm", "kich_thuoc": "450x300x78mm", "chi_so_chong_am": "IP 65", "thong_so_tam_pin_solar_panel": "36V 150W, Kích thước: 1480*670, Sạc 7H", "thong_so_pin_luu_tru_battery": "(25.6V/24AH) 614WH / Lithium iron Phosphate battery", "bo_dieu_khien_nguon_controller": "MPPT 24V automatic ON/OFF", "goc_chieu": "70°*140°", "vat_lieu": "Die-casting Aluminium"}</t>
         </is>
       </c>
       <c r="L3" t="inlineStr">
@@ -8694,6 +8993,27 @@
 Bảo hành: 2-5 năm</t>
         </is>
       </c>
+      <c r="T3" t="inlineStr">
+        <is>
+          <t>Đặc điểm nổi bật của đèn đường LED năng lượng mặt trời TLC 75W
+Chip LED
+Đèn đường LED năng lượng mặt trời TLC 75W
+sử dụng chip LED với hiệu suất quang cao: 14200 Lm/W,
+hiệu quả chiếu sáng vượt trồi
+, tiết kiệm năng lượng, giải pháp hoàn hảo cho chiếu sáng khu vực đi lại của khu độ thị mới, khu công nghiệp, nội khu nhà máy.
+Được trang bị thấu kính đi kèm mỗi hạt Chip LED, giúp tăng diện tích chiếu sáng, đảm bảo độ sáng đồng đều, khu vực chiếu sáng rộng, tiết kiệm điện năng và hiệu quả sử dụng
+Chi tiết đ
+èn đường LED năng lượng mặt trời TLC 75W
+Tấm pin
+Đèn đường LED năng lượng mặt trời TLC 75W sử dụng tấm pin Mono 36V/ 150W cao cấp, cho hiệu suất chuyển đổi năng lượng vượt trội so với tâm pin poly thông thường. Tối ưu hóa khả năng hấp thụ ánh sáng, giúp đèn vận hành ổn định trong mọi điều kiện thời tiết kể cả tại những vùng ít nắng, những ngày mưa bão hay trời âm u, nhiều mây.
+Pin lưu trữ
+Pin Lithium cao cấp của đèn đường LED năng lượng mặt trời TLC 75W sở hữu hiệu suất nạp xả cực cao, cho độ bền vượt trội lên đến 10 năm mà không cần thay mới.
+Dung lượng pin lớn và chất lượng pin ưu việt, giúp đèn có thể sáng liên tục đến 7 tiếng, đảm bảo an toàn cho khu vực nội khu đô thị, khu công nghiệp.
+Với thiết kế thông minh, hạn chế hoàn toàn việc xâm nhập nước, hơi ẩm làm giảm tuổi thọ của pin.
+Thân đèn
+Thân đèn làm bằng nhôm đúc giúp tản nhiệt hiệu quả, giảm tác động của nhiệt đến các linh kiện điện tử khác, tăng tuổi thọ của đèn.. Thước thuỷ kế giúp đảm bảo độ cân bằng chính xác, dễ dàng căn chỉnh thân đèn theo phương nằm ngang hoàn hảo trong quá trình thi công, tránh tình trạng đèn bị nghiêng hoặc lệch góc.</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -8716,7 +9036,7 @@
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>{"cong_suat": "100W", "nhiet_do_mau": "6500K", "kich_thuoc": "527*196*87mm", "chip_led": "Sanan", "hieu_suat_quang": "140 Lm/W", "chi_so_hoan_mau": "CRI &gt;70Ra", "dien_ap": "AC100~277VAC", "thuong_hieu": "TLC LIGHTING", "bao_hanh": "2-5 năm", "dien_ap_ac": "AC100~277VAC", "do_hoan_mau": "CRI&gt;70Ra", "chi_so_chong_am": "IP 65", "pf": "&gt;0.95", "nguon": "Philips 50W"}</t>
+          <t>{"cong_suat": "100W", "nhiet_do_mau": "6500K", "kich_thuoc": "527*196*87mm", "chip_led": "Sanan", "hieu_suat_quang": "140 Lm/W", "do_hoan_mau": "CRI &gt;70Ra", "dien_ap": "AC100~277VAC", "thuong_hieu": "TLC LIGHTING", "bao_hanh": "2-5 năm", "chi_so_chong_am": "IP 65", "pf": "&gt;0.95", "nguon": "Philips 50W"}</t>
         </is>
       </c>
       <c r="L4" t="inlineStr">
@@ -8745,6 +9065,19 @@
 Bảo hành: 2-5 năm</t>
         </is>
       </c>
+      <c r="T4" t="inlineStr">
+        <is>
+          <t>Đặc điểm nổi bật của đèn đường LED TLC 100W
+Chip LED
+Đèn đường LED TLC sử dụng chip LED với hiệu suất quang cao: 140 Lm/W, ánh sáng phân bổ đều, tiết kiệm năng lượng, tăng hiệu suất làm việc cho khu công nghiệp, kho bãi, đô thị.
+Được trang bị thấu kính đi kèm mỗi hạt Chip LED, giúp tăng diện tích chiếu sáng, đảm bảo độ sáng đồng đều, khu vực chiếu sáng rộng, tiết kiệm điện năng và hiệu quả sử dụng
+Chi tiết đèn đường LED TLC 100W
+Nguồn đèn
+Đèn đường LED 50W sử dụng nguồn công suất lớn đảm bảo đèn hoạt động ổn định và bền bỉ trong môi trường khắc nghiệt bên ngoài trời, nội khu và khu công nghiệp với chỉ số PF 0.95, chống nước, kháng bụi IP65, đạt tiêu chuẩn chống sét 10kV.
+Thân đèn
+Thiết kế thông minh dễ dàng tháo lắp giảm tối đa thời gian, thao tác thay thế, sửa chữa, lắp ráp. Thước thuỷ kế giúp đảm bảo độ cân bằng chính xác, dễ dàng căn chỉnh thân đèn theo phương nằm ngang hoàn hảo trong quá trình thi công, tránh tình trạng đèn bị nghiêng hoặc lệch góc. Thân đèn làm bằng nhôm đúc giúp tản nhiệt hiệu quả, giảm tác động của nhiệt đến các linh kiện điện tử khác, tăng tuổi thọ của đèn.</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -8796,6 +9129,19 @@
 Bảo hành: 2-5 năm</t>
         </is>
       </c>
+      <c r="T5" t="inlineStr">
+        <is>
+          <t>Đặc điểm nổi bật của đèn đường LED TLC 150W
+Chip LED
+Đèn đường LED TLC sử dụng chip LED với hiệu suất quang cao: 145 Lm/W, ánh sáng phân bổ đều, tiết kiệm năng lượng, tăng hiệu suất làm việc cho khu công nghiệp, kho bãi, đô thị.
+Được trang bị thấu kính đi kèm mỗi hạt Chip LED, giúp tăng diện tích chiếu sáng, đảm bảo độ sáng đồng đều, khu vực chiếu sáng rộng, tiết kiệm điện năng và hiệu quả sử dụng
+Chi tiết đèn đường LED TLC 150W
+Nguồn đèn
+Đèn đường LED 150W sử dụng nguồn công suất lớn đảm bảo đèn hoạt động ổn định và bền bỉ trong môi trường khắc nghiệt bên ngoài trời, nội khu và khu công nghiệp với chỉ số PF 0.95, chống nước, kháng bụi IP65, đạt tiêu chuẩn chống sét 10kV.
+Thân đèn
+Thiết kế thông minh dễ dàng tháo lắp giảm tối đa thời gian, thao tác thay thế, sửa chữa, lắp ráp. Thước thuỷ kế giúp đảm bảo độ cân bằng chính xác, dễ dàng căn chỉnh thân đèn theo phương nằm ngang hoàn hảo trong quá trình thi công, tránh tình trạng đèn bị nghiêng hoặc lệch góc. Thân đèn làm bằng nhôm đúc giúp tản nhiệt hiệu quả, giảm tác động của nhiệt đến các linh kiện điện tử khác, tăng tuổi thọ của đèn.</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -8818,7 +9164,7 @@
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>{"cong_suat": "200W", "nhiet_do_mau": "6500K", "kich_thuoc": "590*244*87mm", "chip_led": "Sanan", "hieu_suat_quang": "140 Lm/W", "do_hoan_mau": "CRI &gt;70Ra", "dien_ap": "AC100~277VAC", "thuong_hieu": "TLC LIGHTING", "bao_hanh": "2-5 năm", "chi_so_chong_am": "IP 65", "pf": "&gt;0.95", "nguon": "Philips 50W"}</t>
+          <t>{"cong_suat": "200W", "nhiet_do_mau": "6500K", "kich_thuoc": "590*244*87mm", "chip_led": "Sanan", "hieu_suat_quang": "140 Lm/W", "chi_so_hoan_mau": "CRI &gt;70Ra", "dien_ap": "AC100~277VAC", "thuong_hieu": "TLC LIGHTING", "bao_hanh": "2-5 năm", "do_hoan_mau": "CRI&gt;70Ra", "chi_so_chong_am": "IP 65", "pf": "&gt;0.95", "nguon": "Philips 50W"}</t>
         </is>
       </c>
       <c r="L6" t="inlineStr">
@@ -8847,6 +9193,19 @@
 Bảo hành: 2-5 năm</t>
         </is>
       </c>
+      <c r="T6" t="inlineStr">
+        <is>
+          <t>Đặc điểm nổi bật của đèn đường LED TLC 200W
+Chip LED
+Đèn đường LED TLC sử dụng chip LED với hiệu suất quang cao: 140 Lm/W, ánh sáng phân bổ đều, tiết kiệm năng lượng, tăng hiệu suất làm việc cho khu công nghiệp, kho bãi, đô thị.
+Được trang bị thấu kính đi kèm mỗi hạt Chip LED, giúp tăng diện tích chiếu sáng, đảm bảo độ sáng đồng đều, khu vực chiếu sáng rộng, tiết kiệm điện năng và hiệu quả sử dụng
+Chi tiết đèn đường LED TLC 200W
+Nguồn đèn
+Đèn đường LED 50W sử dụng nguồn công suất lớn đảm bảo đèn hoạt động ổn định và bền bỉ trong môi trường khắc nghiệt bên ngoài trời, nội khu và khu công nghiệp với chỉ số PF 0.95, chống nước, kháng bụi IP65, đạt tiêu chuẩn chống sét 10kV.
+Thân đèn
+Thiết kế thông minh dễ dàng tháo lắp giảm tối đa thời gian, thao tác thay thế, sửa chữa, lắp ráp. Thước thuỷ kế giúp đảm bảo độ cân bằng chính xác, dễ dàng căn chỉnh thân đèn theo phương nằm ngang hoàn hảo trong quá trình thi công, tránh tình trạng đèn bị nghiêng hoặc lệch góc. Thân đèn làm bằng nhôm đúc giúp tản nhiệt hiệu quả, giảm tác động của nhiệt đến các linh kiện điện tử khác, tăng tuổi thọ của đèn.</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -8869,7 +9228,7 @@
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>{"cong_suat": "50W", "nhiet_do_mau": "6500K", "kich_thuoc": "471*196*86mm, 537x244x87mm", "chip_led": "Sanan", "hieu_suat_quang": "140 Lm/W", "chi_so_hoan_mau": "CRI &gt;70Ra", "dien_ap": "AC100~277VAC", "thuong_hieu": "TLC LIGHTING", "bao_hanh": "2-5 năm", "chi_so_chong_am": "IP 65", "pf": "&gt;0.95", "nguon": "Philips 50W"}</t>
+          <t>{"cong_suat": "50W", "nhiet_do_mau": "6500K", "kich_thuoc": "471*196*86mm, 537x244x87mm", "chip_led": "Sanan", "hieu_suat_quang": "140 Lm/W", "chi_so_hoan_mau": "CRI &gt;70Ra", "dien_ap": "AC100~277VAC", "thuong_hieu": "TLC LIGHTING", "bao_hanh": "2-5 năm", "do_hoan_mau": "CRI&gt;70Ra", "chi_so_chong_am": "IP 65", "pf": "&gt;0.95", "nguon": "Philips 50W"}</t>
         </is>
       </c>
       <c r="L7" t="inlineStr">
@@ -8898,6 +9257,19 @@
 Bảo hành: 2-5 năm</t>
         </is>
       </c>
+      <c r="T7" t="inlineStr">
+        <is>
+          <t>Đặc điểm nổi bật của đèn đường LED TLC 50W
+Chip LED
+Đèn đường LED TLC sử dụng chip LED với hiệu suất quang cao: 140 Lm/W, ánh sáng phân bổ đều, tiết kiệm năng lượng, tăng hiệu suất làm việc cho khu công nghiệp, kho bãi, đô thị.
+Được trang bị thấu kính đi kèm mỗi hạt Chip LED, giúp tăng diện tích chiếu sáng, đảm bảo độ sáng đồng đều, khu vực chiếu sáng rộng, tiết kiệm điện năng và hiệu quả sử dụng
+Chi tiết đèn đường LED TLC 50W
+Nguồn đèn
+Đèn đường LED 50W sử dụng nguồn công suất lớn đảm bảo đèn hoạt động ổn định và bền bỉ trong môi trường khắc nghiệt bên ngoài trời, nội khu và khu công nghiệp với chỉ số PF 0.95, chống nước, kháng bụi IP65, đạt tiêu chuẩn chống sét 10kV.
+Thân đèn
+Thiết kế thông minh dễ dàng tháo lắp giảm tối đa thời gian, thao tác thay thế, sửa chữa, lắp ráp. Thước thuỷ kế giúp đảm bảo độ cân bằng chính xác, dễ dàng căn chỉnh thân đèn theo phương nằm ngang hoàn hảo trong quá trình thi công, tránh tình trạng đèn bị nghiêng hoặc lệch góc. Thân đèn làm bằng nhôm đúc giúp tản nhiệt hiệu quả, giảm tác động của nhiệt đến các linh kiện điện tử khác, tăng tuổi thọ của đèn.</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -9011,7 +9383,7 @@
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>{"cong_suat": "100W", "anh_sang": "Trắng/ Vàng/Trung tinh, Trắng, Vàng, Trung tinh", "hieu_suat_quang": "130 Lm/w", "chi_so_hoan_mau": "CRI=85", "dien_ap": "100-275V", "thuong_hieu": "TLC LIGHTING", "tuoi_tho": "40.000h", "bao_hanh": "24 tháng", "quang_thong": "13000 Lm", "do_hoan_mau": "80", "dien_ap_ac": "100-275V", "tuoi_tho_chip_led": "40.000 giờ"}</t>
+          <t>{"cong_suat": "100W", "anh_sang": "Trắng/ Vàng/Trung tinh", "chip_led": "Chip Citizen – Nhật Bản", "hieu_suat_quang": "130 Lm/w", "chi_so_hoan_mau": "CRI=85", "dien_ap": "100-275V", "thuong_hieu": "TLC LIGHTING", "tuoi_tho": "40.000h", "bao_hanh": "24 tháng", "quang_thong": "13000 Lm", "do_hoan_mau": "80", "dien_ap_ac": "100-275V", "tuoi_tho_chip_led": "40.000 giờ", "chi_so_hoan_mau_ra": "Ra &gt; 85", "khu_vuc_chong_nuoc": "IP67", "dien_ap_rong": "ac 85 – 265"}</t>
         </is>
       </c>
       <c r="J9" t="n">
@@ -9095,7 +9467,7 @@
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>{"cong_suat": "150W", "hieu_suat_quang": "130 Lm/w", "quang_thong": "13000Lm", "do_hoan_mau": "=85", "anh_sang": "Trắng, Vàng, Trung tinh", "dien_ap_ac": "100-275V", "chip_led": "Chip Citizen – Nhật Bản", "tuoi_tho_chip_led": "40.000 giờ", "bao_hanh": "24 tháng", "thuong_hieu": "TLC LIGHTING", "chi_so_hoan_mau": "Ra &gt; 85", "tieu_chuan": "IP 67"}</t>
+          <t>{"ma_san_pham": "TLC-ĐCA-150W", "thuong_hieu": "TLC LIGHTING", "cong_suat": "150W", "hieu_suat_quang": "130 Lm/w", "quang_thong": "13000Lm", "do_hoan_mau": "=85", "anh_sang": "Trắng, Vàng, Trung tinh", "dien_ap_ac": "100-275V", "chip_led": "Chip Citizen – Nhật Bản", "tuoi_tho_chip_led": "40.000 giờ", "bao_hanh": "24 tháng"}</t>
         </is>
       </c>
       <c r="J10" t="n">
@@ -9177,7 +9549,7 @@
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>{"cong_suat": "20W", "anh_sang": "Trắng/ Vàng/Trung tinh", "chip_led": "Chip Citizen – Nhật Bản", "hieu_suat_quang": "130 Lm/w", "chi_so_hoan_mau": "CRI=85", "dien_ap": "100-275V", "thuong_hieu": "TLC LIGHTING", "tuoi_tho": "40.000h", "bao_hanh": "24 tháng", "quang_thong": "2600 Lm", "do_hoan_mau": "=85", "dien_ap_ac": "100-275V", "tuoi_tho_chip_led": "40.000 giờ"}</t>
+          <t>{"cong_suat": "20W", "chip_led": "Chip Citizen – Nhật Bản", "hieu_suat_quang": "130 Lm/w", "chi_so_hoan_mau": "CRI=85", "dien_ap": "100-275V", "thuong_hieu": "TLC LIGHTING", "tuoi_tho": "40.000h", "bao_hanh": "24 tháng", "quang_thong": "2600 Lm", "do_hoan_mau": "=85", "dien_ap_ac": "100-275V", "tuoi_tho_chip_led": "40.000 giờ"}</t>
         </is>
       </c>
       <c r="J11" t="n">
@@ -9260,7 +9632,7 @@
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>{"cong_suat": "168W", "anh_sang": "Trắng, Vàng, Trung tinh", "chip_led": "Chip Citizen – Nhật Bản", "hieu_suat_quang": "130 Lm/w", "chi_so_hoan_mau": "CRI=85", "dien_ap": "100-275V", "thuong_hieu": "TLC LIGHTING", "tuoi_tho": "40.000h", "bao_hanh": "24 tháng", "quang_thong": "21840Lm", "kich_thuoc": "950x340x100", "do_hoan_mau": "=85", "dien_ap_ac": "100-275V", "tuoi_tho_chip_led": "40.000 giờ"}</t>
+          <t>{"cong_suat": "168W", "anh_sang": "Trắng/ Vàng/Trung tinh", "chip_led": "Chip Citizen – Nhật Bản", "hieu_suat_quang": "130 Lm/w", "chi_so_hoan_mau": "CRI=85", "dien_ap": "100-275V", "thuong_hieu": "TLC LIGHTING", "tuoi_tho": "40.000h", "bao_hanh": "24 tháng", "quang_thong": "21840Lm", "kich_thuoc": "950x340x100", "do_hoan_mau": "=85", "dien_ap_ac": "100-275V", "tuoi_tho_chip_led": "40.000 giờ"}</t>
         </is>
       </c>
       <c r="J12" t="n">
@@ -9337,7 +9709,7 @@
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>{"cong_suat": "56W", "anh_sang": "Trắng/ Vàng/Trung tinh, Trắng, Vàng, Trung tinh", "chip_led": "Chip Citizen – Nhật Bản", "hieu_suat_quang": "130 Lm/w", "chi_so_hoan_mau": "CRI=85", "dien_ap": "100-275V", "thuong_hieu": "TLC LIGHTING", "tuoi_tho": "40.000h", "bao_hanh": "24 tháng", "quang_thong": "7280Lm", "kich_thuoc": "435x305x80", "do_hoan_mau": "=85", "dien_ap_ac": "100-275V", "tuoi_tho_chip_led": "40.000 giờ"}</t>
+          <t>{"cong_suat": "56W", "anh_sang": "Trắng/ Vàng/Trung tinh", "chip_led": "Chip Citizen – Nhật Bản", "hieu_suat_quang": "130 Lm/w", "chi_so_hoan_mau": "CRI=85", "dien_ap": "100-275V", "thuong_hieu": "TLC LIGHTING", "tuoi_tho": "40.000h", "bao_hanh": "24 tháng", "quang_thong": "7280Lm", "kich_thuoc": "435x305x80", "do_hoan_mau": "=85", "dien_ap_ac": "100-275V", "tuoi_tho_chip_led": "40.000 giờ"}</t>
         </is>
       </c>
       <c r="J13" t="n">
@@ -9418,7 +9790,7 @@
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>{"cong_suat": "84W", "anh_sang": "Trắng/ Vàng/Trung tinh, Trắng, Vàng, Trung tinh", "chip_led": "Chip Citizen – Nhật Bản", "hieu_suat_quang": "130 Lm/w", "chi_so_hoan_mau": "CRI=85", "dien_ap": "100-275V", "thuong_hieu": "TLC LIGHTING", "tuoi_tho": "40.000h", "bao_hanh": "24 tháng", "quang_thong": "10920Lm", "kich_thuoc": "610x340x100", "do_hoan_mau": "=85", "dien_ap_ac": "100-275V", "tuoi_tho_chip_led": "40.000 giờ"}</t>
+          <t>{"cong_suat": "84W", "anh_sang": "Trắng/ Vàng/Trung tinh", "chip_led": "Chip Citizen – Nhật Bản", "hieu_suat_quang": "130 Lm/w", "chi_so_hoan_mau": "CRI=85", "dien_ap": "100-275V", "thuong_hieu": "TLC LIGHTING", "tuoi_tho": "40.000h", "bao_hanh": "24 tháng", "quang_thong": "10920Lm", "kich_thuoc": "610x340x100", "do_hoan_mau": "=85", "dien_ap_ac": "100-275V", "tuoi_tho_chip_led": "40.000 giờ"}</t>
         </is>
       </c>
       <c r="J14" t="n">
@@ -9583,7 +9955,7 @@
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>{"cong_suat": "126W", "anh_sang": "Trắng, Vàng, Trung tinh", "chip_led": "Chip Citizen – Nhật Bản", "hieu_suat_quang": "130 Lm/w", "chi_so_hoan_mau": "CRI=85", "dien_ap": "100-275V", "thuong_hieu": "TLC LIGHTING", "tuoi_tho": "40.000h", "bao_hanh": "24 tháng", "quang_thong": "1638Lm", "kich_thuoc": "735x305x112", "do_hoan_mau": "=85", "dien_ap_ac": "100-275V"}</t>
+          <t>{"cong_suat": "126W", "anh_sang": "Trắng/ Vàng/Trung tinh", "chip_led": "Chip Citizen – Nhật Bản", "hieu_suat_quang": "130 Lm/w", "chi_so_hoan_mau": "CRI=85", "dien_ap": "100-275V", "thuong_hieu": "TLC LIGHTING", "tuoi_tho": "40.000h", "bao_hanh": "24 tháng", "quang_thong": "1638Lm", "kich_thuoc": "735x305x112", "do_hoan_mau": "=85", "dien_ap_ac": "100-275V", "tuoi_tho_chip_led": "40.000 giờ"}</t>
         </is>
       </c>
       <c r="J16" t="n">
@@ -9827,7 +10199,7 @@
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>{"cong_suat": "50W", "anh_sang": "Trắng/ Vàng/Trung tinh, Trắng, Vàng, Trung tinh", "chip_led": "Chip Citizen – Nhật Bản", "hieu_suat_quang": "130 Lm/w", "chi_so_hoan_mau": "CRI=85", "dien_ap": "100-275V", "thuong_hieu": "TLC LIGHTING", "tuoi_tho": "40.000h", "bao_hanh": "24 tháng", "quang_thong": "6500Lm", "do_hoan_mau": "=85", "dien_ap_ac": "100-275V", "tuoi_tho_chip_led": "40.000 giờ", "he_so_hoan_mau": "CRI &gt;= 80", "kha_nang_chong_nuoc": "IP67"}</t>
+          <t>{"cong_suat": "50W", "anh_sang": "Trắng/ Vàng/Trung tinh", "chip_led": "Chip Citizen – Nhật Bản", "hieu_suat_quang": "130 Lm/w", "chi_so_hoan_mau": "CRI=85", "dien_ap": "100-275V", "thuong_hieu": "TLC LIGHTING", "tuoi_tho": "40.000h", "bao_hanh": "24 tháng", "quang_thong": "6500Lm", "do_hoan_mau": "=85", "dien_ap_ac": "100-275V", "tuoi_tho_chip_led": "40.000 giờ"}</t>
         </is>
       </c>
       <c r="J19" t="n">
@@ -10044,7 +10416,7 @@
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>{"hang_san_xuat": "TLC LIGHTING", "xuat_xu": "Việt Nam", "pin_sac": "1.2V/800 mA", "dong_dien_sac": "60mA", "chip_led": "Super LED", "thoi_gian_canh_bao_khi_mat_dien": "3 giờ DC", "bao_hanh": "24 tháng", "thuong_hieu": "TLC LIGHTING"}</t>
+          <t>{"hang_san_xuat": "TLC LIGHTING", "xuat_xu": "Việt Nam", "pin_sac": "1.2V/800 mA", "dong_dien_sac": "60mA", "chip_led": "Super LED", "thoi_gian_canh_bao_khi_mat_dien": "3 giờ DC", "bao_hanh": "24 tháng"}</t>
         </is>
       </c>
       <c r="J2" t="n">
@@ -10083,6 +10455,31 @@
 Đèn chiếu sáng khẩn cấp: Tham khảo tại đây</t>
         </is>
       </c>
+      <c r="T2" t="inlineStr">
+        <is>
+          <t>Thông số kỹ thuật:
+Tên sản phẩm
+Đèn Lối thoát – Đèn Exit TLC Lighting
+Thương hiệu
+TLC LIGHTING
+Pin sạc
+1.2V/800 mA
+Chip LED
+Super LED
+Dòng điện sạc
+60mA
+Thời gian cảnh báo khi mất điện
+3 giờ DC
+Bảo hành
+24 tháng
+Sản phẩm tương tự:
+Ghi chú
+Đèn Exit-Đèn chỉ dẫn lối thoát một mặt
+Tham khảo tại đây
+Đèn Exit-Đèn chỉ dẫn lối thoát hai mặt
+Đèn chiếu sáng khẩn cấp</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -10119,6 +10516,14 @@
       <c r="M3" t="inlineStr">
         <is>
           <t>https://tlclighting.com.vn/wp-content/uploads/2019/10/den-exit-den-chi-dan2.jpg</t>
+        </is>
+      </c>
+      <c r="P3" t="inlineStr">
+        <is>
+          <t>Nguồn điện dự phòng – Pin luôn đảm bảo đèn sáng 3 giờ liên tục khi xảy ra sự cố mất điện, cháy nổ, động đất
+Đèn chỉ dẫn rất rõ ràng chữ “EXIT” và “LỐI RA”. Ở khoảng cách 30m trong điều kiện chiếu sáng hoặc sự cố đều nhìn thấy rõ ràng
+Đảm bảo hướng dẫn sử dụng khi lắp đặt cần được bố trí ở chỗ dễ quan sát, chỉ dẫn lối đi, lối rẽ, cầu thang thoát nạn. Vị trí lắp lắp đặt giữa các đèn đảm bảo nhìn thấy lối thoát nạn và khoảng cách không lớn.
+Chiều cao tối thiểu của đèn Exit là 100m và không bị giới hạn về chiều cao này. Có 4 kích thước thường dùng của chiều cao đèn exit là 100mm, 120mm, 200mm, 250mm.</t>
         </is>
       </c>
       <c r="Q3" t="inlineStr">
@@ -10144,6 +10549,14 @@
 Đèn chiếu sáng khẩn cấp: Tham khảo tại đây</t>
         </is>
       </c>
+      <c r="T3" t="inlineStr">
+        <is>
+          <t>Nguồn điện dự phòng – Pin luôn đảm bảo đèn sáng 3 giờ liên tục khi xảy ra sự cố mất điện, cháy nổ, động đất
+Đèn chỉ dẫn rất rõ ràng chữ “EXIT” và “LỐI RA”. Ở khoảng cách 30m trong điều kiện chiếu sáng hoặc sự cố đều nhìn thấy rõ ràng
+Đảm bảo hướng dẫn sử dụng khi lắp đặt cần được bố trí ở chỗ dễ quan sát, chỉ dẫn lối đi, lối rẽ, cầu thang thoát nạn. Vị trí lắp lắp đặt giữa các đèn đảm bảo nhìn thấy lối thoát nạn và khoảng cách không lớn.
+Chiều cao tối thiểu của đèn Exit là 100m và không bị giới hạn về chiều cao này. Có 4 kích thước thường dùng của chiều cao đèn exit là 100mm, 120mm, 200mm, 250mm.</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -10166,7 +10579,7 @@
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>{"hang_san_xuat": "TLC LIGHTING", "xuat_xu": "Việt Nam", "pin_sac": "LIFE PO4 BATTERY 3.2V", "dong_dien_sac": "60mA", "chip_led": "Super LED", "thoi_gian_canh_bao_khi_mat_dien": "6 giờ", "bao_hanh": "24 tháng", "thoi_gian_chieu_sang_canh_bao": "6 giờ", "thoi_gian_chieu_sang_lien_tuc": "24 giờ", "tuoi_tho": "50.000 giờ"}</t>
+          <t>{"hang_san_xuat": "TLC LIGHTING", "xuat_xu": "Việt Nam", "pin_sac": "LIFE PO4 BATTERY 3.2V", "dong_dien_sac": "60mA", "chip_led": "Super LED", "thoi_gian_canh_bao_khi_mat_dien": "6 giờ", "bao_hanh": "24 tháng", "pin_kho": "LIFE PO4 BATTERY 3.2V", "thoi_gian_chieu_sang_canh_bao": "6 giờ", "thoi_gian_chieu_sang_lien_tuc": "24 giờ", "tuoi_tho": "50.000 giờ"}</t>
         </is>
       </c>
       <c r="J4" t="n">
@@ -10396,7 +10809,7 @@
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>{"cong_suat": "5W", "anh_sang": "Ba màu", "nhiet_do_mau": "3500K/6500K", "kich_thuoc": "Ø110×65", "hieu_suat_quang": "110-120 Lm/w", "chi_so_hoan_mau": "CRI≥85", "dien_ap": "85-265V", "lo_khoet": "Ø76", "thuong_hieu": "TLC LIGHTING", "tuoi_tho": "40.000h", "bao_hanh": "24 tháng", "do_hoan_mau": "&gt;85Ra", "quang_thong": "400Lm", "dien_ap_ac": "85-265V"}</t>
+          <t>{"cong_suat": "5W", "anh_sang": "Ba màu", "nhiet_do_mau": "3500K/6500K", "kich_thuoc": "Ø110×65", "hieu_suat_quang": "110-120 Lm/w", "chi_so_hoan_mau": "CRI≥85", "dien_ap": "85-265V", "lo_khoet": "Ø76", "thuong_hieu": "TLC LIGHTING", "tuoi_tho": "40.000h", "bao_hanh": "24 tháng", "dien_ap_ac": "85-265V", "do_hoan_mau": "&gt;85Ra", "quang_thong": "400Lm", "tuoi_tho_don_vi": "40.000 giờ", "bao_hanh_don_vi": "2 năm"}</t>
         </is>
       </c>
       <c r="J2" t="n">
@@ -10487,7 +10900,7 @@
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>{"cong_suat": "5W", "anh_sang": "Ba màu", "nhiet_do_mau": "3500K/6500K", "kich_thuoc": "Ø110×65", "chip_led": "Epistar", "hieu_suat_quang": "110-120 Lm/w", "chi_so_hoan_mau": "CRI≥85", "dien_ap": "85-265V", "lo_khoet": "Ø76", "thuong_hieu": "TLC LIGHTING", "tuoi_tho": "40.000h", "bao_hanh": "24 tháng", "do_hoan_mau": "&gt;85Ra", "quang_thong": "400Lm", "dien_ap_ac": "85-265V"}</t>
+          <t>{"cong_suat": "5W", "anh_sang": "Ba màu", "nhiet_do_mau": "3500K/6500K", "kich_thuoc": "Ø110×65", "chip_led": "Epistar", "hieu_suat_quang": "110-120 Lm/w", "chi_so_hoan_mau": "CRI≥85", "dien_ap": "85-265V", "lo_khoet": "Ø76", "thuong_hieu": "TLC LIGHTING", "tuoi_tho": "40.000h", "bao_hanh": "24 tháng", "do_hoan_mau": "&gt;85Ra", "quang_thong": "400Lm", "tuoi_tho_gio": "40.000 giờ", "bao_hanh_nam": "2 năm"}</t>
         </is>
       </c>
       <c r="J3" t="n">
@@ -10573,7 +10986,7 @@
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>{"cong_suat": "5W", "anh_sang": "Trắng, Vàng", "nhiet_do_mau": "3500K/6500K", "kich_thuoc": "Ø110×65", "hieu_suat_quang": "110-120 Lm/w", "chi_so_hoan_mau": "CRI≥85", "dien_ap": "85-265V", "lo_khoet": "Ø76", "thuong_hieu": "TLC LIGHTING", "tuoi_tho": "40.000h", "bao_hanh": "24 tháng", "dien_ap_ac": "85-265V", "do_hoan_mau": "&gt;85Ra", "quang_thong": "400Lm", "tuoi_tho_don_vi_gio": "40.000 giờ"}</t>
+          <t>{"cong_suat": "5W", "anh_sang": "Trắng/ Vàng", "nhiet_do_mau": "3500K/6500K", "kich_thuoc": "Ø110×65", "hieu_suat_quang": "110-120 Lm/w", "chi_so_hoan_mau": "CRI≥85", "dien_ap": "85-265V", "lo_khoet": "Ø76", "thuong_hieu": "TLC LIGHTING", "tuoi_tho": "40.000 giờ", "bao_hanh": "2 năm", "dien_ap_ac": "85-265V", "do_hoan_mau": "&gt;85Ra", "quang_thong": "400Lm"}</t>
         </is>
       </c>
       <c r="J4" t="n">
@@ -10659,7 +11072,7 @@
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>{"cong_suat": "7W", "anh_sang": "Ba màu", "nhiet_do_mau": "3500K/6500K", "kich_thuoc": "Ø120×65", "hieu_suat_quang": "110-120 Lm/w", "chi_so_hoan_mau": "CRI≥85", "dien_ap": "85-265V", "lo_khoet": "Ø90", "thuong_hieu": "TLC LIGHTING", "tuoi_tho": "40.000h", "bao_hanh": "24 tháng", "do_hoan_mau": "&gt;85Ra", "quang_thong": "560Lm"}</t>
+          <t>{"cong_suat": "7W", "anh_sang": "Ba màu", "nhiet_do_mau": "3500K/6500K", "kich_thuoc": "Ø120×65", "hieu_suat_quang": "110-120 Lm/w", "chi_so_hoan_mau": "CRI≥85", "dien_ap": "85-265V", "lo_khoet": "Ø90", "thuong_hieu": "TLC LIGHTING", "tuoi_tho": "40.000h", "bao_hanh": "24 tháng", "dien_ap_ac": "85-265V", "do_hoan_mau": "&gt;85Ra", "quang_thong": "560Lm", "tuoi_tho_gio": "40.000 giờ", "bao_hanh_nam": "2 năm"}</t>
         </is>
       </c>
       <c r="J5" t="n">
@@ -10754,7 +11167,7 @@
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>{"cong_suat": "7W", "anh_sang": "Vàng/trắng", "nhiet_do_mau": "3500K/6500K", "kich_thuoc": "Ø120×65", "hieu_suat_quang": "110-120 Lm/w", "chi_so_hoan_mau": "CRI≥85", "dien_ap": "85-265V", "lo_khoet": "Ø90", "thuong_hieu": "TLC LIGHTING", "tuoi_tho": "40.000h", "bao_hanh": "24 tháng", "dien_ap_ac": "85-265V", "do_hoan_mau": "&gt;85Ra", "quang_thong": "560Lm", "tuoi_tho_don_vi": "40.000 giờ"}</t>
+          <t>{"cong_suat": "7W", "anh_sang": "Vàng/trắng", "nhiet_do_mau": "3500K/6500K", "kich_thuoc": "Ø120×65", "hieu_suat_quang": "110-120 Lm/w", "chi_so_hoan_mau": "CRI≥85", "dien_ap": "85-265V", "lo_khoet": "Ø90", "thuong_hieu": "TLC LIGHTING", "tuoi_tho": "40.000h", "bao_hanh": "24 tháng", "dien_ap_ac": "85-265V", "do_hoan_mau": "&gt;85Ra", "quang_thong": "560Lm", "tuoi_tho_gio": "40.000 giờ", "bao_hanh_nam": "2 năm"}</t>
         </is>
       </c>
       <c r="J6" t="n">
@@ -10849,7 +11262,7 @@
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>{"cong_suat": "7W", "anh_sang": "Ba màu", "nhiet_do_mau": "3500K/6500K", "kich_thuoc": "Ø120×65", "chip_led": "Epistar", "hieu_suat_quang": "110-120 Lm/w", "chi_so_hoan_mau": "CRI≥85", "dien_ap": "85-265V", "lo_khoet": "Ø90", "thuong_hieu": "TLC LIGHTING", "tuoi_tho": "40.000h", "bao_hanh": "24 tháng", "do_hoan_mau": "&gt;85Ra", "quang_thong": "560Lm", "dien_ap_ac": "85-265V"}</t>
+          <t>{"cong_suat": "7W", "anh_sang": "Ba màu", "nhiet_do_mau": "3500K/6500K", "kich_thuoc": "Ø120×65", "chip_led": "Epistar", "hieu_suat_quang": "110-120 Lm/w", "chi_so_hoan_mau": "CRI≥85", "dien_ap": "85-265V", "lo_khoet": "Ø90", "thuong_hieu": "TLC LIGHTING", "tuoi_tho": "40.000h", "bao_hanh": "24 tháng", "dien_ap_ac": "85-265V", "do_hoan_mau": "&gt;85Ra", "quang_thong": "560Lm", "tuoi_tho_gio": "40.000 giờ", "bao_hanh_nam": "2 năm"}</t>
         </is>
       </c>
       <c r="J7" t="n">
@@ -10937,7 +11350,7 @@
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>{"cong_suat": "7W", "anh_sang": "Trắng/vàng", "nhiet_do_mau": "3500K/6500K", "kich_thuoc": "Ø120×65", "chip_led": "Epistar", "hieu_suat_quang": "110-120 Lm/w", "chi_so_hoan_mau": "CRI≥85", "dien_ap": "85-265V", "lo_khoet": "Ø90", "thuong_hieu": "TLC LIGHTING", "tuoi_tho": "40.000h", "bao_hanh": "24 tháng", "dien_ap_ac": "85-265V", "do_hoan_mau": "&gt;85Ra", "quang_thong": "560Lm", "tuoi_tho_gio": "40.000 giờ"}</t>
+          <t>{"cong_suat": "7W", "anh_sang": "Trắng/vàng", "nhiet_do_mau": "3500K/6500K", "kich_thuoc": "Ø120×65", "chip_led": "Epistar", "hieu_suat_quang": "110-120 Lm/w", "chi_so_hoan_mau": "CRI≥85", "dien_ap": "85-265V", "lo_khoet": "Ø90", "thuong_hieu": "TLC LIGHTING", "tuoi_tho": "40.000h", "bao_hanh": "24 tháng", "dien_ap_ac": "85-265V", "do_hoan_mau": "&gt;85Ra", "quang_thong": "560Lm", "tuoi_tho_gio": "40.000 giờ", "bao_hanh_nam": "2 năm"}</t>
         </is>
       </c>
       <c r="J8" t="n">
@@ -11107,7 +11520,7 @@
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>{"cong_suat": "9W", "anh_sang": "Trắng/vàng", "nhiet_do_mau": "3500K/6500K", "kich_thuoc": "Ø150×65", "hieu_suat_quang": "110-120 Lm/w", "chi_so_hoan_mau": "CRI≥85", "dien_ap": "85-265V", "lo_khoet": "Ø110", "thuong_hieu": "TLC LIGHTING", "tuoi_tho": "40.000h", "bao_hanh": "24 tháng", "do_hoan_mau": "&gt;85Ra", "quang_thong": "720Lm"}</t>
+          <t>{"cong_suat": "9W", "anh_sang": "Trắng/vàng, Ba màu", "nhiet_do_mau": "3500K/6500K", "kich_thuoc": "Ø150×65", "hieu_suat_quang": "110-120 Lm/w", "chi_so_hoan_mau": "CRI≥85, &gt;85Ra", "dien_ap": "85-265V", "lo_khoet": "Ø110", "thuong_hieu": "TLC LIGHTING", "tuoi_tho": "40.000h, 40.000 giờ", "bao_hanh": "24 tháng, 2 năm", "do_hoan_mau": "&gt;85Ra", "quang_thong": "720Lm"}</t>
         </is>
       </c>
       <c r="J10" t="n">
@@ -11195,7 +11608,7 @@
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>{"cong_suat": "9W", "anh_sang": "Ba màu", "nhiet_do_mau": "3500K/6500K", "kich_thuoc": "Ø150×65", "chip_led": "Epistar", "hieu_suat_quang": "110-120 Lm/w", "chi_so_hoan_mau": "CRI≥85", "dien_ap": "85-265V", "lo_khoet": "Ø110", "thuong_hieu": "TLC LIGHTING", "tuoi_tho": "40.000h", "bao_hanh": "24 tháng", "dien_ap_ac": "85-265V", "do_hoan_mau": "&gt;85Ra", "quang_thong": "720Lm", "tuoi_tho_gio": "40.000 giờ", "bao_hanh_nam": "2 năm"}</t>
+          <t>{"cong_suat": "9W", "anh_sang": "Ba màu", "nhiet_do_mau": "3500K/6500K", "kich_thuoc": "Ø150×65", "chip_led": "Epistar", "hieu_suat_quang": "110-120 Lm/w", "chi_so_hoan_mau": "CRI≥85", "dien_ap": "85-265V", "lo_khoet": "Ø110", "thuong_hieu": "TLC LIGHTING", "tuoi_tho": "40.000h", "bao_hanh": "24 tháng", "do_hoan_mau": "&gt;85Ra", "quang_thong": "720Lm"}</t>
         </is>
       </c>
       <c r="J11" t="n">
@@ -11209,6 +11622,17 @@
       <c r="M11" t="inlineStr">
         <is>
           <t>https://tlclighting.com.vn/wp-content/uploads/2019/06/IMG_2455-min.jpg</t>
+        </is>
+      </c>
+      <c r="P11" t="inlineStr">
+        <is>
+          <t>Sản phẩm đèn LED âm trần chống chói đế dày 9W ba màu viền vàng sử dụng công nghệ hiện đại nên có chất lượng vượt trội; tiện dụng, tính thẩm mỹ cao và rất an toàn khi dùng.
+Đèn LED 3 màu này có thể sử dụng lắp đặt trên các loại trần như: âm tường, trần thạch cao, trần gỗ để ánh sáng được tỏa màu và thay đổi màu tốt hơn.
+Được thiết kế khác biệt so với những loại LED thông thường; với bộ nguồn 3 dây 3 màu khác nhau để đổi màu linh hoạt trong khi chiếu sáng.
+Chip LED giúp chuyển hóa điện năng thành quang năng; giúp ánh sáng mạnh hơn, rõ hơn và ổn định hơn. Thông thường chip LED sẽ có công suất cao và an toàn, thân thiện với môi trường. Đồng thời có khả năng chịu nhiệt tốt và chiếu sáng liên tục.
+Chip LED của đèn 3 màu có sự khác biệt lớn so với những loại đèn khác; khả năng chịu nhiệt tốt, có thể chịu được thời gian chiếu sáng dài và thay đổi liên tục của các ánh sáng màu.
+An toàn và thân thiện: Trong quá trình phát sáng không gây ra các tia có hại như tia UV, tia hồng ngoại, tia tử ngoại, và các tia độc hại khác.
+Giá thành sản phẩm hợp lý, phù hợp với khả năng chi trả của đa số khách hàng cả ở thành thị và nông thôn.</t>
         </is>
       </c>
       <c r="Q11" t="inlineStr">
@@ -11232,6 +11656,18 @@
 3 màu: Tham khảo tại đâ</t>
         </is>
       </c>
+      <c r="T11" t="inlineStr">
+        <is>
+          <t>Ưu điểm vượt trội
+Sản phẩm đèn LED âm trần chống chói đế dày 9W ba màu viền vàng sử dụng công nghệ hiện đại nên có chất lượng vượt trội; tiện dụng, tính thẩm mỹ cao và rất an toàn khi dùng.
+Đèn LED 3 màu này có thể sử dụng lắp đặt trên các loại trần như: âm tường, trần thạch cao, trần gỗ để ánh sáng được tỏa màu và thay đổi màu tốt hơn.
+Được thiết kế khác biệt so với những loại LED thông thường; với bộ nguồn 3 dây 3 màu khác nhau để đổi màu linh hoạt trong khi chiếu sáng.
+Chip LED giúp chuyển hóa điện năng thành quang năng; giúp ánh sáng mạnh hơn, rõ hơn và ổn định hơn. Thông thường chip LED sẽ có công suất cao và an toàn, thân thiện với môi trường. Đồng thời có khả năng chịu nhiệt tốt và chiếu sáng liên tục.
+Chip LED của đèn 3 màu có sự khác biệt lớn so với những loại đèn khác; khả năng chịu nhiệt tốt, có thể chịu được thời gian chiếu sáng dài và thay đổi liên tục của các ánh sáng màu.
+An toàn và thân thiện: Trong quá trình phát sáng không gây ra các tia có hại như tia UV, tia hồng ngoại, tia tử ngoại, và các tia độc hại khác.
+Giá thành sản phẩm hợp lý, phù hợp với khả năng chi trả của đa số khách hàng cả ở thành thị và nông thôn.</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
@@ -11259,7 +11695,7 @@
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>{"cong_suat": "9W", "anh_sang": "Trắng/vàng", "nhiet_do_mau": "3500K/6500K", "kich_thuoc": "Ø150×65", "chip_led": "Epistar", "hieu_suat_quang": "110-120 Lm/w", "chi_so_hoan_mau": "CRI≥85", "dien_ap": "85-265V", "lo_khoet": "Ø110", "thuong_hieu": "TLC LIGHTING", "tuoi_tho": "40.000h", "bao_hanh": "24 tháng", "dien_ap_ac": "85-265V", "do_hoan_mau": "&gt;85Ra", "quang_thong": "720Lm", "tuoi_tho_gio": "40.000 giờ"}</t>
+          <t>{"cong_suat": "9W", "anh_sang": "Trắng/vàng", "nhiet_do_mau": "3500K/6500K", "kich_thuoc": "Ø150×65", "chip_led": "Epistar", "hieu_suat_quang": "110-120 Lm/w", "chi_so_hoan_mau": "CRI≥85", "dien_ap": "85-265V", "lo_khoet": "Ø110", "thuong_hieu": "TLC LIGHTING", "tuoi_tho": "40.000h", "bao_hanh": "24 tháng", "do_hoan_mau": "&gt;85Ra", "quang_thong": "720Lm"}</t>
         </is>
       </c>
       <c r="J12" t="n">
@@ -11579,7 +12015,7 @@
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>{"cong_suat": "12W", "anh_sang": "Ba màu", "nhiet_do_mau": "3500K/6500K", "kich_thuoc": "ø150x52mm", "lo_khoet": "ø110mm", "hieu_suat_quang": "110-120 Lm/w,~110Lm/w", "chi_so_hoan_mau": "CRI≥85,&gt;90Ra", "dien_ap": "85-265V", "thuong_hieu": "TLC LIGHTING", "tuoi_tho": "40.000h,40.000 giờ", "bao_hanh": "24 tháng,2 năm", "dien_ap_ac": "85-265V", "che_do_anh_sang": "Chống chói", "duong_kinh_lo_khoet": "D110mm", "duong_kinh_mat": "D150mm", "chieu_day": "52mm", "chat_lieu": "Hợp kim nhôm sơn tĩnh điện"}</t>
+          <t>{"cong_suat": "12W", "anh_sang": "Ba màu", "nhiet_do_mau": "3500K/6500K", "kich_thuoc": "ø150x52mm", "lo_khoet": "ø110mm", "hieu_suat_quang": "110-120 Lm/w", "chi_so_hoan_mau": "CRI≥85", "dien_ap": "85-265V", "thuong_hieu": "TLC LIGHTING", "tuoi_tho": "40.000h", "bao_hanh": "24 tháng", "dien_ap_ac": "85-265V", "hieu_suat_quang_2": "~110Lm/w", "do_hoan_mau": "&gt;90Ra", "che_do_anh_sang": "Chống chói", "duong_kinh_lo_khoet": "D110mm", "duong_kinh_mat": "D150mm", "chieu_day": "52mm", "chat_lieu": "Hợp kim nhôm sơn tĩnh điện", "tuoi_tho_2": "40.000 giờ", "bao_hanh_2": "2 năm"}</t>
         </is>
       </c>
       <c r="J2" t="n">
@@ -11684,7 +12120,7 @@
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>{"cong_suat": "12W", "anh_sang": "Trắng/vàng/trung tính", "nhiet_do_mau": "3500K/6500K", "kich_thuoc": "ø150x52mm", "lo_khoet": "ø110mm", "hieu_suat_quang": "110-120 Lm/w", "chi_so_hoan_mau": "CRI≥85", "dien_ap": "85-265V", "thuong_hieu": "TLC LIGHTING", "tuoi_tho": "40.000h", "bao_hanh": "24 tháng", "dien_ap_ac": "85-265V", "hieu_suat_quang_2": "~110Lm/w", "do_hoan_mau": "&gt;90Ra", "che_do_anh_sang": "Chống chói", "duong_kinh_lo_khoet": "D110mm", "duong_kinh_mat": "D150mm", "chieu_day": "52mm", "chat_lieu": "Hợp kim nhôm sơn tĩnh điện", "tuoi_tho_2": "40.000 giờ", "bao_hanh_2": "2 năm"}</t>
+          <t>{"cong_suat": "12W", "anh_sang": "Trắng/vàng/trung tính", "nhiet_do_mau": "3500K/6500K", "kich_thuoc": "ø150x52mm", "lo_khoet": "ø110mm", "hieu_suat_quang": "110-120 Lm/w", "chi_so_hoan_mau": "CRI≥85", "dien_ap": "85-265V", "thuong_hieu": "TLC LIGHTING", "tuoi_tho": "40.000h", "bao_hanh": "24 tháng", "dien_ap_AC": "85-265V", "hieu_suat_quang_2": "~110Lm/w", "do_hoan_mau": "&gt;90Ra", "che_do_anh_sang": "Chống chói", "duong_kinh_lo_khoet": "D110mm", "duong_kinh_mat": "D150mm", "chieu_day": "52mm", "chat_lieu": "Hợp kim nhôm sơn tĩnh điện", "tuoi_tho_2": "40.000 giờ", "bao_hanh_2": "2 năm"}</t>
         </is>
       </c>
       <c r="J3" t="n">
@@ -11783,7 +12219,7 @@
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>{"cong_suat": "12W", "anh_sang": "Ba màu", "nhiet_do_mau": "3500K/6500K", "kich_thuoc": "ø150x52mm", "lo_khoet": "ø110mm", "hieu_suat_quang": "110-120 Lm/w", "chi_so_hoan_mau": "CRI≥85", "dien_ap": "85-265V", "thuong_hieu": "TLC LIGHTING", "tuoi_tho": "40.000h", "bao_hanh": "24 tháng", "dien_ap_ac": "85-265V", "do_hoan_mau": "&gt;90Ra", "che_do_anh_sang": "Chống chói", "duong_kinh_lo_khoet": "D110mm", "duong_kinh_mat": "D150mm", "chieu_day": "52mm", "chat_lieu": "Hợp kim nhôm sơn tĩnh điện", "chip_led": "Chip Osram – CHLB Đức"}</t>
+          <t>{"cong_suat": "12W", "anh_sang": "Ba màu", "nhiet_do_mau": "3500K/6500K", "kich_thuoc": "ø150x52mm", "lo_khoet": "ø110mm", "hieu_suat_quang": "110-120 Lm/w", "chi_so_hoan_mau": "CRI≥85", "dien_ap": "85-265V", "thuong_hieu": "TLC LIGHTING", "tuoi_tho": "40.000h", "bao_hanh": "24 tháng", "dien_ap_ac": "85-265V", "hieu_suat_quang_2": "~110Lm/w", "do_hoan_mau": "&gt;90Ra", "che_do_anh_sang": "Chống chói", "duong_kinh_lo_khoet": "D110mm", "duong_kinh_mat": "D150mm", "chieu_day": "52mm", "chat_lieu": "Hợp kim nhôm sơn tĩnh điện", "chip_led": "Chip Osram – CHLB Đức", "tuoi_tho_2": "40.000 giờ", "bao_hanh_2": "2 năm"}</t>
         </is>
       </c>
       <c r="J4" t="n">
@@ -11887,7 +12323,7 @@
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>{"cong_suat": "12W", "anh_sang": "Trắng/vàng/trung tính", "nhiet_do_mau": "3500K/6500K", "kich_thuoc": "ø150x52mm", "lo_khoet": "ø110mm", "hieu_suat_quang": "~110Lm/w", "chi_so_hoan_mau": "CRI≥85", "dien_ap": "85-265V", "thuong_hieu": "TLC LIGHTING", "tuoi_tho": "40.000 giờ", "bao_hanh": "2 năm", "dien_ap_ac": "85-265V", "do_hoan_mau": "&gt;90Ra", "che_do_anh_sang": "Chống chói", "duong_kinh_lo_khoet": "D110mm", "duong_kinh_mat": "D150mm", "chieu_day": "52mm", "chat_lieu": "Hợp kim nhôm sơn tĩnh điện"}</t>
+          <t>{"cong_suat": "12W", "anh_sang": "Trắng/vàng/trung tính", "nhiet_do_mau": "3500K/6500K", "kich_thuoc": "ø150x52mm", "lo_khoet": "ø110mm", "hieu_suat_quang": "110-120 Lm/w", "chi_so_hoan_mau": "CRI≥85", "dien_ap": "85-265V", "thuong_hieu": "TLC LIGHTING", "tuoi_tho": "40.000 giờ", "bao_hanh": "24 tháng", "dien_ap_ac": "85-265V", "do_hoan_mau": "&gt;90Ra", "che_do_anh_sang": "Chống chói", "duong_kinh_lo_khoet": "D110mm", "duong_kinh_mat": "D150mm", "chieu_day": "52mm", "chat_lieu": "Hợp kim nhôm sơn tĩnh điện"}</t>
         </is>
       </c>
       <c r="J5" t="n">
@@ -12092,7 +12528,7 @@
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>{"cong_suat": "5W", "anh_sang": "Ba màu", "nhiet_do_mau": "3500K/6500K", "kich_thuoc": "ø106x52mm", "lo_khoet": "ø76mm", "hieu_suat_quang": "110-120 Lm/w", "chi_so_hoan_mau": "CRI≥85", "dien_ap": "85-265V", "thuong_hieu": "TLC LIGHTING", "tuoi_tho": "40.000h", "bao_hanh": "24 tháng", "dien_ap_ac": "85-265V", "do_hoan_mau": "&gt;90Ra", "che_do_anh_sang": "Chống chói", "duong_kinh_lo_khoet": "D76mm", "duong_kinh_mat": "D106mm", "chieu_day": "52mm", "chat_lieu": "Hợp kim nhôm sơn tĩnh điện"}</t>
+          <t>{"cong_suat": "5W", "anh_sang": "Ba màu", "nhiet_do_mau": "3500K/6500K", "kich_thuoc": "ø106x52mm", "lo_khoet": "ø76mm", "hieu_suat_quang": "110-120 Lm/w", "chi_so_hoan_mau": "CRI≥85", "dien_ap": "85-265V", "thuong_hieu": "TLC LIGHTING", "tuoi_tho": "40.000h", "bao_hanh": "24 tháng", "dien_ap_ac": "85-265V", "do_hoan_mau": "&gt;90Ra", "che_do_anh_sang": "Chống chói", "duong_kinh_lo_khoet": "D76mm", "duong_kinh_mat": "D106mm", "chieu_day": "52mm", "chat_lieu": "Hợp kim nhôm sơn tĩnh điện", "tuoi_tho_gio": "40.000 giờ"}</t>
         </is>
       </c>
       <c r="J7" t="n">
@@ -12202,7 +12638,7 @@
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>{"cong_suat": "5W", "anh_sang": "Ba màu", "nhiet_do_mau": "3500K/6500K", "kich_thuoc": "ø106x52mm", "lo_khoet": "ø76mm", "hieu_suat_quang": "110-120 Lm/w", "chi_so_hoan_mau": "CRI≥85", "dien_ap": "85-265V", "thuong_hieu": "TLC LIGHTING", "tuoi_tho": "40.000h", "bao_hanh": "24 tháng", "dien_ap_ac": "85-265V", "hieu_suat_quang_2": "~110Lm/w", "do_hoan_mau": "&gt;90Ra", "che_do_anh_sang": "Chống chói", "duong_kinh_lo_khoet": "ø76 mm", "duong_kinh_mat": "ø106 mm", "chieu_day": "52mm", "chat_lieu": "Hợp kim nhôm sơn tĩnh điện", "tuoi_tho_2": "40.000 giờ", "bao_hanh_2": "2 năm"}</t>
+          <t>{"cong_suat": "5W", "anh_sang": "Ba màu", "nhiet_do_mau": "3500K/6500K", "kich_thuoc": "ø106x52mm", "lo_khoet": "ø76mm", "hieu_suat_quang": "110-120 Lm/w", "chi_so_hoan_mau": "CRI≥85", "dien_ap": "85-265V", "thuong_hieu": "TLC LIGHTING", "tuoi_tho": "40.000h", "bao_hanh": "24 tháng", "che_do_anh_sang": "Chống chói", "duong_kinh_lo_khoet": "ø76 mm", "duong_kinh_mat": "ø106 mm", "chieu_day": "52mm", "chat_lieu": "Hợp kim nhôm sơn tĩnh điện", "tuoi_tho_2": "40.000 giờ", "bao_hanh_2": "2 năm"}</t>
         </is>
       </c>
       <c r="J8" t="n">
@@ -12306,7 +12742,7 @@
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>{"cong_suat": "5W", "anh_sang": "Trắng/vàng/trung tính", "nhiet_do_mau": "3500K/6500K", "kich_thuoc": "ø106x52mm", "lo_khoet": "ø76mm", "hieu_suat_quang": "110-120 Lm/w", "chi_so_hoan_mau": "CRI≥85", "dien_ap": "85-265V", "thuong_hieu": "TLC LIGHTING", "tuoi_tho": "40.000h", "bao_hanh": "24 tháng", "dien_ap_ac": "85-265V", "hieu_suat_quang_2": "~110Lm/w", "do_hoan_mau": "&gt;90Ra", "che_do_anh_sang": "Chống chói", "duong_kinh_lo_khoet": "D76mm", "duong_kinh_mat": "D106mm", "chieu_day": "52mm", "chat_lieu": "Hợp kim nhôm sơn tĩnh điện", "tuoi_tho_2": "40.000 giờ", "bao_hanh_2": "2 năm"}</t>
+          <t>{"cong_suat": "5W", "anh_sang": "Trắng/vàng/trung tính", "nhiet_do_mau": "3500K/6500K", "kich_thuoc": "ø106x52mm", "lo_khoet": "ø76mm", "hieu_suat_quang": "110-120 Lm/w", "chi_so_hoan_mau": "CRI≥85", "dien_ap": "85-265V", "thuong_hieu": "TLC LIGHTING", "tuoi_tho": "40.000h", "bao_hanh": "24 tháng", "dien_ap_ac": "85-265V", "do_hoan_mau": "&gt;90Ra", "che_do_anh_sang": "Chống chói", "duong_kinh_lo_khoet": "D76mm", "duong_kinh_mat": "D106mm", "chieu_day": "52mm", "chat_lieu": "Hợp kim nhôm sơn tĩnh điện", "tuoi_tho_gio": "40.000 giờ", "bao_hanh_nam": "2 năm"}</t>
         </is>
       </c>
       <c r="J9" t="n">
@@ -12625,7 +13061,7 @@
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>{"cong_suat": "7W", "anh_sang": "Ba màu", "nhiet_do_mau": "3500K/6500K", "kich_thuoc": "ø118x52mm", "lo_khoet": "ø90mm", "hieu_suat_quang": "110-120 Lm/w", "chi_so_hoan_mau": "CRI≥85", "dien_ap": "85-265V", "thuong_hieu": "TLC LIGHTING", "tuoi_tho": "40.000h", "bao_hanh": "24 tháng", "chat_lieu": "Hợp kim nhôm sơn tĩnh điện"}</t>
+          <t>{"cong_suat": "7W", "anh_sang": "Ba màu", "nhiet_do_mau": "3500K/6500K", "kich_thuoc": "ø118x52mm", "lo_khoet": "ø90mm", "hieu_suat_quang": "110-120 Lm/w", "chi_so_hoan_mau": "CRI≥85, &gt;90Ra", "dien_ap": "85-265V", "thuong_hieu": "TLC LIGHTING", "tuoi_tho": "40.000h, 40.000 giờ", "bao_hanh": "24 tháng, 2 năm", "dien_ap_ac": "85-265V", "che_do_anh_sang": "Chống chói", "duong_kinh_lo_khoet": "D90mm", "duong_kinh_mat": "D118mm", "chieu_day": "52mm", "chat_lieu": "Hợp kim nhôm sơn tĩnh điện"}</t>
         </is>
       </c>
       <c r="J12" t="n">
@@ -12704,7 +13140,7 @@
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>{"cong_suat": "7W", "anh_sang": "Trắng/vàng/trung tính", "nhiet_do_mau": "3500K/6500K", "kich_thuoc": "ø118x52mm", "lo_khoet": "ø90mm", "hieu_suat_quang": "110-120 Lm/w", "chi_so_hoan_mau": "CRI≥85", "dien_ap": "85-265V", "thuong_hieu": "TLC LIGHTING", "tuoi_tho": "40.000h", "bao_hanh": "24 tháng"}</t>
+          <t>{"cong_suat": "7W", "anh_sang": "Trắng/vàng/trung tính", "nhiet_do_mau": "3500K/6500K", "kich_thuoc": "ø118x52mm", "lo_khoet": "ø90mm", "hieu_suat_quang": "110-120 Lm/w", "chi_so_hoan_mau": "CRI≥85", "dien_ap": "85-265V", "thuong_hieu": "TLC LIGHTING", "tuoi_tho": "40.000h", "bao_hanh": "24 tháng", "dien_ap_ac": "85-265V", "do_hoan_mau": "&gt;90Ra", "che_do_anh_sang": "Chống chói", "duong_kinh_lo_khoet": "D90mm", "duong_kinh_mat": "D118mm", "chieu_day": "52mm", "chat_lieu": "Hợp kim nhôm sơn tĩnh điện"}</t>
         </is>
       </c>
       <c r="J13" t="n">
@@ -12937,7 +13373,7 @@
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>{"ten_san_pham": "Âm trần mặt cong đế mỏng 10w mặt trắng", "cong_suat": "10W", "hieu_suat_quang": "110-120Lm/w", "quang_thong": "1100 Lm", "chi_so_hoan_mau": "RA &gt; 85", "lo_khoet": "90mm", "mau_sac": "Đơn sắc (trắng/vàng/trung tính)", "dien_ap": "AC 85-265", "tuoi_tho": "40.000 giờ", "bao_hanh": "24 tháng", "hieu_suat_phat_quang": "120Lm/w"}</t>
+          <t>{"ten_san_pham": "Âm trần mặt cong đế mỏng 10w mặt trắng", "cong_suat": "10W", "hieu_suat_quang": "110-120Lm/w", "quang_thong": "1100 Lm", "chi_so_hoan_mau": "RA &gt; 85", "lo_khoet": "90mm", "mau_sac": "Đơn sắc (trắng/vàng/trung tính)", "dien_ap": "AC 85-265", "tuoi_tho": "40.000 giờ.", "bao_hanh": "24 tháng", "chip_led": "Bridgelux", "de_day": "37mm"}</t>
         </is>
       </c>
       <c r="J2" t="n">
@@ -13002,7 +13438,7 @@
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>{"cong_suat": "10W", "hieu_suat_quang": "110 – 120 Lm/w", "quang_thong": "1100 Lm", "chi_so_hoan_mau": "RA &gt; 85", "lo_khoet": "110mm", "mau_sac": "3 màu", "dien_ap": "AC 85-265", "tuoi_tho": "40.000 giờ", "bao_hanh": "24 tháng", "de_den_mong": "37mm", "anh_sang": "3 màu tổng hợp thay đổi qua mỗi lần bật/ tắt đèn"}</t>
+          <t>{"cong_suat": "10W", "hieu_suat_quang": "110 – 120 Lm/w", "quang_thong": "1100 Lm", "chi_so_hoan_mau_RA": "&gt; 85", "lo_khoet": "110mm", "mau_sac": "3 màu", "dien_ap": "AC 85-265", "tuoi_tho": "40.000 giờ", "bao_hanh": "24 tháng", "do_day_de": "37mm"}</t>
         </is>
       </c>
       <c r="J3" t="n">
@@ -13016,6 +13452,27 @@
       <c r="M3" t="inlineStr">
         <is>
           <t>https://tlclighting.com.vn/wp-content/uploads/2018/08/IMG_2557-min.jpg</t>
+        </is>
+      </c>
+      <c r="P3" t="inlineStr">
+        <is>
+          <t>Thiết kế tinh tế, sang trọng
+Đế đèn mỏng chỉ 37mm
+Công suất đèn: 10w thông dụng
+Ánh sáng: 3 màu tổng hợp thay đổi qua mỗi lần bật/ tắt đèn.
+Tuổi thọ cao lên đến 40.000 giờ
+Chính sách bảo hành 24 tháng</t>
+        </is>
+      </c>
+      <c r="T3" t="inlineStr">
+        <is>
+          <t>Đặc điểm đèn Led âm trần mặt cong đế mỏng 10w mặt vàng
+Thiết kế tinh tế, sang trọng
+Đế đèn mỏng chỉ 37mm
+Công suất đèn: 10w thông dụng
+Ánh sáng: 3 màu tổng hợp thay đổi qua mỗi lần bật/ tắt đèn.
+Tuổi thọ cao lên đến 40.000 giờ
+Chính sách bảo hành 24 tháng</t>
         </is>
       </c>
     </row>
@@ -13045,7 +13502,7 @@
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>{"cong_suat": "10W", "hieu_suat_quang": "110 – 120 Lm/w", "quang_thong": "1100 Lm", "chi_so_hoan_mau": "RA &gt; 85", "lo_khoet": "110mm", "mau_sac": "trắng/vàng/trung tính", "dien_ap": "AC 85-265", "tuoi_tho": "40.000 giờ", "bao_hanh": "24 tháng", "de_den_mong": "37mm"}</t>
+          <t>{"cong_suat": "10W", "hieu_suat_quang": "110 – 120 Lm/w", "quang_thong": "1100 Lm", "chi_so_hoan_mau_RA": "&gt; 85", "lo_khoet": "110mm", "mau_sac": "trắng/vàng/trung tính", "dien_ap": "AC 85-265", "tuoi_tho": "40.000 giờ", "bao_hanh": "24 tháng", "do_day_de": "37mm", "anh_sang": "đơn sắc (trắng, vàng hoặc trung tính)"}</t>
         </is>
       </c>
       <c r="J4" t="n">
@@ -13059,6 +13516,27 @@
       <c r="M4" t="inlineStr">
         <is>
           <t>https://tlclighting.com.vn/wp-content/uploads/2018/08/IMG_2557-min.jpg</t>
+        </is>
+      </c>
+      <c r="P4" t="inlineStr">
+        <is>
+          <t>Thiết kế tinh tế, sang trọng
+Đế đèn mỏng chỉ 37mm
+Công suất đèn: 10w thông dụng
+Ánh sáng: đèn có 2 loại ánh sáng gồm đơn sắc (trắng, vàng hoặc trung tính)
+Tuổi thọ cao lên đến 40.000 giờ
+Chính sách bảo hành 24 tháng</t>
+        </is>
+      </c>
+      <c r="T4" t="inlineStr">
+        <is>
+          <t>Đặc điểm đèn Led âm trần mặt cong đế mỏng 10w mặt vàng đơn sắc
+Thiết kế tinh tế, sang trọng
+Đế đèn mỏng chỉ 37mm
+Công suất đèn: 10w thông dụng
+Ánh sáng: đèn có 2 loại ánh sáng gồm đơn sắc (trắng, vàng hoặc trung tính)
+Tuổi thọ cao lên đến 40.000 giờ
+Chính sách bảo hành 24 tháng</t>
         </is>
       </c>
     </row>
@@ -13088,7 +13566,7 @@
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>{"ten_san_pham": "Âm trần mặt cong đế mỏng 10w mặt trắng", "cong_suat": "10W", "hieu_suat_quang": "110-120Lm/w", "quang_thong": "1100 Lm", "chi_so_hoan_mau_ra": "&gt; 85", "lo_khoet": "90mm", "mau_sac": "3 màu", "dien_ap": "AC 85-265", "tuoi_tho": "40.000 giờ", "bao_hanh": "24 tháng", "hieu_suat_phat_quang": "120Lm/w", "do_day": "37mm"}</t>
+          <t>{"ten_san_pham": "Âm trần mặt cong đế mỏng 10w mặt trắng", "cong_suat": "10W", "hieu_suat_quang": "110-120Lm/w", "quang_thong": "1100 Lm", "chi_so_hoan_mau_ra": "&gt; 85", "lo_khoet": "90mm", "mau_sac": "3 màu", "dien_ap": "AC 85-265", "tuoi_tho": "40.000 giờ", "bao_hanh": "24 tháng", "hieu_suat_phat_quang": "120Lm/w", "de_day": "37mm"}</t>
         </is>
       </c>
       <c r="J5" t="n">
@@ -13153,7 +13631,7 @@
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>{"ten_san_pham": "Âm trần mặt cong đế mỏng 6w mặt trắng", "cong_suat": "6W", "hieu_suat_quang": "110-120Lm/w", "quang_thong": "660 Lm", "chi_so_hoan_mau_RA": "&gt; 85", "lo_khoet": "76mm", "mau_sac": "trắng/vàng/trung tính", "dien_ap": "AC 85-265", "tuoi_tho": "40.000 giờ", "bao_hanh": "24 tháng", "mau_anh_sang": "3 màu"}</t>
+          <t>{"ten_san_pham": "Âm trần mặt cong đế mỏng 6w mặt trắng", "cong_suat": "6W", "hieu_suat_quang": "110-120Lm/w", "quang_thong": "660 Lm", "chi_so_hoan_mau": "RA &gt; 85", "lo_khoet": "76mm", "mau_sac": "trắng/vàng/trung tính", "dien_ap": "AC 85-265", "tuoi_tho": "40.000 giờ", "bao_hanh": "24 tháng", "chip_led": "Bridgelux", "hieu_suat_quang_chip": "120Lm/w", "chi_so_hoan_mau_chip": "Ra &gt; 85", "pc_thau_quang": "92%", "vat_lieu_vo_den": "mica trắng, viền nhôm", "vat_lieu_de_tan_nhiet": "nhôm", "mau_anh_sang": "3 màu"}</t>
         </is>
       </c>
       <c r="J6" t="n">
@@ -13167,6 +13645,25 @@
       <c r="M6" t="inlineStr">
         <is>
           <t>https://tlclighting.com.vn/wp-content/uploads/2018/08/IMG_2583-min.jpg</t>
+        </is>
+      </c>
+      <c r="P6" t="inlineStr">
+        <is>
+          <t>Tuổi thọ đèn cao, lên đến 40.000 giờ
+Bảo hành đổi mới trong 24 tháng
+Màu ánh sáng đa dạng: 3 màu tuỳ theo nhu cầu sử dụng của mỗi người
+Giá thành cạnh tranh so với những sản phẩm cùng chất lượng khác</t>
+        </is>
+      </c>
+      <c r="T6" t="inlineStr">
+        <is>
+          <t>Ngoài ra, đèn Led
+âm trần mặt cong đế mỏng 6w mặt trắng ba màu
+còn có những đặc điểm sau:
+Tuổi thọ đèn cao, lên đến 40.000 giờ
+Bảo hành đổi mới trong 24 tháng
+Màu ánh sáng đa dạng: 3 màu tuỳ theo nhu cầu sử dụng của mỗi người
+Giá thành cạnh tranh so với những sản phẩm cùng chất lượng khác</t>
         </is>
       </c>
     </row>
@@ -13196,7 +13693,7 @@
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>{"cong_suat": "6W", "hieu_suat_quang": "110-120Lm/w", "quang_thong": "660 Lm", "chi_so_hoan_mau": "RA &gt; 85", "lo_khoet": "76mm", "mau_sac": "trắng/vàng/trung tính", "dien_ap": "AC 85-265", "tuoi_tho": "40.000 giờ", "bao_hanh": "24 tháng", "mau_anh_sang": "trắng, vàng, trung tính hoặc 3 màu"}</t>
+          <t>{"ten_san_pham": "Âm trần mặt cong đế mỏng 6w mặt trắng đơn sắc", "cong_suat": "6W", "hieu_suat_quang": "110-120Lm/w", "quang_thong": "660 Lm", "chi_so_hoan_mau": "RA &gt; 85", "lo_khoet": "76mm", "mau_sac": "trắng/vàng/trung tính", "dien_ap": "AC 85-265", "tuoi_tho": "40.000 giờ", "bao_hanh": "24 tháng", "hieu_suat_quang_chip": "120Lm/w", "chi_so_hoan_mau_chip": "Ra &gt; 85", "pc_thau_quang": "92%", "mau_anh_sang_da_dang": "trắng, vàng, trung tính hoặc 3 màu"}</t>
         </is>
       </c>
       <c r="J7" t="n">
@@ -13210,6 +13707,25 @@
       <c r="M7" t="inlineStr">
         <is>
           <t>https://tlclighting.com.vn/wp-content/uploads/2018/08/IMG_2583-min.jpg</t>
+        </is>
+      </c>
+      <c r="P7" t="inlineStr">
+        <is>
+          <t>Tuổi thọ đèn cao, lên đến 40.000 giờ
+Bảo hành đổi mới trong 24 tháng
+Màu ánh sáng đa dạng: trắng, vàng, trung tính hoặc 3 màu tuỳ theo nhu cầu sử dụng của mỗi người
+Giá thành cạnh tranh so với những sản phẩm cùng chất lượng khác</t>
+        </is>
+      </c>
+      <c r="T7" t="inlineStr">
+        <is>
+          <t>Ngoài ra, đèn Led
+âm trần mặt cong đế mỏng 6w mặt trắng đơn sắc
+còn có những đặc điểm sau:
+Tuổi thọ đèn cao, lên đến 40.000 giờ
+Bảo hành đổi mới trong 24 tháng
+Màu ánh sáng đa dạng: trắng, vàng, trung tính hoặc 3 màu tuỳ theo nhu cầu sử dụng của mỗi người
+Giá thành cạnh tranh so với những sản phẩm cùng chất lượng khác</t>
         </is>
       </c>
     </row>
@@ -13239,7 +13755,7 @@
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>{"ten_san_pham": "Âm trần mặt cong đế mỏng 6w mặt vàng", "thuong_hieu": "TLC Lighting", "cong_suat": "6W", "hieu_suat_quang": "110-120Lm/w", "quang_thong": "660 Lm", "chi_so_hoan_mau": "RA &gt; 85", "lo_khoet": "76mm", "mau_sac": "3 màu", "dien_ap": "AC 85-265", "tuoi_tho": "40.000 giờ", "bao_hanh": "24 tháng"}</t>
+          <t>{"ten_san_pham": "Âm trần mặt cong đế mỏng 6w mặt vàng", "thuong_hieu": "TLC Lighting", "cong_suat": "6W", "hieu_suat_quang": "110-120Lm/w", "quang_thong": "660 Lm", "chi_so_hoan_mau_RA": "&gt; 85", "lo_khoet": "76mm", "mau_sac": "3 màu", "dien_ap": "AC 85-265", "tuoi_tho": "40.000 giờ", "bao_hanh": "24 tháng"}</t>
         </is>
       </c>
       <c r="J8" t="n">
@@ -13253,6 +13769,34 @@
       <c r="M8" t="inlineStr">
         <is>
           <t>https://tlclighting.com.vn/wp-content/uploads/2018/08/IMG_2557-min.jpg</t>
+        </is>
+      </c>
+      <c r="P8" t="inlineStr">
+        <is>
+          <t>Thiết kế đèn
+Cấu tạo đèn
+Tuổi thọ đèn và bảo hành</t>
+        </is>
+      </c>
+      <c r="T8" t="inlineStr">
+        <is>
+          <t>Đặc điểm của đèn âm trần mặt cong đế mỏng ba màu
+Thiết kế đèn
+Mặt đèn hình tròn, choá đèn sử dụng Mica trắng giúp phản quang tốt hơn và chống nhức mỏi mắt cho người sử dụng. Xung quanh viền đèn được làm bằng nhôm có phun sơn tĩnh điện màu vàng giúp giữ màu bền lâu.
+Phần tai đèn được thiết kế giúp định vị cố định chiếc đèn khi được lắp vào trần nhà.
+Cấu tạo đèn
+Đèn được cấu tạo gồm: vỏ đèn, đế đèn, chip Led và nguồn khiển.
+Vỏ đèn được làm từ nhôm có thiết kế cong nhẹ, khiến mặt đèn trở nên tinh tế, đảm bảo yếu tố thẩm mĩ. Chóa đèn được làm từ mica trắng, PC thấu quang 92%  chống lóa, nhức mỏi mắt cho người sử dụng.
+Chip LED Bridgelux – thương hiệu nổi tiếng của Mỹ, hiệu suất phát quang lên đến 120Lm/w, chỉ số hoàn màu Ra&gt;85 giúp đèn sở hữu chất lượng ánh sáng trung thực, màu sắc sự vật được chiếu sáng tự nhiên.
+Đế tản nhiệt được làm từ nhôm có tính năng tản nhiệt tốt gấp 2 lần những loại đế thông thường như nhựa hay hợp kim nhôm. Với chiều dày đế khoảng 37mm giúp đèn thích hợp lắp cho mọi trần nhà.
+Đèn Led
+âm trần mặt cong đế mỏng 6w mặt vàng ba màu
+sử dụng bộ nguồn của đèn có chức năng biến đổi dòng điện 2 chiều thành dòng điện 1 chiều để phù hợp với nguyên lý hoạt động của đèn. Bộ nguồn có dải điện áp lớn 85-265 chống chớp nháy, duy trì tình ổn định của dòng điện, kéo dài tuổi thọ của đèn.
+Tuổi thọ đèn và bảo hành
+Sau quá trình thử nghiệm sản phẩm, đèn
+có tuổi thọ cao lên đến 40.000 giờ.
+Với chính sách bảo hành đổi mới sản phẩm trong vòng 24 tháng nếu có lỗi từ nhà sản xuất, TLC Lighting tự tin khi làm hài lòng quý khách hàng.
+Những hình ảnh mới nhất của đèn LED âm trần mặt cong đế mỏng</t>
         </is>
       </c>
     </row>
@@ -13282,7 +13826,7 @@
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>{"thuong_hieu": "TLC Lighting", "cong_suat": "6W", "hieu_suat_quang": "110-120Lm/w", "quang_thong": "660 Lm", "chi_so_hoan_mau": "RA &gt; 85", "lo_khoet": "76mm", "mau_sac": "trắng/vàng/trung tính", "dien_ap": "AC 85-265", "tuoi_tho": "40.000 giờ", "bao_hanh": "24 tháng"}</t>
+          <t>{"ten_san_pham": "Âm trần mặt cong đế mỏng 6w mặt vàng", "thuong_hieu": "TLC Lighting", "cong_suat": "6W", "hieu_suat_quang": "110-120Lm/w", "quang_thong": "660 Lm", "chi_so_hoan_mau_RA": "&gt; 85", "lo_khoet": "76mm", "mau_sac": "trắng/vàng/trung tính", "dien_ap": "AC 85-265", "tuoi_tho": "40.000 giờ", "bao_hanh": "24 tháng"}</t>
         </is>
       </c>
       <c r="J9" t="n">
@@ -13296,6 +13840,34 @@
       <c r="M9" t="inlineStr">
         <is>
           <t>https://tlclighting.com.vn/wp-content/uploads/2018/08/IMG_2557-min.jpg</t>
+        </is>
+      </c>
+      <c r="P9" t="inlineStr">
+        <is>
+          <t>Thiết kế đèn
+Cấu tạo đèn
+Tuổi thọ đèn và bảo hành</t>
+        </is>
+      </c>
+      <c r="T9" t="inlineStr">
+        <is>
+          <t>Đặc điểm của đèn âm trần mặt cong đế mỏng đơn sắc
+Thiết kế đèn
+Mặt đèn hình tròn, choá đèn sử dụng Mica trắng giúp phản quang tốt hơn và chống nhức mỏi mắt cho người sử dụng. Xung quanh viền đèn được làm bằng nhôm có phun sơn tĩnh điện màu vàng giúp giữ màu bền lâu.
+Phần tai đèn được thiết kế giúp định vị cố định chiếc đèn khi được lắp vào trần nhà.
+Cấu tạo đèn
+Đèn được cấu tạo gồm: vỏ đèn, đế đèn, chip Led và nguồn khiển.
+Vỏ đèn được làm từ nhôm có thiết kế cong nhẹ, khiến mặt đèn trở nên tinh tế, đảm bảo yếu tố thẩm mĩ. Chóa đèn được làm từ mica trắng, PC thấu quang 92%  chống lóa, nhức mỏi mắt cho người sử dụng.
+Chip LED Bridgelux – thương hiệu nổi tiếng của Mỹ, hiệu suất phát quang lên đến 120Lm/w, chỉ số hoàn màu Ra&gt;85 giúp đèn sở hữu chất lượng ánh sáng trung thực, màu sắc sự vật được chiếu sáng tự nhiên.
+Đế tản nhiệt được làm từ nhôm có tính năng tản nhiệt tốt gấp 2 lần những loại đế thông thường như nhựa hay hợp kim nhôm. Với chiều dày đế khoảng 37mm giúp đèn thích hợp lắp cho mọi trần nhà.
+Đèn Led
+âm trần mặt cong đế mỏng 6w mặt vàng đơn sắc
+sử dụng bộ nguồn của đèn có chức năng biến đổi dòng điện 2 chiều thành dòng điện 1 chiều để phù hợp với nguyên lý hoạt động của đèn. Bộ nguồn có dải điện áp lớn 85-265 chống chớp nháy, duy trì tình ổn định của dòng điện, kéo dài tuổi thọ của đèn.
+Tuổi thọ đèn và bảo hành
+Sau quá trình thử nghiệm sản phẩm, đèn
+có tuổi thọ cao lên đến 40.000 giờ.
+Với chính sách bảo hành đổi mới sản phẩm trong vòng 24 tháng nếu có lỗi từ nhà sản xuất, TLC Lighting tự tin khi làm hài lòng quý khách hàng.
+Những hình ảnh mới nhất của đèn LED âm trần mặt cong đế mỏng</t>
         </is>
       </c>
     </row>
@@ -13325,7 +13897,7 @@
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>{"ten_san_pham": "Âm trần mặt cong đế mỏng 8W mặt trắng", "cong_suat": "8W", "hieu_suat_quang": "110-120Lm/w", "quang_thong": "880 Lm", "chi_so_hoan_mau_ra": "&gt; 85", "lo_khoet": "90mm", "mau_sac": "3 màu", "dien_ap": "AC 85-265", "tuoi_tho": "40.000 giờ", "bao_hanh": "24 tháng"}</t>
+          <t>{"ten_san_pham": "Âm trần mặt cong đế mỏng 8W mặt trắng", "cong_suat": "8W", "hieu_suat_quang": "110-120Lm/w", "quang_thong": "880 Lm", "chi_so_hoan_mau": "RA &gt; 85", "lo_khoet": "90mm", "mau_sac": "3 màu", "dien_ap": "AC 85-265", "tuoi_tho": "40.000 giờ", "bao_hanh": "24 tháng"}</t>
         </is>
       </c>
       <c r="J10" t="n">
@@ -13339,6 +13911,12 @@
       <c r="M10" t="inlineStr">
         <is>
           <t>https://tlclighting.com.vn/wp-content/uploads/2018/08/IMG_2583-min.jpg</t>
+        </is>
+      </c>
+      <c r="T10" t="inlineStr">
+        <is>
+          <t>Đặc điểm
+LED âm trần mặt cong đế mỏng viền trắng</t>
         </is>
       </c>
     </row>
@@ -13368,7 +13946,7 @@
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>{"cong_suat": "8W", "hieu_suat_quang": "110-120Lm/w", "quang_thong": "880 Lm", "chi_so_hoan_mau_RA": "&gt; 85", "lo_khoet": "90mm", "mau_sac": "trắng/vàng/trung tính", "dien_ap": "AC 85-265", "tuoi_tho": "40.000 giờ", "bao_hanh": "24 tháng"}</t>
+          <t>{"ten_san_pham": "Âm trần mặt cong đế mỏng 8W mặt trắng đơn sắc", "cong_suat": "8W", "hieu_suat_quang": "110-120Lm/w", "quang_thong": "880 Lm", "chi_so_hoan_mau": "RA &gt; 85", "lo_khoet": "90mm", "mau_sac": "trắng/vàng/trung tính", "dien_ap": "AC 85-265", "tuoi_tho": "40.000 giờ", "bao_hanh": "24 tháng"}</t>
         </is>
       </c>
       <c r="J11" t="n">
@@ -13382,6 +13960,12 @@
       <c r="M11" t="inlineStr">
         <is>
           <t>https://tlclighting.com.vn/wp-content/uploads/2018/08/IMG_2583-min.jpg</t>
+        </is>
+      </c>
+      <c r="T11" t="inlineStr">
+        <is>
+          <t>Đặc điểm
+LED âm trần mặt cong đế mỏng viền trắng</t>
         </is>
       </c>
     </row>
@@ -13411,7 +13995,7 @@
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>{"ten_san_pham": "Âm trần mặt cong đế mỏng 8w mặt vàng", "cong_suat": "8W", "hieu_suat_quang": "110-120Lm/w", "quang_thong": "880 Lm", "chi_so_hoan_mau": "RA &gt; 85", "lo_khoet": "90mm", "mau_sac": "3 màu", "dien_ap": "AC 85-265", "tuoi_tho": "40.000 giờ", "bao_hanh": "24 tháng"}</t>
+          <t>{"ten_san_pham": "Âm trần mặt cong đế mỏng 8w mặt vàng", "cong_suat": "8W", "hieu_suat_quang": "110-120Lm/w", "quang_thong": "880 Lm", "chi_so_hoan_mau_ra": "&gt; 85", "lo_khoet": "90mm", "mau_sac": "3 màu", "dien_ap": "AC 85-265", "tuoi_tho": "40.000 giờ", "bao_hanh": "24 tháng", "hieu_suat_quang_chip": "120Lm/w", "chi_so_hoan_mau": "Ra &gt; 85", "mau_anh_sang": "3 màu"}</t>
         </is>
       </c>
       <c r="J12" t="n">
@@ -13425,6 +14009,39 @@
       <c r="M12" t="inlineStr">
         <is>
           <t>https://tlclighting.com.vn/wp-content/uploads/2018/08/IMG_2557-min.jpg</t>
+        </is>
+      </c>
+      <c r="P12" t="inlineStr">
+        <is>
+          <t>Vỏ của đèn
+Bộ nguồn điều khiển
+Đế đèn Led
+Chip Led Bridgelux – Mỹ</t>
+        </is>
+      </c>
+      <c r="T12" t="inlineStr">
+        <is>
+          <t>Vỏ của đèn
+Vỏ đèn gồm 2 thành phần: mica trắng và viền nhôm được phun lớp sơn tĩnh điện giúp vỏ đèn giữ màu bền hơn.
+Chóa đèn được làm từ mica trắng có PC thấu quang lên đến 92%, ánh sáng đèn chống lóa, chống nhức mỏi mắt cho người sử dụng.
+Viền đèn được làm từ nhôm có thiết kế cong nhẹ, lớp phun sơn màu vàng xung quanh viền giúp chiếc đèn trông bắt mắt, sang trọng hơn khi lắp vào trần.
+Bộ nguồn điều khiển
+Bộ nguồn điều khiển chịu nhiệt của đèn Led
+âm trần mặt cong đế mỏng 8w mặt vàng ba màu
+giúp duy trì tính ổn định của dòng điện, kéo dài tuổi thọ của đèn, chống chớp nháy.
+Đế đèn Led
+Đế đèn
+được làm hoàn toàn từ nhôm, có tính năng tản nhiệt tốt gấp 2 lần so với những loại đế thông thường được làm từ hợp kim nhôm hoặc nhựa.
+Chip Led Bridgelux – Mỹ
+Chip Led Bridgelux thuộc dòng chip Led cao cấp đến từ Mỹ.
+Chip giúp chất lượng ánh sáng của đèn đồng đều với hiệu suất quang: 120Lm/w. Với chỉ số hoàn màu Ra &gt; 85, đèn khi chiếu sáng sẽ có ánh sáng trung thực và màu sắc của các vật được chiếu vào rất tự nhiên.
+Ngoài ra, đèn Led
+âm trần mặt cong đế mỏng 6w mặt trắng ba màu
+còn có những đặc điểm sau:
+Tuổi thọ đèn cao, lên đến 40.000 giờ
+Giá thành cạnh tranh cao so với các sản phẩm cùng chất lượng khác
+Bảo hành đổi mới trong 24 tháng
+Màu ánh sáng đa dạng kết hợp 3 màu</t>
         </is>
       </c>
     </row>
@@ -13454,7 +14071,7 @@
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>{"ten_san_pham": "Âm trần mặt cong đế mỏng 8w mặt vàng", "cong_suat": "8W", "hieu_suat_quang": "110-120Lm/w", "quang_thong": "880 Lm", "chi_so_hoan_mau": "RA &gt; 85", "lo_khoet": "90mm", "mau_sac": "trắng/vàng/trung tính", "dien_ap": "AC 85-265", "tuoi_tho": "40.000 giờ", "bao_hanh": "24 tháng"}</t>
+          <t>{"ten_san_pham": "Âm trần mặt cong đế mỏng 8w mặt vàng", "cong_suat": "8W", "hieu_suat_quang": "110-120Lm/w", "quang_thong": "880 Lm", "chi_so_hoan_mau_ra": "&gt; 85", "lo_khoet": "90mm", "mau_sac": "trắng/vàng/trung tính", "dien_ap": "AC 85-265", "tuoi_tho": "40.000 giờ", "bao_hanh": "24 tháng"}</t>
         </is>
       </c>
       <c r="J13" t="n">
@@ -13468,6 +14085,25 @@
       <c r="M13" t="inlineStr">
         <is>
           <t>https://tlclighting.com.vn/wp-content/uploads/2018/08/IMG_2557-min.jpg</t>
+        </is>
+      </c>
+      <c r="P13" t="inlineStr">
+        <is>
+          <t>Tuổi thọ đèn cao, lên đến 40.000 giờ
+Giá thành cạnh tranh cao so với các sản phẩm cùng chất lượng khác
+Bảo hành đổi mới trong 24 tháng
+Màu ánh sáng đa dạng: trắng, vàng, trung tính hoặc 3 màu</t>
+        </is>
+      </c>
+      <c r="T13" t="inlineStr">
+        <is>
+          <t>Ngoài ra, đèn Led
+âm trần mặt cong đế mỏng 6w mặt trắng đơn sắc
+còn có những đặc điểm sau:
+Tuổi thọ đèn cao, lên đến 40.000 giờ
+Giá thành cạnh tranh cao so với các sản phẩm cùng chất lượng khác
+Bảo hành đổi mới trong 24 tháng
+Màu ánh sáng đa dạng: trắng, vàng, trung tính hoặc 3 màu</t>
         </is>
       </c>
     </row>
@@ -13635,7 +14271,7 @@
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>{"cong_suat": "12W", "anh_sang": "ba màu", "nhiet_do_mau": "3500K/6500K", "kich_thuoc": "ø148x37mm", "lo_khoet": "ø110mm", "chip_led": "OSRAM", "hieu_suat_quang": "110-120 Lm/w", "chi_so_hoan_mau": "CRI≥85", "dien_ap": "85-265V", "thuong_hieu": "TLC LIGHTING", "tuoi_tho": "40.000h", "bao_hanh": "24 tháng", "dien_ap_ac": "85-265V", "hieu_suat_quang_2": "~110Lm/w", "do_hoan_mau": "&gt;90Ra", "che_do_anh_sang": "Chống chói", "duong_kinh_lo_khoet": "D110mm", "duong_kinh_mat": "D148mm", "chieu_day": "37mm", "chat_lieu": "Hợp kim nhôm sơn tĩnh điện", "tuoi_tho_2": "40.000 giờ"}</t>
+          <t>{"cong_suat": "12W", "anh_sang": "ba màu", "nhiet_do_mau": "3500K/6500K", "kich_thuoc": "ø148x37mm", "lo_khoet": "ø110mm", "chip_led": "OSRAM", "hieu_suat_quang": "110-120 Lm/w", "chi_so_hoan_mau": "CRI≥85", "dien_ap": "85-265V", "thuong_hieu": "TLC LIGHTING", "tuoi_tho": "40.000h", "bao_hanh": "24 tháng", "dien_ap_ac": "85-265V", "do_hoan_mau": "&gt;90Ra", "che_do_anh_sang": "Chống chói", "duong_kinh_lo_khoet": "D110mm", "duong_kinh_mat": "D148mm", "chieu_day": "37mm", "chat_lieu": "Hợp kim nhôm sơn tĩnh điện", "chip_led_2": "Chip Osram – CHLB Đức", "tuoi_tho_2": "40.000 giờ"}</t>
         </is>
       </c>
       <c r="J2" t="n">
@@ -13744,7 +14380,7 @@
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>{"cong_suat": "12W", "anh_sang": "trắng/vàng/trung tính, Trắng, Vàng, trung tính", "nhiet_do_mau": "3500K/6500K", "kich_thuoc": "ø148x37mm", "lo_khoet": "ø110mm", "chip_led": "OSRAM, Chip Osram – CHLB Đức", "hieu_suat_quang": "110-120 Lm/w, ~110Lm/w, 157 – 185 Lm/W", "chi_so_hoan_mau": "CRI≥85", "dien_ap": "85-265V", "thuong_hieu": "TLC LIGHTING", "tuoi_tho": "40.000h, 40.000 giờ", "bao_hanh": "24 tháng, 2 năm", "dien_ap_ac": "85-265V", "do_hoan_mau": "&gt;90Ra", "che_do_anh_sang": "Chống chói", "duong_kinh_lo_khoet": "D110mm", "duong_kinh_mat": "D148mm", "chieu_day": "37mm", "chat_lieu": "Hợp kim nhôm sơn tĩnh điện"}</t>
+          <t>{"cong_suat": "12W", "anh_sang": "trắng/vàng/trung tính", "nhiet_do_mau": "3500K/6500K", "kich_thuoc": "ø148x37mm", "lo_khoet": "ø110mm", "chip_led": "OSRAM", "hieu_suat_quang": "110-120 Lm/w", "chi_so_hoan_mau": "CRI≥85", "dien_ap": "85-265V", "thuong_hieu": "TLC LIGHTING", "tuoi_tho": "40.000h", "bao_hanh": "24 tháng", "dien_ap_ac": "85-265V", "do_hoan_mau": "&gt;90Ra", "che_do_anh_sang": "Chống chói", "duong_kinh_lo_khoet": "D110mm", "duong_kinh_mat": "D148mm", "chieu_day": "37mm", "chat_lieu": "Hợp kim nhôm sơn tĩnh điện"}</t>
         </is>
       </c>
       <c r="J3" t="n">
@@ -13853,7 +14489,7 @@
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>{"cong_suat": "12W", "anh_sang": "ba màu", "nhiet_do_mau": "3500K/6500K", "kich_thuoc": "ø148x37mm", "lo_khoet": "ø110mm", "chip_led": "OSRAM", "hieu_suat_quang": "110-120 Lm/w", "chi_so_hoan_mau": "CRI≥85", "dien_ap": "85-265V", "thuong_hieu": "TLC LIGHTING", "tuoi_tho": "40.000h", "bao_hanh": "24 tháng", "dien_ap_ac": "85-265V", "do_hoan_mau": "&gt;85Ra", "che_do_anh_sang": "Chống chói", "duong_kinh_lo_khoet": "D110mm", "duong_kinh_mat": "D148mm", "chieu_day": "37mm", "chat_lieu": "Hợp kim nhôm sơn tĩnh điện"}</t>
+          <t>{"cong_suat": "12W", "anh_sang": "ba màu", "nhiet_do_mau": "3500K/6500K", "kich_thuoc": "ø148x37mm", "lo_khoet": "ø110mm", "chip_led": "OSRAM", "hieu_suat_quang": "110-120 Lm/w", "chi_so_hoan_mau": "CRI≥85", "dien_ap": "85-265V", "thuong_hieu": "TLC LIGHTING", "tuoi_tho": "40.000h", "bao_hanh": "24 tháng", "dien_ap_ac": "85-265V", "hieu_suat_quang_2": "~110Lm/w", "do_hoan_mau": "&gt;85Ra", "che_do_anh_sang": "Chống chói", "duong_kinh_lo_khoet": "D110mm", "duong_kinh_mat": "D148mm", "chieu_day": "37mm", "chat_lieu": "Hợp kim nhôm sơn tĩnh điện", "chip_led_2": "Chip Osram – CHLB Đức", "tuoi_tho_2": "40.000 giờ"}</t>
         </is>
       </c>
       <c r="J4" t="n">
@@ -13961,7 +14597,7 @@
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>{"cong_suat": "12W", "anh_sang": "trắng/vàng/trung tính", "nhiet_do_mau": "3500K/6500K", "kich_thuoc": "ø148x37mm", "lo_khoet": "ø110mm", "chip_led": "OSRAM", "hieu_suat_quang": "110-120 Lm/w", "chi_so_hoan_mau": "CRI≥85", "dien_ap": "85-265V", "thuong_hieu": "TLC LIGHTING", "tuoi_tho": "40.000h", "bao_hanh": "24 tháng", "dien_ap_ac": "85-265V", "do_hoan_mau": "&gt;90Ra", "che_do_anh_sang": "Chống chói", "duong_kinh_lo_khoet": "D110mm", "duong_kinh_mat": "D148mm", "chieu_day": "37mm", "chat_lieu": "Hợp kim nhôm sơn tĩnh điện", "chip_led_chlb_duc": "Chip Osram – CHLB Đức", "tuoi_tho_gio": "40.000 giờ"}</t>
+          <t>{"cong_suat": "12W", "anh_sang": "trắng/vàng/trung tính", "nhiet_do_mau": "3500K/6500K", "kich_thuoc": "ø148x37mm", "lo_khoet": "ø110mm", "chip_led": "OSRAM", "hieu_suat_quang": "110-120 Lm/w", "chi_so_hoan_mau": "CRI≥85", "dien_ap": "85-265V", "thuong_hieu": "TLC LIGHTING", "tuoi_tho": "40.000h", "bao_hanh": "24 tháng", "dien_ap_ac": "85-265V", "hieu_suat_quang_2": "~110Lm/w", "do_hoan_mau": "&gt;90Ra", "che_do_anh_sang": "Chống chói", "duong_kinh_lo_khoet": "D110mm", "duong_kinh_mat": "D148mm", "chieu_day": "37mm", "chat_lieu": "Hợp kim nhôm sơn tĩnh điện", "chip_led_2": "Chip Osram – CHLB Đức", "tuoi_tho_2": "40.000 giờ"}</t>
         </is>
       </c>
       <c r="J5" t="n">
@@ -14184,7 +14820,7 @@
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>{"cong_suat": "7W", "anh_sang": "Trắng/vàng/trung tính, Trắng, Vàng, trung tính", "nhiet_do_mau": "3500K/6500K", "kich_thuoc": "ø120x37mm", "lo_khoet": "ø90mm", "chip_led": "OSRAM, Chip Osram – CHLB Đức, chip LED Osram", "hieu_suat_quang": "110-120 Lm/w, ~110Lm/w", "chi_so_hoan_mau": "CRI≥85, &gt;90Ra, Ra&gt;85", "dien_ap": "85-265V", "thuong_hieu": "TLC LIGHTING", "tuoi_tho": "40.000h, 40.000 giờ", "bao_hanh": "24 tháng", "dien_ap_ac": "85-265V", "che_do_anh_sang": "Chống chói", "duong_kinh_lo_khoet": "D90mm", "duong_kinh_mat": "D120mm", "chieu_day": "37mm", "chat_lieu": "Hợp kim nhôm sơn tĩnh điện"}</t>
+          <t>{"cong_suat": "7W", "anh_sang": "Trắng/vàng/trung tính, Trắng, Vàng, trung tính", "nhiet_do_mau": "3500K/6500K", "kich_thuoc": "ø120x37mm", "lo_khoet": "ø90mm", "chip_led": "OSRAM, Chip Osram – CHLB Đức", "hieu_suat_quang": "110-120 Lm/w, ~110Lm/w", "chi_so_hoan_mau": "CRI≥85", "dien_ap": "85-265V", "thuong_hieu": "TLC LIGHTING", "tuoi_tho": "40.000h, 40.000 giờ", "bao_hanh": "24 tháng", "dien_ap_ac": "85-265V", "do_hoan_mau": "&gt;90Ra", "che_do_anh_sang": "Chống chói", "duong_kinh_lo_khoet": "D90mm", "duong_kinh_mat": "D120mm", "chieu_day": "37mm", "chat_lieu": "Hợp kim nhôm sơn tĩnh điện"}</t>
         </is>
       </c>
       <c r="J7" t="n">
@@ -14299,7 +14935,7 @@
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>{"cong_suat": "7W", "anh_sang": "Ba màu", "nhiet_do_mau": "3500K/6500K", "kich_thuoc": "ø120x37mm", "lo_khoet": "ø90mm", "chip_led": "OSRAM", "hieu_suat_quang": "110-120 Lm/w", "chi_so_hoan_mau": "CRI≥85", "dien_ap": "85-265V", "thuong_hieu": "TLC LIGHTING", "tuoi_tho": "40.000h", "bao_hanh": "24 tháng", "dien_ap_ac": "85-265V", "do_hoan_mau": "&gt;90Ra", "che_do_anh_sang": "Chống chói", "duong_kinh_lo_khoet": "D90mm", "duong_kinh_mat": "D120mm", "chieu_day": "37mm", "chat_lieu": "Hợp kim nhôm sơn tĩnh điện", "tuoi_tho_gio": "40.000 giờ"}</t>
+          <t>{"cong_suat": "7W", "anh_sang": "Ba màu", "nhiet_do_mau": "3500K/6500K", "kich_thuoc": "ø120x37mm", "lo_khoet": "ø90mm", "chip_led": "OSRAM, Chip Osram – CHLB Đức", "hieu_suat_quang": "110-120 Lm/w, ~110Lm/w", "chi_so_hoan_mau": "CRI≥85", "dien_ap": "85-265V", "thuong_hieu": "TLC LIGHTING", "tuoi_tho": "40.000h, 40.000 giờ", "bao_hanh": "24 tháng", "dien_ap_ac": "85-265V", "do_hoan_mau": "&gt;90Ra", "che_do_anh_sang": "Chống chói", "duong_kinh_lo_khoet": "D90mm", "duong_kinh_mat": "D120mm", "chieu_day": "37mm", "chat_lieu": "Hợp kim nhôm sơn tĩnh điện"}</t>
         </is>
       </c>
       <c r="J8" t="n">
@@ -14414,7 +15050,7 @@
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>{"cong_suat": "7W", "anh_sang": "Trắng/vàng/trung tính", "nhiet_do_mau": "3500K/6500K", "kich_thuoc": "ø120x37mm", "lo_khoet": "ø90mm", "chip_led": "OSRAM", "hieu_suat_quang": "110-120 Lm/w", "chi_so_hoan_mau": "CRI≥85", "dien_ap": "85-265V", "thuong_hieu": "TLC LIGHTING", "tuoi_tho": "40.000h", "bao_hanh": "24 tháng", "dien_ap_AC": "85-265V", "do_hoan_mau": "&gt;90Ra", "che_do_anh_sang": "Chống chói", "duong_kinh_lo_khoet": "D90mm", "duong_kinh_mat": "D120mm", "chieu_day": "37mm", "chat_lieu": "Hợp kim nhôm sơn tĩnh điện"}</t>
+          <t>{"cong_suat": "7W", "anh_sang": "Trắng/vàng/trung tính", "nhiet_do_mau": "3500K/6500K", "kich_thuoc": "ø120x37mm", "lo_khoet": "ø90mm", "chip_led": "OSRAM", "hieu_suat_quang": "110-120 Lm/w,~110Lm/w", "chi_so_hoan_mau": "CRI≥85", "dien_ap": "85-265V", "thuong_hieu": "TLC LIGHTING", "tuoi_tho": "40.000h,40.000 giờ", "bao_hanh": "24 tháng", "dien_ap_ac": "85-265V", "do_hoan_mau": "&gt;90Ra", "che_do_anh_sang": "Chống chói", "duong_kinh_lo_khoet": "D90mm", "duong_kinh_mat": "D120mm", "chieu_day": "37mm", "chat_lieu": "Hợp kim nhôm sơn tĩnh điện"}</t>
         </is>
       </c>
       <c r="J9" t="n">
@@ -14428,6 +15064,13 @@
       <c r="M9" t="inlineStr">
         <is>
           <t>https://tlclighting.com.vn/wp-content/uploads/2020/09/IMG_2635.jpg</t>
+        </is>
+      </c>
+      <c r="P9" t="inlineStr">
+        <is>
+          <t>Ánh sáng vàng: Thích hợp với không gian về đêm để nghỉ ngơi, thư giãn tạo cho người dùng cảm giác thư thái, thoải mái.
+Ánh sáng trắng:Thích hợp với không gian làm việc tạo cho bạn một nguồn sáng rõ ràng, chất lượng để làm việc được một cách hiệu quả nhất.
+Ánh sáng trung tính: Nó có khả năng phát ra ánh sáng trắng bắt chước ánh sáng trung tính tự nhiên và có thể được sử dụng thoải mái bất cứ nơi nào trong nhà của bạn.</t>
         </is>
       </c>
       <c r="Q9" t="inlineStr">
@@ -14471,6 +15114,31 @@
 3 màu: Tham khảo tại đây</t>
         </is>
       </c>
+      <c r="T9" t="inlineStr">
+        <is>
+          <t>Ưu điểm đèn LED âm trần khối đúc
+Ánh sáng vượt trội
+Đèn LED
+âm trần khối đúc TOS 7W viền bạc đơn sắc
+sử dụng chip Led Osram với công nghệ màu sắc độc quyền “độc quyền”
+Brilliant Mix, có
+chỉ số hoàn màu
+Ra &gt;85 cho ánh sáng đồng đều, không nhấp nháy giúp bảo vệ mắt.
+Màu ánh sáng chân thực và tự nhiên theo tiêu chuẩn châu Âu giúp chống cận thị và an toàn cho mắt khi sử dụng.
+Tuổi thọ cao
+Chip LED được xem là thành phần chính giúp phát sáng và liên quan trực tiếp đến tuổi thọ sử dụng đèn.
+Đèn có tuổi thọ cao lên đến 40.000h nhờ sử dụng Chip LED Osram – có tuổi thọ cao, và đế đúc nhôm nguyên khối giúp đèn tản nhiệt tốt hơn trong quá trình sử dụng, từ đó bảo vệ được tuổi thọ của đèn.
+Ánh sáng đa dạng
+Với đa dạng màu ánh sáng, quý khách có thể lựa chọn theo nhu cầu sử dụng cho gia đình mình: ánh sáng trắng, ánh sáng vàng, ánh sáng trung tính
+Ánh sáng vàng: Thích hợp với không gian về đêm để nghỉ ngơi, thư giãn tạo cho người dùng cảm giác thư thái, thoải mái.
+Ánh sáng trắng:Thích hợp với không gian làm việc tạo cho bạn một nguồn sáng rõ ràng, chất lượng để làm việc được một cách hiệu quả nhất.
+Ánh sáng trung tính: Nó có khả năng phát ra ánh sáng trắng bắt chước ánh sáng trung tính tự nhiên và có thể được sử dụng thoải mái bất cứ nơi nào trong nhà của bạn.
+Sử dụng thông dụng
+Đèn LED âm trần khối đúc 7W viền bạc – TLC LIGHTING được cải tiến hoàn toàn mới có thiết kế đế đèn phi 90 phục vụ tối đa nhu cầu sử dụng của khách hàng. Đáp ứng được nhu cầu sử dụng ống nhựa PVC cho trần bê tông lại 1 số công trình.
+Tính thẩm mĩ cao
+Mặt đèn được thiết kế tỉ mỉ, tinh xảo với đường viền bạc ấn tượng, ánh kim toả sáng tạo sự hài hòa cho bộ đèn và cho cả vị trí của đèn cho nhiều không gian khác nhau.</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -14498,7 +15166,7 @@
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>{"cong_suat": "7W", "anh_sang": "Ba màu", "nhiet_do_mau": "3500K/6500K", "kich_thuoc": "ø120x37mm", "lo_khoet": "ø90mm", "chip_led": "OSRAM", "hieu_suat_quang": "110-120 Lm/w", "chi_so_hoan_mau": "CRI≥85", "dien_ap": "85-265V", "thuong_hieu": "TLC LIGHTING", "tuoi_tho": "40.000h", "bao_hanh": "24 tháng", "dien_ap_ac": "85-265V", "do_hoan_mau": "&gt;90Ra", "che_do_anh_sang": "Chống chói", "duong_kinh_lo_khoet": "D90mm", "duong_kinh_mat": "D120mm", "chieu_day": "37mm", "chat_lieu": "Hợp kim nhôm sơn tĩnh điện", "chip_led_chi_do_duc": "Chip Osram – CHLB Đức"}</t>
+          <t>{"cong_suat": "7W", "anh_sang": "Ba màu", "nhiet_do_mau": "3500K/6500K", "kich_thuoc": "ø120x37mm", "lo_khoet": "ø90mm", "chip_led": "OSRAM", "hieu_suat_quang": "110-120 Lm/w", "chi_so_hoan_mau": "CRI≥85", "dien_ap": "85-265V", "thuong_hieu": "TLC LIGHTING", "tuoi_tho": "40.000h", "bao_hanh": "24 tháng", "dien_ap_ac": "85-265V", "do_hoan_mau": "&gt;90Ra", "che_do_anh_sang": "Chống chói", "duong_kinh_lo_khoet": "D90mm", "duong_kinh_mat": "D120mm", "chieu_day": "37mm", "chat_lieu": "Hợp kim nhôm sơn tĩnh điện", "chip_led_tuy_chon": "Chip Osram – CHLB Đức", "tuoi_tho_don_vi_gio": "40.000 giờ"}</t>
         </is>
       </c>
       <c r="J10" t="n">
@@ -14612,7 +15280,7 @@
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>{"cong_suat": "7W", "anh_sang": "Trắng/vàng/trung tính", "nhiet_do_mau": "3500K/6500K", "kich_thuoc": "ø120x37mm", "lo_khoet": "ø90mm", "chip_led": "OSRAM", "hieu_suat_quang": "110-120 Lm/w", "chi_so_hoan_mau": "CRI≥85", "dien_ap": "85-265V", "thuong_hieu": "TLC LIGHTING", "tuoi_tho": "40.000h", "bao_hanh": "24 tháng", "dien_ap_ac": "85-265V", "do_hoan_mau": "&gt;90Ra", "che_do_anh_sang": "Chống chói", "duong_kinh_lo_khoet": "D90mm", "duong_kinh_mat": "D120mm", "chieu_day": "37mm", "chat_lieu": "Hợp kim nhôm sơn tĩnh điện", "tuoi_tho_gio": "40.000 giờ"}</t>
+          <t>{"cong_suat": "7W", "anh_sang": "Trắng/vàng/trung tính", "nhiet_do_mau": "3500K/6500K", "kich_thuoc": "ø120x37mm", "lo_khoet": "ø90mm", "chip_led": "OSRAM", "hieu_suat_quang": "110-120 Lm/w", "chi_so_hoan_mau": "CRI≥85", "dien_ap": "85-265V", "thuong_hieu": "TLC LIGHTING", "tuoi_tho": "40.000h", "bao_hanh": "24 tháng", "dien_ap_ac": "85-265V", "hieu_suat_quang_2": "~110Lm/w", "do_hoan_mau": "&gt;90Ra", "che_do_anh_sang": "Chống chói", "duong_kinh_lo_khoet": "D90mm", "duong_kinh_mat": "D120mm", "chieu_day": "37mm", "chat_lieu": "Hợp kim nhôm sơn tĩnh điện", "chip_led_2": "Chip Osram – CHLB Đức", "tuoi_tho_2": "40.000 giờ"}</t>
         </is>
       </c>
       <c r="J11" t="n">
@@ -14726,7 +15394,7 @@
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>{"cong_suat": "9W", "anh_sang": "ba màu", "nhiet_do_mau": "3500K/6500K", "kich_thuoc": "ø120x37mm", "lo_khoet": "ø90mm", "chip_led": "OSRAM", "hieu_suat_quang": "110-120 Lm/w", "chi_so_hoan_mau": "CRI≥85", "dien_ap": "85-265V", "thuong_hieu": "TLC LIGHTING", "tuoi_tho": "40.000h", "bao_hanh": "24 tháng", "dien_ap_AC": "85-265V", "do_hoan_mau": "&gt;90Ra", "che_do_anh_sang": "Chống chói", "duong_kinh_lo_khoet": "D90mm", "duong_kinh_mat": "D120mm", "chieu_day": "37mm", "chat_lieu": "Hợp kim nhôm sơn tĩnh điện", "chip_led_chi_p_osram": "CHLB Đức", "tuoi_tho_gio": "40.000 giờ"}</t>
+          <t>{"cong_suat": "9W", "anh_sang": "ba màu", "nhiet_do_mau": "3500K/6500K", "kich_thuoc": "ø120x37mm", "lo_khoet": "ø90mm", "chip_led": "OSRAM", "hieu_suat_quang": "110-120 Lm/w", "chi_so_hoan_mau": "CRI≥85", "dien_ap": "85-265V", "thuong_hieu": "TLC LIGHTING", "tuoi_tho": "40.000h", "bao_hanh": "24 tháng", "dien_ap_ac": "85-265V", "do_hoan_mau": "&gt;90Ra", "che_do_anh_sang": "Chống chói", "duong_kinh_lo_khoet": "D90mm", "duong_kinh_mat": "D120mm", "chieu_day": "37mm", "chat_lieu": "Hợp kim nhôm sơn tĩnh điện", "chip_led_chi_lb_duc": "Chip Osram – CHLB Đức", "tuoi_tho_gio": "40.000 giờ", "bao_hanh_nam": "2 năm"}</t>
         </is>
       </c>
       <c r="J12" t="n">
@@ -14740,6 +15408,15 @@
       <c r="M12" t="inlineStr">
         <is>
           <t>https://tlclighting.com.vn/wp-content/uploads/2020/08/IMG_2444.jpg</t>
+        </is>
+      </c>
+      <c r="P12" t="inlineStr">
+        <is>
+          <t>Tuổi thọ cao
+Bảo vệ mắt
+Ánh sáng đa dạng
+Dễ lắp đặt, thông dụng
+Thẩm mĩ cao</t>
         </is>
       </c>
       <c r="Q12" t="inlineStr">
@@ -14783,6 +15460,30 @@
 3 màu: Tham khảo tại đây</t>
         </is>
       </c>
+      <c r="T12" t="inlineStr">
+        <is>
+          <t>4.Tại sao nên lựa chọn đèn LED âm trần khối đúc TOS 9W mặt trắng ba màu?
+Hiện nay, đèn LED
+âm trần khối đúc TOS mặt trắng 3 màu
+là sự lựa chọn hoàn hảo được khá nhiều các gia đình quan tâm vì những
+ƯU ĐIỂM VƯỢT TRỘI
+mà sản phẩm đen lại:
+Tuổi thọ cao
+Đèn được sử dụng
+chip LED OSRAM
+đến từ hang chip nổi  tiếng OSRAM- Đức một trong những đơn vị uy tín hàng đầu thế giới trong lĩnh vực chip LED, đem tới hiệu suất hoạt động cao, có thể hoạt động liên tục giúp đèn chiếu sáng liên tục trong khoảng thời gian dài.
+Thân đèn cấu tạo từ vỏ hợp kim nhôm nguyên khối với độ bền cao giúp khả năng tản nhiệt hiệu quả trong bảo vệ bộ phận bên trong đèn hay chip LED trong quá trình hoạt động duy trì hiệu quả tăng tuổi thọ cao.
+Bảo vệ mắt
+Đèn LED âm trần TOS với kiểu dáng mỏng, nhẹ nhưng có chỉ số hoàn màu Ra &gt;85 giúp mắt của bạn cũng như người thân cảm thấy thoải mái vì mọi vật xung quanh sẽ hiện lên một cách sắc nét và chân thực.
+Chip LED có hiệu suất chiếu sáng từ  157 – 185 Lm/W giúp đèn có khả năng chiếu sáng tốt trong thời gian dài và đem lại ánh sáng hài hòa tự nhiên.
+Ánh sáng đa dạng
+Đèn chế độ 3 màu cơ bản: Vàng – trung tính – trắng, chuyển màu chỉ bằng 1 thao tác bật/tắt đèn đơn giản.
+Dễ lắp đặt, thông dụng
+Đèn LED âm trần khối đúc TOS 9W mặt trắng có thiết kế lỗ khoét tiêu chuẩn phi 90 phù hợp với nhiều công trình thiết kế nên được rất nhiều người tiêu dùng ưu ái lựa chọn.
+Thẩm mĩ cao
+Thiết kế đơn giản ôm sát trần. Đèn có dạng hình tròn, màu trắng tinh tế sang trọng  đẹp mắt, dễ tạo thiện cảm cho người dùng. Với thiết kế đèn âm trần, đèn sẽ không làm bạn phải thất vọng để tô điểm cho không gian hiện đại hiện đại của mọi công trình.</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
@@ -14810,7 +15511,7 @@
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>{"cong_suat": "9W", "anh_sang": "Trắng/vàng/trung tính", "nhiet_do_mau": "3500K/6500K", "kich_thuoc": "ø120x37mm", "lo_khoet": "ø90mm", "chip_led": "OSRAM", "hieu_suat_quang": "110-120 Lm/w", "chi_so_hoan_mau": "CRI≥85", "dien_ap": "85-265V", "thuong_hieu": "TLC LIGHTING", "tuoi_tho": "40.000h", "bao_hanh": "24 tháng", "dien_ap_ac": "85-265V", "do_hoan_mau": "&gt;90Ra", "che_do_anh_sang": "Chống chói", "duong_kinh_lo_khoet": "D90mm", "duong_kinh_mat": "D120mm", "chieu_day": "37mm", "chat_lieu": "Hợp kim nhôm sơn tĩnh điện", "tuoi_tho_gio": "40.000 giờ"}</t>
+          <t>{"cong_suat": "9W", "anh_sang": "Trắng/vàng/trung tính", "nhiet_do_mau": "3500K/6500K", "kich_thuoc": "ø120x37mm", "lo_khoet": "ø90mm", "chip_led": "OSRAM", "hieu_suat_quang": "110-120 Lm/w", "chi_so_hoan_mau": "CRI≥85", "dien_ap": "85-265V", "thuong_hieu": "TLC LIGHTING", "tuoi_tho": "40.000h", "bao_hanh": "24 tháng"}</t>
         </is>
       </c>
       <c r="J13" t="n">
@@ -14824,6 +15525,15 @@
       <c r="M13" t="inlineStr">
         <is>
           <t>https://tlclighting.com.vn/wp-content/uploads/2020/08/IMG_2444.jpg</t>
+        </is>
+      </c>
+      <c r="P13" t="inlineStr">
+        <is>
+          <t>Tuổi thọ cao
+Bảo vệ mắt
+Ánh sáng đa dạng
+Dễ lắp đặt, thông dụng
+Thẩm mĩ cao</t>
         </is>
       </c>
       <c r="Q13" t="inlineStr">
@@ -14867,6 +15577,36 @@
 3 màu: Tham khảo tại đây</t>
         </is>
       </c>
+      <c r="T13" t="inlineStr">
+        <is>
+          <t>Tại sao nên lựa chọn đèn LED âm trần khối đúc TOS 9W mặt trắng đơn sắc?
+Hiện nay, đèn LED
+âm trần 9W TOS mặt trắng
+là sự lựa chọn hoàn hảo được khá nhiều các gia đình quan tâm vì những
+ƯU ĐIỂM VƯỢT TRỘI
+mà sản phẩm đem lại:
+Tuổi thọ cao
+Đèn được sử dụng
+chip LED OSRAM
+đến từ hang chip nổi  tiếng OSRAM- Đức một trong những đơn vị uy tín hàng đầu thế giới trong lĩnh vực chip LED, đem tới hiệu suất hoạt động cao, có thể hoạt động liên tục giúp đèn chiếu sáng liên tục trong khoảng thời gian dài.
+Thân đèn cấu tạo từ vỏ hợp kim nhôm nguyên khối với độ bền cao giúp khả năng tản nhiệt hiệu quả trong bảo vệ bộ phận bên trong đèn hay chip LED trong quá trình hoạt động duy trì hiệu quả tăng tuổi thọ cao.
+Bảo vệ mắt
+Đèn LED âm trần 9W TOS với kiểu dáng mỏng, nhẹ nhưng có chỉ số hoàn màu Ra &gt;85 giúp mắt của bạn cũng như người thân cảm thấy thoải mái vì mọi vật xung quanh sẽ hiện lên một cách sắc nét và chân thực.
+Chip LED có hiệu suất chiếu sáng từ  157 – 185 Lm/W giúp đèn có khả năng chiếu sáng tốt trong thời gian dài và đem lại ánh sáng hài hòa tự nhiên.
+Đèn LED âm trần khối đúc TOS của TLC LIGHTING.
+Ánh sáng đa dạng
+Đèn có ánh sáng trắng
+,
+ánh sáng vàng, ánh sáng trung tính và chế độ 3 màu cơ bản: Vàng – trung tính – trắng, chuyển màu chỉ bằng 1 thao tác bật/tắt đèn đơn giản.
+Dễ lắp đặt, thông dụng
+Đèn LED âm trần khối đúc TOS 9W mặt trắng có thiết kế lỗ khoét tiêu chuẩn phi 90 phù hợp với nhiều công trình thiết kế nên được rất nhiều người tiêu dùng ưu ái lựa chọn.
+Thẩm mĩ cao
+Thiết kế đơn giản ôm sát trần. Đèn có dạng hình tròn, màu trắng tinh tế sang trọng  đẹp mắt, dễ tạo thiện cảm cho người dùng. Với thiết kế đèn âm trần, đèn sẽ không làm bạn phải thất vọng để tô điểm cho không gian hiện đại hiện đại của mọi công trình.
+Bộ sưu tập
+đèn LED âm trần 3 màu
+được ưa chuộng nhất</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
@@ -14894,7 +15634,7 @@
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>{"cong_suat": "9W", "anh_sang": "Ba màu", "nhiet_do_mau": "3500K/6500K", "kich_thuoc": "ø120x37mm", "lo_khoet": "ø90mm", "chip_led": "OSRAM", "hieu_suat_quang": "110-120 Lm/w", "chi_so_hoan_mau": "CRI≥85", "dien_ap": "85-265V", "thuong_hieu": "TLC LIGHTING", "tuoi_tho": "40.000h", "bao_hanh": "24 tháng", "dien_ap_ac": "85-265V", "hieu_suat_quang_2": "~110Lm/w", "do_hoan_mau": "&gt;90Ra", "che_do_anh_sang": "Chống chói", "duong_kinh_lo_khoet": "D90mm", "duong_kinh_mat": "D120mm", "chieu_day": "37mm", "chat_lieu": "Hợp kim nhôm sơn tĩnh điện", "chip_led_2": "Chip Osram – CHLB Đức", "tuoi_tho_2": "40.000 giờ"}</t>
+          <t>{"cong_suat": "9W", "anh_sang": "Ba màu", "nhiet_do_mau": "3500K/6500K", "kich_thuoc": "ø120x37mm", "lo_khoet": "ø90mm", "chip_led": "OSRAM, Chip Osram – CHLB Đức", "hieu_suat_quang": "110-120 Lm/w, ~110Lm/w", "chi_so_hoan_mau": "CRI≥85", "dien_ap": "85-265V", "thuong_hieu": "TLC LIGHTING", "tuoi_tho": "40.000h, 40.000 giờ", "bao_hanh": "24 tháng", "dien_ap_ac": "85-265V", "do_hoan_mau": "&gt;90Ra", "che_do_anh_sang": "Chống chói", "duong_kinh_lo_khoet": "D90mm", "duong_kinh_mat": "D120mm", "chieu_day": "37mm", "chat_lieu": "Hợp kim nhôm sơn tĩnh điện"}</t>
         </is>
       </c>
       <c r="J14" t="n">
@@ -15004,7 +15744,7 @@
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>{"cong_suat": "9W", "anh_sang": "trắngs/vàng/trung tính", "nhiet_do_mau": "3500K/6500K", "kich_thuoc": "ø120x37mm", "lo_khoet": "ø90mm", "chip_led": "OSRAM", "hieu_suat_quang": "110-120 Lm/w", "chi_so_hoan_mau": "CRI≥85", "dien_ap": "85-265V", "thuong_hieu": "TLC LIGHTING", "tuoi_tho": "40.000h", "bao_hanh": "24 tháng", "dien_ap_ac": "85-265V", "do_hoan_mau": "&gt;90Ra", "che_do_anh_sang": "Chống chói", "duong_kinh_lo_khoet": "D90mm", "duong_kinh_mat": "D120mm", "chieu_day": "37mm", "chat_lieu": "Hợp kim nhôm sơn tĩnh điện", "chip_led_tld": "Chip Osram – CHLB Đức"}</t>
+          <t>{"cong_suat": "9W", "anh_sang": "trắngs/vàng/trung tính, Trắng/vàng/trung tính", "nhiet_do_mau": "3500K/6500K", "kich_thuoc": "ø120x37mm", "lo_khoet": "ø90mm", "chip_led": "OSRAM, Chip Osram – CHLB Đức", "hieu_suat_quang": "110-120 Lm/w, ~110Lm/w", "chi_so_hoan_mau": "CRI≥85", "dien_ap": "85-265V", "thuong_hieu": "TLC LIGHTING", "tuoi_tho": "40.000h, 40.000 giờ", "bao_hanh": "24 tháng, 2 năm", "dien_ap_ac": "85-265V", "do_hoan_mau": "&gt;90Ra", "che_do_anh_sang": "Chống chói", "duong_kinh_lo_khoet": "D90mm", "duong_kinh_mat": "D120mm", "chieu_day": "37mm", "chat_lieu": "Hợp kim nhôm sơn tĩnh điện"}</t>
         </is>
       </c>
       <c r="J15" t="n">
@@ -15115,7 +15855,7 @@
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>{"cong_suat": "12W", "anh_sang": "Trắng/vàng/trung tính", "nhiet_do_mau": "3500K/6500K", "kich_thuoc": "ø148x37mm", "lo_khoet": "ø110mm", "chip_led": "OSRAM", "hieu_suat_quang": "110-120 Lm/w", "chi_so_hoan_mau": "CRI≥85", "dien_ap": "85-265V", "thuong_hieu": "TLC LIGHTING", "tuoi_tho": "40.000h", "bao_hanh": "24 tháng", "dien_ap_ac": "85-265V", "do_hoan_mau": "&gt;90Ra", "che_do_anh_sang": "Chống chói", "duong_kinh_lo_khoet": "D110mm", "duong_kinh_mat": "D148mm", "chieu_day": "37mm", "chat_lieu": "Hợp kim nhôm sơn tĩnh điện"}</t>
+          <t>{"cong_suat": "12W", "anh_sang": "Trắng/vàng/trung tính", "nhiet_do_mau": "3500K/6500K", "kich_thuoc": "ø148x37mm", "lo_khoet": "ø110mm", "chip_led": "OSRAM", "hieu_suat_quang": "110-120 Lm/w", "chi_so_hoan_mau": "CRI≥85", "dien_ap": "85-265V", "thuong_hieu": "TLC LIGHTING", "tuoi_tho": "40.000h", "bao_hanh": "24 tháng", "dien_ap_ac": "85-265V", "do_hoan_mau": "&gt;90Ra", "che_do_anh_sang": "Chống chói", "duong_kinh_lo_khoet": "D110mm", "duong_kinh_mat": "D148mm", "chieu_day": "37mm", "chat_lieu": "Hợp kim nhôm sơn tĩnh điện", "tuoi_tho_don_vi": "40.000 giờ"}</t>
         </is>
       </c>
       <c r="J16" t="n">
@@ -15227,7 +15967,7 @@
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>{"cong_suat": "5W", "anh_sang": "Ba màu", "nhiet_do_mau": "3500K/6500K", "kich_thuoc": "ø110x40mm, 110x40mm", "hieu_suat_quang": "110-120 Lm/w, 110~120Lm/w", "chi_so_hoan_mau": "CRI≥85", "dien_ap": "85-265V", "thuong_hieu": "TLC LIGHTING", "tuoi_tho": "40.000h", "bao_hanh": "24 tháng", "quang_thong": "450Lm", "do_hoan_mau": "&gt;85", "dien_ap_ac": "85-265V", "lo_khoet": "76", "chip_led": "Chip OSRAM", "tuoi_tho_chip_led": "40.000 giờ"}</t>
+          <t>{"cong_suat": "5W", "anh_sang": "Ba màu", "nhiet_do_mau": "3500K/6500K", "kich_thuoc": "ø110x40mm, 110x40mm", "hieu_suat_quang": "110-120 Lm/w, 110~120Lm/w", "chi_so_hoan_mau": "CRI≥85", "dien_ap": "85-265V", "thuong_hieu": "TLC LIGHTING", "tuoi_tho": "40.000h", "bao_hanh": "24 tháng", "lo_khoet": "ø76mm, 76", "quang_thong": "450Lm", "do_hoan_mau": "&gt;85", "chip_led": "Chip OSRAM", "tuoi_tho_chip_led": "40.000 giờ", "do_day": "4cm"}</t>
         </is>
       </c>
       <c r="J17" t="n">
@@ -15241,6 +15981,17 @@
       <c r="M17" t="inlineStr">
         <is>
           <t>https://tlclighting.com.vn/wp-content/uploads/2019/10/IMG_2627-min.jpg</t>
+        </is>
+      </c>
+      <c r="P17" t="inlineStr">
+        <is>
+          <t>âm trần khối đúc 5W ba màu
+Đèn được phủ sơn tĩnh điện dày, đảm bảo không ố vàng hay bong tróc theo thời gian.
+Đèn với thiết kế tản nhiệt nhôm đa chiều, đúc rãnh dày với đế tản nhiệt đúc từ nhôm nguyên khối, tăng khả năng tản nhiệt gấp 5 lần so với các sản phẩm âm trần hiện nay trên thị trường.
+Độ dày đèn chỉ 4 cm, phù hợp với mọi thiết kế trần, ứng dụng đa dạng trong các công trình cao cấp hiện nay.
+Đèn led âm trần khối đúc được thiết kế với ánh sáng 3 màu phù hợp với nhu cầu đa dạng của người dùng.
+Ngoài tác dụng chiếu sáng đèn được ứng dụng trang trí và thiết kế ánh sáng là chủ yếu, tiết kiệm 50% điện năng so với đèn huỳnh quang, 90% so với đèn sợi đốt trên thị trường.
+Sản phẩm được TLC Lighting bảo hành đổi mới trong 24 tháng trên toàn quốc.</t>
         </is>
       </c>
       <c r="Q17" t="inlineStr">
@@ -15258,6 +16009,22 @@
 Chip LED: Chip OSRAM
 Tuổi thọ chip LED: 40.000 giờ
 Bảo hành: 24 tháng</t>
+        </is>
+      </c>
+      <c r="T17" t="inlineStr">
+        <is>
+          <t>4. Ưu điểm đèn LED âm trần khối đúc 5W
+Đèn Led
+âm trần khối đúc 5W ba màu
+được sản xuất bởi hãng đèn LED TLC LIGHTING, một trong những đơn vị đi đầu trong việc cũng cấp thiết bị chiếu sáng tốt nhất hiện nay.
+Không giống như đèn LED downlight âm trần đế dày, dòng đèn LED
+nói riêng và dòng đèn âm trần khối đúc nói chung được đúc nguyên khối từ hợp kim nhôm.
+Đèn được phủ sơn tĩnh điện dày, đảm bảo không ố vàng hay bong tróc theo thời gian.
+Đèn với thiết kế tản nhiệt nhôm đa chiều, đúc rãnh dày với đế tản nhiệt đúc từ nhôm nguyên khối, tăng khả năng tản nhiệt gấp 5 lần so với các sản phẩm âm trần hiện nay trên thị trường.
+Độ dày đèn chỉ 4 cm, phù hợp với mọi thiết kế trần, ứng dụng đa dạng trong các công trình cao cấp hiện nay.
+Đèn led âm trần khối đúc được thiết kế với ánh sáng 3 màu phù hợp với nhu cầu đa dạng của người dùng.
+Ngoài tác dụng chiếu sáng đèn được ứng dụng trang trí và thiết kế ánh sáng là chủ yếu, tiết kiệm 50% điện năng so với đèn huỳnh quang, 90% so với đèn sợi đốt trên thị trường.
+Sản phẩm được TLC Lighting bảo hành đổi mới trong 24 tháng trên toàn quốc.</t>
         </is>
       </c>
     </row>
@@ -15385,7 +16152,7 @@
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>{"cong_suat": "7W", "anh_sang": "Ba màu", "nhiet_do_mau": "3500K/6500K", "kich_thuoc": "ø120x40mm", "lo_khoet": "ø90mm", "hieu_suat_quang": "110-120 Lm/w", "chi_so_hoan_mau": "CRI≥85", "dien_ap": "85-265V", "thuong_hieu": "TLC LIGHTING", "tuoi_tho": "40.000h", "bao_hanh": "24 tháng"}</t>
+          <t>{"cong_suat": "7W", "anh_sang": "Ba màu", "nhiet_do_mau": "3500K/6500K", "kich_thuoc": "ø120x40mm", "hieu_suat_quang": "110-120 Lm/w", "chi_so_hoan_mau": "CRI≥85", "dien_ap": "85-265V", "thuong_hieu": "TLC LIGHTING", "tuoi_tho": "40.000h", "bao_hanh": "24 tháng", "quang_thong": "630Lm", "do_hoan_mau": "&gt;85", "lo_khoet": "ø90", "tuoi_tho_chip_led": "40.000 giờ"}</t>
         </is>
       </c>
       <c r="J19" t="n">
@@ -15470,7 +16237,7 @@
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t>{"cong_suat": "7W", "anh_sang": "Trắng/vàng, Trắng, Vàng", "nhiet_do_mau": "3500K/6500K", "kich_thuoc": "ø120x40mm, 120x40mm", "lo_khoet": "ø90mm, ø90", "hieu_suat_quang": "110-120 Lm/w, 110~120Lm/w", "chi_so_hoan_mau": "CRI≥85, &gt;85", "dien_ap": "85-265V", "thuong_hieu": "TLC LIGHTING", "tuoi_tho": "40.000h", "bao_hanh": "24 tháng", "quang_thong": "630Lm", "dien_ap_ac": "85-265V", "tuoi_tho_chip_led": "40.000 giờ"}</t>
+          <t>{"cong_suat": "7W", "anh_sang": "Trắng/vàng", "nhiet_do_mau": "3500K/6500K", "kich_thuoc": "ø120x40mm", "lo_khoet": "ø90mm", "hieu_suat_quang": "110-120 Lm/w", "chi_so_hoan_mau": "CRI≥85", "dien_ap": "85-265V", "thuong_hieu": "TLC LIGHTING", "tuoi_tho": "40.000h", "bao_hanh": "24 tháng", "quang_thong": "630Lm", "do_hoan_mau": "&gt;85", "dien_ap_ac": "85-265V", "tuoi_tho_chip_LED": "40.000 giờ"}</t>
         </is>
       </c>
       <c r="J20" t="n">
@@ -15568,7 +16335,7 @@
       </c>
       <c r="I21" t="inlineStr">
         <is>
-          <t>{"cong_suat": "9W", "anh_sang": "Ba màu", "nhiet_do_mau": "3500K/6500K", "kich_thuoc": "ø148x40mm", "chip_led": "OSRAM", "hieu_suat_quang": "110-120 Lm/w", "chi_so_hoan_mau": "CRI≥85", "dien_ap": "85-265V", "thuong_hieu": "TLC LIGHTING", "tuoi_tho": "40.000h", "bao_hanh": "24 tháng", "quang_thong": "810Lm", "do_hoan_mau": "&gt;85", "dien_ap_ac": "85-265V", "lo_khoet": "110", "tuoi_tho_chip_led": "40.000 giờ"}</t>
+          <t>{"cong_suat": "9W", "anh_sang": "Ba màu", "nhiet_do_mau": "3500K/6500K", "kich_thuoc": "ø148x40mm", "chip_led": "OSRAM", "hieu_suat_quang": "110-120 Lm/w", "chi_so_hoan_mau": "CRI≥85", "dien_ap": "85-265V", "thuong_hieu": "TLC LIGHTING", "tuoi_tho": "40.000h", "bao_hanh": "24 tháng", "lo_khoet": "110", "quang_thong": "810Lm", "do_hoan_mau": "&gt;85", "dien_ap_ac": "85-265V", "tuoi_tho_chip_led": "40.000 giờ"}</t>
         </is>
       </c>
       <c r="J21" t="n">
@@ -15582,6 +16349,15 @@
       <c r="M21" t="inlineStr">
         <is>
           <t>https://tlclighting.com.vn/wp-content/uploads/2019/10/IMG_2627-min.jpg</t>
+        </is>
+      </c>
+      <c r="P21" t="inlineStr">
+        <is>
+          <t>Đèn LED âm trần khối đúc 9w có mức điện áp khá rộng: tối thiểu 85V và tối đa 265V. (Sử dụng dòng điện 1 chiều nhờ có bộ chuyển nguồn Led Driver)
+Tuổi thọ trung bình khá cao, đạt mức 40.000 giờ phát sáng, tương đương khoảng 10  năm.
+âm trần khối đúc 9w ba màu
+Chế độ bảo hành 2 năm từ nhà sản xuất như một lời khẳng định chất lượng uy tin, tốt nhất dành cho người tiêu dùng.
+Đèn LED âm trần khối đúc 9w có 2 loại ánh sáng: đơn sắc (trắng, vàng, trung tính) và ánh sáng 3 màu tích hợp</t>
         </is>
       </c>
       <c r="Q21" t="inlineStr">
@@ -15600,6 +16376,18 @@
 Bảo hành: 24 tháng</t>
         </is>
       </c>
+      <c r="T21" t="inlineStr">
+        <is>
+          <t>Đặc điểm của đèn LED âm trần khối đúc 9W đơn sắc
+Đèn LED âm trần khối đúc 9w có mức điện áp khá rộng: tối thiểu 85V và tối đa 265V. (Sử dụng dòng điện 1 chiều nhờ có bộ chuyển nguồn Led Driver)
+Tuổi thọ trung bình khá cao, đạt mức 40.000 giờ phát sáng, tương đương khoảng 10  năm.
+Bên cạnh đó cùng với mức hiệu suất 110-120lm/w, đèn LED
+âm trần khối đúc 9w ba màu
+có nguồn ánh sáng rất trung thực giúp cho mắt bạn luôn điều tiết tốt trong quá trình làm việc dưới ánh sáng nhân tạo của đèn LED âm trần khối đúc. Đây cũng là mức hiệu suất tương đối cao giúp bạn tiết kiệm điện hiệu quả gấp 2-3 lần so với việc dùng đèn trần bóng compact.
+Chế độ bảo hành 2 năm từ nhà sản xuất như một lời khẳng định chất lượng uy tin, tốt nhất dành cho người tiêu dùng.
+Đèn LED âm trần khối đúc 9w có 2 loại ánh sáng: đơn sắc (trắng, vàng, trung tính) và ánh sáng 3 màu tích hợp</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="n">
@@ -15627,7 +16415,7 @@
       </c>
       <c r="I22" t="inlineStr">
         <is>
-          <t>{"cong_suat": "9W", "anh_sang": "Trắng/vàng, Trắng, Vàng", "nhiet_do_mau": "3500K/6500K", "kich_thuoc": "ø148x40mm, 148x40mm", "lo_khoet": "ø90mm, 110", "hieu_suat_quang": "110-120 Lm/w, 110~120Lm/w", "chi_so_hoan_mau": "CRI≥85", "dien_ap": "85-265V", "thuong_hieu": "TLC LIGHTING", "tuoi_tho": "40.000h", "bao_hanh": "24 tháng", "quang_thong": "810Lm", "do_hoan_mau": "&gt;85", "dien_ap_ac": "85-265V", "tuoi_tho_chip_led": "40.000 giờ"}</t>
+          <t>{"cong_suat": "9W", "anh_sang": "Trắng/vàng, Trắng, Vàng", "nhiet_do_mau": "3500K/6500K", "kich_thuoc": "ø148x40mm, 148x40mm", "lo_khoet": "ø90mm, 110", "hieu_suat_quang": "110-120 Lm/w, 110~120Lm/w", "chi_so_hoan_mau": "CRI≥85", "dien_ap": "85-265V", "thuong_hieu": "TLC LIGHTING", "tuoi_tho": "40.000h", "bao_hanh": "24 tháng", "quang_thong": "810Lm", "do_hoan_mau": "&gt;85", "dien_ap_AC": "85-265V", "tuoi_tho_chip_LED": "40.000 giờ"}</t>
         </is>
       </c>
       <c r="J22" t="n">
@@ -15641,6 +16429,15 @@
       <c r="M22" t="inlineStr">
         <is>
           <t>https://tlclighting.com.vn/wp-content/uploads/2019/10/IMG_2627-min.jpg</t>
+        </is>
+      </c>
+      <c r="P22" t="inlineStr">
+        <is>
+          <t>Đèn LED âm trần khối đúc 9w có mức điện áp khá rộng: tối thiểu 85V và tối đa 265V. (Sử dụng dòng điện 1 chiều nhờ có bộ chuyển nguồn Led Driver)
+Tuổi thọ trung bình khá cao, đạt mức 40.000 giờ phát sáng, tương đương khoảng 10  năm.
+âm trần khối đúc 9w đơn sắc
+Chế độ bảo hành 2 năm từ nhà sản xuất như một lời khẳng định chất lượng uy tin, tốt nhất dành cho người tiêu dùng.
+Đèn LED âm trần khối đúc 9w có 2 loại ánh sáng: đơn sắc (trắng, vàng, trung tính) và ánh sáng 3 màu tích hợp</t>
         </is>
       </c>
       <c r="Q22" t="inlineStr">
@@ -15671,6 +16468,18 @@
 Bảo hành: 24 tháng</t>
         </is>
       </c>
+      <c r="T22" t="inlineStr">
+        <is>
+          <t>Đặc điểm của đèn LED âm trần khối đúc 9W đơn sắc
+Đèn LED âm trần khối đúc 9w có mức điện áp khá rộng: tối thiểu 85V và tối đa 265V. (Sử dụng dòng điện 1 chiều nhờ có bộ chuyển nguồn Led Driver)
+Tuổi thọ trung bình khá cao, đạt mức 40.000 giờ phát sáng, tương đương khoảng 10  năm.
+Bên cạnh đó cùng với mức hiệu suất 110-120lm/w, đèn LED
+âm trần khối đúc 9w đơn sắc
+có nguồn ánh sáng rất trung thực giúp cho mắt bạn luôn điều tiết tốt trong quá trình làm việc dưới ánh sáng nhân tạo của đèn LED âm trần khối đúc. Đây cũng là mức hiệu suất tương đối cao giúp bạn tiết kiệm điện hiệu quả gấp 2-3 lần so với việc dùng đèn trần bóng compact.
+Chế độ bảo hành 2 năm từ nhà sản xuất như một lời khẳng định chất lượng uy tin, tốt nhất dành cho người tiêu dùng.
+Đèn LED âm trần khối đúc 9w có 2 loại ánh sáng: đơn sắc (trắng, vàng, trung tính) và ánh sáng 3 màu tích hợp</t>
+        </is>
+      </c>
     </row>
     <row r="23">
       <c r="A23" t="n">
@@ -15698,7 +16507,7 @@
       </c>
       <c r="I23" t="inlineStr">
         <is>
-          <t>{"cong_suat": "12W", "anh_sang": "Ba màu", "nhiet_do_mau": "3500K/6500K", "kich_thuoc": "ø148x37mm", "lo_khoet": "ø110mm", "chip_led": "OSRAM", "hieu_suat_quang": "110-120 Lm/w", "chi_so_hoan_mau": "CRI≥85", "dien_ap": "85-265V", "thuong_hieu": "TLC LIGHTING", "tuoi_tho": "40.000h", "bao_hanh": "24 tháng", "dien_ap_ac": "85-265V", "do_hoan_mau": "&gt;90Ra", "che_do_anh_sang": "Chống chói", "duong_kinh_lo_khoet": "D110mm", "duong_kinh_mat": "D148mm", "chieu_day": "37mm", "chat_lieu": "Hợp kim nhôm sơn tĩnh điện", "chip_led_2": "Chip Osram – CHLB Đức", "tuoi_tho_2": "40.000 giờ", "bao_hanh_2": "2 năm"}</t>
+          <t>{"cong_suat": "12W", "anh_sang": "Ba màu", "nhiet_do_mau": "3500K/6500K", "kich_thuoc": "ø148x37mm", "lo_khoet": "ø110mm", "chip_led": "OSRAM", "hieu_suat_quang": "110-120 Lm/w", "chi_so_hoan_mau": "CRI≥85", "dien_ap": "85-265V", "thuong_hieu": "TLC LIGHTING", "tuoi_tho": "40.000h", "bao_hanh": "24 tháng", "dien_ap_ac": "85-265V", "do_hoan_mau": "&gt;90Ra", "che_do_anh_sang": "Chống chói", "duong_kinh_lo_khoet": "D110mm", "duong_kinh_mat": "D148mm", "chieu_day": "37mm", "chat_lieu": "Hợp kim nhôm sơn tĩnh điện", "chip_led_chlb_duc": "Chip Osram – CHLB Đức", "tuoi_tho_gio": "40.000 giờ", "bao_hanh_nam": "2 năm"}</t>
         </is>
       </c>
       <c r="J23" t="n">
@@ -15942,7 +16751,7 @@
       </c>
       <c r="I25" t="inlineStr">
         <is>
-          <t>{"cong_suat": "9W", "anh_sang": "Ba màu", "nhiet_do_mau": "3500K/6500K", "kich_thuoc": "ø120x37mm", "lo_khoet": "ø90mm", "chip_led": "OSRAM", "hieu_suat_quang": "110-120 Lm/w", "chi_so_hoan_mau": "CRI≥85", "dien_ap": "85-265V", "thuong_hieu": "TLC LIGHTING", "tuoi_tho": "40.000h", "bao_hanh": "24 tháng", "dien_ap_ac": "85-265V", "do_hoan_mau": "&gt;85Ra", "duong_kinh_lo_khoet": "D90mm", "duong_kinh_mat": "D120mm", "chieu_day": "37mm", "chat_lieu": "Hợp kim nhôm sơn tĩnh điện", "chip_led_2": "Chip Osram – CHLB Đức", "tuoi_tho_2": "40.000 giờ"}</t>
+          <t>{"cong_suat": "9W", "anh_sang": "Ba màu", "nhiet_do_mau": "3500K/6500K", "kich_thuoc": "ø120x37mm", "lo_khoet": "ø90mm", "chip_led": "OSRAM", "hieu_suat_quang": "110-120 Lm/w", "chi_so_hoan_mau": "CRI≥85", "dien_ap": "85-265V", "thuong_hieu": "TLC LIGHTING", "tuoi_tho": "40.000h", "bao_hanh": "24 tháng", "dien_ap_ac": "85-265V", "do_hoan_mau": "&gt;85Ra", "che_do_anh_sang": "Chống chói", "duong_kinh_lo_khoet": "D90mm", "duong_kinh_mat": "D120mm", "chieu_day": "37mm", "chat_lieu": "Hợp kim nhôm sơn tĩnh điện", "chip_led_2": "Chip Osram – CHLB Đức", "tuoi_tho_2": "40.000 giờ"}</t>
         </is>
       </c>
       <c r="J25" t="n">
@@ -16369,7 +17178,7 @@
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>{"cong_suat": "6W", "anh_sang": "Trắng/ vàng", "nhiet_do_mau": "3500K/6500K", "kich_thuoc": "ø120x40mm", "hieu_suat_quang": "110-120 Lm/w", "chi_so_hoan_mau": "CRI≥85", "dien_ap": "85-265V", "thuong_hieu": "TLC LIGHTING", "tuoi_tho": "40.000h", "bao_hanh": "24 tháng", "quang_thong": "480Lm", "do_hoan_mau": "&gt;85", "dien_ap_AC": "85-265V", "tuoi_tho_chip_LED": "40.000 giờ"}</t>
+          <t>{"cong_suat": "6W", "anh_sang": "Trắng/ vàng", "nhiet_do_mau": "3500K/6500K", "kich_thuoc": "ø120x40mm", "hieu_suat_quang": "110-120 Lm/w", "chi_so_hoan_mau": "CRI≥85", "dien_ap": "85-265V", "thuong_hieu": "TLC LIGHTING", "tuoi_tho": "40.000h", "bao_hanh": "24 tháng", "quang_thong": "480Lm", "do_hoan_mau": "&gt;85", "dien_ap_ac": "85-265V", "tuoi_tho_chip_LED": "40.000 giờ"}</t>
         </is>
       </c>
       <c r="J4" t="n">
@@ -16458,7 +17267,7 @@
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>{"cong_suat": "20W", "anh_sang": "3 màu(Trắng/Vàng/Trung tính)", "nhiet_do_mau": "3500K/6500K", "kich_thuoc": "267x137x46mm", "hieu_suat_quang": "110-120 Lm/WD", "chi_so_hoan_mau": "CRI=85", "dien_ap": "175-265V", "thuong_hieu": "TLC LIGHTING", "chi_dinh_su_dung": "10h/ngày", "bao_hanh": "24 tháng", "quang_thong": "2000 Lm", "do_hoan_mau": "Ra = 85", "dien_ap_ac": "175-265V", "che_do_anh_sang": "Chống chói", "chat_lieu": "Nhựa"}</t>
+          <t>{"ma_san_pham": "TLC-OCA-HO-20W-03", "cong_suat": "20W", "anh_sang": "3 màu(Trắng/Vàng/Trung tính)", "nhiet_do_mau": "3500K/6500K", "kich_thuoc": "267x137x46mm", "hieu_suat_quang": "110-120 Lm/WD", "chi_so_hoan_mau": "CRI=85", "dien_ap": "175-265V", "thuong_hieu": "TLC LIGHTING", "chi_dinh_su_dung": "10h/ngày", "bao_hanh": "24 tháng", "quang_thong": "2000 Lm", "do_hoan_mau": "Ra = 85", "dien_ap_ac": "175-265V", "che_do_anh_sang": "Chống chói", "chat_lieu": "Nhựa"}</t>
         </is>
       </c>
       <c r="J5" t="n">
@@ -16545,7 +17354,7 @@
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>{"cong_suat": "20W", "anh_sang": "Trắng", "nhiet_do_mau": "3500K/6500K", "kich_thuoc": "267x137x46mm", "hieu_suat_quang": "110-120 Lm/WD", "chi_so_hoan_mau": "CRI=85", "dien_ap": "175-265V", "thuong_hieu": "TLC LIGHTING", "chi_dinh_su_dung": "10h/ngày", "bao_hanh": "24 tháng", "quang_thong": "2000 Lm", "do_hoan_mau": "Ra = 85", "dien_ap_ac": "175-265V", "che_do_anh_sang": "Chống chói", "chat_lieu": "Nhựa"}</t>
+          <t>{"cong_suat": "20W", "anh_sang": "Trắng", "nhiet_do_mau": "3500K/6500K", "kich_thuoc": "267x137x46mm", "hieu_suat_quang": "110-120 Lm/WD", "chi_so_hoan_mau": "CRI=85", "dien_ap": "175-265V", "thuong_hieu": "TLC LIGHTING", "chi_dinh_su_dung": "10h/ngày", "bao_hanh": "24 tháng", "quang_thong": "2000 Lm", "do_hoan_mau": "Ra = 85", "che_do_anh_sang": "Chống chói", "chat_lieu": "Nhựa"}</t>
         </is>
       </c>
       <c r="J6" t="n">
@@ -16632,7 +17441,7 @@
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>{"cong_suat": "12W", "anh_sang": "Ba màu", "nhiet_do_mau": "3500K/6500K", "kich_thuoc": "ø170x40mm", "hieu_suat_quang": "110-120 Lm/w", "chi_so_hoan_mau": "CRI≥85", "dien_ap": "85-265V", "thuong_hieu": "TLC LIGHTING", "tuoi_tho": "40.000h", "bao_hanh": "24 tháng"}</t>
+          <t>{"cong_suat": "12W", "anh_sang": "Ba màu", "nhiet_do_mau": "3500K/6500K", "kich_thuo": "ø170x40mm", "hieu_suat_quang": "110-120 Lm/w", "chi_so_hoan_mau": "CRI≥85", "dien_ap": "85-265V", "thuong_hieu": "TLC LIGHTING", "tuoi_tho": "40.000h", "bao_hanh": "24 tháng", "kich_thuoc": "170x40mm", "quang_thong": "960Lm", "do_hoan_mau": "&gt;85", "dien_ap_AC": "85-265V", "tuoi_tho_chip_LED": "40.000 giờ"}</t>
         </is>
       </c>
       <c r="J7" t="n">
@@ -16721,7 +17530,7 @@
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>{"cong_suat": "12W", "anh_sang": "Trắng/vàng", "nhiet_do_mau": "3500K/6500K", "kich_thuoc": "ø170x40mm, 170x40mm", "hieu_suat_quang": "110-120 Lm/w, 110~120Lm/w", "chi_so_hoan_mau": "CRI≥85", "dien_ap": "85-265V", "thuong_hieu": "TLC LIGHTING", "tuoi_tho": "40.000h", "bao_hanh": "24 tháng", "quang_thong": "960Lm", "do_hoan_mau": "&gt;85", "dien_ap_ac": "85-265V", "tuoi_tho_chip_led": "40.000 giờ"}</t>
+          <t>{"cong_suat": "12W", "anh_sang": "Trắng/vàng", "nhiet_do_mau": "3500K/6500K", "kich_thuoc": "ø170x40mm, 170x40mm", "hieu_suat_quang": "110-120 Lm/w, 110~120Lm/w, 90-100 Lm/W", "chi_so_hoan_mau": "CRI≥85", "dien_ap": "85-265V", "thuong_hieu": "TLC LIGHTING", "tuoi_tho": "40.000h", "bao_hanh": "24 tháng", "quang_thong": "960Lm", "do_hoan_mau": "&gt;85", "dien_ap_ac": "85-265V", "tuoi_tho_chip_led": "40.000 giờ"}</t>
         </is>
       </c>
       <c r="J8" t="n">
@@ -16910,7 +17719,7 @@
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>{"cong_suat": "12W", "anh_sang": "Ba màu", "nhiet_do_mau": "3500K/6500K", "kich_thuoc": "ø170x40mm, 170x40mm", "hieu_suat_quang": "110-120 Lm/w, 110~120Lm/w", "chi_so_hoan_mau": "CRI≥85, &gt;85", "dien_ap": "85-265V", "thuong_hieu": "TLC LIGHTING", "tuoi_tho": "40.000h", "bao_hanh": "24 tháng", "quang_thong": "960Lm", "dien_ap_ac": "85-265V", "tuoi_tho_chip_led": "40.000 giờ"}</t>
+          <t>{"cong_suat": "12W", "anh_sang": "Ba màu", "nhiet_do_mau": "3500K/6500K", "kich_thuoc": "ø170x40mm", "hieu_suat_quang": "110-120 Lm/w", "chi_so_hoan_mau": "CRI≥85", "dien_ap": "85-265V", "thuong_hieu": "TLC LIGHTING", "tuoi_tho": "40.000h", "bao_hanh": "24 tháng", "quang_thong": "960Lm", "do_hoan_mau": "&gt;85", "dien_ap_ac": "85-265V", "tuoi_tho_chip_led": "40.000 giờ"}</t>
         </is>
       </c>
       <c r="J10" t="n">
@@ -17003,7 +17812,7 @@
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>{"cong_suat": "18W", "anh_sang": "Ba màu", "nhiet_do_mau": "3500K/6500K", "kich_thuoc": "ø210x40mm", "chip_led": "Epistar", "hieu_suat_quang": "110-120 Lm/w", "chi_so_hoan_mau": "CRI≥85", "dien_ap": "85-265V", "thuong_hieu": "TLC LIGHTING", "tuoi_tho": "40.000h", "bao_hanh": "24 tháng", "quang_thong": "1440Lm", "do_hoan_mau": "&gt;85", "dien_ap_ac": "85-265V", "tuoi_tho_chip_led": "40.000 giờ"}</t>
+          <t>{"cong_suat": "18W", "anh_sang": "Ba màu", "nhiet_do_mau": "3500K/6500K", "kich_thuoc": "ø210x40mm, 210x40mm", "chip_led": "Epistar", "hieu_suat_quang": "110-120 Lm/w, 110~120Lm/w", "chi_so_hoan_mau": "CRI≥85", "dien_ap": "85-265V", "thuong_hieu": "TLC LIGHTING", "tuoi_tho": "40.000h", "bao_hanh": "24 tháng", "quang_thong": "1440Lm", "do_hoan_mau": "&gt;85", "dien_ap_ac": "85-265V", "tuoi_tho_chip_led": "40.000 giờ"}</t>
         </is>
       </c>
       <c r="J11" t="n">
@@ -17098,7 +17907,7 @@
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>{"cong_suat": "18W", "anh_sang": "Trắng/vàng", "nhiet_do_mau": "3500K/6500K", "kich_thuoc": "ø210x40mm, 210x40mm", "hieu_suat_quang": "110-120 Lm/w, 110~120Lm/w", "chi_so_hoan_mau": "CRI≥85, &gt;85", "dien_ap": "85-265V", "thuong_hieu": "TLC LIGHTING", "tuoi_tho": "40.000h", "bao_hanh": "24 tháng", "quang_thong": "1440Lm", "tuoi_tho_chip_LED": "40.000 giờ"}</t>
+          <t>{"cong_suat": "18W", "anh_sang": "Trắng/vàng", "nhiet_do_mau": "3500K/6500K", "kich_thuoc": "ø210x40mm", "hieu_suat_quang": "110-120 Lm/w", "chi_so_hoan_mau": "CRI≥85", "dien_ap": "85-265V", "thuong_hieu": "TLC LIGHTING", "tuoi_tho": "40.000h", "bao_hanh": "24 tháng", "quang_thong": "1440Lm", "do_hoan_mau": "&gt;85", "dien_ap_ac": "85-265V", "tuoi_tho_chip_led": "40.000 giờ"}</t>
         </is>
       </c>
       <c r="J12" t="n">
@@ -17192,7 +18001,7 @@
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>{"cong_suat": "18W", "anh_sang": "Ba màu", "nhiet_do_mau": "3500K/6500K", "kich_thuoc": "ø210x40mm", "hieu_suat_quang": "110-120 Lm/w", "chi_so_hoan_mau": "CRI≥85", "dien_ap": "85-265V", "thuong_hieu": "TLC LIGHTING", "tuoi_tho": "40.000h", "bao_hanh": "24 tháng", "quang_thong": "1440Lm", "do_hoan_mau": "&gt;85", "dien_ap_AC": "85-265V", "tuoi_tho_chip_LED": "40.000 giờ"}</t>
+          <t>{"cong_suat": "18W", "anh_sang": "Ba màu", "nhiet_do_mau": "3500K/6500K", "kich_thuoc": "ø210x40mm, 210x40mm", "hieu_suat_quang": "110-120 Lm/w, 110~120Lm/w", "chi_so_hoan_mau": "CRI≥85", "dien_ap": "85-265V", "thuong_hieu": "TLC LIGHTING", "tuoi_tho": "40.000h", "bao_hanh": "24 tháng", "quang_thong": "1440Lm", "do_hoan_mau": "&gt;85", "dien_ap_ac": "85-265V", "tuoi_tho_chip_LED": "40.000 giờ"}</t>
         </is>
       </c>
       <c r="J13" t="n">
@@ -17206,6 +18015,16 @@
       <c r="M13" t="inlineStr">
         <is>
           <t>https://tlclighting.com.vn/wp-content/uploads/2019/11/Untitled-10.jpg</t>
+        </is>
+      </c>
+      <c r="P13" t="inlineStr">
+        <is>
+          <t>Đèn có hiệu suất quang đạt 90 -100 Lm/w. Ánh sáng tốt hơn gấp 2-3 lần so với dòng đèn compac, huỳnh quang thông thường.
+Tiết kiệm 50% điện năng tiêu thụ so với đèn huỳnh quang, 80% so với đèn sợi đốt – vừa đảm bảo tiêu chuẩn ánh sáng vừa tiết kiệm chi phí điện năng cho người tiêu thụ.
+Đèn được cấu tạo từ chip LED cao cấp cho chỉ số hoàn màu CRI &gt; 80 độ bền vượt trội, ánh sáng dịu mát, an toàn cho mắt, chống lóa – mỏi mắt.
+Tuổi thọ của đèn cao: Tuổi thọ của đèn đạt 40.000 giờ chiếu sáng giúp hạn chế chi phí thay thế, bảo hành, bảo dưỡng cho người sử dụng.
+Bảo vệ môi trường và sức khỏe: Khi phát sáng, đèn không phát ra các tia có hại như tia UV, tia hồng ngoại và các chất độc hại cho sức khỏe con người.
+Chế độ bảo hành 24 tháng trên toàn quốc.</t>
         </is>
       </c>
       <c r="Q13" t="inlineStr">
@@ -17234,6 +18053,21 @@
 Bảo hành: 24 tháng</t>
         </is>
       </c>
+      <c r="T13" t="inlineStr">
+        <is>
+          <t>Ưu điểm đèn LED ốp nổi công suất 18W
+Đèn được thiết kế
+hình vuông, thân đèn màu đen và mặt đèn m
+ặt đèn được bảo vệ bởi hợp kim nhôm sơn tĩnh điện cao cấp với mặt Mica sần mờ có khả năng chống bụi và côn trùng xâm nhập đồng thời cho khả năng ánh sáng đi qua cao, không gây chói mắt, an toàn cho sức khỏe và thị lực của con người.
+Đèn có hiệu suất quang đạt 90 -100 Lm/w. Ánh sáng tốt hơn gấp 2-3 lần so với dòng đèn compac, huỳnh quang thông thường.
+Tiết kiệm 50% điện năng tiêu thụ so với đèn huỳnh quang, 80% so với đèn sợi đốt – vừa đảm bảo tiêu chuẩn ánh sáng vừa tiết kiệm chi phí điện năng cho người tiêu thụ.
+Đèn được cấu tạo từ chip LED cao cấp cho chỉ số hoàn màu CRI &gt; 80 độ bền vượt trội, ánh sáng dịu mát, an toàn cho mắt, chống lóa – mỏi mắt.
+Tuổi thọ của đèn cao: Tuổi thọ của đèn đạt 40.000 giờ chiếu sáng giúp hạn chế chi phí thay thế, bảo hành, bảo dưỡng cho người sử dụng.
+Bảo vệ môi trường và sức khỏe: Khi phát sáng, đèn không phát ra các tia có hại như tia UV, tia hồng ngoại và các chất độc hại cho sức khỏe con người.
+Chế độ bảo hành 24 tháng trên toàn quốc.
+TLC LIGHTING mang những sản phẩm chiếu sáng tốt nhất đến với người tiêu dùng. Các sản phẩm đèn LED và thiết bị chiếu sáng nói chung, đèn led ốp nổi trần nói riêng chắc chắn sẽ làm hài lòng khách hàng ngay cả những khách hàng khó tính nhất bởi các ưu điểm nổi trội của dòng sản phẩm mang thương hiệu TLC LIGHTING.</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
@@ -17261,7 +18095,7 @@
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>{"cong_suat": "18W", "anh_sang": "Trắng/vàng", "nhiet_do_mau": "3500K/6500K", "kich_thuoc": "ø210x40mm", "hieu_suat_quang": "110-120 Lm/w", "chi_so_hoan_mau": "CRI≥85", "dien_ap": "85-265V", "thuong_hieu": "TLC LIGHTING", "tuoi_tho": "40.000h", "bao_hanh": "24 tháng", "quang_thong": "1440Lm", "do_hoan_mau": "&gt;85", "dien_ap_ac": "85-265V", "tuoi_tho_chip_led": "40.000 giờ"}</t>
+          <t>{"cong_suat": "18W", "anh_sang": "Trắng/vàng", "nhiet_do_mau": "3500K/6500K", "kich_thuoc": "ø210x40mm", "hieu_suat_quang": "110-120 Lm/w", "chi_so_hoan_mau": "CRI≥85", "dien_ap": "85-265V", "thuong_hieu": "TLC LIGHTING", "tuoi_tho": "40.000h", "bao_hanh": "24 tháng", "quang_thong": "1440Lm", "do_hoan_mau": "&gt;85", "dien_ap_ac": "85-265V", "tuoi_tho_chip_LED": "40.000 giờ"}</t>
         </is>
       </c>
       <c r="J14" t="n">
@@ -17350,7 +18184,7 @@
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>{"cong_suat": "6W", "anh_sang": "Ba màu", "nhiet_do_mau": "3500K/6500K", "kich_thuoc": "ø120x40mm", "hieu_suat_quang": "110-120 Lm/w", "chi_so_hoan_mau": "CRI≥85", "dien_ap": "85-265V", "thuong_hieu": "TLC LIGHTING", "tuoi_tho": "40.000h", "quang_thong": "480Lm", "do_hoan_mau": "&gt;85", "dien_ap_ac": "85-265V", "tuoi_tho_chip_led": "40.000 giờ"}</t>
+          <t>{"cong_suat": "6W", "anh_sang": "Ba màu", "nhiet_do_mau": "3500K/6500K", "kich_thuoc": "ø120x40mm", "hieu_suat_quang": "110-120 Lm/w", "chi_so_hoan_mau": "CRI≥85", "dien_ap": "85-265V", "thuong_hieu": "TLC LIGHTING", "tuoi_tho": "40.000h", "bao_hanh": "24 tháng", "quang_thong": "480Lm", "do_hoan_mau": "&gt;85", "dien_ap_ac": "85-265V", "tuoi_tho_chip_led": "40.000 giờ"}</t>
         </is>
       </c>
       <c r="J15" t="n">
@@ -17442,7 +18276,7 @@
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>{"cong_suat": "6W", "anh_sang": "Ba màu", "nhiet_do_mau": "3500K/6500K", "kich_thuoc": "ø120x40mm, 120x40mm", "hieu_suat_quang": "110-120 Lm/w, 110~120Lm/w", "chi_so_hoan_mau": "CRI≥85", "dien_ap": "85-265V", "thuong_hieu": "TLC LIGHTING", "tuoi_tho": "40.000h", "bao_hanh": "24 tháng", "quang_thong": "480Lm", "do_hoan_mau": "&gt;85", "dien_ap_AC": "85-265V", "chip_LED": "SMD", "tuoi_tho_chip_LED": "40.000 giờ"}</t>
+          <t>{"cong_suat": "6W", "anh_sang": "Ba màu", "nhiet_do_mau": "3500K/6500K", "kich_thuoc": "ø120x40mm, 120x40mm", "hieu_suat_quang": "110-120 Lm/w, 110~120Lm/w", "chi_so_hoan_mau": "CRI≥85", "dien_ap": "85-265V", "thuong_hieu": "TLC LIGHTING", "tuoi_tho": "40.000h", "bao_hanh": "24 tháng", "quang_thong": "480Lm", "do_hoan_mau": "&gt;85", "dien_ap_ac": "85-265V", "chip_led": "SMD", "tuoi_tho_chip_led": "40.000 giờ"}</t>
         </is>
       </c>
       <c r="J16" t="n">
@@ -17532,7 +18366,7 @@
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>{"cong_suat": "6W", "anh_sang": "Ba màu", "nhiet_do_mau": "3500K/6500K", "kich_thuoc": "ø120x40mm, 120x40mm", "hieu_suat_quang": "110-120 Lm/w, 110~120Lm/w", "chi_so_hoan_mau": "CRI≥85", "dien_ap": "85-265V", "thuong_hieu": "TLC LIGHTING", "tuoi_tho": "40.000h", "bao_hanh": "24 tháng", "quang_thong": "480Lm", "do_hoan_mau": "&gt;85", "dien_ap_ac": "85-265V", "tuoi_tho_chip_LED": "40.000 giờ"}</t>
+          <t>{"cong_suat": "6W", "anh_sang": "Ba màu", "nhiet_do_mau": "3500K/6500K", "kich_thuoc": "ø120x40mm", "hieu_suat_quang": "110-120 Lm/w", "chi_so_hoan_mau": "CRI≥85", "dien_ap": "85-265V", "thuong_hieu": "TLC LIGHTING", "tuoi_tho": "40.000h", "bao_hanh": "24 tháng", "quang_thong": "480Lm", "do_hoan_mau": "&gt;85", "dien_ap_ac": "85-265V"}</t>
         </is>
       </c>
       <c r="J17" t="n">
@@ -17718,7 +18552,7 @@
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>{"thuong_hieu": "TLC LIGHTING", "cong_suat": "12W", "anh_sang": "Trắng | Vàng", "dien_ap_ac": "85 – 265V", "hieu_suat_quang": "1200 Lm", "chip_led": "OSRAM", "bao_hanh": "36 tháng"}</t>
+          <t>{"thuong_hieu": "TLC LIGHTING", "cong_suat": "12W", "anh_sang": "Trắng, Vàng", "dien_ap": "85 – 265V", "hieu_suat_quang": "1200 Lm", "kich_thuoc_den": "120×40 mm", "chip_led": "OSRAM", "bao_hanh": "36 tháng"}</t>
         </is>
       </c>
       <c r="J19" t="n">
@@ -17795,7 +18629,7 @@
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t>{"cong_suat": "32W", "anh_sang": "Trắng/vàng", "nhiet_do_mau": "3500K/6500K", "kich_thuoc": "ø220x42mm, ϕ220x42mm", "hieu_suat_quang": "110 Lm/W, 110 Lm/w", "chi_so_hoan_mau": "CRI≥85, &gt;85", "dien_ap": "85-265V, 85-265V", "thuong_hieu": "TLC LIGHTING", "tuoi_tho": "40.000h, 40.000 giờ", "bao_hanh": "24 tháng", "quang_thong": "3520 Lm"}</t>
+          <t>{"cong_suat": "32W", "anh_sang": "Trắng/vàng", "nhiet_do_mau": "3500K/6500K", "kich_thuoc": "ø220x42mm, ϕ220x42mm", "hieu_suat_quang": "110 Lm/W", "chi_so_hoan_mau": "CRI≥85, &gt;85", "dien_ap": "85-265V", "thuong_hieu": "TLC LIGHTING", "tuoi_tho": "40.000h", "bao_hanh": "24 tháng", "quang_thong": "3520 Lm", "dien_ap_ac": "85-265V", "tuoi_tho_chip_led": "40.000 giờ", "goc_chieu_sang": "180 độ"}</t>
         </is>
       </c>
       <c r="J20" t="n">
@@ -17882,7 +18716,7 @@
       </c>
       <c r="I21" t="inlineStr">
         <is>
-          <t>{"cong_suat": "36W", "anh_sang": "Trắng/vàng", "nhiet_do_mau": "3500K/6500K", "kich_thuoc": "ø300x42mm", "hieu_suat_quang": "110 Lm/W", "chi_so_hoan_mau": "CRI≥85", "dien_ap": "85-265V", "thuong_hieu": "TLC LIGHTING", "tuoi_tho": "40.000h", "bao_hanh": "24 tháng", "quang_thong": "3960 Lm", "do_hoan_mau": "&gt;85", "dien_ap_ac": "150-265V", "tuoi_tho_chip_led": "40.000 giờ"}</t>
+          <t>{"cong_suat": "36W", "anh_sang": "Trắng/vàng", "nhiet_do_mau": "3500K/6500K", "kich_thuoc": "ø300x42mm, ϕ300x42mm", "hieu_suat_quang": "110 Lm/W, 110 Lm/w", "chi_so_hoan_mau": "CRI≥85, &gt;85, Ra &gt; 85", "dien_ap": "85-265V, 150-265V", "thuong_hieu": "TLC LIGHTING", "tuoi_tho": "40.000h, 40.000 giờ", "bao_hanh": "24 tháng", "quang_thong": "3960 Lm", "tuoi_tho_chip_LED": "40.000 giờ", "goc_chieu_sang": "180 độ"}</t>
         </is>
       </c>
       <c r="J21" t="n">
@@ -18082,7 +18916,7 @@
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>TLC-ONV-TT-24W-03</t>
+          <t>TLC-ONV-TĐ-24W-03</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
@@ -18092,7 +18926,7 @@
       </c>
       <c r="I23" t="inlineStr">
         <is>
-          <t>{"cong_suat": "24W", "anh_sang": "Ba màu", "nhiet_do_mau": "3500K/6500K", "kich_thuoc": "ø290x40mm, 290x40mm", "hieu_suat_quang": "110-120 Lm/w, 110~120Lm/w, 80-100 Lm/w", "chi_so_hoan_mau": "CRI≥85, &gt;85", "dien_ap": "85-265V", "thuong_hieu": "TLC LIGHTING", "tuoi_tho": "40.000h, 40.000 giờ", "bao_hanh": "24 tháng", "quang_thong": "1920Lm", "dien_ap_ac": "85-265V", "tuoi_tho_chip_led": "40.000 giờ"}</t>
+          <t>{"cong_suat": "24W", "anh_sang": "Ba màu", "nhiet_do_mau": "3500K/6500K", "kich_thuoc": "ø290x40mm", "hieu_suat_quang": "110-120 Lm/w", "chi_so_hoan_mau": "CRI≥85", "dien_ap": "85-265V", "thuong_hieu": "TLC LIGHTING", "tuoi_tho": "40.000h", "bao_hanh": "24 tháng", "quang_thong": "1920Lm", "do_hoan_mau": "&gt;85", "dien_ap_ac": "85-265V", "tuoi_tho_chip_led": "40.000 giờ"}</t>
         </is>
       </c>
       <c r="J23" t="n">
@@ -18187,7 +19021,7 @@
       </c>
       <c r="I24" t="inlineStr">
         <is>
-          <t>{"cong_suat": "24W", "anh_sang": "Trắng/vàng", "nhiet_do_mau": "3500K/6500K", "kich_thuoc": "ø290x40mm, 290x40mm", "hieu_suat_quang": "110-120 Lm/w, 110~120Lm/w", "chi_so_hoan_mau": "CRI≥85", "dien_ap": "85-265V", "thuong_hieu": "TLC LIGHTING", "tuoi_tho": "40.000h", "bao_hanh": "24 tháng", "quang_thong": "1920Lm", "do_hoan_mau": "&gt;85", "dien_ap_ac": "85-265V", "tuoi_tho_chip_LED": "40.000 giờ"}</t>
+          <t>{"cong_suat": "24W", "anh_sang": "Trắng/vàng", "nhiet_do_mau": "3500K/6500K", "kich_thuoc": "ø290x40mm, 290x40mm", "hieu_suat_quang": "110-120 Lm/w, 110~120Lm/w", "chi_so_hoan_mau": "CRI≥85", "dien_ap": "85-265V", "thuong_hieu": "TLC LIGHTING", "tuoi_tho": "40.000h", "bao_hanh": "24 tháng", "quang_thong": "1920Lm", "do_hoan_mau": "&gt;85", "dien_ap_ac": "85-265V", "tuoi_tho_chip_led": "40.000 giờ"}</t>
         </is>
       </c>
       <c r="J24" t="n">
@@ -18279,7 +19113,7 @@
       </c>
       <c r="I25" t="inlineStr">
         <is>
-          <t>{"cong_suat": "22W", "anh_sang": "Trắng/vàng", "nhiet_do_mau": "3500K/6500K", "kich_thuoc": "ø180x42mm", "hieu_suat_quang": "110 Lm/W", "chi_so_hoan_mau": "CRI≥85", "dien_ap": "85-265V", "thuong_hieu": "TLC LIGHTING", "tuoi_tho": "40.000h", "bao_hanh": "24 tháng"}</t>
+          <t>{"cong_suat": "22W", "anh_sang": "Trắng/vàng", "nhiet_do_mau": "3500K/6500K", "kich_thuoc": "ø180x42mm", "hieu_suat_quang": "110 Lm/W", "chi_so_hoan_mau": "CRI≥85", "dien_ap": "85-265V", "thuong_hieu": "TLC LIGHTING", "tuoi_tho": "40.000h", "bao_hanh": "24 tháng", "quang_thong": "2420 Lm", "do_hoan_mau": "&gt;85", "dien_ap_ac": "85-265V", "tuoi_tho_chip_led": "40.000 giờ"}</t>
         </is>
       </c>
       <c r="J25" t="n">
@@ -18371,7 +19205,7 @@
       </c>
       <c r="I26" t="inlineStr">
         <is>
-          <t>{"cong_suat": "22W", "anh_sang": "Trắng/vàng", "nhiet_do_mau": "3500K/6500K", "kich_thuoc": "180x180x42mm", "hieu_suat_quang": "110 Lm/W", "chi_so_hoan_mau": "CRI≥85", "dien_ap": "85-265V", "thuong_hieu": "TLC LIGHTING", "tuoi_tho": "40.000h", "bao_hanh": "24 tháng", "quang_thong": "2420 Lm", "tuoi_tho_chip_LED": "40.000 giờ"}</t>
+          <t>{"cong_suat": "22W", "anh_sang": "Trắng/vàng", "nhiet_do_mau": "3500K/6500K", "kich_thuoc": "180x180x42mm", "hieu_suat_quang": "110 Lm/W", "chi_so_hoan_mau": "CRI≥85", "dien_ap": "85-265V", "thuong_hieu": "TLC LIGHTING", "tuoi_tho": "40.000h", "bao_hanh": "24 tháng", "quang_thong": "2420 Lm", "do_hoan_mau": "&gt;85", "dien_ap_ac": "85-265V", "tuoi_tho_chip_led": "40.000 giờ"}</t>
         </is>
       </c>
       <c r="J26" t="n">
@@ -18459,7 +19293,7 @@
       </c>
       <c r="I27" t="inlineStr">
         <is>
-          <t>{"cong_suat": "28W", "anh_sang": "Trắng/vàng", "nhiet_do_mau": "3500K/6500K", "kich_thuoc": "ø220x42mm, ϕ220x42mm", "hieu_suat_quang": "110 Lm/W, 110 Lm/w", "chi_so_hoan_mau": "CRI≥85, &gt;85", "dien_ap": "85-265V", "thuong_hieu": "TLC LIGHTING", "tuoi_tho": "40.000h", "bao_hanh": "24 tháng", "quang_thong": "3080 Lm", "tuoi_tho_chip_LED": "40.000 giờ", "dien_ap_AC": "85-265V"}</t>
+          <t>{"cong_suat": "28W", "anh_sang": "Trắng/vàng", "nhiet_do_mau": "3500K/6500K", "kich_thuoc": "ø220x42mm, ϕ220x42mm", "hieu_suat_quang": "110 Lm/W, 110 Lm/w", "chi_so_hoan_mau": "CRI≥85, &gt;85", "dien_ap": "85-265V", "thuong_hieu": "TLC LIGHTING", "tuoi_tho": "40.000h", "bao_hanh": "24 tháng", "quang_thong": "3080 Lm", "dien_ap_ac": "85-265V", "tuoi_tho_chip_led": "40.000 giờ"}</t>
         </is>
       </c>
       <c r="J27" t="n">
@@ -18546,7 +19380,7 @@
       </c>
       <c r="I28" t="inlineStr">
         <is>
-          <t>{"cong_suat": "28W", "anh_sang": "Trắng/vàng", "nhiet_do_mau": "3500K/6500K", "kich_thuoc": "220x220x42mm", "hieu_suat_quang": "110 Lm/W", "chi_so_hoan_mau": "CRI≥85", "dien_ap": "85-265V", "thuong_hieu": "TLC LIGHTING", "tuoi_tho": "40.000h", "bao_hanh": "24 tháng", "quang_thong": "3080 Lm", "tuoi_tho_chip_led": "40.000 giờ"}</t>
+          <t>{"cong_suat": "28W", "anh_sang": "Trắng/vàng", "nhiet_do_mau": "3500K/6500K", "kich_thuoc": "220x220x42mm", "hieu_suat_quang": "110 Lm/W", "chi_so_hoan_mau": "CRI≥85", "dien_ap": "85-265V", "thuong_hieu": "TLC LIGHTING", "tuoi_tho": "40.000h", "bao_hanh": "24 tháng", "quang_thong": "3080 Lm", "do_hoan_mau": "&gt;85", "dien_ap_ac": "85-265V", "tuoi_tho_chip_led": "40.000 giờ"}</t>
         </is>
       </c>
       <c r="J28" t="n">
@@ -18731,7 +19565,7 @@
       </c>
       <c r="I30" t="inlineStr">
         <is>
-          <t>{"cong_suat": "12W", "anh_sang": "Ba màu", "nhiet_do_mau": "3500K/6500K", "kich_thuoc": "ø170x40mm, 170x40mm", "hieu_suat_quang": "110-120 Lm/w, 110~120Lm/w", "chi_so_hoan_mau": "CRI≥85", "dien_ap": "85-265V", "thuong_hieu": "TLC LIGHTING", "tuoi_tho": "40.000h", "bao_hanh": "24 tháng", "quang_thong": "960Lm", "do_hoan_mau": "&gt;85", "dien_ap_ac": "85-265V", "tuoi_tho_chip_led": "40.000 giờ"}</t>
+          <t>{"cong_suat": "12W", "anh_sang": "Ba màu", "nhiet_do_mau": "3500K/6500K", "kich_thuoc": "ø170x40mm", "hieu_suat_quang": "110-120 Lm/w", "chi_so_hoan_mau": "CRI≥85", "dien_ap": "85-265V", "thuong_hieu": "TLC LIGHTING", "tuoi_tho": "40.000h", "bao_hanh": "24 tháng", "quang_thong": "960Lm", "do_hoan_mau": "&gt;85", "dien_ap_ac": "85-265V", "tuoi_tho_chip_led": "40.000 giờ"}</t>
         </is>
       </c>
       <c r="J30" t="n">
@@ -18820,7 +19654,7 @@
       </c>
       <c r="I31" t="inlineStr">
         <is>
-          <t>{"cong_suat": "12W", "anh_sang": "Ba màu", "nhiet_do_mau": "3500K/6500K", "kich_thuoc": "ø170x40mm, 170x40mm", "chip_led": "Epistar, SMD công nghệ cao", "hieu_suat_quang": "110-120 Lm/w, 110~120Lm/w", "chi_so_hoan_mau": "CRI≥85, &gt;85, CRI &gt;85Ra", "dien_ap": "85-265V", "thuong_hieu": "TLC LIGHTING", "tuoi_tho": "40.000h", "bao_hanh": "24 tháng", "quang_thong": "960Lm", "dien_ap_ac": "85-265V", "tuoi_tho_chip_led": "40.000 giờ"}</t>
+          <t>{"cong_suat": "12W", "anh_sang": "Ba màu", "nhiet_do_mau": "3500K/6500K", "kich_thuoc": "ø170x40mm", "chip_led": "Epistar", "hieu_suat_quang": "110-120 Lm/w", "chi_so_hoan_mau": "CRI≥85", "dien_ap": "85-265V", "thuong_hieu": "TLC LIGHTING", "tuoi_tho": "40.000h", "bao_hanh": "24 tháng", "quang_thong": "960Lm", "do_hoan_mau": "&gt;85", "dien_ap_ac": "85-265V", "tuoi_tho_chip_led": "40.000 giờ"}</t>
         </is>
       </c>
       <c r="J31" t="n">
@@ -18913,7 +19747,7 @@
       </c>
       <c r="I32" t="inlineStr">
         <is>
-          <t>{"cong_suat": "12W", "anh_sang": "Trắng/vàng", "nhiet_do_mau": "3500K/6500K", "kich_thuoc": "ø170x40mm, 170x40mm", "hieu_suat_quang": "110-120 Lm/w, 110~120Lm/w", "chi_so_hoan_mau": "CRI≥85", "dien_ap": "85-265V", "thuong_hieu": "TLC LIGHTING", "tuoi_tho": "40.000h", "bao_hanh": "24 tháng", "quang_thong": "960Lm", "do_hoan_mau": "&gt;85", "dien_ap_AC": "85-265V", "tuoi_tho_chip_LED": "40.000 giờ"}</t>
+          <t>{"cong_suat": "12W", "anh_sang": "Trắng/vàng", "nhiet_do_mau": "3500K/6500K", "kich_thuoc": "ø170x40mm", "hieu_suat_quang": "110-120 Lm/w", "chi_so_hoan_mau": "CRI≥85", "dien_ap": "85-265V", "thuong_hieu": "TLC LIGHTING", "tuoi_tho": "40.000h", "bao_hanh": "24 tháng", "quang_thong": "960Lm", "do_hoan_mau": "&gt;85", "dien_ap_ac": "85-265V", "tuoi_tho_chip_led": "40.000 giờ"}</t>
         </is>
       </c>
       <c r="J32" t="n">
@@ -19013,7 +19847,7 @@
       </c>
       <c r="I33" t="inlineStr">
         <is>
-          <t>{"cong_suat": "18W", "anh_sang": "Ba màu", "nhiet_do_mau": "3500K/6500K", "kich_thuoc": "ø210x40mm", "hieu_suat_quang": "80 Lm/w", "chi_so_hoan_mau": "CRI≥85", "dien_ap": "85-265V", "thuong_hieu": "TLC LIGHTING", "tuoi_tho": "40.000h", "bao_hanh": "24 tháng", "quang_thong": "1440Lm", "do_hoan_mau": "&gt;85", "dien_ap_ac": "85-265V", "tuoi_tho_chip_led": "40.000 giờ"}</t>
+          <t>{"cong_suat": "18W", "anh_sang": "Ba màu", "nhiet_do_mau": "3500K/6500K", "kich_thuoc": "ø210x40mm, 210x40mm", "hieu_suat_quang": "80 Lm/w, 80Lm/w", "chi_so_hoan_mau": "CRI≥85", "dien_ap": "85-265V", "thuong_hieu": "TLC LIGHTING", "tuoi_tho": "40.000h", "bao_hanh": "24 tháng", "quang_thong": "1440Lm", "do_hoan_mau": "&gt;85", "dien_ap_ac": "85-265V", "tuoi_tho_chip_led": "40.000 giờ"}</t>
         </is>
       </c>
       <c r="J33" t="n">
@@ -19109,7 +19943,7 @@
       </c>
       <c r="I34" t="inlineStr">
         <is>
-          <t>{"cong_suat": "18W", "anh_sang": "Ba màu", "nhiet_do_mau": "3500K/6500K", "kich_thuoc": "ø210x40mm", "hieu_suat_quang": "110-120 Lm/w", "chi_so_hoan_mau": "CRI≥85", "dien_ap": "85-265V", "thuong_hieu": "TLC LIGHTING", "tuoi_tho": "40.000h", "bao_hanh": "24 tháng", "quang_thong": "1440Lm", "do_hoan_mau": "&gt;85", "dien_ap_ac": "85-265V", "tuoi_tho_chip_led": "40.000 giờ"}</t>
+          <t>{"cong_suat": "18W", "anh_sang": "Ba màu", "nhiet_do_mau": "3500K/6500K", "kich_thuoc": "ø210x40mm", "hieu_suat_quang": "110-120 Lm/w", "chi_so_hoan_mau": "CRI≥85", "dien_ap": "85-265V", "thuong_hieu": "TLC LIGHTING", "tuoi_tho": "40.000h", "bao_hanh": "24 tháng", "quang_thong": "1440Lm", "do_hoan_mau": "&gt;85", "dien_ap_ac": "85-265V", "tuoi_tho_chip_LED": "40.000 giờ"}</t>
         </is>
       </c>
       <c r="J34" t="n">
@@ -19357,7 +20191,7 @@
       </c>
       <c r="I37" t="inlineStr">
         <is>
-          <t>{"cong_suat": "24W", "anh_sang": "Ba màu", "nhiet_do_mau": "3500K/6500K", "kich_thuoc": "ø290x40mm", "hieu_suat_quang": "110-120 Lm/w", "chi_so_hoan_mau": "CRI≥85", "dien_ap": "85-265V", "thuong_hieu": "TLC LIGHTING", "tuoi_tho": "40.000h", "bao_hanh": "24 tháng", "quang_thong": "1920Lm", "do_hoan_mau": "&gt;85", "dien_ap_ac": "85-265V", "tuoi_tho_chip_led": "40.000 giờ"}</t>
+          <t>{"cong_suat": "24W", "anh_sang": "Ba màu", "nhiet_do_mau": "3500K/6500K", "kich_thuoc": "ø290x40mm", "hieu_suat_quang": "110-120 Lm/w, 110~120Lm/w", "chi_so_hoan_mau": "CRI≥85, &gt;85", "dien_ap": "85-265V", "thuong_hieu": "TLC LIGHTING", "tuoi_tho": "40.000h, 40.000 giờ", "bao_hanh": "24 tháng", "quang_thong": "1920Lm"}</t>
         </is>
       </c>
       <c r="J37" t="n">
@@ -19617,7 +20451,7 @@
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>TLC-ONV-TT-24W</t>
+          <t>TLC-ONV-TĐ-24W</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
@@ -19627,7 +20461,7 @@
       </c>
       <c r="I40" t="inlineStr">
         <is>
-          <t>{"cong_suat": "24W", "anh_sang": "Trắng/vàng", "nhiet_do_mau": "3500K/6500K", "kich_thuoc": "ø290x40mm", "hieu_suat_quang": "110-120 Lm/w", "chi_so_hoan_mau": "CRI≥85", "dien_ap": "85-265V", "thuong_hieu": "TLC LIGHTING", "tuoi_tho": "40.000h", "bao_hanh": "24 tháng", "quang_thong": "1920Lm", "do_hoan_mau": "&gt;85", "dien_ap_ac": "85-265V", "tuoi_tho_chip_led": "40.000 giờ"}</t>
+          <t>{"cong_suat": "24W", "anh_sang": "Trắng/vàng", "nhiet_do_mau": "3500K/6500K", "kich_thuoc": "ø290x40mm, 290x40mm", "hieu_suat_quang": "110-120 Lm/w, 110~120Lm/w", "chi_so_hoan_mau": "CRI≥85, &gt;85", "dien_ap": "85-265V", "thuong_hieu": "TLC LIGHTING", "tuoi_tho": "40.000h", "bao_hanh": "24 tháng", "quang_thong": "1920Lm", "dien_ap_ac": "85-265V", "tuoi_tho_chip_led": "40.000 giờ"}</t>
         </is>
       </c>
       <c r="J40" t="n">
@@ -19815,7 +20649,7 @@
       </c>
       <c r="I42" t="inlineStr">
         <is>
-          <t>{"cong_suat": "12W", "anh_sang": "Trắng/vàng", "nhiet_do_mau": "3500K/6500K", "kich_thuoc": "ø170x40mm, 170x40mm", "hieu_suat_quang": "110-120 Lm/w, 110~120Lm/w", "chi_so_hoan_mau": "CRI≥85", "dien_ap": "85-265V", "thuong_hieu": "TLC LIGHTING", "tuoi_tho": "40.000h, 40.000 giờ", "bao_hanh": "24 tháng", "quang_thong": "960Lm", "do_hoan_mau": "&gt;85", "dien_ap_ac": "85-265V", "tuoi_tho_chip_led": "40.000 giờ"}</t>
+          <t>{"cong_suat": "12W", "anh_sang": "Trắng/vàng", "nhiet_do_mau": "3500K/6500K", "kich_thuoc": "ø170x40mm", "hieu_suat_quang": "110-120 Lm/w", "chi_so_hoan_mau": "CRI≥85", "dien_ap": "85-265V", "thuong_hieu": "TLC LIGHTING", "tuoi_tho": "40.000h", "bao_hanh": "24 tháng", "quang_thong": "960Lm", "do_hoan_mau": "&gt;85", "dien_ap_ac": "85-265V", "tuoi_tho_chip_led": "40.000 giờ"}</t>
         </is>
       </c>
       <c r="J42" t="n">
@@ -20130,7 +20964,7 @@
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>{"cong_suat": "8 W/m, 8W/m", "anh_sang": "Trắng /Vàng/Trung tính, Trắng/Vàng/Trung tính", "kich_thuoc": "D14mmx100m", "cat_doan": "20cm", "vat_lieu": "Nhựa slicon chống cháy", "thuong_hieu": "TLC LIGHTING", "dong_goi": "100m/cuộn", "bao_hanh": "24 tháng", "so_luong_chip_led": "120 LED/m", "so_m_nguon": "20m/ nguồn", "bao_hanh_tai_nha": "24 tháng"}</t>
+          <t>{"cong_suat": "8 W/m", "anh_sang": "Trắng /Vàng/Trung tính", "kich_thuoc": "D14mmx100m", "cat_doan": "20cm", "vat_lieu": "Nhựa slicon chống cháy", "thuong_hieu": "TLC LIGHTING", "dong_goi": "100m/cuộn", "bao_hanh": "24 tháng", "so_luong_chip_LED": "120 LED/m", "so_m_nguon": "20m/ nguồn", "bao_hanh_tai_nha": "24 tháng"}</t>
         </is>
       </c>
       <c r="J3" t="n">
@@ -20217,7 +21051,7 @@
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>{"cong_suat": "12W/m", "anh_sang": "Nhiều màu", "hieu_suat_quang": "110-120 Lm/w", "dien_ap": "85-265V", "thuong_hieu": "TLC LIGHTING", "tuoi_tho": "40.000h", "bao_hanh": "24 tháng", "chi_so_hoan_mau": "Ra &gt; 80", "chip_led": "2835 siêu sáng"}</t>
+          <t>{"cong_suat": "12W/m, 8w/m", "hieu_suat_quang": "110-120 Lm/w", "dien_ap": "85-265V", "thuong_hieu": "TLC LIGHTING", "tuoi_tho": "40.000h", "bao_hanh": "24 tháng, 12 tháng theo mét", "anh_sang": "Nhiều màu, trắng, vàng, trung tính", "chip_led": "2835 siêu sáng", "chi_so_hoan_mau": "Ra &gt; 80, Ra &gt; 85", "so_luong_bong_led": "156 bóng LED/ m"}</t>
         </is>
       </c>
       <c r="J4" t="n">
@@ -20292,7 +21126,7 @@
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>{"cong_suat": "12W/m", "anh_sang": "Trắng/Vàng/Xanh dương", "hieu_suat_quang": "110-120 Lm/w", "dien_ap": "85-265V", "thuong_hieu": "TLC LIGHTING", "tuoi_tho": "40.000h", "bao_hanh": "24 tháng", "quang_thong": "435Lm", "chi_so_hoan_mau": "Ra &gt; 80", "chip_led": "2835 siêu sáng"}</t>
+          <t>{"cong_suat": "12W/m", "anh_sang": "Trắng/Vàng/Xanh dương", "hieu_suat_quang": "110-120 Lm/w", "dien_ap": "85-265V", "thuong_hieu": "TLC LIGHTING", "tuoi_tho": "40.000h", "bao_hanh": "24 tháng", "quang_thong": "435Lm", "chi_so_hoan_mau": "Ra &gt; 80", "chip_LED": "2835 siêu sáng"}</t>
         </is>
       </c>
       <c r="J5" t="n">
@@ -20456,7 +21290,7 @@
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>{"cong_suat": "6 W/m", "anh_sang": "Đơn sắc", "chieu_dai": "100m", "hieu_suat_quang": "90 Lm/w", "dien_ap": "85-265V", "thuong_hieu": "TLC LIGHTING", "tuoi_tho": "40.000h", "bao_hanh": "24 tháng", "chi_so_hoan_mau": "Ra &gt; 80", "chip_led": "2835", "bao_hanh_tai_nha": "24 tháng"}</t>
+          <t>{"cong_suat": "6 W/m", "anh_sang": "Đơn sắc", "chieu_dai": "100m", "hieu_suat_quang": "90 Lm/w", "dien_ap": "85-265V", "thuong_hieu": "TLC LIGHTING", "tuoi_tho": "40.000h", "bao_hanh": "24 tháng", "chi_so_hoan_mau": "Ra &gt; 80", "chip_led": "2835"}</t>
         </is>
       </c>
       <c r="J7" t="n">
@@ -20540,7 +21374,7 @@
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>{"cong_suat": "12W/m", "hieu_suat_quang": "110-120 Lm/w", "dien_ap": "85-265V", "thuong_hieu": "TLC LIGHTING", "tuoi_tho": "40.000h", "bao_hanh": "24 tháng", "anh_sang": "Nhiều màu", "chi_so_hoan_mau": "Ra &gt; 80", "chip_LED": "5730 siêu sáng", "chip_led_so_luong": "180 chip LED/ mét dây"}</t>
+          <t>{"cong_suat": "12W/m", "hieu_suat_quang": "110-120 Lm/w", "dien_ap": "85-265V", "thuong_hieu": "TLC LIGHTING", "tuoi_tho": "40.000h", "bao_hanh": "24 tháng", "chi_so_hoan_mau": "Ra &gt; 80", "anh_sang": "Nhiều màu", "chip_led": "5730 siêu sáng"}</t>
         </is>
       </c>
       <c r="J8" t="n">
@@ -20686,7 +21520,7 @@
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>{"cong_suat": "14 W/m", "anh_sang": "Trắng /Vàng", "chieu_dai": "100m", "hieu_suat_quang": "78 Lm/w", "dien_ap": "85-265V", "thuong_hieu": "TLC LIGHTING", "chi_so_hoan_mau": "Ra=70", "bao_hanh": "24 tháng", "so_luong_chip_LED": "120x2", "bao_hanh_tai_nha": "24 tháng"}</t>
+          <t>{"cong_suat": "14 W/m", "anh_sang": "Trắng /Vàng", "chieu_dai": "100m", "hieu_suat_quang": "78 Lm/w", "dien_ap": "85-265V", "thuong_hieu": "TLC LIGHTING", "chi_so_hoan_mau": "Ra=70", "bao_hanh": "24 tháng", "so_luong_chip_LED": "120×2", "bao_hanh_tai_nha": "24 tháng"}</t>
         </is>
       </c>
       <c r="J10" t="n">
@@ -20909,7 +21743,7 @@
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>{"cong_suat": "14W", "anh_sang": "Ba màu", "quang_thong": "1050Lm", "kich_thuoc": "90×210", "chi_so_hoan_mau": "CRI&gt;80", "hoa_tiet": "Cá Chép Hóa Rồng", "thuong_hieu": "TLC LIGHTING", "tuoi_tho": "40.000h, 40.000 giờ", "bao_hanh": "24 tháng, 2 năm", "dien_ap_ac": "85-265V", "do_hoan_mau": "&gt;80Ra", "chieu_day": "37mm", "chat_lieu": "Acrylic, hợp kim nhôm sơn tĩnh điện"}</t>
+          <t>{"cong_suat": "14W", "anh_sang": "Ba màu", "quang_thong": "1050Lm", "kich_thuoc": "90×210", "chi_so_hoan_mau": "CRI&gt;80", "hoa_tiet": "Cá Chép Hóa Rồng", "thuong_hieu": "TLC LIGHTING", "tuoi_tho": "40.000h", "bao_hanh": "24 tháng", "dien_ap_ac": "85-265V", "do_hoan_mau": "&gt;80Ra", "chieu_day": "37mm", "chat_lieu": "Acrylic, hợp kim nhôm sơn tĩnh điện", "tuoi_tho_gio": "40.000 giờ", "bao_hanh_nam": "2 năm"}</t>
         </is>
       </c>
       <c r="J2" t="n">
@@ -21002,7 +21836,7 @@
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>{"cong_suat": "14W", "anh_sang": "Đơn sắc( Vàng)", "quang_thong": "1050Lm", "kich_thuoc": "90×210", "chi_so_hoan_mau": "CRI&gt;80", "hoa_tiet": "Cá Chép Hóa Rồng", "thuong_hieu": "TLC LIGHTING", "tuoi_tho": "40.000h", "bao_hanh": "24 tháng", "dien_ap_ac": "85-265V", "do_hoan_mau": "&gt;80Ra", "chieu_day": "37mm", "chat_lieu": "Acrylic, hợp kim nhôm sơn tĩnh điện"}</t>
+          <t>{"cong_suat": "14W", "anh_sang": "Đơn sắc( Vàng)", "quang_thong": "1050Lm", "kich_thuoc": "90×210", "chi_so_hoan_mau": "CRI&gt;80", "hoa_tiet": "Cá Chép Hóa Rồng", "thuong_hieu": "TLC LIGHTING", "tuoi_tho": "40.000h, 40.000 giờ", "bao_hanh": "24 tháng, 2 năm", "dien_ap_ac": "85-265V", "chieu_day": "37mm", "chat_lieu": "Acrylic, hợp kim nhôm sơn tĩnh điện"}</t>
         </is>
       </c>
       <c r="J3" t="n">
@@ -21095,7 +21929,7 @@
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>{"cong_suat": "14W", "anh_sang": "Ba màu", "quang_thong": "1050Lm", "kich_thuoc": "90×210", "chi_so_hoan_mau": "CRI&gt;80", "hoa_tiet": "Chùa một cột", "thuong_hieu": "TLC LIGHTING", "tuoi_tho": "40.000h, 40.000 giờ", "bao_hanh": "24 tháng, 2 năm", "dien_ap_ac": "85-265V", "do_hoan_mau": "&gt;80Ra", "chat_lieu": "Acrylic, hợp kim nhôm sơn tĩnh điện"}</t>
+          <t>{"cong_suat": "14W", "anh_sang": "Ba màu", "quang_thong": "1050Lm", "kich_thuoc": "90×210", "chi_so_hoan_mau": "CRI&gt;80", "hoa_tiet": "Chùa một cột", "thuong_hieu": "TLC LIGHTING", "tuoi_tho": "40.000h", "bao_hanh": "24 tháng", "dien_ap_ac": "85-265V", "do_hoan_mau": "&gt;80Ra", "chat_lieu": "Acrylic, hợp kim nhôm sơn tĩnh điện", "tuoi_tho_gio": "40.000 giờ", "bao_hanh_nam": "2 năm"}</t>
         </is>
       </c>
       <c r="J4" t="n">
@@ -21281,7 +22115,7 @@
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>{"cong_suat": "14W", "anh_sang": "Ba màu", "dien_ap": "85-265V", "do_hoan_mau": "&gt;80Ra", "chieu_day": "37mm", "chat_lieu": "Acrylic, hợp kim nhôm sơn tĩnh điện", "tuoi_tho": "40.000 giờ", "bao_hanh": "2 năm"}</t>
+          <t>{"cong_suat": "14W", "anh_sang": "Ba màu", "quang_thong": "1050Lm", "kich_thuoc": "90×210", "chi_so_hoan_mau": "CRI&gt;80", "hoa_tiet": "Cột cờ Hà Nội", "thuong_hieu": "TLC LIGHTING", "tuoi_tho": "40.000h, 40.000 giờ", "bao_hanh": "24 tháng, 2 năm", "dien_ap_ac": "85-265V", "do_hoan_mau": "&gt;80Ra", "chieu_day": "37mm", "chat_lieu": "Acrylic, hợp kim nhôm sơn tĩnh điện"}</t>
         </is>
       </c>
       <c r="J6" t="n">
@@ -21373,7 +22207,7 @@
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>{"cong_suat": "14W", "anh_sang": "Đơn sắc( Vàng)", "quang_thong": "1050Lm", "kich_thuoc": "90×210", "chi_so_hoan_mau": "CRI&gt;80", "hoa_tiet": "Cột cờ Hà Nội", "thuong_hieu": "TLC LIGHTING", "tuoi_tho": "40.000h", "bao_hanh": "24 tháng", "dien_ap_AC": "85-265V", "do_hoan_mau": "&gt;80Ra", "chieu_day": "37mm", "chat_lieu": "Acrylic, hợp kim nhôm sơn tĩnh điện", "tuoi_tho_gio": "40.000 giờ", "bao_hanh_nam": "2 năm"}</t>
+          <t>{"cong_suat": "14W", "anh_sang": "Đơn sắc( Vàng)", "quang_thong": "1050Lm", "kich_thuoc": "90×210", "chi_so_hoan_mau": "CRI&gt;80", "hoa_tiet": "Cột cờ Hà Nội", "thuong_hieu": "TLC LIGHTING", "tuoi_tho": "40.000h", "bao_hanh": "24 tháng", "dien_ap_(AC)": "85-265V", "do_hoan_mau": "&gt;80Ra", "chieu_day": "37mm", "chat_lieu": "Acrylic, hợp kim nhôm sơn tĩnh điện"}</t>
         </is>
       </c>
       <c r="J7" t="n">
@@ -21465,7 +22299,7 @@
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>{"cong_suat": "14W", "anh_sang": "Ba màu", "quang_thong": "1050Lm", "kich_thuoc": "90×210", "chi_so_hoan_mau": "CRI&gt;80", "hoa_tiet": "Hoa sen", "thuong_hieu": "TLC LIGHTING", "tuoi_tho": "40.000h", "bao_hanh": "24 tháng", "dien_ap_ac": "85-265V", "do_hoan_mau": "&gt;80Ra", "chieu_day": "37mm", "chat_lieu": "Acrylic, hợp kim nhôm sơn tĩnh điện"}</t>
+          <t>{"cong_suat": "14W", "anh_sang": "Ba màu", "quang_thong": "1050Lm", "kich_thuoc": "90×210", "chi_so_hoan_mau": "CRI&gt;80", "hoa_tiet": "Hoa sen", "thuong_hieu": "TLC LIGHTING", "tuoi_tho": "40.000h, 40.000 giờ", "bao_hanh": "24 tháng, 2 năm", "dien_ap_ac": "85-265V", "do_hoan_mau": "&gt;80Ra", "chieu_day": "37mm", "chat_lieu": "Acrylic, hợp kim nhôm sơn tĩnh điện"}</t>
         </is>
       </c>
       <c r="J8" t="n">
@@ -21557,7 +22391,7 @@
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>{"cong_suat": "14W", "anh_sang": "Đơn sắc( Vàng), Ba màu, Xanh dương", "quang_thong": "1050Lm", "kich_thuoc": "90×210", "chi_so_hoan_mau": "CRI&gt;80", "hoa_tiet": "Hoa sen", "thuong_hieu": "TLC LIGHTING", "tuoi_tho": "40.000h, 40.000 giờ", "bao_hanh": "24 tháng, 2 năm", "dien_ap_ac": "85-265V", "do_hoan_mau": "&gt;80Ra", "chieu_day": "37mm", "chat_lieu": "Acrylic, hợp kim nhôm sơn tĩnh điện"}</t>
+          <t>{"cong_suat": "14W", "anh_sang": "Đơn sắc( Vàng), Ba màu, Xanh dương", "quang_thong": "1050Lm", "kich_thuoc": "90×210, 90x210mm", "chi_so_hoan_mau": "CRI&gt;80", "hoa_tiet": "Hoa sen", "thuong_hieu": "TLC LIGHTING", "tuoi_tho": "40.000h, 40.000 giờ", "bao_hanh": "24 tháng, 2 năm", "dien_ap_ac": "85-265V", "do_hoan_mau": "&gt;80Ra", "chieu_day": "37mm", "chat_lieu": "Acrylic, hợp kim nhôm sơn tĩnh điện"}</t>
         </is>
       </c>
       <c r="J9" t="n">
@@ -21649,7 +22483,7 @@
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>{"cong_suat": "14W", "anh_sang": "Ba màu", "quang_thong": "1050Lm", "kich_thuoc": "90×210", "chi_so_hoan_mau": "CRI&gt;80", "hoa_tiet": "Chợ Bến Thành", "thuong_hieu": "TLC LIGHTING", "tuoi_tho": "40.000h", "bao_hanh": "24 tháng", "dien_ap_AC": "85-265V", "do_hoan_mau": "&gt;80Ra", "chieu_day": "37mm", "chat_lieu": "Acrylic, hợp kim nhôm sơn tĩnh điện"}</t>
+          <t>{"cong_suat": "14W", "anh_sang": "Ba màu", "quang_thong": "1050Lm", "kich_thuoc": "90×210", "chi_so_hoan_mau": "CRI&gt;80", "hoa_tiet": "Chợ Bến Thành", "thuong_hieu": "TLC LIGHTING", "tuoi_tho": "40.000h", "bao_hanh": "24 tháng", "dien_ap_ac": "85-265V", "do_hoan_mau": "&gt;80Ra", "chieu_day": "37mm", "chat_lieu": "Acrylic, hợp kim nhôm sơn tĩnh điện"}</t>
         </is>
       </c>
       <c r="J10" t="n">
@@ -21733,7 +22567,7 @@
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>{"cong_suat": "14W", "anh_sang": "Đơn sắc", "quang_thong": "1050Lm", "kich_thuoc": "90×210", "chi_so_hoan_mau": "CRI&gt;80", "hoa_tiet": "Chợ Bến Thành", "thuong_hieu": "TLC LIGHTING", "tuoi_tho": "40.000h", "bao_hanh": "24 tháng", "dien_ap": "85-265V", "do_hoan_mau": "&gt;80Ra", "chieu_day": "37mm", "chat_lieu": "Acrylic, hợp kim nhôm sơn tĩnh điện", "tuoi_tho_gio": "40.000 giờ"}</t>
+          <t>{"cong_suat": "14W", "anh_sang": "Đơn sắc", "quang_thong": "1050Lm", "kich_thuoc": "90×210", "chi_so_hoan_mau": "CRI&gt;80", "hoa_tiet": "Chợ Bến Thành", "thuong_hieu": "TLC LIGHTING", "tuoi_tho": "40.000h", "bao_hanh": "24 tháng", "dien_ap_ac": "85-265V", "do_hoan_mau": "&gt;80Ra", "chieu_day": "37mm", "chat_lieu": "Acrylic, hợp kim nhôm sơn tĩnh điện"}</t>
         </is>
       </c>
       <c r="J11" t="n">
@@ -21815,7 +22649,7 @@
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>{"cong_suat": "14W", "anh_sang": "Đơn sắc", "dien_ap": "85-265V", "do_hoan_mau": "&gt;80Ra", "chieu_day": "37mm", "chat_lieu": "Acrylic, hợp kim nhôm sơn tĩnh điện", "tuoi_tho": "40.000 giờ", "bao_hanh": "24 tháng"}</t>
+          <t>{"cong_suat": "14W", "anh_sang": "Đơn sắc", "quang_thong": "1050Lm", "kich_thuoc": "90×210", "chi_so_hoan_mau": "CRI&gt;80", "hoa_tiet": "Chùa Một Cột", "thuong_hieu": "TLC LIGHTING", "tuoi_tho": "40.000h", "bao_hanh": "24 tháng", "dien_ap_ac": "85-265V", "do_hoan_mau": "&gt;80Ra", "chieu_day": "37mm", "chat_lieu": "Acrylic, hợp kim nhôm sơn tĩnh điện"}</t>
         </is>
       </c>
       <c r="J12" t="n">
@@ -22068,7 +22902,7 @@
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>{"cong_suat": "14W", "anh_sang": "Ba màu", "quang_thong": "1050Lm", "kich_thuoc": "90×210", "chi_so_hoan_mau": "CRI&gt;80", "hoa_tiet": "Chợ Bến Thành", "thuong_hieu": "TLC LIGHTING", "tuoi_tho": "40.000h", "bao_hanh": "24 tháng", "dien_ap_ac": "85-265V", "do_hoan_mau": "&gt;80Ra", "chat_lieu": "Acrylic, hợp kim nhôm sơn tĩnh điện"}</t>
+          <t>{"cong_suat": "14W", "anh_sang": "Ba màu", "quang_thong": "1050Lm", "kich_thuoc": "90×210", "chi_so_hoan_mau": "CRI&gt;80", "hoa_tiet": "Chợ Bến Thành", "thuong_hieu": "TLC LIGHTING", "tuoi_tho": "40.000h", "bao_hanh": "24 tháng", "dien_ap_ac": "85-265V", "do_hoan_mau": "&gt;80Ra", "chat_lieu": "Acrylic, hợp kim nhôm sơn tĩnh điện", "tuoi_tho_": "40.000 giờ"}</t>
         </is>
       </c>
       <c r="J15" t="n">
@@ -22155,7 +22989,7 @@
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>{"cong_suat": "14W", "anh_sang": "Đơn sắc( Vàng)", "quang_thong": "1050Lm", "kich_thuoc": "90×210", "chi_so_hoan_mau": "CRI&gt;80", "hoa_tiet": "Chợ Bến Thành", "thuong_hieu": "TLC LIGHTING", "tuoi_tho": "40.000h", "bao_hanh": "24 tháng", "dien_ap_ac": "85-265V", "do_hoan_mau": "&gt;80Ra", "chat_lieu": "Acrylic, hợp kim nhôm sơn tĩnh điện"}</t>
+          <t>{"cong_suat": "14W", "anh_sang": "Đơn sắc( Vàng)", "quang_thong": "1050Lm", "kich_thuoc": "90×210", "chi_so_hoan_mau": "CRI&gt;80", "hoa_tiet": "Chợ Bến Thành", "thuong_hieu": "TLC LIGHTING", "tuoi_tho": "40.000h, 40.000 giờ", "bao_hanh": "24 tháng, 2 năm", "dien_ap_ac": "85-265V", "do_hoan_mau": "&gt;80Ra", "chat_lieu": "Acrylic, hợp kim nhôm sơn tĩnh điện"}</t>
         </is>
       </c>
       <c r="J16" t="n">
@@ -22247,7 +23081,7 @@
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>{"cong_suat": "14W", "anh_sang": "Đơn sắc", "quang_thong": "1050Lm", "kich_thuoc": "90×210", "chi_so_hoan_mau": "CRI&gt;80", "hoa_tiet": "Hoa sen", "thuong_hieu": "TLC LIGHTING", "tuoi_tho": "40.000 giờ", "bao_hanh": "24 tháng", "dien_ap_ac": "85-265V", "do_hoan_mau": "&gt;80Ra", "chieu_day": "37mm", "chat_lieu": "Acrylic, hợp kim nhôm sơn tĩnh điện"}</t>
+          <t>{"cong_suat": "14W", "anh_sang": "Đơn sắc", "quang_thong": "1050Lm", "kich_thuoc": "90×210", "chi_so_hoan_mau": "CRI&gt;80", "hoa_tiet": "Hoa sen", "thuong_hieu": "TLC LIGHTING", "tuoi_tho": "40.000h", "bao_hanh": "24 tháng", "dien_ap_AC": "85-265V", "do_hoan_mau": "&gt;80Ra", "chieu_day": "37mm", "chat_lieu": "Acrylic, hợp kim nhôm sơn tĩnh điện"}</t>
         </is>
       </c>
       <c r="J17" t="n">
@@ -22287,8 +23121,7 @@
       </c>
       <c r="T17" t="inlineStr">
         <is>
-          <t>4.Ưu điểm và ứng dụng đèn tường trang trí trong không gian
-Đèn LED trang trí gắn tường hai đầu hoạ tiết Hoa sen là một sản phẩm có khả năng tiêu thụ điện thấp và tiết kiệm năng lượng tối ưu.
+          <t>Đèn LED trang trí gắn tường hai đầu hoạ tiết Hoa sen là một sản phẩm có khả năng tiêu thụ điện thấp và tiết kiệm năng lượng tối ưu.
 Đèn phát ánh sáng chân thực, tự nhiên nhờ sử dụng công nghệ LED hiện đại, không gây hại cho mắt, không phát ra tia cực tím.
 Mắt LED được kết nối với nhau trên bản mạch, có khả năng tỏa nhiệt trực tiếp giúp đèn không bị nóng, tăng tuổi thọ chiếu sáng cho toàn bộ chiếc đèn.
 Đèn tường trang trí hai đầu TLC LIGHTING
@@ -22324,7 +23157,7 @@
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>{"cong_suat": "6W", "anh_sang": "Vàng", "nhiet_do_mau": "3500K/6500K", "kich_thuoc": "200x75x90", "hieu_suat_quang": "110-120 Lm/w", "chi_so_hoan_mau": "CRI≥85", "dien_ap": "85-265V", "thuong_hieu": "TLC LIGHTING", "tuoi_tho": "40.000h", "bao_hanh": "24 tháng", "quang_thong": "480 Lm", "do_hoan_mau": "&gt;85", "dien_ap_ac": "85-265V", "tuoi_tho_chip_led": "40.000 giờ"}</t>
+          <t>{"cong_suat": "6W", "anh_sang": "Vàng", "nhiet_do_mau": "3500K/6500K", "kich_thuoc": "200x75x90", "hieu_suat_quang": "110-120 Lm/w", "chi_so_hoan_mau": "CRI≥85", "dien_ap": "85-265V", "thuong_hieu": "TLC LIGHTING", "tuoi_tho": "40.000h", "bao_hanh": "24 tháng", "quang_thong": "480 Lm", "do_hoan_mau": "&gt;85", "dien_ap_ac": "85-265V"}</t>
         </is>
       </c>
       <c r="J18" t="n">
@@ -22485,7 +23318,7 @@
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t>{"cong_suat": "12W", "anh_sang": "Vàng", "nhiet_do_mau": "3500K/6500K", "kich_thuoc": "240x170x90", "hieu_suat_quang": "110-120 Lm/w", "chi_so_hoan_mau": "CRI≥85", "dien_ap": "85-265V", "thuong_hieu": "TLC LIGHTING", "tuoi_tho": "40.000h", "bao_hanh": "24 tháng", "quang_thong": "480 Lm", "do_hoan_mau": "&gt;85", "dien_ap_ac": "85-265V", "tuoi_tho_chip_led": "40.000 giờ", "chip_led": "SMD", "hieu_suat_phat_quang": "80 -100 Lm/w", "chi_so_hoan_mau_ra": "&gt; 85"}</t>
+          <t>{"cong_suat": "12W", "anh_sang": "Vàng", "nhiet_do_mau": "3500K/6500K", "kich_thuoc": "240x170x90", "hieu_suat_quang": "110-120 Lm/w", "chi_so_hoan_mau": "CRI≥85", "dien_ap": "85-265V", "thuong_hieu": "TLC LIGHTING", "tuoi_tho": "40.000h", "bao_hanh": "24 tháng", "quang_thong": "480 Lm", "do_hoan_mau": "&gt;85", "dien_ap_ac": "85-265V", "tuoi_tho_chip_led": "40.000 giờ"}</t>
         </is>
       </c>
       <c r="J20" t="n">
@@ -22577,7 +23410,7 @@
       </c>
       <c r="I21" t="inlineStr">
         <is>
-          <t>{"cong_suat": "12W", "anh_sang": "Vàng", "nhiet_do_mau": "3500K/6500K", "kich_thuoc": "240x170x90", "hieu_suat_quang": "110-120 Lm/w", "chi_so_hoan_mau": "CRI≥85", "dien_ap": "85-265V", "thuong_hieu": "TLC LIGHTING", "tuoi_tho": "40.000h", "bao_hanh": "24 tháng"}</t>
+          <t>{"cong_suat": "12W", "anh_sang": "Vàng", "nhiet_do_mau": "3500K/6500K", "kich_thuoc": "240x170x90", "hieu_suat_quang": "110-120 Lm/w", "chi_so_hoan_mau": "CRI≥85", "dien_ap": "85-265V", "thuong_hieu": "TLC LIGHTING", "tuoi_tho": "40.000h", "bao_hanh": "24 tháng", "quang_thong": "480 Lm", "do_hoan_mau": "&gt;85", "dien_ap_AC": "85-265V", "tuoi_tho_chip_LED": "40.000 giờ"}</t>
         </is>
       </c>
       <c r="J21" t="n">
@@ -22877,8 +23710,7 @@
       </c>
       <c r="T24" t="inlineStr">
         <is>
-          <t>4.Ưu điểm và ứng dụng
-Đèn LED trang trí gắn tường hai đầu hoạ tiết Cột cờ Hà Nội là một sản phẩm có khả năng tiêu thụ điện thấp và tiết kiệm năng lượng tối ưu.
+          <t>Đèn LED trang trí gắn tường hai đầu hoạ tiết Cột cờ Hà Nội là một sản phẩm có khả năng tiêu thụ điện thấp và tiết kiệm năng lượng tối ưu.
 Đèn phát ánh sáng chân thực, tự nhiên nhờ sử dụng công nghệ LED hiện đại, không gây hại cho mắt, không phát ra tia cực tím.
 Mắt LED được kết nối với nhau trên bản mạch, có khả năng tỏa nhiệt trực tiếp giúp đèn không bị nóng, tăng tuổi thọ chiếu sáng cho toàn bộ chiếc đèn.
 Với cấu tạo đặc biệt, nhỏ gọn cùng sự đa dạng về màu sắc và kích thước, đèn trang trí hai đầu họa tiết hoa Sen được ứng dụng trang trí nhiều ở các khu trung tâm thương mại, các quán bar, các lễ hội lớn nhỏ…
@@ -22905,7 +23737,7 @@
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>TLC-DTT/TV-CCHN-14W</t>
+          <t>TLC-DTT/TV-CCHN-14W-02</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
@@ -22915,7 +23747,7 @@
       </c>
       <c r="I25" t="inlineStr">
         <is>
-          <t>{"cong_suat": "14W", "anh_sang": "Đơn sắc", "quang_thong": "1050Lm", "kich_thuoc": "90×210", "chi_so_hoan_mau": "CRI&gt;80", "hoa_tiet": "Cột Cờ Hà Nội", "thuong_hieu": "TLC LIGHTING", "tuoi_tho": "40.000h, 40.000 giờ", "bao_hanh": "24 tháng", "dien_ap_ac": "85-265V", "do_hoan_mau": "&gt;80Ra", "chieu_day": "37mm", "chat_lieu": "Acrylic, hợp kim nhôm sơn tĩnh điện"}</t>
+          <t>{"cong_suat": "14W", "anh_sang": "Đơn sắc", "quang_thong": "1050Lm", "kich_thuoc": "90×210", "chi_so_hoan_mau": "CRI&gt;80", "hoa_tiet": "Cột Cờ Hà Nội", "thuong_hieu": "TLC LIGHTING", "tuoi_tho": "40.000h", "bao_hanh": "24 tháng", "dien_ap_AC": "85-265V", "do_hoan_mau": "&gt;80Ra", "chieu_day": "37mm", "chat_lieu": "Acrylic, hợp kim nhôm sơn tĩnh điện", "tuoi_tho_gio": "40.000 giờ"}</t>
         </is>
       </c>
       <c r="J25" t="n">
@@ -22955,8 +23787,7 @@
       </c>
       <c r="T25" t="inlineStr">
         <is>
-          <t>4.Ưu điểm và ứng dụng
-Đèn LED trang trí gắn tường hai đầu hoạ tiết Cột cờ Hà Nội là một sản phẩm có khả năng tiêu thụ điện thấp và tiết kiệm năng lượng tối ưu.
+          <t>Đèn LED trang trí gắn tường hai đầu hoạ tiết Cột cờ Hà Nội là một sản phẩm có khả năng tiêu thụ điện thấp và tiết kiệm năng lượng tối ưu.
 Đèn phát ánh sáng chân thực, tự nhiên nhờ sử dụng công nghệ LED hiện đại, không gây hại cho mắt, không phát ra tia cực tím.
 Mắt LED được kết nối với nhau trên bản mạch, có khả năng tỏa nhiệt trực tiếp giúp đèn không bị nóng, tăng tuổi thọ chiếu sáng cho toàn bộ chiếc đèn.
 Với cấu tạo đặc biệt, nhỏ gọn cùng sự đa dạng về màu sắc và kích thước, đèn trang trí hai đầu họa tiết hoa Sen được ứng dụng trang trí nhiều ở các khu trung tâm thương mại, các quán bar, các lễ hội lớn nhỏ…
@@ -22992,7 +23823,7 @@
       </c>
       <c r="I26" t="inlineStr">
         <is>
-          <t>{"cong_suat": "14W", "anh_sang": "Ba màu", "quang_thong": "1050Lm", "kich_thuoc": "90×210", "chi_so_hoan_mau": "CRI&gt;80", "hoa_tiet": "Hoa sen", "thuong_hieu": "TLC LIGHTING", "tuoi_tho": "40.000h", "bao_hanh": "24 tháng", "dien_ap_ac": "85-265V", "do_hoan_mau": "&gt;80Ra", "chieu_day": "37mm", "chat_lieu": "Acrylic, hợp kim nhôm sơn tĩnh điện", "tuoi_tho_don_vi": "40.000 giờ"}</t>
+          <t>{"cong_suat": "14W", "anh_sang": "Ba màu", "quang_thong": "1050Lm", "kich_thuoc": "90×210", "chi_so_hoan_mau": "CRI&gt;80", "hoa_tiet": "Hoa sen", "thuong_hieu": "TLC LIGHTING", "tuoi_tho": "40.000h", "bao_hanh": "24 tháng", "dien_ap_ac": "85-265V", "do_hoan_mau": "&gt;80Ra", "chieu_day": "37mm", "chat_lieu": "Acrylic, hợp kim nhôm sơn tĩnh điện"}</t>
         </is>
       </c>
       <c r="J26" t="n">
@@ -23006,14 +23837,6 @@
       <c r="M26" t="inlineStr">
         <is>
           <t>https://tlclighting.com.vn/wp-content/uploads/2021/12/HS1.png</t>
-        </is>
-      </c>
-      <c r="P26" t="inlineStr">
-        <is>
-          <t>Đèn phát ánh sáng chân thực, tự nhiên nhờ sử dụng công nghệ LED hiện đại, không gây hại cho mắt, không phát ra tia cực tím.
-Mắt LED được kết nối với nhau trên bản mạch, có khả năng tỏa nhiệt trực tiếp giúp đèn không bị nóng, tăng tuổi thọ chiếu sáng cho toàn bộ chiếc đèn. Đèn tường trang trí hai đầu TLC LIGHTING
-Với cấu tạo đặc biệt, nhỏ gọn cùng sự đa dạng về màu sắc và kích thước, đèn trang trí hai đầu họa tiết hoa Sen được ứng dụng trang trí nhiều ở các khu trung tâm thương mại, các quán bar, các lễ hội lớn nhỏ…
-Thân thiện với môi trường và an toàn cho người sử dụng.</t>
         </is>
       </c>
       <c r="Q26" t="inlineStr">
@@ -23030,18 +23853,6 @@
 Bảo hành: 24 tháng</t>
         </is>
       </c>
-      <c r="T26" t="inlineStr">
-        <is>
-          <t>4.Ưu điểm và ứng dụng đèn tường trang trí trong không gian
-Đèn LED trang trí gắn tường hai đầu hoạ tiết Hoa sen là một sản phẩm có khả năng tiêu thụ điện thấp và tiết kiệm năng lượng tối ưu.
-Đèn phát ánh sáng chân thực, tự nhiên nhờ sử dụng công nghệ LED hiện đại, không gây hại cho mắt, không phát ra tia cực tím.
-Mắt LED được kết nối với nhau trên bản mạch, có khả năng tỏa nhiệt trực tiếp giúp đèn không bị nóng, tăng tuổi thọ chiếu sáng cho toàn bộ chiếc đèn.
-Đèn tường trang trí hai đầu TLC LIGHTING
-Với cấu tạo đặc biệt, nhỏ gọn cùng sự đa dạng về màu sắc và kích thước, đèn trang trí hai đầu họa tiết hoa Sen được ứng dụng trang trí nhiều ở các khu trung tâm thương mại, các quán bar, các lễ hội lớn nhỏ…
-Thân thiện với môi trường và an toàn cho người sử dụng.
-Để lựa chọn một mẫu đèn trang trí có chất lượng tốt và tính thẩm mỹ cao thì đèn LED họa tiết hoa Sen thực sự là một “cực phẩm” hoàn hảo cho không gian của bạn. Quý khách có thể tìm thấy sản phẩm của chúng tôi tại 5600 đại lý của TLC LIGHTING tại 64 tỉnh thành. Vui lòng liên hệ hotline 18006921 để được hướng dẫn và tư vấn mua hàng chính hãng trên hệ thống cửa hàng trên toàn quốc.</t>
-        </is>
-      </c>
     </row>
     <row r="27">
       <c r="A27" t="n">
@@ -23069,7 +23880,7 @@
       </c>
       <c r="I27" t="inlineStr">
         <is>
-          <t>{"cong_suat": "14W", "anh_sang": "Ba màu", "quang_thong": "1050Lm", "kich_thuoc": "90×210", "chi_so_hoan_mau": "CRI&gt;80", "hoa_tiet": "Cá chép hóa rồng", "thuong_hieu": "TLC LIGHTING", "tuoi_tho": "40.000h", "bao_hanh": "24 tháng", "dien_ap_ac": "85-265V", "do_hoan_mau": "&gt;80Ra", "chieu_day": "37mm", "chat_lieu": "Acrylic, hợp kim nhôm sơn tĩnh điện"}</t>
+          <t>{"cong_suat": "14W", "anh_sang": "Ba màu", "dien_ap": "85-265V", "do_hoan_mau": "&gt;80Ra", "chieu_day": "37mm", "chat_lieu": "Acrylic, hợp kim nhôm sơn tĩnh điện", "tuoi_tho": "40.000 giờ", "bao_hanh": "24 tháng", "hoa_tiet": "Cá chép hóa rồng", "thuong_hieu": "TLC LIGHTING", "kich_thuoc": "90×210", "quang_thong": "1050Lm"}</t>
         </is>
       </c>
       <c r="J27" t="n">
@@ -23143,7 +23954,7 @@
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>TLC-DTT/TV-CCHR-14W-02</t>
+          <t>TLC-DTT/TV-CCHR-14W</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
@@ -23406,7 +24217,7 @@
       </c>
       <c r="I31" t="inlineStr">
         <is>
-          <t>{"cong_suat": "6W", "anh_sang": "Vàng", "nhiet_do_mau": "3500K/6500K", "kich_thuoc": "90x40x110", "hieu_suat_quang": "110-120 Lm/w", "chi_so_hoan_mau": "CRI≥85", "dien_ap": "85-265V", "thuong_hieu": "TLC LIGHTING", "tuoi_tho": "40.000h", "bao_hanh": "24 tháng", "quang_thong": "480 Lm", "do_hoan_mau": "&gt;85", "dien_ap_ac": "85-265V", "tuoi_tho_chip_led": "40.000 giờ"}</t>
+          <t>{"cong_suat": "6W", "anh_sang": "Vàng", "nhiet_do_mau": "3500K/6500K", "kich_thuoc": "90x40x110", "hieu_suat_quang": "110-120 Lm/w, 110~120Lm/w", "chi_so_hoan_mau": "CRI≥85", "dien_ap": "85-265V", "thuong_hieu": "TLC LIGHTING", "tuoi_tho": "40.000h", "bao_hanh": "24 tháng", "quang_thong": "480 Lm", "do_hoan_mau": "&gt;85", "dien_ap_ac": "85-265V", "tuoi_tho_chip_led": "40.000 giờ"}</t>
         </is>
       </c>
       <c r="J31" t="n">
@@ -23483,7 +24294,7 @@
       </c>
       <c r="I32" t="inlineStr">
         <is>
-          <t>{"cong_suat": "12W", "anh_sang": "Vàng", "nhiet_do_mau": "3500K/6500K", "kich_thuoc": "170x40x90", "hieu_suat_quang": "110-120 Lm/w", "chi_so_hoan_mau": "CRI≥85", "dien_ap": "85-265V", "thuong_hieu": "TLC LIGHTING", "tuoi_tho": "40.000h", "bao_hanh": "24 tháng", "quang_thong": "480 Lm", "do_hoan_mau": "&gt;85", "dien_ap_ac": "85-265V", "tuoi_tho_chip_led": "40.000 giờ", "mau_sac_vo_den": "thân đen", "mau_sac_anh_sang": "Màu vàng", "ra": "&gt; 85", "tuoi_tho_gio_chieu_sang": "40.000 giờ chiếu sáng", "dien_ap_ac_v": "AC 85 – 265"}</t>
+          <t>{"cong_suat": "12W", "anh_sang": "Vàng", "nhiet_do_mau": "3500K/6500K", "kich_thuoc": "170x40x90", "hieu_suat_quang": "110-120 Lm/w", "chi_so_hoan_mau": "CRI≥85", "dien_ap": "85-265V", "thuong_hieu": "TLC LIGHTING", "tuoi_tho": "40.000h", "bao_hanh": "24 tháng", "quang_thong": "480 Lm", "do_hoan_mau": "&gt;85", "dien_ap_ac": "85-265V", "tuoi_tho_chip_led": "40.000 giờ", "ten_san_pham": "Đèn tường trang trí TL917 vỏ đen", "mau_sac_vo_den": "thân đen", "mau_sac_anh_sang": "Màu vàng", "tuoi_tho_gio_chieu_sang": "40.000 giờ chiếu sáng", "dien_ap_ac_v": "85 – 265"}</t>
         </is>
       </c>
       <c r="J32" t="n">
@@ -23573,7 +24384,7 @@
       </c>
       <c r="I33" t="inlineStr">
         <is>
-          <t>{"cong_suat": "12W", "anh_sang": "Vàng", "nhiet_do_mau": "3500K/6500K", "kich_thuoc": "170x40x90", "hieu_suat_quang": "110-120 Lm/w, 110~120Lm/w, 80-100 Lm/w", "chi_so_hoan_mau": "CRI≥85", "dien_ap": "85-265V", "thuong_hieu": "TLC LIGHTING", "tuoi_tho": "40.000h", "bao_hanh": "24 tháng", "quang_thong": "480 Lm", "do_hoan_mau": "&gt;85", "dien_ap_ac": "85-265V", "tuoi_tho_chip_led": "40.000 giờ"}</t>
+          <t>{"cong_suat": "12W", "anh_sang": "Vàng", "nhiet_do_mau": "3500K/6500K", "kich_thuoc": "170x40x90", "hieu_suat_quang": "110-120 Lm/w, 110~120Lm/w", "chi_so_hoan_mau": "CRI≥85", "dien_ap": "85-265V", "thuong_hieu": "TLC LIGHTING", "tuoi_tho": "40.000h", "bao_hanh": "24 tháng", "quang_thong": "480 Lm", "do_hoan_mau": "&gt;85", "dien_ap_ac": "85-265V", "tuoi_tho_chip_led": "40.000 giờ"}</t>
         </is>
       </c>
       <c r="J33" t="n">
@@ -23789,7 +24600,7 @@
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>{"cong_suat": "100W", "nhiet_do_mau": "6500K", "kich_thuoc": "Φ305*H115", "chip_led": "Sanan", "hieu_suat_quang": "~140 Lm/W", "chi_so_hoan_mau": "CRI &gt;70Ra", "dien_ap": "AC 100~277V", "thuong_hieu": "TLC LIGHTING", "bao_hanh": "2-5 năm", "vat_lieu": "Alu + PC", "kich_thuoc_den": "Φ305*H115", "chi_so_chong_am": "IP 65", "pf": "&gt;0.97", "nguon": "Philips hoặc tuỳ chỉnh theo yêu cầu"}</t>
+          <t>{"cong_suat": "100W", "nhiet_do_mau": "6500K", "kich_thuoc": "Φ305*H115", "chip_led": "Sanan", "hieu_suat_quang": "~140 Lm/W", "chi_so_hoan_mau": "CRI &gt;70Ra", "dien_ap": "AC 100~277V", "thuong_hieu": "TLC LIGHTING", "bao_hanh": "2-5 năm", "dien_ap_ac": "AC100~277V", "vat_lieu": "Alu + PC", "kich_thuoc_den": "Φ305*H115", "chi_so_chong_am": "IP 65", "pf": "&gt;0.97", "nguon": "Philips hoặc tuỳ chỉnh theo yêu cầu"}</t>
         </is>
       </c>
       <c r="L2" t="inlineStr">
@@ -23818,6 +24629,17 @@
 Bảo hành: 2-5 năm</t>
         </is>
       </c>
+      <c r="T2" t="inlineStr">
+        <is>
+          <t>Đặc điểm nổi bật của Đèn LED Highbay UFO TLC 100W
+Chip LED
+Đèn LED UFO TLC sử dụng chip LED với hiệu suất quang cao: ~140 Lm/W, ánh sáng phân bổ đều, tiết kiệm năng lượng, tăng hiệu suất làm việc cho khu vực sản xuất, lắp ráp, kho bãi
+Nguồn Đèn
+Đèn LED UFO nhà xưởng sử dụng nguồn Philips công suất lớn đảm bảo đèn hoạt động ổn định và bền bỉ trong môi trường khắc nhiệt của nhà máy, khu vực sản xuất và kho bãi với chỉ số PF &gt;0.9, đạt tiêu chuẩn chống sét 4kV.
+Tản nhiệt
+Được làm bằng vật liệu nhôm, công nghệ đúc nguyên khối, nhiều cánh tản nhiệt đan xen, đèn LED UFO TLC được thiết kế thông minh giúp tản nhiệt hiệu quả, giảm tác động của nhiệt đến các linh kiện điện tử khác, tăng tuổi thọ của đèn.</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -23840,7 +24662,7 @@
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>{"cong_suat": "100W", "nhiet_do_mau": "6500K", "kich_thuoc": "Φ305*H120", "chip_led": "Sanan", "hieu_suat_quang": "140 Lm/W", "chi_so_hoan_mau": "CRI &gt;70Ra", "dien_ap": "AC 100~277V", "thuong_hieu": "TLC LIGHTING", "bao_hanh": "2-5 năm", "vat_lieu": "Alu + PC", "kich_thuoc_den": "Φ355*H120", "chi_so_chong_am": "IP 65", "pf": "&gt;0.97", "nguon": "Philips hoặc tuỳ chỉnh theo yêu cầu"}</t>
+          <t>{"cong_suat": "150W", "nhiet_do_mau": "6500K", "kich_thuoc": "Φ305*H120, Φ355*H120", "chip_led": "Sanan", "hieu_suat_quang": "140 Lm/W, 145 Lm/W", "chi_so_hoan_mau": "CRI &gt;70Ra", "dien_ap": "AC 100~277V, AC100~277VAC", "thuong_hieu": "TLC LIGHTING", "bao_hanh": "2-5 năm", "vat_lieu": "Alu + PC", "chi_so_chong_am": "IP 65", "pf": "&gt;0.97, 0.9", "nguon": "Philips hoặc tuỳ chỉnh theo yêu cầu, Philips"}</t>
         </is>
       </c>
       <c r="L3" t="inlineStr">
@@ -23869,6 +24691,17 @@
 Bảo hành: 2-5 năm</t>
         </is>
       </c>
+      <c r="T3" t="inlineStr">
+        <is>
+          <t>Đặc điểm nổi bật của Đèn LED Highbay UFO TLC 150W
+Chip LED
+Đèn LED UFO TLC sử dụng chip LED với hiệu suất quang cao: 145 Lm/W, ánh sáng phân bổ đều, tiết kiệm năng lượng, tăng hiệu suất làm việc cho khu vực sản xuất, lắp ráp, kho bãi
+Nguồn Đèn
+Đèn LED UFO nhà xưởng sử dụng nguồn Philips công suất lớn đảm bảo đèn hoạt động ổn định và bền bỉ trong môi trường khắc nhiệt của nhà máy, khu vực sản xuất và kho bãi với chỉ số PF 0.9, đạt tiêu chuẩn chống sét 4kV.
+Tản nhiệt
+Được làm bằng vật liệu nhôm, công nghệ đúc nguyên khối, nhiều cánh tản nhiệt đan xen, đèn LED UFO TLC được thiết kế thông minh giúp tản nhiệt hiệu quả, giảm tác động của nhiệt đến các linh kiện điện tử khác, tăng tuổi thọ của đèn.</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -23891,7 +24724,7 @@
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>{"cong_suat": "200W", "nhiet_do_mau": "6500K", "kich_thuoc": "Φ382.3*H159.5mm", "chip_led": "Sanan", "hieu_suat_quang": "140 Lm/W", "chi_so_hoan_mau": "CRI &gt;70Ra", "dien_ap": "AC 100~277V", "thuong_hieu": "TLC LIGHTING", "bao_hanh": "2-5 năm", "dien_ap_ac": "AC100~277V", "vat_lieu": "Alu + PC", "kich_thuoc_den": "Φ382.3*H159.5mm", "chi_so_chong_am": "IP 65", "pf": "&gt;0.97", "nguon": "Philips hoặc tuỳ chỉnh theo yêu cầu"}</t>
+          <t>{"cong_suat": "200W", "nhiet_do_mau": "6500K", "kich_thuoc": "Φ382.3*H159.5mm", "chip_led": "Sanan", "hieu_suat_quang": "~140 Lm/W", "chi_so_hoan_mau": "CRI &gt;70Ra", "dien_ap": "AC 100~277V", "thuong_hieu": "TLC LIGHTING", "bao_hanh": "2-5 năm", "vat_lieu": "Alu + PC", "chi_so_chong_am": "IP 65", "pf": "&gt;0.97", "nguon": "Philips hoặc tuỳ chỉnh theo yêu cầu"}</t>
         </is>
       </c>
       <c r="L4" t="inlineStr">
@@ -23920,6 +24753,17 @@
 Bảo hành: 2-5 năm</t>
         </is>
       </c>
+      <c r="T4" t="inlineStr">
+        <is>
+          <t>Đặc điểm nổi bật của Đèn LED Highbay UFO TLC 200W
+Chip LED
+Đèn LED UFO TLC sử dụng chip LED với hiệu suất quang cao: ~140 Lm/W, ánh sáng phân bổ đều, tiết kiệm năng lượng, tăng hiệu suất làm việc cho khu vực sản xuất, lắp ráp, kho bãi
+Nguồn Đèn
+Đèn LED UFO nhà xưởng sử dụng nguồn Philips công suất lớn đảm bảo đèn hoạt động ổn định và bền bỉ trong môi trường khắc nhiệt của nhà máy, khu vực sản xuất và kho bãi với chỉ số PF &gt;0.9, đạt tiêu chuẩn chống sét 4kV.
+Tản nhiệt
+Được làm bằng vật liệu nhôm, công nghệ đúc nguyên khối, nhiều cánh tản nhiệt đan xen, đèn LED UFO TLC được thiết kế thông minh giúp tản nhiệt hiệu quả, giảm tác động của nhiệt đến các linh kiện điện tử khác, tăng tuổi thọ của đèn.</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -23937,7 +24781,7 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>TLC-ĐX–50W</t>
+          <t>TLC-ĐX-50W</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
@@ -23947,7 +24791,7 @@
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>{"cong_suat": "50W", "anh_sang": "Trắng/ Vàng, Trắng, Vàng", "chip_led": "Chip Osram, Chip LED OSRAM", "hieu_suat_quang": "110 -120 Lm/w", "chi_so_hoan_mau": "CRI&gt;85", "dien_ap": "AC100-275", "thuong_hieu": "TLC LIGHTING", "tuoi_tho": "40.000h", "bao_hanh": "36 tháng", "chieu_cao_lap_dat": "&lt;5m", "do_hoan_mau": "&gt;85", "dien_ap_ac": "AC100-275", "tuoi_tho_chip_led": "40.000 giờ"}</t>
+          <t>{"cong_suat": "50W", "anh_sang": "Trắng/ Vàng", "chip_led": "Chip Osram", "hieu_suat_quang": "110 -120 Lm/w", "chi_so_hoan_mau": "CRI&gt;85", "dien_ap": "AC100-275", "thuong_hieu": "TLC LIGHTING", "tuoi_tho": "40.000h", "bao_hanh": "36 tháng"}</t>
         </is>
       </c>
       <c r="J5" t="n">
@@ -24035,7 +24879,7 @@
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>{"cong_suat": "100W", "anh_sang": "Trắng, Vàng", "chip_led": "Chip Bridgelux – USA", "hieu_suat_quang": "110 -120 Lm/w", "chi_so_hoan_mau": "CRI&gt;85", "dien_ap": "AC100-275", "thuong_hieu": "TLC LIGHTING", "tuoi_tho": "40.000h", "bao_hanh": "36 tháng", "chieu_cao_lap_dat": "&lt;8m", "do_hoan_mau": "&gt;85", "dien_ap_ac": "AC100-275", "tuoi_tho_chip_led": "40.000 giờ"}</t>
+          <t>{"cong_suat": "100W", "anh_sang": "Trắng/ Vàng, Trắng, Vàng", "chip_led": "Chip Bridgelux – USA", "hieu_suat_quang": "110 -120 Lm/w", "chi_so_hoan_mau": "CRI&gt;85", "dien_ap": "AC100-275", "thuong_hieu": "TLC LIGHTING", "tuoi_tho": "40.000h", "bao_hanh": "36 tháng", "chieu_cao_lap_dat": "&lt;8m", "do_hoan_mau": "&gt;85", "tuoi_tho_chip_led": "40.000 giờ", "quang_thong": "110-120 Lm/w"}</t>
         </is>
       </c>
       <c r="J6" t="n">
@@ -24201,7 +25045,7 @@
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>{"cong_suat": "200W", "anh_sang": "Trắng, Vàng", "chip_led": "Chip Bridgelux", "hieu_suat_quang": "110 -120 Lm/w", "chi_so_hoan_mau": "CRI&gt;80", "dien_ap": "AC100-275", "thuong_hieu": "TLC LIGHTING", "tuoi_tho": "40.000h", "bao_hanh": "36 tháng", "chieu_cao_lap_dat": "&lt;15m", "do_hoan_mau": "Ra&gt;80", "dien_ap_ac": "AC100-275", "tuoi_tho_chip_led": "40.000 giờ"}</t>
+          <t>{"cong_suat": "200W", "anh_sang": "Trắng/ Vàng", "chip_led": "Chip Bridgelux", "hieu_suat_quang": "110 -120 Lm/w", "chi_so_hoan_mau": "CRI&gt;80", "dien_ap": "AC100-275", "thuong_hieu": "TLC LIGHTING", "tuoi_tho": "40.000h", "bao_hanh": "24 tháng", "chieu_cao_lap_dat": "&lt;15m", "do_hoan_mau": "Ra&gt;80", "dien_ap_ac": "AC100-275", "tuoi_tho_chip_led": "40.000 giờ"}</t>
         </is>
       </c>
       <c r="J8" t="n">
@@ -24372,7 +25216,7 @@
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>{"cong_suat": "100W", "anh_sang": "Trắng, Vàng", "chip_led": "Chip Osram", "hieu_suat_quang": "110 -120 Lm/w", "chi_so_hoan_mau": "CRI&gt;85", "dien_ap": "85-265V", "thuong_hieu": "TLC LIGHTING", "tuoi_tho": "40.000h", "bao_hanh": "36 tháng", "quang_thong": "11500Lm", "chieu_cao_lap_dat": "&lt;8m", "do_hoan_mau": "Ra&gt;85", "dien_ap_ac": "AC 85-265", "tuoi_tho_chip_led": "40.000 giờ"}</t>
+          <t>{"cong_suat": "100W", "anh_sang": "Trắng/ Vàng", "chip_led": "Chip Osram", "hieu_suat_quang": "110 -120 Lm/w", "chi_so_hoan_mau": "CRI&gt;85", "dien_ap": "85-265V", "thuong_hieu": "TLC LIGHTING", "tuoi_tho": "40.000h", "bao_hanh": "36 tháng", "quang_thong": "11500Lm", "chieu_cao_lap_dat": "&lt;8m", "do_hoan_mau": "Ra&gt;85", "dien_ap_ac": "AC 85-265", "tuoi_tho_chip_led": "40.000 giờ"}</t>
         </is>
       </c>
       <c r="J10" t="n">
@@ -24462,7 +25306,7 @@
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>{"cong_suat": "50W", "anh_sang": "Trắng/ Vàng", "chip_led": "Chip Osram", "hieu_suat_quang": "110 -120 Lm/w", "chi_so_hoan_mau": "CRI&gt;85", "dien_ap": "85-265V", "thuong_hieu": "TLC LIGHTING", "tuoi_tho": "40.000h", "bao_hanh": "36 tháng", "quang_thong": "5750Lm", "chieu_cao_lap_dat": "&lt;5m", "do_hoan_mau": "&gt;80 Ra", "dien_ap_ac": "AC 85-265", "tuoi_tho_chip_led": "40.000 giờ"}</t>
+          <t>{"cong_suat": "50W", "anh_sang": "Trắng/ Vàng, Trắng, Vàng", "chip_led": "Chip Osram", "hieu_suat_quang": "110 -120 Lm/w", "chi_so_hoan_mau": "CRI&gt;85", "dien_ap": "85-265V", "thuong_hieu": "TLC LIGHTING", "tuoi_tho": "40.000h", "bao_hanh": "36 tháng", "quang_thong": "5750Lm", "chieu_cao_lap_dat": "&lt;5m", "do_hoan_mau": "&gt;80 Ra", "dien_ap_ac": "AC 85-265", "tuoi_tho_chip_led": "40.000 giờ"}</t>
         </is>
       </c>
       <c r="J11" t="n">
@@ -24694,7 +25538,7 @@
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>{"thuong_hieu": "TLC LIGHTING", "cong_suat": "12W", "anh_sang": "Ba màu", "dien_ap": "85 – 265V", "hieu_suat_quang": "1200 Lm", "kich_thuoc_den": "120×40 mm", "chip_led": "OSRAM", "bao_hanh": "36 tháng"}</t>
+          <t>{"thuong_hieu": "TLC LIGHTING", "cong_suat": "12W", "anh_sang": "Ba màu", "dien_ap": "85 – 265V", "hieu_suat_quang": "1200 Lm", "kich_thuoc_den": "120×40 mm", "chip_led": "OSRAM", "bao_hanh": "24 tháng"}</t>
         </is>
       </c>
       <c r="J2" t="n">
@@ -25004,7 +25848,7 @@
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>{"cong_suat": "33W", "anh_sang": "Trắng, Màu trắng", "nhiet_do_mau": "3500K/6500K", "kich_thuoc": "Φ 330×80", "chip_led": "Chip Epistar", "hieu_suat_quang": "110-120 Lm/w, 85-95 Lm/w", "chi_so_hoan_mau": "CRI≥85", "dien_ap": "85-265V", "thuong_hieu": "TLC LIGHTING", "tuoi_tho": "40.000h", "bao_hanh": "24 tháng", "hang_san_xuat": "TLC LIGHTING", "vung_cam_bien": "360°/ 8m", "quang_thong": "3069Lm", "do_hoan_mau": "&gt;85", "dien_ap_ac": "85-265V", "tuoi_tho_chip_led": "40.000 giờ"}</t>
+          <t>{"Cong_suat": "33W", "Anh_sang": "Trắng", "Nhiet_do_mau": "3500K/6500K", "Kich_thuoc": "Φ 330×80", "Chip_Led": "Chip Epistar", "Hieu_suat_quang": "110-120 Lm/w", "Chi_so_hoan_mau": "CRI≥85", "Dien_ap": "85-265V", "Thuong_hieu": "TLC LIGHTING", "Tuoi_tho": "40.000h", "Bao_hanh": "24 tháng", "Hang_san_xuat": "TLC LIGHTING", "Vung_cam_bien": "360°/ 8m", "Quang_thong": "3069Lm", "Do_hoan_mau": "&gt;85", "Anh_sang_1": "Màu trắng", "Dien_ap_AC": "85-265V", "Tuoi_tho_chip_LED": "40.000 giờ"}</t>
         </is>
       </c>
       <c r="J3" t="n">
@@ -25018,6 +25862,15 @@
       <c r="M3" t="inlineStr">
         <is>
           <t>https://tlclighting.com.vn/wp-content/uploads/2019/11/ỐP-TRẦN.png</t>
+        </is>
+      </c>
+      <c r="P3" t="inlineStr">
+        <is>
+          <t>Chip Led
+Bộ nguồn
+Tản nhiệt
+Vỏ đèn
+Bộ cảm ứng Radar</t>
         </is>
       </c>
       <c r="Q3" t="inlineStr">
@@ -25047,6 +25900,23 @@
 Chip LED: Chip Epistar
 Tuổi thọ chip LED: 40.000 giờ
 Bảo hành: 24 tháng</t>
+        </is>
+      </c>
+      <c r="T3" t="inlineStr">
+        <is>
+          <t>Chip Led
+chip LED của đèn được sử dụng là dòng chip Led siêu sáng. Toàn bộ bề mặt chip được bọc bởi lớp Nano có tác dụng tán quang tốt, cho ánh sáng đều đẹp, tốt cho mắt. Bảo vệ mắt hiệu quả theo tiêu chuẩn Châu Âu, chống lóa – mỏi mắt, chống cận thị.
+Bộ nguồn
+Nguồn đèn được cấu tạo từ những linh kiện cao cấp chất lượng tốt, đảm bảo chuyển dòng điện xoay chiều thành dòng điện 1 chiều, tạo điều kiện tốt nhất cho đèn hoạt động ổn định, đảm bảo tuổi thọ cho đèn.
+Cảm biến vi sóng đèn Led ốp trần Radar
+Tản nhiệt
+Bộ phận tản nhiệt của đèn được thiết kế từ hợp kim nhôm, có tác dụng tản nhiệt rất tốt cho hoạt động của đèn.
+Vỏ đèn
+Bộ vỏ đèn được thiết kế chắc chắn, toàn bộ khung viền được bao bọc bằng hợp kim nhôm phủ sơn Nano cao cấp giúp chống trầy xước hiệu quả. Thêm vào đó, chóa đèn được thiết kế cong tinh tế giúp vùng chiếu ánh sáng rộng hơn.
+Chóa được thiết kế mica với độ thấu quang 92% cho ánh sáng mờ, đồng đều, tốt cho mắt, giảm cận thị, bảo vệ mắt theo tiêu chuẩn Châu Âu.
+Bộ cảm ứng Radar
+Bộ cảm ứng sóng Radar được thiết kế riêng, đặt bên trong đèn bên cạnh phần nguồn.
+Thêm vào đó, so với các dòng đèn cảm ứng sử dụng cảm ứng hồng ngoại thì đèn ốp trần Radar có cảm ứng nhạy gấp 10 lần do ứng dụng công nghệ Radar cao cấp nhất từ Châu Âu.</t>
         </is>
       </c>
     </row>
@@ -25214,7 +26084,7 @@
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>{"cong_suat": "48W", "anh_sang": "Trắng/ Vàng", "kich_thuoc": "305×1205", "dien_ap": "AC 100-275", "thuong_hieu": "TLC LIGHTING", "tuoi_tho": "40.000h", "bao_hanh": "24 tháng", "chung_loai": "Có tai", "quang_thong": "4560 lm", "dien_ap_ac": "AC100-275", "tuoi_tho_chip_led": "40.000 giờ"}</t>
+          <t>{"cong_suat": "48W", "anh_sang": "Trắng/ Vàng, Trắng và Vàng", "kich_thuoc": "305×1205", "dien_ap": "AC 100-275", "thuong_hieu": "TLC LIGHTING", "tuoi_tho": "40.000h", "bao_hanh": "24 tháng", "chung_loai": "Có tai", "quang_thong": "4560 lm", "dien_ap_ac": "AC100-275", "tuoi_tho_chip_led": "40.000 giờ", "hieu_suat_phat_quang": "90-100 Lm/w", "chi_so_hoan_mau": "Ra &gt; 85"}</t>
         </is>
       </c>
       <c r="J2" t="n">
@@ -25293,7 +26163,7 @@
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>{"cong_suat": "48W", "anh_sang": "Trắng/ Vàng", "kich_thuoc": "300×1200", "dien_ap": "AC100-275", "thuong_hieu": "TLC LIGHTING", "tuoi_tho": "40.000h", "bao_hanh": "24 tháng", "chung_loai": "Không tai", "quang_thong": "4560 lm", "dien_ap_ac": "AC100-275", "tuoi_tho_chip_led": "40.000 giờ", "hieu_suat_phat_quang": "90-100 Lm/w", "chi_so_hoan_mau": "Ra &gt; 85"}</t>
+          <t>{"cong_suat": "48W", "anh_sang": "Trắng/ Vàng, Trắng và Vàng", "kich_thuoc": "300×1200, 305×1205", "dien_ap": "AC100-275", "thuong_hieu": "TLC LIGHTING", "tuoi_tho": "40.000h", "bao_hanh": "24 tháng", "chung_loai": "Không tai", "quang_thong": "4560 lm", "tuoi_tho_chip_LED": "40.000 giờ"}</t>
         </is>
       </c>
       <c r="J3" t="n">
@@ -25428,7 +26298,7 @@
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>{"cong_suat": "16W", "anh_sang": "Trắng, Vàng", "kich_thuoc": "295×295", "dien_ap": "AC 100-275", "thuong_hieu": "TLC LIGHTING", "tuoi_tho": "40.000h", "bao_hanh": "24 tháng", "chung_loai": "Không tai", "quang_thong": "1520 lm", "tuoi_tho_chip_LED": "40.000 giờ"}</t>
+          <t>{"cong_suat": "16W", "anh_sang": "Trắng/ Vàng", "kich_thuoc": "295×295", "dien_ap": "AC 100-275", "thuong_hieu": "TLC LIGHTING", "tuoi_tho": "40.000h", "bao_hanh": "24 tháng", "chung_loai": "Không tai", "quang_thong": "1520 lm", "tuoi_tho_chip_LED": "40.000 giờ"}</t>
         </is>
       </c>
       <c r="J5" t="n">
@@ -25503,7 +26373,7 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>TLC-TOS-CT-30×60</t>
+          <t>TLC-TOS-KT-30X60</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
@@ -25513,7 +26383,7 @@
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>{"cong_suat": "24W", "anh_sang": "Trắng/ Vàng", "kich_thuoc": "305×605", "dien_ap": "AC100-275", "thuong_hieu": "TLC LIGHTING", "tuoi_tho": "40.000h", "bao_hanh": "24 tháng", "chung_loai": "Không tai", "quang_thong": "2280 lm", "tuoi_tho_chip_LED": "40.000 giờ", "dien_ap_AC": "AC100-275"}</t>
+          <t>{"cong_suat": "24W", "anh_sang": "Trắng/Vàng", "kich_thuoc": "305×605", "dien_ap": "AC100-275", "thuong_hieu": "TLC LIGHTING", "tuoi_tho": "40.000h", "bao_hanh": "24 tháng", "chung_loai": "Không tai", "quang_thong": "2280 lm", "dien_ap_ac": "AC100-275", "tuoi_tho_chip_led": "40.000 giờ"}</t>
         </is>
       </c>
       <c r="J6" t="n">
@@ -25597,7 +26467,7 @@
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>{"cong_suat": "24W", "chung_loai": "Không tai", "kich_thuoc": "295×595", "quang_thong": "2280 lm", "anh_sang": "Trắng/Vàng", "dien_ap_ac": "AC100-275", "tuoi_tho_chip_led": "40.000 giờ", "bao_hanh": "24 tháng", "thuong_hieu": "TLC LIGHTING"}</t>
+          <t>{"cong_suat": "24W", "chung_loai": "Không tai", "kich_thuoc": "295×595", "quang_thong": "2280 lm", "anh_sang": "Trắng/Vàng", "dien_ap_ac": "AC100-275", "tuoi_tho_chip_led": "40.000 giờ", "bao_hanh": "24 tháng"}</t>
         </is>
       </c>
       <c r="J7" t="n">
@@ -25674,7 +26544,7 @@
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>{"cong_suat": "72W", "anh_sang": "Trắng/ Vàng", "kich_thuoc": "605×1205", "dien_ap": "AC100-275", "thuong_hieu": "TLC LIGHTING", "tuoi_tho": "40.000h", "bao_hanh": "24 tháng", "quang_thong": "6840 lm", "loai": "Có tai", "hieu_suat_phat_quang": "90-100 Lm/w", "chi_so_hoan_mau": "Ra &gt; 85"}</t>
+          <t>{"cong_suat": "72W", "anh_sang": "Trắng/ Vàng, Trắng và Vàng", "kich_thuoc": "605×1205", "dien_ap": "AC100-275", "thuong_hieu": "TLC LIGHTING", "tuoi_tho": "40.000h", "bao_hanh": "24 tháng", "chung_loai": "Có tai", "quang_thong": "6840 lm", "dien_ap_ac": "AC100-275", "tuoi_tho_chip_led": "40.000 giờ", "hieu_suat_phat_quang": "90-100 Lm/w", "chi_so_hoan_mau": "Ra &gt; 85"}</t>
         </is>
       </c>
       <c r="J8" t="n">
@@ -25821,7 +26691,7 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>TLC-TOS-CT-600×600</t>
+          <t>TLC-TOS-CT-60X60</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
@@ -25831,7 +26701,7 @@
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>{"cong_suat": "48W", "anh_sang": "Trắng/ Vàng", "kich_thuoc": "605×605", "dien_ap": "AC 100-275", "thuong_hieu": "TLC LIGHTING", "tuoi_tho": "40.000h", "bao_hanh": "24 tháng", "chung_loai": "Có tai", "quang_thong": "4560 lm", "dien_ap_ac": "AC100-275", "tuoi_tho_chip_led": "40.000 giờ", "chi_so_hoan_mau": "Ra &gt; 85"}</t>
+          <t>{"thuong_hieu": "TLC LIGHTING", "cong_suat": "48W", "chu_loai": "Có tai", "kich_thuoc": "605×605", "quang_thong": "4560 lm", "anh_sang": "Trắng/Vàng", "dien_ap": "AC100-275", "tuoi_tho_chip_led": "40.000 giờ", "bao_hanh": "24 tháng"}</t>
         </is>
       </c>
       <c r="J10" t="n">
@@ -25914,7 +26784,7 @@
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>{"cong_suat": "48W", "anh_sang": "Trắng/ Vàng", "kich_thuoc": "595×595", "dien_ap": "AC 100-275", "thuong_hieu": "TLC LIGHTING", "tuoi_tho": "40.000h", "bao_hanh": "24 tháng", "chung_loai": "Không tai", "quang_thong": "4560 Lm", "dien_ap_ac": "AC100-275", "tuoi_tho_chip_led": "40.000 giờ", "chi_so_hoan_mau": "Ra &gt; 85"}</t>
+          <t>{"cong_suat": "48W", "anh_sang": "Trắng/ Vàng", "kich_thuoc": "595×595", "dien_ap": "AC 100-275", "thuong_hieu": "TLC LIGHTING", "tuoi_tho": "40.000h", "bao_hanh": "24 tháng", "chung_loai": "Không tai", "quang_thong": "4560 Lm", "dien_ap_ac": "AC100-275", "tuoi_tho_chip_led": "40.000 giờ", "chi_so_hoan_mau": "Ra &gt; 85", "hieu_suat_phat_quang": "90-100 Lm/w"}</t>
         </is>
       </c>
       <c r="J11" t="n">
@@ -25995,7 +26865,7 @@
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>{"cong_suat": "68W", "anh_sang": "Trắng/ Vàng", "kich_thuoc": "595×1195", "tuoi_tho": "40.000h", "bao_hanh": "24 tháng", "thuong_hieu": "TLC LIGHTING", "chung_loai": "Không tai", "quang_thong": "5440 lm", "dien_ap_ac": "AC 85-265", "tuoi_tho_chip_led": "40.000 giờ"}</t>
+          <t>{"anh_sang": "Trắng/ Vàng", "kich_thuoc": "595×1195", "tuoi_tho": "40.000h", "bao_hanh": "24 tháng", "thuong_hieu": "TLC LIGHTING", "cong_suat": "68W", "chung_loai": "Không tai", "quang_thong": "5440 lm", "dien_ap_ac": "AC 85-265", "tuoi_tho_chip_LED": "40.000 giờ", "chi_so_hoan_mau": "Ra &gt; 85"}</t>
         </is>
       </c>
       <c r="J12" t="n">
@@ -26071,7 +26941,7 @@
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>{"cong_suat": "42W", "anh_sang": "Trắng/ Vàng", "kich_thuoc": "606×606", "tuoi_tho": "40.000h", "bao_hanh": "24 tháng", "thuong_hieu": "TLC LIGHTING", "chung_loai": "Có tai", "dien_ap_ac": "AC 85-265", "tuoi_tho_chip_LED": "40.000 giờ", "chi_so_CRI": "&gt;80 Ra"}</t>
+          <t>{"cong_suat": "42W", "anh_sang": "Trắng/ Vàng", "kich_thuoc": "606×606", "tuoi_tho": "40.000h", "bao_hanh": "24 tháng", "thuong_hieu": "TLC LIGHTING", "chung_loai": "Có tai", "dien_ap_AC": "AC 85-265", "tuoi_tho_chip_LED": "40.000 giờ", "CRI": "&gt;80 Ra"}</t>
         </is>
       </c>
       <c r="J13" t="n">
@@ -26153,7 +27023,7 @@
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>{"anh_sang": "Trắng/ Vàng, Trắng và Vàng", "kich_thuoc": "305×1205", "tuoi_tho": "40.000h", "bao_hanh": "24 tháng", "thuong_hieu": "TLC LIGHTING", "cong_suat": "42W", "chung_loai": "Có tai", "quang_thong": "3360 lm", "dien_ap_AC": "AC 85-265", "tuoi_tho_chip_LED": "40.000 giờ", "chi_so_hoan_mau": "Ra &gt; 85"}</t>
+          <t>{"cong_suat": "42W", "anh_sang": "Trắng/ Vàng, Trắng và Vàng", "kich_thuoc": "305×1205", "tuoi_tho": "40.000h", "bao_hanh": "24 tháng", "thuong_hieu": "TLC LIGHTING", "chung_loai": "Có tai", "quang_thong": "3360 lm", "dien_ap_ac": "AC 85-265", "tuoi_tho_chip_led": "40.000 giờ", "chi_so_hoan_mau": "Ra &gt; 85"}</t>
         </is>
       </c>
       <c r="J14" t="n">
@@ -26234,7 +27104,7 @@
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>{"thuong_hieu": "TLC LIGHTING", "cong_suat": "20W", "chung_loai": "Có tai", "quang_thong": "1600 lm", "anh_sang": "Trắng/ Vàng", "dien_ap_ac": "AC 85-265", "tuoi_tho_chip_led": "40.000 giờ", "bao_hanh": "24 tháng", "hieu_suat_phat_quang": "80-90 Lm/w", "chi_so_hoan_mau": "Ra &gt; 85"}</t>
+          <t>{"thuong_hieu": "TLC LIGHTING", "anh_sang": "Trắng/ Vàng", "kich_thuoc": "305×605", "tuoi_tho": "40.000h", "bao_hanh": "24 tháng", "cong_suat": "20W", "chung_loai": "Có tai", "quang_thong": "1600 lm", "dien_ap_ac": "AC 85-265", "tuoi_tho_chip_led": "40.000 giờ"}</t>
         </is>
       </c>
       <c r="J15" t="n">
@@ -26328,6 +27198,18 @@
           <t>https://tlclighting.com.vn/wp-content/uploads/2019/10/T-Panel-OS-30x120-CT.jpg</t>
         </is>
       </c>
+      <c r="P16" t="inlineStr">
+        <is>
+          <t>Kích thước phổ biến, phù hợp với nhiều không gian.
+Màu sắc ánh sáng: màu trắng đem lại không gian hiện đại, màu vàng mang đến sự tinh tế.
+Đèn có thiết kế thẩm mỹ, sang trọng, hiện đại – được ưu tiên ứng dụng cho các công trình cao cấp: khách sạn, nhà hàng, phòng họp, phòng hội nghị, trường học, bệnh viện,….
+Tuổi thọ của đèn cao, đạt 40,000 giờ chiếu sáng. Do vậy, khách hàng có thể tiết kiệm được đáng kể chi phí thay mới.
+Chỉ số hoàn màu của đèn Ra &gt; 85, ánh sáng đồng đều, chóa đèn sần mờ, cho ánh sáng đều, chống lóa, mỏi mắt.
+Đèn led tấm panel có 3 loại cơ bản theo cách lắp đặt là loại gắn trần bằng đai vít, loại dùng đai cài (tương tự đèn led âm trần siêu mỏng) và loại trần thả (được thả như 1 tấm trần).
+Vỏ kim loại đúc nguồn khối chắc chắn, sơn tĩnh điện tinh tế trong rất sang trọng. Đèn led panel sử dụng loại nguồn vỏ nhôm nên rất bền bỉ. Đèn led panel đang dần thay thế các loại máng đèn huỳnh quang 60cm 2 bóng tuýp.
+Chính sách bảo hành 24 tháng trên toàn quốc</t>
+        </is>
+      </c>
       <c r="Q16" t="inlineStr">
         <is>
           <t>Mã sản phẩm: : 42W
@@ -26346,6 +27228,18 @@
 Bảo hành: 24 tháng</t>
         </is>
       </c>
+      <c r="T16" t="inlineStr">
+        <is>
+          <t>Kích thước phổ biến, phù hợp với nhiều không gian.
+Màu sắc ánh sáng: màu trắng đem lại không gian hiện đại, màu vàng mang đến sự tinh tế.
+Đèn có thiết kế thẩm mỹ, sang trọng, hiện đại – được ưu tiên ứng dụng cho các công trình cao cấp: khách sạn, nhà hàng, phòng họp, phòng hội nghị, trường học, bệnh viện,….
+Tuổi thọ của đèn cao, đạt 40,000 giờ chiếu sáng. Do vậy, khách hàng có thể tiết kiệm được đáng kể chi phí thay mới.
+Chỉ số hoàn màu của đèn Ra &gt; 85, ánh sáng đồng đều, chóa đèn sần mờ, cho ánh sáng đều, chống lóa, mỏi mắt.
+Đèn led tấm panel có 3 loại cơ bản theo cách lắp đặt là loại gắn trần bằng đai vít, loại dùng đai cài (tương tự đèn led âm trần siêu mỏng) và loại trần thả (được thả như 1 tấm trần).
+Vỏ kim loại đúc nguồn khối chắc chắn, sơn tĩnh điện tinh tế trong rất sang trọng. Đèn led panel sử dụng loại nguồn vỏ nhôm nên rất bền bỉ. Đèn led panel đang dần thay thế các loại máng đèn huỳnh quang 60cm 2 bóng tuýp.
+Chính sách bảo hành 24 tháng trên toàn quốc</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
@@ -26368,7 +27262,7 @@
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>{"anh_sang": "Trắng/ Vàng, Trắng và Vàng", "kich_thuoc": "600×600, 595×595", "tuoi_tho": "40.000h", "bao_hanh": "24 tháng", "thuong_hieu": "TLC LIGHTING", "cong_suat": "42W", "chung_loai": "Không tai", "quang_thong": "3360 lm", "dien_ap_ac": "AC 85-265", "tuoi_tho_chip_LED": "40.000 giờ", "chi_so_CRI": "&gt;80 Ra"}</t>
+          <t>{"anh_sang": "Trắng/ Vàng, Trắng và Vàng", "kich_thuoc": "600×600, 595×595", "tuoi_tho": "40.000h", "bao_hanh": "24 tháng", "thuong_hieu": "TLC LIGHTING", "cong_suat": "42W", "chung_loai": "Không tai", "quang_thong": "3360 lm", "dien_ap_ac": "AC 85-265", "tuoi_tho_chip_led": "40.000 giờ", "chi_so_cri": "&gt;80 Ra"}</t>
         </is>
       </c>
       <c r="J17" t="n">
@@ -26546,7 +27440,7 @@
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>{"cong_suat": "24W", "anh_sang": "Trắng", "kich_thuoc": "305×605", "dien_ap": "AC 100-265", "thuong_hieu": "TLC LIGHTING", "tuoi_tho": "40.000h", "bao_hanh": "24 tháng", "quang_thong": "2280 Lm", "dien_ap_ac": "AC100-265", "tuoi_tho_chip_led": "40.000 giờ", "chi_so_hoan_mau": "CRI &gt; 85", "nguon_den": "110-265V"}</t>
+          <t>{"cong_suat": "24W", "anh_sang": "Trắng", "kich_thuoc": "305×605", "dien_ap": "AC 100-265", "thuong_hieu": "TLC LIGHTING", "tuoi_tho": "40.000h", "bao_hanh": "24 tháng", "quang_thong": "2280 Lm", "dien_ap_ac": "AC100-265", "tuoi_tho_chip_led": "40.000 giờ", "chip_led": "SMD", "hieu_suat_quang": "110-120 Lm/W", "chi_so_hoan_mau": "CRI &gt; 85", "nguon_dien_ap": "110-265V"}</t>
         </is>
       </c>
       <c r="J19" t="n">
@@ -26627,7 +27521,7 @@
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t>{"cong_suat": "48W", "anh_sang": "Trắng", "kich_thuoc": "600×600", "dien_ap": "AC 100-265", "thuong_hieu": "TLC LIGHTING", "tuoi_tho": "40.000h", "bao_hanh": "24 tháng", "quang_thong": "4590Lm", "dien_ap_ac": "AC100-265", "tuoi_tho_chip_led": "40.000 giờ"}</t>
+          <t>{"cong_suat": "48W", "anh_sang": "Trắng", "kich_thuoc": "600×600", "dien_ap": "AC 100-265", "thuong_hieu": "TLC LIGHTING", "tuoi_tho": "40.000h", "bao_hanh": "24 tháng", "quang_thong": "4590Lm", "dien_ap_ac": "AC100-265", "tuoi_tho_chip_led": "40.000 giờ", "hieu_suat_quang": "110-120 Lm/W", "ra": "&gt; 85"}</t>
         </is>
       </c>
       <c r="J20" t="n">
@@ -26695,7 +27589,7 @@
       </c>
       <c r="I21" t="inlineStr">
         <is>
-          <t>{"cong_suat": "12W", "anh_sang": "Trắng/ Vàng", "kich_thuoc": "300×300", "dien_ap": "AC 85-240", "thuong_hieu": "TLC LIGHTING", "tuoi_tho": "40.000h", "bao_hanh": "24 tháng", "quang_thong": "960 lm", "dien_ap_ac": "AC 85-265", "tuoi_tho_chip_led": "40.000 giờ"}</t>
+          <t>{"cong_suat": "12W", "anh_sang": "Trắng/ Vàng, Trắng và Vàng", "kich_thuoc": "300×300, 305×305", "dien_ap": "AC 85-240", "thuong_hieu": "TLC LIGHTING", "tuoi_tho": "40.000h", "bao_hanh": "24 tháng", "chung_loai": "Có tai", "quang_thong": "960 lm", "dien_ap_ac": "AC 85-265", "tuoi_tho_chip_led": "40.000 giờ", "chi_so_hoan_mau": "CRI &gt;80 Ra"}</t>
         </is>
       </c>
       <c r="J21" t="n">
@@ -26920,7 +27814,7 @@
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>{"cong_suat": "100W", "anh_sang": "Trắng, Vàng", "kich_thuoc": "345x260x36", "dien_ap": "AC145-265", "thuong_hieu": "TLC LIGHTING", "tuoi_tho": "40.000h", "bao_hanh": "24 tháng", "quang_thong": "11.500 lm", "tieu_chuan_chong_nuoc": "IP67", "chip_led": "SMD 2835", "tuoi_tho_chip_led": "40.000 giờ"}</t>
+          <t>{"cong_suat": "100W", "anh_sang": "Trắng/ Vàng, Trắng, Vàng", "kich_thuoc": "345x260x36", "dien_ap": "AC145-265", "thuong_hieu": "TLC LIGHTING", "tuoi_tho": "40.000h", "bao_hanh": "24 tháng", "quang_thong": "11.500 lm", "tieu_chuan_chong_nuoc": "IP67", "dien_ap_ac": "AC145-265", "chip_led": "SMD 2835", "tuoi_tho_chip_led": "40.000 giờ"}</t>
         </is>
       </c>
       <c r="J2" t="n">
@@ -26996,7 +27890,7 @@
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>{"cong_suat": "130W", "anh_sang": "Trắng, Vàng", "kich_thuoc": "460x280x36", "dien_ap": "AC145-265", "thuong_hieu": "TLC LIGHTING", "tuoi_tho": "40.000h", "bao_hanh": "24 tháng", "quang_thong": "14.950 lm", "cong_nghe_sieu_chong_nuoc": "IP67", "dien_ap_ac": "AC145-265", "tuoi_tho_chip_led": "40.000 giờ"}</t>
+          <t>{"cong_suat": "130W", "anh_sang": "Trắng/ Vàng, Trắng, Vàng", "kich_thuoc": "460x280x36", "dien_ap": "AC145-265", "thuong_hieu": "TLC LIGHTING", "tuoi_tho": "40.000h", "bao_hanh": "24 tháng", "quang_thong": "14.950 lm", "cong_nghe_sieu_chong_nuoc": "IP67", "tuoi_tho_chip_LED": "40.000 giờ", "dien_ap_AC": "AC145-265", "cong_nghe": "IP67", "hieu_suat_quang": "110 -120 Lm/w", "chi_so_hoan_mau": "Ra &gt; 80"}</t>
         </is>
       </c>
       <c r="J3" t="n">
@@ -27073,7 +27967,7 @@
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>{"cong_suat": "20W", "anh_sang": "Trắng, Vàng", "kich_thuoc": "170x105x25", "chip_led": "2835", "dien_ap": "AC145-265", "thuong_hieu": "TLC LIGHTING", "tuoi_tho": "40.000h", "bao_hanh": "24 tháng", "quang_thong": "2.300 lm", "tieu_chuan_chong_nuoc": "IP67", "tuoi_tho_chip_led": "40.000 giờ"}</t>
+          <t>{"cong_suat": "20W", "anh_sang": "Trắng, Vàng", "kich_thuoc": "170x105x25", "chip_led": "2835", "dien_ap": "AC145-265", "thuong_hieu": "TLC LIGHTING", "tuoi_tho": "40.000h", "bao_hanh": "24 tháng", "quang_thong": "2.300 lm", "tieu_chuan_chong_nuoc": "IP67", "dien_ap_ac": "AC145-265", "tuoi_tho_chip_led": "40.000 giờ", "hieu_suat_quang": "110 -120 Lm/w", "chi_so_hoan_mau": "Ra &gt; 80"}</t>
         </is>
       </c>
       <c r="J4" t="n">
@@ -27148,7 +28042,7 @@
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>{"cong_suat": "30W", "anh_sang": "Trắng/ Vàng, Trắng, Vàng", "kich_thuoc": "170x105x25, 180x135x30", "chip_led": "SMD 2835", "dien_ap": "AC 145V-265V", "thuong_hieu": "TLC LIGHTING", "tuoi_tho": "40.000h", "bao_hanh": "24 tháng", "quang_thong": "3.450 lm", "tieu_chuan": "IP67", "tuoi_tho_chip_LED": "40.000 giờ", "dien_ap_AC": "AC145-265", "hieu_suat_quang": "110 -120 Lm/w", "Ra": "&gt; 80"}</t>
+          <t>{"cong_suat": "30W", "anh_sang": "Trắng, Vàng", "kich_thuoc": "180x135x30", "chip_led": "SMD 2835", "dien_ap": "AC 145V-265V", "thuong_hieu": "TLC LIGHTING", "tuoi_tho": "40.000h", "bao_hanh": "24 tháng", "quang_thong": "3.450 lm", "tieu_chuan": "IP67", "tuoi_tho_chip_LED": "40.000 giờ"}</t>
         </is>
       </c>
       <c r="J5" t="n">
@@ -27225,7 +28119,7 @@
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>{"cong_suat": "50W", "anh_sang": "Trắng, Vàng", "kich_thuoc": "241x180x36", "dien_ap": "AC145-265", "thuong_hieu": "TLC LIGHTING", "tuoi_tho": "40.000h", "bao_hanh": "24 tháng", "quang_thong": "5.750 lm", "cong_nghe_sieu_chong_nuoc": "IP67", "tuoi_tho_chip_LED": "40.000 giờ", "cong_nghe": "IP67"}</t>
+          <t>{"cong_suat": "50W", "anh_sang": "Trắng/ Vàng", "kich_thuoc": "241x180x36", "dien_ap": "AC145-265", "thuong_hieu": "TLC LIGHTING", "tuoi_tho": "40.000h", "bao_hanh": "24 tháng", "quang_thong": "5.750 lm", "cong_nghe_sieu_chong_nuoc": "IP67", "dien_ap_ac": "AC145-265", "tuoi_tho_chip_led": "40.000 giờ"}</t>
         </is>
       </c>
       <c r="J6" t="n">
@@ -27383,7 +28277,7 @@
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>{"cong_suat": "150W", "anh_sang": "Trắng, Vàng", "kich_thuoc": "249*277*33", "chip_led": "LuniLeds – Philips", "dien_ap": "AC175-265V /50-60Hz", "thuong_hieu": "TLC LIGHTING", "tuoi_tho": "40.000h", "bao_hanh": "24 tháng", "quang_thong": "17250 Lm", "tieu_chuan_chong_nuoc": "IP67", "dien_ap_ac": "AC 175-265V/ 50 – 60Hz", "tuoi_tho_chip_led": "40.000 giờ"}</t>
+          <t>{"cong_suat": "150W", "anh_sang": "Trắng/ Vàng", "kich_thuoc": "249*277*33", "chip_led": "LuniLeds – Philips", "dien_ap": "AC175-265V /50-60Hz", "thuong_hieu": "TLC LIGHTING", "tuoi_tho": "40.000h", "bao_hanh": "24 tháng", "quang_thong": "17250 Lm", "tieu_chuan_chong_nuoc": "IP67", "dien_ap_ac": "AC 175-265V/ 50 – 60Hz", "tuoi_tho_chip_led": "40.000 giờ"}</t>
         </is>
       </c>
       <c r="J8" t="n">
@@ -27463,7 +28357,7 @@
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>{"cong_suat": "20W", "anh_sang": "Trắng, Vàng", "kich_thuoc": "121x131x23", "chip_led": "LuniLeds – Philips", "dien_ap": "AC175-265/50-60Hz", "thuong_hieu": "TLC LIGHTING", "tuoi_tho": "40.000h", "bao_hanh": "24 tháng", "quang_thong": "1800 Lm", "tieu_chuan_chong_nuoc": "IP67", "dien_ap_ac": "AC 175-265/ 50Hz", "tuoi_tho_chip_led": "40.000 giờ", "cong_nghe": "IP67", "hieu_suat_quang": "110 -120 Lm/w", "chi_so_hoan_mau": "Ra &gt; 80"}</t>
+          <t>{"cong_suat": "20W", "anh_sang": "Trắng/ Vàng", "kich_thuoc": "121x131x23", "chip_led": "LuniLeds – Philips", "dien_ap": "AC175-265/50-60Hz", "thuong_hieu": "TLC LIGHTING", "tuoi_tho": "40.000h", "bao_hanh": "24 tháng", "quang_thong": "1800 Lm", "tieu_chuan_chong_nuoc": "IP67", "dien_ap_ac": "AC 175-265/ 50Hz", "tuoi_tho_chip_led": "40.000 giờ"}</t>
         </is>
       </c>
       <c r="J9" t="n">
@@ -27543,7 +28437,7 @@
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>{"cong_suat": "30W", "anh_sang": "Trắng, Vàng", "kich_thuoc": "154*170*31", "chip_led": "LuniLeds – Philips", "dien_ap": "AC175-265/50-60Hz", "thuong_hieu": "TLC LIGHTING", "tuoi_tho": "40.000h", "bao_hanh": "24 tháng", "quang_thong": "3450 Lm", "tieu_chuan_chong_nuoc": "IP67", "tuoi_tho_chip_LED": "40.000 giờ"}</t>
+          <t>{"cong_suat": "30W", "anh_sang": "Trắng/ Vàng", "kich_thuoc": "154*170*31", "chip_led": "LuniLeds – Philips", "dien_ap": "AC175-265/50-60Hz", "thuong_hieu": "TLC LIGHTING", "tuoi_tho": "40.000h", "bao_hanh": "24 tháng", "quang_thong": "3450 Lm", "tieu_chuan_chong_nuoc": "IP67", "dien_ap_ac": "AC 175-265/ 50Hz", "tuoi_tho_chip_led": "40.000 giờ"}</t>
         </is>
       </c>
       <c r="J10" t="n">
@@ -27624,7 +28518,7 @@
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>{"cong_suat": "50W", "anh_sang": "Trắng/ Vàng, Trắng, Vàng", "kich_thuoc": "183*205*32", "chip_led": "LuniLeds – Philips, LumiLeds – Philips", "dien_ap": "AC 175-265/50-60Hz", "thuong_hieu": "TLC LIGHTING", "tuoi_tho": "40.000h", "bao_hanh": "24 tháng", "quang_thong": "5750 Lm", "tieu_chuan_chong_nuoc": "IP67", "dien_ap_ac": "AC 175-265/ 50Hz", "tuoi_tho_chip_led": "40.000 giờ"}</t>
+          <t>{"cong_suat": "50W", "anh_sang": "Trắng/ Vàng", "kich_thuoc": "183*205*32", "chip_led": "LuniLeds – Philips", "dien_ap": "AC 175-265/50-60Hz", "thuong_hieu": "TLC LIGHTING", "tuoi_tho": "40.000h", "bao_hanh": "24 tháng", "quang_thong": "5750 Lm", "tieu_chuan_chong_nuoc": "IP67", "dien_ap_ac": "AC 175-265/ 50Hz", "tuoi_tho_chip_led": "40.000 giờ"}</t>
         </is>
       </c>
       <c r="J11" t="n">
@@ -27705,7 +28599,7 @@
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>{"cong_suat": "100W", "anh_sang": "Trắng, Vàng", "kich_thuoc": "286x96x350", "chip_led": "Osram", "dien_ap": "AC 85-240", "thuong_hieu": "TLC LIGHTING", "tuoi_tho": "40.000h", "bao_hanh": "24 tháng", "quang_thong": "900 lm", "cong_nghe_sieu_chong_nuoc": "IP66", "dien_ap_ac": "AC 85-240", "tuoi_tho_chip_led": "40.000 giờ", "cong_nghe": "IP66", "tieu_chuan": "Ip66"}</t>
+          <t>{"cong_suat": "100W", "anh_sang": "Trắng, Vàng", "kich_thuoc": "286x96x350", "chip_led": "Osram", "dien_ap": "AC 85-240", "thuong_hieu": "TLC LIGHTING", "tuoi_tho": "40.000h", "bao_hanh": "24 tháng", "quang_thong": "900 lm", "cong_nghe_sieu_chong_nuoc": "IP66", "dien_ap_ac": "AC 85-240", "tuoi_tho_chip_led": "40.000 giờ"}</t>
         </is>
       </c>
       <c r="J12" t="n">
@@ -27791,7 +28685,7 @@
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>{"cong_suat": "10W", "anh_sang": "Trắng/ Vàng, Trắng, Vàng", "kich_thuoc": "130x57x166", "dien_ap": "AC 85-240", "thuong_hieu": "TLC LIGHTING", "tuoi_tho": "40.000h", "bao_hanh": "24 tháng", "quang_thong": "900 lm", "cong_nghe_sieu_chong_nuoc": "IP66", "dien_ap_ac": "AC 85-240", "chip_led": "Osram", "tuoi_tho_chip_led": "40.000 giờ"}</t>
+          <t>{"cong_suat": "10W", "anh_sang": "Trắng/ Vàng", "kich_thuoc": "130x57x166", "dien_ap": "AC 85-240", "thuong_hieu": "TLC LIGHTING", "tuoi_tho": "40.000h", "bao_hanh": "24 tháng", "quang_thong": "900 lm", "cong_nghe_sieu_chong_nuoc": "IP66", "dien_ap_ac": "AC 85-240", "chip_led": "Osram", "tuoi_tho_chip_led": "40.000 giờ", "chi_so_hoan_mau": "Ra &gt; 85"}</t>
         </is>
       </c>
       <c r="J13" t="n">
@@ -27874,7 +28768,7 @@
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>{"cong_suat": "200W", "anh_sang": "Trắng, Vàng", "kich_thuoc": "380x110x420", "dien_ap": "AC 85-240", "thuong_hieu": "TLC LIGHTING", "tuoi_tho": "40.000h", "bao_hanh": "24 tháng", "quang_thong": "18.500 lm", "cong_nghe_sieu_chong_nuoc": "IP66", "tuoi_tho_chip_LED": "40.000 giờ"}</t>
+          <t>{"cong_suat": "200W", "anh_sang": "Trắng/ Vàng, Trắng, Vàng", "kich_thuoc": "380x110x420", "dien_ap": "AC 85-240", "thuong_hieu": "TLC LIGHTING", "tuoi_tho": "40.000h", "bao_hanh": "24 tháng", "quang_thong": "18.500 lm", "cong_nghe_sieu_chong_nuoc": "IP66", "tuoi_tho_chip_LED": "40.000 giờ"}</t>
         </is>
       </c>
       <c r="J14" t="n">
@@ -28048,7 +28942,7 @@
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>{"cong_suat": "30W", "anh_sang": "Trắng, Vàng", "kich_thuoc": "203x71x246", "dien_ap": "AC 85-240", "thuong_hieu": "TLC LIGHTING", "tuoi_tho": "40.000h", "bao_hanh": "24 tháng", "quang_thong": "2.700 lm", "cong_nghe_sieu_chong_nuoc": "IP66", "dien_ap_ac": "AC 85-240", "tuoi_tho_chip_led": "40.000 giờ"}</t>
+          <t>{"cong_suat": "30W", "anh_sang": "Trắng, Vàng", "kich_thuoc": "203x71x246", "dien_ap": "AC 85-240", "thuong_hieu": "TLC LIGHTING", "tuoi_tho": "40.000h", "bao_hanh": "24 tháng", "quang_thong": "2.700 lm", "cong_nghe_sieu_chong_nuoc": "IP66", "tuoi_tho_chip_led": "40.000 giờ"}</t>
         </is>
       </c>
       <c r="J16" t="n">
@@ -28134,7 +29028,7 @@
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>{"cong_suat": "50W", "anh_sang": "Trắng/ Vàng, Trắng, Vàng", "kich_thuoc": "229x72x295", "dien_ap": "AC 85-240", "thuong_hieu": "TLC LIGHTING", "tuoi_tho": "40.000h", "bao_hanh": "24 tháng", "quang_thong": "4500 lm", "cong_nghe_sieu_chong_nuoc": "IP66", "dien_ap_ac": "AC 85-240", "tuoi_tho_chip_led": "40.000 giờ", "cong_nghe": "IP66"}</t>
+          <t>{"cong_suat": "50W", "anh_sang": "Trắng/ Vàng", "kich_thuoc": "229x72x295", "dien_ap": "AC 85-240", "thuong_hieu": "TLC LIGHTING", "tuoi_tho": "40.000h", "bao_hanh": "24 tháng", "quang_thong": "4500 lm", "cong_nghe_sieu_chong_nuoc": "IP66", "dien_ap_ac": "AC 85-240", "tuoi_tho_chip_led": "40.000 giờ"}</t>
         </is>
       </c>
       <c r="J17" t="n">
@@ -28221,7 +29115,7 @@
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>{"cong_suat": "100W", "quang_thong": "11000Lm", "kich_thuoc": "250x250x31 mm", "dien_ap": "AC 180-265V", "thuong_hieu": "TLC LIGHTING", "tuoi_tho": "40.000h", "bao_hanh": "24 tháng", "hieu_suat_quang": "Ra&gt;80", "chi_dinh_su_dung": "&lt;8h/ngày", "dien_ap_ac": "AC 180-265V", "tuoi_tho_chip_led": "40.000 giờ", "chong_nuoc_chong_bui": "IP66"}</t>
+          <t>{"cong_suat": "100W", "quang_thong": "11000Lm", "kich_thuoc": "250x250x31 mm", "dien_ap": "AC 180-265V", "thuong_hieu": "TLC LIGHTING", "tuoi_tho": "40.000h", "bao_hanh": "24 tháng", "hieu_suat_quang": "Ra&gt;80", "chi_dinh_su_dung": "&lt;8h/ngày", "dien_ap_ac": "AC 180-265V", "tuoi_tho_chip_led": "40.000 giờ"}</t>
         </is>
       </c>
       <c r="J18" t="n">
@@ -28305,7 +29199,7 @@
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>{"cong_suat": "200W", "quang_thong": "22000Lm", "kich_thuoc": "350x345x50mm", "dien_ap": "AC 180-265V", "thuong_hieu": "TLC LIGHTING", "tuoi_tho": "40.000h", "bao_hanh": "24 tháng", "hieu_suat_quang": "Ra&gt;80", "chi_dinh_su_dung": "&lt;8h/ngày", "tuoi_tho_chip_LED": "40.000 giờ"}</t>
+          <t>{"cong_suat": "200W", "quang_thong": "22000Lm", "kich_thuoc": "350x345x50mm", "dien_ap": "AC 180-265V", "thuong_hieu": "TLC LIGHTING", "tuoi_tho": "40.000h", "bao_hanh": "24 tháng", "hieu_suat_quang": "Ra&gt;80", "chi_dinh_su_dung": "&lt;8h/ngày", "dien_ap_ac": "AC 180-265V", "tuoi_tho_chip_led": "40.000 giờ"}</t>
         </is>
       </c>
       <c r="J19" t="n">
@@ -28397,7 +29291,7 @@
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t>{"cong_suat": "50W", "quang_thong": "5500Lm", "kich_thuoc": "105x205x31 mm", "dien_ap": "AC 180-265V", "thuong_hieu": "TLC LIGHTING", "tuoi_tho": "40.000h", "bao_hanh": "24 tháng", "hieu_suat_quang": "Ra&gt;80", "chi_dinh_su_dung": "&lt;8h/ngày", "dien_ap_ac": "AC 180-265V", "tuoi_tho_chip_led": "40.000 giờ"}</t>
+          <t>{"cong_suat": "50W", "quang_thong": "5500Lm", "kich_thuoc": "105x205x31 mm", "dien_ap": "AC 180-265V", "thuong_hieu": "TLC LIGHTING", "tuoi_tho": "40.000h", "bao_hanh": "24 tháng", "hieu_suat_quang": "Ra&gt;80", "chi_dinh_su_dung": "&lt;8h/ngày", "dien_ap_ac": "AC 180-265V", "tuoi_tho_chip_led": "40.000 giờ", "chong_nuoc_chong_bui": "IP66"}</t>
         </is>
       </c>
       <c r="J20" t="n">
@@ -28481,7 +29375,7 @@
       </c>
       <c r="I21" t="inlineStr">
         <is>
-          <t>{"cong_suat": "100W", "anh_sang": "Trắng/ Vàng, Trắng, Vàng", "kich_thuoc": "365x310x60", "dien_ap": "AC 85-265", "thuong_hieu": "TLC LIGHTING", "tuoi_tho": "40.000h", "bao_hanh": "24 tháng", "quang_thong": "11.500 lm", "hieu_suat_quang": "110-120 Lm/w", "chi_so_hoan_mau": "Ra&gt;85", "tieu_chuan": "IP67", "dien_ap_AC": "AC 85-240", "tuoi_tho_chip_LED": "40.000 giờ", "cong_nghe": "IP67", "chi_so_chong_nuoc": "IP67"}</t>
+          <t>{"cong_suat": "100W", "anh_sang": "Trắng, Vàng", "kich_thuoc": "365x310x60", "dien_ap": "AC 85-265", "thuong_hieu": "TLC LIGHTING", "tuoi_tho": "40.000h", "bao_hanh": "24 tháng", "quang_thong": "11.500 lm", "hieu_suat_quang": "110-120 Lm/w", "chi_so_hoan_mau": "Ra&gt;85", "tieu_chuan": "IP67", "dien_ap_ac": "AC 85-240", "tuoi_tho_chip_led": "40.000 giờ"}</t>
         </is>
       </c>
       <c r="J21" t="n">
@@ -28566,7 +29460,7 @@
       </c>
       <c r="I22" t="inlineStr">
         <is>
-          <t>{"cong_suat": "150W", "anh_sang": "Trắng/ Vàng, Trắng, Vàng", "kich_thuoc": "410x350x110", "dien_ap": "AC 85-240", "thuong_hieu": "TLC LIGHTING", "tuoi_tho": "40.000h", "bao_hanh": "24 tháng", "quang_thong": "16.500 lm", "hieu_suat_quang": "110-120 Lm/w", "chi_so_hoan_mau": "Ra&gt;85", "tieu_chuan": "IP67", "tuoi_tho_chip_LED": "40.000 giờ"}</t>
+          <t>{"cong_suat": "150W", "anh_sang": "Trắng/ Vàng", "kich_thuoc": "410x350x110", "dien_ap": "AC 85-240", "thuong_hieu": "TLC LIGHTING", "tuoi_tho": "40.000h", "bao_hanh": "24 tháng", "quang_thong": "16.500 lm", "hieu_suat_quang": "110-120 Lm/w", "chi_so_hoan_mau": "Ra&gt;85", "tieu_chuan": "IP67", "dien_ap_ac": "AC 85-240", "tuoi_tho_chip_led": "40.000 giờ"}</t>
         </is>
       </c>
       <c r="J22" t="n">
@@ -28639,7 +29533,7 @@
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>TLC-PAE-200W</t>
+          <t>TLC-PS-200W</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
@@ -28649,7 +29543,7 @@
       </c>
       <c r="I23" t="inlineStr">
         <is>
-          <t>{"cong_suat": "200W", "anh_sang": "Trắng/ Vàng, Trắng, Vàng", "kich_thuoc": "420x380x120", "dien_ap": "AC 85-265, AC 85-240", "thuong_hieu": "TLC LIGHTING", "tuoi_tho": "40.000h", "bao_hanh": "24 tháng", "quang_thong": "23.000 lm", "hieu_suat_quang": "110-120 Lm/w", "chi_so_hoan_mau": "Ra&gt;85", "tieu_chuan": "IP65", "tuoi_tho_chip_LED": "40.000 giờ", "cong_nghe": "IP67"}</t>
+          <t>{"cong_suat": "200W", "anh_sang": "Trắng, Vàng", "kich_thuoc": "420x380x120", "dien_ap": "AC 85-265", "thuong_hieu": "TLC LIGHTING", "tuoi_tho": "40.000h", "bao_hanh": "24 tháng", "quang_thong": "23.000 lm", "hieu_suat_quang": "110-120 Lm/w", "chi_so_hoan_mau": "Ra&gt;85", "tieu_chuan": "IP65", "dien_ap_ac": "AC 85-240", "tuoi_tho_chip_led": "40.000 giờ"}</t>
         </is>
       </c>
       <c r="J23" t="n">
@@ -28732,7 +29626,7 @@
       </c>
       <c r="I24" t="inlineStr">
         <is>
-          <t>{"cong_suat": "30W", "anh_sang": "Trắng/ Vàng", "kich_thuoc": "240x205x55", "chip_led": "Osram", "dien_ap": "AC 85-240", "thuong_hieu": "TLC LIGHTING", "tuoi_tho": "40.000h", "bao_hanh": "24 tháng", "quang_thong": "3450 lm", "hieu_suat_quang": "110-120 Lm/w", "chi_so_hoan_mau": "Ra&gt;85", "tieu_chuan": "IP67", "dien_ap_ac": "AC 85-265", "tuoi_tho_chip_led": "40.000 giờ"}</t>
+          <t>{"cong_suat": "30W", "anh_sang": "Trắng/ Vàng", "kich_thuoc": "240x205x55", "chip_led": "Osram", "dien_ap": "AC 85-240", "thuong_hieu": "TLC LIGHTING", "tuoi_tho": "40.000h", "bao_hanh": "24 tháng", "quang_thong": "3450 lm", "hieu_suat_quang": "110-120 Lm/w", "chi_so_hoan_mau": "Ra&gt;85", "tieu_chuan": "IP67", "tuoi_tho_chip_led": "40.000 giờ"}</t>
         </is>
       </c>
       <c r="J24" t="n">
@@ -28817,7 +29711,7 @@
       </c>
       <c r="I25" t="inlineStr">
         <is>
-          <t>{"cong_suat": "50W", "anh_sang": "Trắng/ Vàng, Trắng, Vàng", "kich_thuoc": "290x235x60", "dien_ap": "AC 85-240", "thuong_hieu": "TLC LIGHTING", "tuoi_tho": "40.000h", "bao_hanh": "24 tháng", "quang_thong": "5750 lm", "hieu_suat_quang": "110-120 Lm/w", "chi_so_hoan_mau": "Ra&gt;85", "tieu_chuan": "IP67", "dien_ap_ac": "AC 85-240", "tuoi_tho_chip_led": "40.000 giờ"}</t>
+          <t>{"cong_suat": "50W", "anh_sang": "Trắng/ Vàng, Trắng, Vàng", "kich_thuoc": "290x235x60", "dien_ap": "AC 85-240, AC 85-240", "thuong_hieu": "TLC LIGHTING", "tuoi_tho": "40.000h, 40.000 giờ", "bao_hanh": "24 tháng", "quang_thong": "5750 lm", "hieu_suat_quang": "110-120 Lm/w", "chi_so_hoan_mau": "Ra&gt;85", "tieu_chuan": "IP67"}</t>
         </is>
       </c>
       <c r="J25" t="n">
@@ -28902,7 +29796,7 @@
       </c>
       <c r="I26" t="inlineStr">
         <is>
-          <t>{"cong_suat": "100W", "anh_sang": "Trắng, Vàng", "kich_thuoc": "246.4×189.4×36 mm", "dien_ap": "AC 220V", "thuong_hieu": "TLC LIGHTING", "tuoi_tho": "40.000h", "bao_hanh": "24 tháng", "quang_thong": "10000 lm", "tieu_chuan_chong_nuoc": "IP66", "dien_ap_ac": "AC 175-265V/ 50Hz", "tuoi_tho_chip_led": "40.000 giờ"}</t>
+          <t>{"cong_suat": "100W", "anh_sang": "Trắng/ Vàng, Trắng, Vàng", "kich_thuoc": "246.4×189.4×36 mm", "dien_ap": "AC 220V", "thuong_hieu": "TLC LIGHTING", "tuoi_tho": "40.000h", "bao_hanh": "24 tháng", "quang_thong": "10000 lm", "tieu_chuan_chong_nuoc": "IP66", "dien_ap_ac": "AC 175-265V/ 50Hz", "tuoi_tho_chip_led": "40.000 giờ"}</t>
         </is>
       </c>
       <c r="J26" t="n">
@@ -28987,7 +29881,7 @@
       </c>
       <c r="I27" t="inlineStr">
         <is>
-          <t>{"cong_suat": "10W", "anh_sang": "Trắng, Vàng", "kich_thuoc": "96x74x21 mm", "dien_ap": "AC 220V", "thuong_hieu": "TLC LIGHTING", "tuoi_tho": "40.000h", "bao_hanh": "24 tháng", "quang_thong": "1000 lm", "tieu_chuan_chong_nuoc": "IP66", "dien_ap_ac": "AC 175-265V/ 50Hz", "tuoi_tho_chip_led": "40.000 giờ"}</t>
+          <t>{"cong_suat": "10W", "anh_sang": "Trắng/ Vàng", "kich_thuoc": "96x74x21 mm", "dien_ap": "AC 220V", "thuong_hieu": "TLC LIGHTING", "tuoi_tho": "40.000h", "bao_hanh": "24 tháng", "quang_thong": "1000 lm", "tieu_chuan_chong_nuoc": "IP66", "dien_ap_ac": "AC 175-265V/ 50Hz", "tuoi_tho_chip_led": "40.000 giờ"}</t>
         </is>
       </c>
       <c r="J27" t="n">
@@ -29071,7 +29965,7 @@
       </c>
       <c r="I28" t="inlineStr">
         <is>
-          <t>{"cong_suat": "150W", "anh_sang": "Trắng/ Vàng, Trắng, Vàng", "kich_thuoc": "292x227x38 mm", "dien_ap": "AC 220V", "thuong_hieu": "TLC LIGHTING", "tuoi_tho": "40.000h", "bao_hanh": "24 tháng", "quang_thong": "15000 lm", "tieu_chuan_chong_nuoc": "IP66", "dien_ap_ac": "AC 175-265V/ 50Hz", "tuoi_tho_chip_led": "40.000 giờ"}</t>
+          <t>{"cong_suat": "150W", "anh_sang": "Trắng, Vàng", "kich_thuoc": "292x227x38 mm", "dien_ap": "AC 220V", "thuong_hieu": "TLC LIGHTING", "tuoi_tho": "40.000h", "bao_hanh": "24 tháng", "quang_thong": "15000 lm", "tieu_chuan_chong_nuoc": "IP66", "dien_ap_ac": "AC 175-265V/ 50Hz", "tuoi_tho_chip_led": "40.000 giờ"}</t>
         </is>
       </c>
       <c r="J28" t="n">
@@ -29152,7 +30046,7 @@
       </c>
       <c r="I29" t="inlineStr">
         <is>
-          <t>{"cong_suat": "20W", "anh_sang": "Trắng/ Vàng", "kich_thuoc": "110.6×87.3×22.8 mm", "dien_ap": "AC 220V", "thuong_hieu": "TLC LIGHTING", "tuoi_tho": "40.000h", "bao_hanh": "24 tháng", "quang_thong": "2000 lm", "tieu_chuan_chong_nuoc": "IP66", "dien_ap_ac": "AC 175-265V/ 50Hz", "tuoi_tho_chip_led": "40.000 giờ"}</t>
+          <t>{"cong_suat": "20W", "anh_sang": "Trắng/ Vàng, Trắng, Vàng", "kich_thuoc": "110.6×87.3×22.8 mm", "dien_ap": "AC 220V", "thuong_hieu": "TLC LIGHTING", "tuoi_tho": "40.000h", "bao_hanh": "24 tháng", "quang_thong": "2000 lm", "tieu_chuan_chong_nuoc": "IP66", "dien_ap_ac": "AC 175-265V/ 50Hz", "tuoi_tho_chip_led": "40.000 giờ"}</t>
         </is>
       </c>
       <c r="J29" t="n">
@@ -29238,7 +30132,7 @@
       </c>
       <c r="I30" t="inlineStr">
         <is>
-          <t>{"cong_suat": "30W", "anh_sang": "Trắng/ Vàng, Trắng, Vàng", "kich_thuoc": "147.5×113.5×29 mm, 148x114x29", "dien_ap": "AC 220V", "thuong_hieu": "TLC LIGHTING", "tuoi_tho": "40.000h", "bao_hanh": "24 tháng", "quang_thong": "15000 lm", "tieu_chuan_chong_nuoc": "IP66", "dien_ap_ac": "AC 175-265V/ 50Hz", "tuoi_tho_chip_led": "40.000 giờ"}</t>
+          <t>{"cong_suat": "30W", "anh_sang": "Trắng, Vàng", "kich_thuoc": "147.5×113.5×29 mm", "dien_ap": "AC 220V", "thuong_hieu": "TLC LIGHTING", "tuoi_tho": "40.000h", "bao_hanh": "24 tháng", "quang_thong": "15000 lm", "tieu_chuan_chong_nuoc": "IP66", "dien_ap_ac": "AC 175-265V/ 50Hz", "tuoi_tho_chip_led": "40.000 giờ"}</t>
         </is>
       </c>
       <c r="J30" t="n">
@@ -29321,7 +30215,7 @@
       </c>
       <c r="I31" t="inlineStr">
         <is>
-          <t>{"cong_suat": "50W", "anh_sang": "Trắng/ Vàng, Trắng, Vàng", "kich_thuoc": "187.2×144.2×34.8 mm, 187x144x35", "dien_ap": "AC 220V, AC 175-265V/ 50Hz", "thuong_hieu": "TLC LIGHTING", "tuoi_tho": "40.000h", "bao_hanh": "24 tháng", "quang_thong": "5000 lm", "tieu_chuan_chong_nuoc": "IP66", "tuoi_tho_chip_LED": "40.000 giờ", "cong_nghe": "IP66"}</t>
+          <t>{"cong_suat": "50W", "anh_sang": "Trắng, Vàng", "kich_thuoc": "187.2×144.2×34.8 mm", "dien_ap": "AC 175-265V/ 50Hz", "thuong_hieu": "TLC LIGHTING", "tuoi_tho": "40.000 giờ", "bao_hanh": "24 tháng", "quang_thong": "5000 lm", "tieu_chuan_chong_nuoc": "IP66"}</t>
         </is>
       </c>
       <c r="J31" t="n">
@@ -29639,7 +30533,7 @@
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>{"cong_suat": "10W", "anh_sang": "Ba màu", "nhiet_do_mau": "3500K/6500K", "kich_thuoc": "Φ 65×105", "chip_led": "COB", "hieu_suat_quang": "110-120 Lm/w", "chi_so_hoan_mau": "CRI≥85", "dien_ap": "85-265V", "thuong_hieu": "TLC LIGHTING", "tuoi_tho": "40.000h", "bao_hanh": "24 tháng", "quang_thong": "1150 Lm", "do_hoan_mau": "Ra &gt; 85", "dien_ap_ac": "85-265V", "chat_lieu": "Nhôm, nhựa", "tuoi_tho_chip_led": "40.000 giờ"}</t>
+          <t>{"cong_suat": "10W", "anh_sang": "Ba màu", "nhiet_do_mau": "3500K/6500K", "kich_thuoc": "Φ 65×105", "chip_led": "Chip LED COB", "hieu_suat_quang": "110-120 Lm/w", "chi_so_hoan_mau": "CRI≥85", "dien_ap": "85-265V", "thuong_hieu": "TLC LIGHTING", "tuoi_tho": "40.000h", "bao_hanh": "24 tháng", "quang_thong": "1150 Lm", "do_hoan_mau": "Ra &gt; 85", "dien_ap_ac": "85-265V", "chat_lieu": "Nhôm, nhựa", "tuoi_tho_chip_led": "40.000 giờ"}</t>
         </is>
       </c>
       <c r="J3" t="n">
@@ -29831,7 +30725,7 @@
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>{"cong_suat": "10W", "anh_sang": "Trắng/ Vàng, Trắng, Vàng", "nhiet_do_mau": "3500K/6500K", "kich_thuoc": "Φ 65×105, ø65×105 mm", "chip_led": "Chip LED COB", "hieu_suat_quang": "110-120 Lm/w, 110 – 120 Lm/W", "chi_so_hoan_mau": "CRI≥85", "dien_ap": "85-265V", "thuong_hieu": "TLC LIGHTING", "tuoi_tho": "40.000h", "bao_hanh": "24 tháng", "quang_thong": "1150 Lm", "do_hoan_mau": "Ra &gt; 85", "dien_ap_ac": "85-265V", "chat_lieu": "Nhôm, nhựa", "tuoi_tho_chip_led": "40.000 giờ"}</t>
+          <t>{"cong_suat": "10W", "anh_sang": "Trắng/ Vàng, Trắng, Vàng", "nhiet_do_mau": "3500K/6500K", "kich_thuoc": "Φ 65×105, ø65×105 mm", "chip_LED": "Chip LED COB", "hieu_suat_quang": "110-120 Lm/w, 110 – 120 Lm/W", "chi_so_hoan_mau": "CRI≥85", "dien_ap": "85-265V", "thuong_hieu": "TLC LIGHTING", "tuoi_tho": "40.000h", "bao_hanh": "24 tháng", "quang_thong": "1150 Lm", "do_hoan_mau": "Ra &gt; 85", "chat_lieu": "Nhôm, nhựa", "tuoi_tho_chip_LED": "40.000 giờ"}</t>
         </is>
       </c>
       <c r="J5" t="n">
@@ -29930,7 +30824,7 @@
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>{"cong_suat": "20W", "anh_sang": "Ba màu(Trắng/ Vàng/trung tính)", "nhiet_do_mau": "3500K/6500K", "kich_thuoc": "Φ 90×120", "chip_led": "Chip LED COB", "hieu_suat_quang": "110-120 Lm/w", "chi_so_hoan_mau": "CRI≥85", "dien_ap": "85-265V", "thuong_hieu": "TLC LIGHTING", "tuoi_tho": "40.000h", "bao_hanh": "24 tháng", "dien_ap_ac": "85-265V", "tuoi_tho_chip_led": "40.000 giờ"}</t>
+          <t>{"cong_suat": "20W, 30W", "anh_sang": "Ba màu(Trắng/ Vàng/trung tính), Ba màu(Trắng/vàng/trung tính)", "nhiet_do_mau": "3500K/6500K", "kich_thuoc": "Φ 90×120", "chip_led": "Chip LED COB", "hieu_suat_quang": "110-120 Lm/w, 110~120Lm/w", "chi_so_hoan_mau": "CRI≥85", "dien_ap": "85-265V", "thuong_hieu": "TLC LIGHTING", "tuoi_tho": "40.000h", "bao_hanh": "24 tháng", "quang_thong": "3600Lm", "do_hoan_mau": "&gt;85", "dien_ap_ac": "85-265V", "tuoi_tho_chip_led": "40.000 giờ"}</t>
         </is>
       </c>
       <c r="J6" t="n">
@@ -30024,7 +30918,7 @@
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>{"cong_suat": "20W", "anh_sang": "Trắng/ Vàng", "nhiet_do_mau": "3500K/6500K", "kich_thuoc": "Φ 90×120", "chip_led": "Chip LED COB", "hieu_suat_quang": "110-120 Lm/w", "chi_so_hoan_mau": "CRI≥85", "dien_ap": "85-265V", "thuong_hieu": "TLC LIGHTING", "tuoi_tho": "40.000h", "bao_hanh": "24 tháng"}</t>
+          <t>{"cong_suat": "20W", "anh_sang": "Trắng/ Vàng, Trắng, Vàng", "nhiet_do_mau": "3500K/6500K", "kich_thuoc": "Φ 90×120, ø90×120mm", "chip_led": "Chip LED COB", "hieu_suat_quang": "110-120 Lm/w, 110 – 120 Lm/W", "chi_so_hoan_mau": "CRI≥85", "dien_ap": "85-265V", "thuong_hieu": "TLC LIGHTING", "tuoi_tho": "40.000h", "bao_hanh": "24 tháng", "quang_thong": "2400 Lm", "do_hoan_mau": "Ra &gt; 85", "dien_ap_ac": "85-265V", "chat_lieu": "Nhôm, nhựa", "tuoi_tho_chip_led": "40.000 giờ"}</t>
         </is>
       </c>
       <c r="J7" t="n">
@@ -30113,7 +31007,7 @@
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>{"cong_suat": "20W", "anh_sang": "Ba màu", "nhiet_do_mau": "3500K/6500K", "kich_thuoc": "Φ 90×120", "chip_led": "Chip LED COB", "hieu_suat_quang": "110-120 Lm/w", "chi_so_hoan_mau": "CRI≥85", "dien_ap": "85-265V", "thuong_hieu": "TLC LIGHTING", "tuoi_tho": "40.000h", "bao_hanh": "24 tháng", "quang_thong": "3600Lm", "do_hoan_mau": "&gt;85", "dien_ap_ac": "85-265V", "tuoi_tho_chip_led": "40.000 giờ"}</t>
+          <t>{"cong_suat": "20W", "anh_sang": "Ba màu", "nhiet_do_mau": "3500K/6500K", "kich_thuoc": "Φ 90×120", "chip_led": "Chip LED COB", "hieu_suat_quang": "110-120 Lm/w", "chi_so_hoan_mau": "CRI≥85", "dien_ap": "85-265V", "thuong_hieu": "TLC LIGHTING", "tuoi_tho": "40.000h", "bao_hanh": "24 tháng", "do_hoan_mau": "&gt;85", "quang_thong": "3600Lm", "dien_ap_ac": "85-265V", "tuoi_tho_chip_led": "40.000 giờ"}</t>
         </is>
       </c>
       <c r="J8" t="n">
@@ -30206,7 +31100,7 @@
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>{"cong_suat": "20W", "anh_sang": "Trắng/ Vàng, Trắng, Vàng", "nhiet_do_mau": "3500K/6500K", "kich_thuoc": "Φ 90×120, ø90×120mm", "chip_LED": "Chip LED COB, chip LED COB", "hieu_suat_quang": "110-120 Lm/w, 110 – 120 Lm/W", "chi_so_hoan_mau": "CRI≥85", "dien_ap": "85-265V", "thuong_hieu": "TLC LIGHTING", "tuoi_tho": "40.000h", "bao_hanh": "24 tháng", "quang_thong": "2400 Lm", "do_hoan_mau": "Ra &gt; 85", "dien_ap_ac": "85-265V", "chat_lieu": "Nhôm, nhựa", "tuoi_tho_chip_LED": "40.000 giờ"}</t>
+          <t>{"cong_suat": "20W", "anh_sang": "Trắng/ Vàng, Trắng, Vàng", "nhiet_do_mau": "3500K/6500K", "kich_thuoc": "Φ 90×120, ø90×120mm", "chip_led": "Chip LED COB, chip LED COB", "hieu_suat_quang": "110-120 Lm/w, 110 – 120 Lm/W", "chi_so_hoan_mau": "CRI≥85", "dien_ap": "85-265V", "thuong_hieu": "TLC LIGHTING", "tuoi_tho": "40.000h", "bao_hanh": "24 tháng", "quang_thong": "2400 Lm", "do_hoan_mau": "Ra &gt; 85", "dien_ap_ac": "85-265V", "chat_lieu": "Nhôm, nhựa", "tuoi_tho_chip_led": "40.000 giờ"}</t>
         </is>
       </c>
       <c r="J9" t="n">
@@ -30297,7 +31191,7 @@
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>{"cong_suat": "10W", "anh_sang": "Trắng/ Vàng", "nhiet_do_mau": "3500K/6500K", "kich_thuoc": "Φ 70x135x90", "chip_led": "Chip LED COB", "hieu_suat_quang": "110-120 Lm/w", "chi_so_hoan_mau": "CRI≥85", "dien_ap": "85-265V", "thuong_hieu": "TLC LIGHTING", "tuoi_tho": "40.000h", "bao_hanh": "24 tháng", "quang_thong": "1200 Lm", "do_hoan_mau": "Ra &gt; 85", "dien_ap_ac": "85-265V", "chat_lieu": "Nhôm, nhựa", "tuoi_tho_chip_led": "40.000 giờ"}</t>
+          <t>{"cong_suat": "10W", "anh_sang": "Trắng/ Vàng, Trắng, Vàng", "nhiet_do_mau": "3500K/6500K", "kich_thuoc": "Φ 70x135x90, ø70×135×90 mm", "chip_led": "Chip LED COB", "hieu_suat_quang": "110-120 Lm/w, 110 – 120 Lm/W", "chi_so_hoan_mau": "CRI≥85", "dien_ap": "85-265V", "thuong_hieu": "TLC LIGHTING", "tuoi_tho": "40.000h", "bao_hanh": "24 tháng", "quang_thong": "1200 Lm", "do_hoan_mau": "Ra &gt; 85", "chat_lieu": "Nhôm, nhựa", "tuoi_tho_chip_led": "40.000 giờ"}</t>
         </is>
       </c>
       <c r="J10" t="n">
@@ -30563,7 +31457,7 @@
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>{"cong_suat": "30W", "anh_sang": "Ba màu(Trắng/ Vàng/trung tính), Ba màu(Trắng/vàng/trung tính)", "nhiet_do_mau": "3500K/6500K", "kich_thuoc": "Φ 85x175x120", "chip_led": "Chip LED COB", "hs_quang": "110-120 Lm/w", "cri": "CRI≥85", "dien_ap": "85-265V", "thuong_hieu": "TLC LIGHTING", "tuoi_tho": "40.000h", "bao_hanh": "24 tháng", "hieu_suat_quang": "110~120Lm/w", "quang_thong": "3600Lm", "do_hoan_mau": "&gt;85", "dien_ap_ac": "85-265V", "tuoi_tho_chip_led": "40.000 giờ"}</t>
+          <t>{"cong_suat": "30W", "anh_sang": "Ba màu(Trắng/ Vàng/trung tính)", "nhiet_do_mau": "3500K/6500K", "kich_thuoc": "Φ 85x175x120", "chip_led": "Chip LED COB", "hs_quang": "110-120 Lm/w", "cri": "CRI≥85", "dien_ap": "85-265V", "thuong_hieu": "TLC LIGHTING", "tuoi_tho": "40.000h", "bao_hanh": "24 tháng", "hieu_suat_quang": "110~120Lm/w", "quang_thong": "3600Lm", "do_hoan_mau": "&gt;85", "dien_ap_ac": "85-265V", "tuoi_tho_chip_led": "40.000 giờ"}</t>
         </is>
       </c>
       <c r="J13" t="n">
@@ -30669,7 +31563,7 @@
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>{"cong_suat": "30W", "kich_thuoc": "Φ 85x175x120", "hieu_suat_quang": "110~120Lm/w", "quang_thong": "3600Lm", "do_hoan_mau": "&gt;85", "anh_sang": "Trắng/vàng", "dien_ap_ac": "85-265V", "chip_led": "Chip LED COB", "tuoi_tho_chip_led": "40.000 giờ", "bao_hanh": "24 tháng", "chi_so_hoan_mau": "Ra&gt;85"}</t>
+          <t>{"thuong_hieu": "TLC LIGHTING", "cong_suat": "30W", "kich_thuoc": "Φ 85x175x120", "hieu_suat_quang": "110~120Lm/w", "quang_thong": "3600Lm", "do_hoan_mau": "&gt;85", "anh_sang": "Trắng/vàng", "dien_ap_ac": "85-265V", "chip_led": "Chip LED COB", "tuoi_tho_chip_led": "40.000 giờ", "bao_hanh": "24 tháng"}</t>
         </is>
       </c>
       <c r="J14" t="n">
@@ -30683,6 +31577,18 @@
       <c r="M14" t="inlineStr">
         <is>
           <t>https://tlclighting.com.vn/wp-content/uploads/2019/12/20053.png</t>
+        </is>
+      </c>
+      <c r="P14" t="inlineStr">
+        <is>
+          <t>Đèn có khả năng tản nhiệt tốt hơn 5 lần so với các dòng đèn LED thông thường. Tản nhiệt gồm nhiều thanh nhôm dẹt và thanh nhôm tròn phía trong tạo nhiều khe thoáng lưu thông không khí giúp tăng hiệu quả tản nhiệt và duy trì tuổi thọ tối đa cho Chip LED.
+Sản phẩm thích hợp dùng cho các showroom, phòng trưng bày, cửa hàng,…yêu cầu thời gian chiếu sáng dài mà vẫn đảm bảo tuổi thọ đèn
+Chóa đèn sâu 7 cm giúp tăng độ chiếu rọi và tập trung ánh sáng.
+Chỉ số hoàn màu Ra&gt;85 giúp ánh sáng trung thực hơn.
+Bộ nguồn đặt trong phần nối thân đến bộ phận kết nối vào ray, thu nhỏ kích thước đế đèn, tăng vẻ thẩm mỹ cho sản phẩm.
+Thiết kế tinh tế cùng màu sơn trắng hoặc đen cao cấp tăng hiệu quả trang trí.
+Màu ánh sáng của đèn: màu trắng, màu vàng và dòng 3 màu: thay đổi linh hoạt giữa trắng, vàng, trung tính để quý khách hàng có đa dạng các lựa chọn phù hợp với thiết kế kiến trúc và sở thích của mình.
+Sản phẩm được bảo hành 24 tháng trên toàn quốc.</t>
         </is>
       </c>
       <c r="Q14" t="inlineStr">
@@ -30713,6 +31619,19 @@
 Bảo hành: 24 tháng</t>
         </is>
       </c>
+      <c r="T14" t="inlineStr">
+        <is>
+          <t>Những đặc điểm cơ bản của dòng đèn LED rọi ray tam cấp
+Đèn có khả năng tản nhiệt tốt hơn 5 lần so với các dòng đèn LED thông thường. Tản nhiệt gồm nhiều thanh nhôm dẹt và thanh nhôm tròn phía trong tạo nhiều khe thoáng lưu thông không khí giúp tăng hiệu quả tản nhiệt và duy trì tuổi thọ tối đa cho Chip LED.
+Sản phẩm thích hợp dùng cho các showroom, phòng trưng bày, cửa hàng,…yêu cầu thời gian chiếu sáng dài mà vẫn đảm bảo tuổi thọ đèn
+Chóa đèn sâu 7 cm giúp tăng độ chiếu rọi và tập trung ánh sáng.
+Chỉ số hoàn màu Ra&gt;85 giúp ánh sáng trung thực hơn.
+Bộ nguồn đặt trong phần nối thân đến bộ phận kết nối vào ray, thu nhỏ kích thước đế đèn, tăng vẻ thẩm mỹ cho sản phẩm.
+Thiết kế tinh tế cùng màu sơn trắng hoặc đen cao cấp tăng hiệu quả trang trí.
+Màu ánh sáng của đèn: màu trắng, màu vàng và dòng 3 màu: thay đổi linh hoạt giữa trắng, vàng, trung tính để quý khách hàng có đa dạng các lựa chọn phù hợp với thiết kế kiến trúc và sở thích của mình.
+Sản phẩm được bảo hành 24 tháng trên toàn quốc.</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
@@ -30912,11 +31831,6 @@
           <t>Đèn LED rọi ray tam cấp 10W thân đen - Ba màu</t>
         </is>
       </c>
-      <c r="D17" t="inlineStr">
-        <is>
-          <t>TLC-RTC-TĐ-10W</t>
-        </is>
-      </c>
       <c r="F17" t="inlineStr">
         <is>
           <t>Đèn LED rọi ray</t>
@@ -30924,7 +31838,7 @@
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>{"cong_suat": "10W", "anh_sang": "Ba màu(Trắng/ Vàng/trung tính)", "nhiet_do_mau": "3500K/6500K", "kich_thuoc": "Φ 70x135x90", "chip_led": "Chip LED COB", "hieu_suat_quang": "110-120 Lm/w", "chi_so_hoan_mau": "CRI≥85", "dien_ap": "85-265V", "thuong_hieu": "TLC LIGHTING", "tuoi_tho": "40.000h", "bao_hanh": "24 tháng", "do_hoan_mau": "&gt;85", "dien_ap_ac": "85-265V", "tuoi_tho_chip_led": "40.000 giờ"}</t>
+          <t>{"cong_suat": "10W", "anh_sang": "Ba màu(Trắng/ Vàng/trung tính)", "nhiet_do_mau": "3500K/6500K", "kich_thuoc": "Φ 70x135x90", "chip_led": "Chip LED COB", "hieu_suat_quang": "110-120 Lm/w", "chi_so_hoan_mau": "CRI≥85", "dien_ap": "85-265V", "thuong_hieu": "TLC LIGHTING", "tuoi_tho": "40.000h", "bao_hanh": "24 tháng"}</t>
         </is>
       </c>
       <c r="J17" t="n">
@@ -31352,7 +32266,7 @@
       </c>
       <c r="I22" t="inlineStr">
         <is>
-          <t>{"cong_suat": "20W", "anh_sang": "Trắng/ Vàng", "nhiet_do_mau": "3500K/6500K", "kich_thuoc": "Φ 80×240", "chip_led": "Chip LED COB", "hieu_suat_quang": "110-120 Lm/w, 110~120Lm/w", "chi_so_hoan_mau": "CRI≥85", "dien_ap": "85-265V", "thuong_hieu": "TLC LIGHTING", "tuoi_tho": "40.000h", "bao_hanh": "24 tháng", "quang_thong": "3600Lm", "do_hoan_mau": "&gt;85", "dien_ap_ac": "85-265V", "tuoi_tho_chip_led": "40.000 giờ"}</t>
+          <t>{"cong_suat": "20W", "anh_sang": "Trắng/ Vàng", "nhiet_do_mau": "3500K/6500K", "kich_thuoc": "Φ 80×240", "chip_led": "Chip LED COB", "hieu_suat_quang": "110-120 Lm/w", "chi_so_hoan_mau": "CRI≥85", "dien_ap": "85-265V", "thuong_hieu": "TLC LIGHTING", "tuoi_tho": "40.000h", "bao_hanh": "24 tháng", "quang_thong": "3600Lm", "do_hoan_mau": "&gt;85", "dien_ap_ac": "85-265V", "tuoi_tho_chip_led": "40.000 giờ"}</t>
         </is>
       </c>
       <c r="J22" t="n">
@@ -31430,7 +32344,7 @@
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>TLC-RTC-TT-10W-03</t>
+          <t>TLC-RTC-TT-10W</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
@@ -31440,7 +32354,7 @@
       </c>
       <c r="I23" t="inlineStr">
         <is>
-          <t>{"cong_suat": "10W", "anh_sang": "Ba màu(Trắng/ Vàng/trung tính), Ba màu", "nhiet_do_mau": "3500K/6500K", "kich_thuoc": "Φ 70x135x90, ø70×135×90 mm", "chip_led": "Chip LED COB", "hieu_suat_quang": "110-120 Lm/w, 110 – 120 Lm/W", "chi_so_hoan_mau": "CRI≥85", "dien_ap": "85-265V", "thuong_hieu": "TLC LIGHTING", "tuoi_tho": "40.000h", "bao_hanh": "24 tháng", "quang_thong": "1200 Lm", "do_hoan_mau": "Ra &gt; 85", "chat_lieu": "Nhôm, nhựa", "tuoi_tho_chip_led": "40.000 giờ"}</t>
+          <t>{"cong_suat": "10W", "anh_sang": "Ba màu(Trắng/ Vàng/trung tính)", "nhiet_do_mau": "3500K/6500K", "kich_thuoc": "Φ 70x135x90", "chip_led": "Chip LED COB", "hieu_suat_quang": "110-120 Lm/w", "chi_so_hoan_mau": "CRI≥85", "dien_ap": "85-265V", "thuong_hieu": "TLC LIGHTING", "tuoi_tho": "40.000h", "bao_hanh": "24 tháng", "quang_thong": "1200 Lm", "do_hoan_mau": "Ra &gt; 85", "dien_ap_ac": "85-265V", "chat_lieu": "Nhôm, nhựa", "tuoi_tho_chip_led": "40.000 giờ"}</t>
         </is>
       </c>
       <c r="J23" t="n">
@@ -31515,7 +32429,7 @@
       </c>
       <c r="I24" t="inlineStr">
         <is>
-          <t>{"cong_suat": "10W", "anh_sang": "Trắng/ Vàng", "nhiet_do_mau": "3500K/6500K", "kich_thuoc": "Φ 60×210", "chip_led": "Chip LED COB", "hieu_suat_quang": "110-120 Lm/w", "chi_so_hoan_mau": "CRI≥85", "dien_ap": "85-265V", "thuong_hieu": "TLC LIGHTING", "tuoi_tho": "40.000h", "bao_hanh": "24 tháng"}</t>
+          <t>{"cong_suat": "10W", "anh_sang": "Trắng/ Vàng", "nhiet_do_mau": "3500K/6500K", "kich_thuoc": "Φ 60×210", "chip_led": "Chip LED COB", "hieu_suat_quang": "110-120 Lm/w", "chi_so_hoan_mau": "CRI≥85", "dien_ap": "85-265V", "thuong_hieu": "TLC LIGHTING", "tuoi_tho": "40.000h", "bao_hanh": "24 tháng", "quang_thong": "3600Lm", "do_hoan_mau": "&gt;85", "dien_ap_ac": "85-265V", "tuoi_tho_chip_led": "40.000 giờ"}</t>
         </is>
       </c>
       <c r="J24" t="n">
@@ -31598,7 +32512,7 @@
       </c>
       <c r="I25" t="inlineStr">
         <is>
-          <t>{"cong_suat": "10W", "anh_sang": "Trắng/ Vàng", "nhiet_do_mau": "3500K/6500K", "kich_thuoc": "Φ 60×210", "chip_led": "Chip LED COB", "hieu_suat_quang": "110-120 Lm/w", "chi_so_hoan_mau": "CRI≥85", "dien_ap": "85-265V", "thuong_hieu": "TLC LIGHTING", "tuoi_tho": "40.000h", "bao_hanh": "24 tháng", "tuoi_tho_chip_led": "40.000 giờ"}</t>
+          <t>{"cong_suat": "10W", "anh_sang": "Trắng/ Vàng", "nhiet_do_mau": "3500K/6500K", "kich_thuoc": "Φ 60×210", "chip_led": "Chip LED COB", "hieu_suat_quang": "110-120 Lm/w", "chi_so_hoan_mau": "CRI≥85", "dien_ap": "85-265V", "thuong_hieu": "TLC LIGHTING", "tuoi_tho": "40.000h", "bao_hanh": "24 tháng"}</t>
         </is>
       </c>
       <c r="J25" t="n">
@@ -31831,7 +32745,7 @@
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>{"cong_suat": "46W", "anh_sang": "5 Chế độ(Trắng-Vàng-Trung Tính-Xanh Dương-chế độ ban ngày), trắng, vàng, trung tính, xanh dương, chế độ ban đêm", "nhiet_do_mau": "3500K/6500K", "kich_thuoc": "Φ 440×70", "chip_led": "Chip Epistar", "hieu_suat_quang": "110-120 Lm/w, 110~120Lm/w", "chi_so_hoan_mau": "CRI≥85, &gt;85", "dien_ap": "85-265V", "thuong_hieu": "TLC LIGHTING", "tuoi_tho": "40.000h", "bao_hanh": "24 tháng", "hang_san_xuat": "TLC LIGHTING", "xuat_xu": "Việt Nam", "quang_thong": "5110Lm", "dien_ap_ac": "85-265V", "tuoi_tho_chip_led": "40.000 giờ"}</t>
+          <t>{"cong_suat": "46W", "anh_sang": "5 Chế độ(Trắng-Vàng-Trung Tính-Xanh Dương-chế độ ban ngày)", "nhiet_do_mau": "3500K/6500K", "kich_thuoc": "Φ 440×70", "chip_led": "Chip Epistar", "hieu_suat_quang": "110-120 Lm/w, 110~120Lm/w", "chi_so_hoan_mau": "CRI≥85", "dien_ap": "85-265V", "thuong_hieu": "TLC LIGHTING", "tuoi_tho": "40.000h", "bao_hanh": "24 tháng", "hang_san_xuat": "TLC LIGHTING", "xuat_xu": "Việt Nam", "quang_thong": "5110Lm", "do_hoan_mau": "&gt;85", "dien_ap_ac": "85-265V", "tuoi_tho_chip_led": "40.000 giờ"}</t>
         </is>
       </c>
       <c r="J2" t="n">
@@ -31969,6 +32883,37 @@
 Chip LED: Chip Epistar
 Tuổi thọ chip LED: 40.000 giờ
 Bảo hành: 24 tháng</t>
+        </is>
+      </c>
+      <c r="T3" t="inlineStr">
+        <is>
+          <t>Thông số kỹ thuật:
+Mã sản phẩm
+TLC-OHS-76W-03
+Hãng sản xuất
+TLC LIGHTING
+Xuất xứ
+Việt Nam
+Công suất
+76W
+Kích thước
+Φ 550×70
+Hiệu suất quang
+110~120Lm/w
+Quang thông
+8350Lm
+Độ hoàn màu:
+&gt;85
+Ánh sáng
+5 Chế độ(Trắng-Vàng-Trung Tính-Xanh Dương-chế độ ban ngày)
+Điện áp (AC)
+85-265V
+Chip LED
+Chip Epistar
+Tuổi thọ chip LED
+40.000 giờ
+Bảo hành
+24 tháng</t>
         </is>
       </c>
     </row>
@@ -32215,7 +33160,7 @@
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>{"cong_suat": "12W", "anh_sang": "Trắng/Vàng/Trung tính", "chip_led": "OSRAM – CHLB Đức", "cri": "85-90Ra", "flicker": "0,1%-0,2% Không nhấp nháy", "ugr": "~19 Hạn chế chói mắt", "duong_kinh_lo_khoet": "D110mm", "kich_thuoc": "Ø148×37 mm", "bao_ve_thi_luc": "Hạn chế ánh sáng xanh", "bao_hanh": "36 tháng", "thuong_hieu": "TLC LIGHTING"}</t>
+          <t>{"cong_suat": "12W", "anh_sang": "Trắng/Vàng/Trung tính", "chip_led": "OSRAM – CHLB Đức", "cri": "85-90Ra", "flicker": "0,1%-0,2% Không nhấp nháy", "ugr": "~19 Hạn chế chói mắt", "duong_kinh_lo_khoet": "D110mm", "kich_thuoc": "Ø148×37 mm", "bao_ve_thi_luc": "Hạn chế ánh sáng xanh", "bao_hanh": "36 tháng"}</t>
         </is>
       </c>
       <c r="J3" t="n">
@@ -32373,7 +33318,7 @@
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>{"cong_suat": "12W", "anh_sang": "Trắng/Vàng/Trung tính", "chip_led": "OSRAM – CHLB Đức", "cri": "85-90Ra", "flicker": "0,1%-0,2% Không nhấp nháy", "ugr": "~19 Hạn chế chói mắt", "duong_kinh_lo_khoet": "D110mm", "kich_thuoc": "Ø148×37 mm", "bao_ve_thi_luc": "Hạn chế ánh sáng xanh", "bao_hanh": "36 tháng"}</t>
+          <t>{"cong_suat": "12W", "anh_sang": "Trắng/Vàng/Trung tính", "cri": "85-90Ra", "flicker": "0,1%-0,2% Không nhấp nháy", "ugr": "~19 Hạn chế chói mắt", "duong_kinh_lo_khoet": "D110mm", "kich_thuoc": "Ø148×37 mm", "bao_ve_thi_luc": "Hạn chế ánh sáng xanh", "bao_hanh": "36 tháng"}</t>
         </is>
       </c>
       <c r="J5" t="n">
@@ -32452,7 +33397,7 @@
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>{"cong_suat": "12W", "anh_sang": "3 màu", "cri": "OSRAM – CHLB Đức, 85-90Ra", "flicker": "0,1%-0,2% Không nhấp nháy", "ugr": "~19 Hạn chế chói mắt", "duong_kinh_lo_khoet": "D110mm", "kich_thuoc": "Ø148×37 mm", "bao_ve_thi_luc": "Hạn chế ánh sáng xanh", "bao_hanh": "36 tháng", "chip_led": "OSRAM – CHLB Đức"}</t>
+          <t>{"cong_suat": "12W", "anh_sang": "3 màu", "chip_led": "OSRAM – CHLB Đức", "flicker": "0,1%-0,2% Không nhấp nháy", "ugr": "~19 Hạn chế chói mắt", "duong_kinh_lo_khoet": "D110mm", "kich_thuoc": "Ø148×37 mm", "bao_ve_thi_luc": "Hạn chế ánh sáng xanh", "bao_hanh": "36 tháng", "cri": "85-90Ra", "do_ben_sang": "L70-50.000h"}</t>
         </is>
       </c>
       <c r="J6" t="n">
@@ -32531,7 +33476,7 @@
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>{"cong_suat": "12W", "anh_sang": "Trắng/Vàng/Trung tính", "cri": "OSRAM – CHLB Đức", "flicker": "0,1%-0,2% Không nhấp nháy", "ugr": "~19 Hạn chế chói mắt", "duong_kinh_lo_khoet": "D110mm", "kich_thuoc": "Ø148×37 mm", "bao_ve_thi_luc": "Hạn chế ánh sáng xanh", "bao_hanh": "36 tháng", "thuong_hieu": "TLC LIGHTING", "chip_led": "OSRAM – CHLB Đức"}</t>
+          <t>{"cong_suat": "12W", "anh_sang": "Trắng/Vàng/Trung tính", "chip_led": "OSRAM – CHLB Đức", "cri": "85-90Ra", "flicker": "0,1%-0,2% Không nhấp nháy", "ugr": "~19 Hạn chế chói mắt", "duong_kinh_lo_khoet": "D110mm", "kich_thuoc": "Ø148×37 mm", "bao_ve_thi_luc": "Hạn chế ánh sáng xanh", "bao_hanh": "36 tháng", "thuong_hieu": "TLC LIGHTING"}</t>
         </is>
       </c>
       <c r="J7" t="n">
@@ -32610,7 +33555,7 @@
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>{"cong_suat": "07W", "anh_sang": "3 màu", "flicker": "0,1%-0,2% Không nhấp nháy", "ugr": "~19 Hạn chế chói mắt", "duong_kinh_lo_khoet": "D90mm", "kich_thuoc": "Ø120×37 mm", "bao_ve_thi_luc": "Hạn chế ánh sáng xanh", "bao_hanh": "36 tháng", "chip_led": "OSRAM – CHLB Đức", "cri": "85-90Ra"}</t>
+          <t>{"cong_suat": "07W, 7W", "anh_sang": "3 màu", "flicker": "0,1%-0,2% Không nhấp nháy", "ugr": "~19 Hạn chế chói mắt", "duong_kinh_lo_khoet": "D90mm", "kich_thuoc": "Ø120×37 mm", "bao_ve_thi_luc": "Hạn chế ánh sáng xanh", "bao_hanh": "36 tháng", "thuong_hieu": "TLC LIGHTING", "chip_led": "OSRAM – CHLB Đức", "cri": "85-90Ra"}</t>
         </is>
       </c>
       <c r="J8" t="n">
@@ -32689,7 +33634,7 @@
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>{"cong_suat": "07W, 7W", "anh_sang": "Trắng/Vàng/Trung tính", "chip_led": "OSRAM – CHLB Đức", "cri": "85-90Ra, 97/100", "flicker": "0,1%-0,2% Không nhấp nháy", "ugr": "~19 Hạn chế chói mắt", "duong_kinh_lo_khoet": "D90mm", "kich_thuoc": "Ø120×37 mm", "bao_ve_thi_luc": "Hạn chế ánh sáng xanh", "bao_hanh": "36 tháng, 30-36 tháng, 2 năm", "nhiet_do_mau": "3000-6000K"}</t>
+          <t>{"cong_suat": "07W", "anh_sang": "Trắng/Vàng/Trung tính", "chip_LED": "OSRAM – CHLB Đức", "CRI": "85-90Ra", "Flicker": "0,1%-0,2% Không nhấp nháy", "UGR": "~19 Hạn chế chói mắt", "duong_kinh_lo_khoet": "D90mm", "kich_thuoc": "Ø120×37 mm", "bao_ve_thi_luc": "Hạn chế ánh sáng xanh", "bao_hanh": "36 tháng"}</t>
         </is>
       </c>
       <c r="J9" t="n">
@@ -32768,7 +33713,7 @@
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>{"cong_suat": "07W", "anh_sang": "3 màu", "cri": "85-90Ra", "flicker": "0,1%-0,2% Không nhấp nháy", "ugr": "~19 Hạn chế chói mắt", "duong_kinh_lo_khoet": "D90mm", "kich_thuoc": "Ø120×37 mm", "bao_ve_thi_luc": "Hạn chế ánh sáng xanh", "bao_hanh": "36 tháng", "chip_led": "OSRAM – CHLB Đức"}</t>
+          <t>{"cong_suat": "07W", "anh_sang": "3 màu", "cri": "85-90Ra", "flicker": "0,1%-0,2% Không nhấp nháy", "ugr": "~19 Hạn chế chói mắt", "duong_kinh_lo_khoet": "D90mm", "kich_thuoc": "Ø120×37 mm", "bao_ve_thi_luc": "Hạn chế ánh sáng xanh", "bao_hanh": "36 tháng", "thuong_hieu": "TLC LIGHTING", "chip_led": "OSRAM – CHLB Đức"}</t>
         </is>
       </c>
       <c r="J10" t="n">
@@ -32847,7 +33792,7 @@
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>{"cong_suat": "07W", "anh_sang": "Trắng/Vàng/Trung tính", "cri": "85-90Ra", "flicker": "0,1%-0,2% Không nhấp nháy", "ugr": "~19 Hạn chế chói mắt", "duong_kinh_lo_khoet": "D90mm", "kich_thuoc": "Ø120×37 mm", "bao_ve_thi_luc": "Hạn chế ánh sáng xanh", "bao_hanh": "36 tháng", "chip_led": "OSRAM – CHLB Đức", "thuong_hieu": "TLC LIGHTING"}</t>
+          <t>{"cong_suat": "07W", "anh_sang": "Trắng/Vàng/Trung tính", "chip_led": "OSRAM – CHLB Đức", "flicker": "0,1%-0,2% Không nhấp nháy", "ugr": "~19 Hạn chế chói mắt", "duong_kinh_lo_khoet": "D90mm", "kich_thuoc": "Ø120×37 mm", "bao_ve_thi_luc": "Hạn chế ánh sáng xanh", "bao_hanh": "36 tháng", "cri": "85-90Ra", "do_ben_sang": "L70-50.000h", "nhiet_do_mau_kelvin": "3000-6000K"}</t>
         </is>
       </c>
       <c r="J11" t="n">
@@ -32926,7 +33871,7 @@
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>{"cong_suat": "07W", "anh_sang": "3 màu", "cri": "OSRAM – CHLB Đức", "flicker": "0,1%-0,2% Không nhấp nháy", "ugr": "~19 Hạn chế chói mắt", "duong_kinh_lo_khoet": "D90mm", "kich_thuoc": "Ø120×37 mm", "bao_ve_thi_luc": "Hạn chế ánh sáng xanh", "bao_hanh": "36 tháng", "chip_led": "OSRAM – CHLB Đức"}</t>
+          <t>{"cong_suat": "07W", "anh_sang": "3 màu", "chip_led": "OSRAM – CHLB Đức", "cri": "0,1%-0,2% Không nhấp nháy", "ugr": "~19 Hạn chế chói mắt", "duong_kinh_lo_khoet": "D90mm", "kich_thuoc": "Ø120×37 mm", "bao_ve_thi_luc": "Hạn chế ánh sáng xanh", "bao_hanh": "36 tháng", "thuong_hieu": "TLC LIGHTING", "flicker": "0,1%-0,2% Không nhấp nháy"}</t>
         </is>
       </c>
       <c r="J12" t="n">
@@ -33005,7 +33950,7 @@
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>{"cong_suat": "9W", "anh_sang": "3 màu", "chip_led": "OSRAM – CHLB Đức", "cri": "85-90Ra", "flicker": "0,1%-0,2% Không nhấp nháy", "ugr": "~19 Hạn chế chói mắt", "duong_kinh_lo_khoet": "D90mm", "kich_thuoc": "Ø120×37 mm", "bao_ve_thi_luc": "Hạn chế ánh sáng xanh", "bao_hanh": "36 tháng", "thuong_hieu": "TLC LIGHTING"}</t>
+          <t>{"cong_suat": "9W", "anh_sang": "3 màu", "chip_led": "OSRAM – CHLB Đức", "cri": "85-90Ra", "flicker": "0,1%-0,2% Không nhấp nháy", "ugr": "~19 Hạn chế chói mắt", "duong_kinh_lo_khoet": "D90mm", "kich_thuoc": "Ø120×37 mm", "bao_ve_thi_luc": "Hạn chế ánh sáng xanh", "bao_hanh": "36 tháng"}</t>
         </is>
       </c>
       <c r="J13" t="n">
@@ -33084,7 +34029,7 @@
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>{"cong_suat": "09W", "anh_sang": "Trắng/Vàng/Trung tính", "chip_led": "OSRAM – CHLB Đức", "cri": "85-90Ra", "flicker": "0,1%-0,2% Không nhấp nháy", "ugr": "~19 Hạn chế chói mắt", "duong_kinh_lo_khoet": "D90mm", "kich_thuoc": "Ø120×37 mm", "bao_ve_thi_luc": "Hạn chế ánh sáng xanh", "bao_hanh": "36 tháng", "thuong_hieu": "TLC LIGHTING"}</t>
+          <t>{"cong_suat": "09W", "anh_sang": "Trắng/Vàng/Trung tính", "CRI": "85-90Ra", "Flicker": "0,1%-0,2% Không nhấp nháy", "UGR": "~19 Hạn chế chói mắt", "duong_kinh_lo_khoet": "D90mm", "kich_thuoc": "Ø120×37 mm", "bao_ve_thi_luc": "Hạn chế ánh sáng xanh", "bao_hanh": "36 tháng", "thuong_hieu": "TLC LIGHTING", "chip_LED": "OSRAM – CHLB Đức"}</t>
         </is>
       </c>
       <c r="J14" t="n">
@@ -33163,7 +34108,7 @@
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>{"cong_suat": "9W", "anh_sang": "3 màu", "chip_led": "OSRAM – CHLB Đức", "cri": "85-90Ra", "flicker": "0,1%-0,2% Không nhấp nháy", "ugr": "~19 Hạn chế chói mắt", "duong_kinh_lo_khoet": "D90mm", "kich_thuoc": "Ø120×37 mm", "bao_ve_thi_luc": "Hạn chế ánh sáng xanh", "bao_hanh": "36 tháng", "thuong_hieu": "TLC LIGHTING"}</t>
+          <t>{"cong_suat": "9W", "anh_sang": "3 màu", "cri": "OSRAM – CHLB Đức", "flicker": "0,1%-0,2% Không nhấp nháy", "ugr": "~19 Hạn chế chói mắt", "duong_kinh_lo_khoet": "D90mm", "kich_thuoc": "Ø120×37 mm", "bao_ve_thi_luc": "Hạn chế ánh sáng xanh", "bao_hanh": "36tháng", "thuong_hieu": "TLC LIGHTING", "chip_led": "OSRAM – CHLB Đức"}</t>
         </is>
       </c>
       <c r="J15" t="n">
@@ -33242,7 +34187,7 @@
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>{"cong_suat": "09W", "anh_sang": "Trắng/Vàng/Trung tính", "chip_led": "OSRAM – CHLB Đức", "flicker": "0,1%-0,2% Không nhấp nháy", "ugr": "~19 Hạn chế chói mắt", "duong_kinh_lo_khoet": "D90mm", "kich_thuoc": "Ø120×37 mm", "bao_ve_thi_luc": "Hạn chế ánh sáng xanh", "bao_hanh": "36 tháng", "cri": "85-90Ra", "do_ben_sang": "L70-50.000h", "hieu_suat_quang_cua_chip_osram": "110 Lm/W", "chi_so_hoan_mau_cao_nhat_dat": "97/100", "chi_so_nhiet_do_mau_kelvin": "3000-6000K"}</t>
+          <t>{"cong_suat": "09W", "anh_sang": "Trắng/Vàng/Trung tính", "cri": "OSRAM – CHLB Đức", "flicker": "0,1%-0,2% Không nhấp nháy", "ugr": "~19 Hạn chế chói mắt", "duong_kinh_lo_khoet": "D90mm", "kich_thuoc": "Ø120×37 mm", "bao_ve_thi_luc": "Hạn chế ánh sáng xanh", "bao_hanh": "36 tháng", "thuong_hieu": "TLC LIGHTING", "chip_led": "OSRAM – CHLB Đức"}</t>
         </is>
       </c>
       <c r="J16" t="n">
@@ -33321,7 +34266,7 @@
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>{"cong_suat": "9W", "anh_sang": "3 màu", "chip_LED": "OSRAM – CHLB Đức", "CRI": "85-90Ra", "Flicker": "0,1%-0,2% Không nhấp nháy", "UGR": "~19 Hạn chế chói mắt", "duong_kinh_lo_khoet": "D90mm", "kich_thuoc": "Ø120×37 mm", "bao_ve_thi_luc": "Hạn chế ánh sáng xanh", "bao_hanh": "36 tháng", "thuong_hieu": "TLC LIGHTING"}</t>
+          <t>{"cong_suat": "9W", "anh_sang": "3 màu", "CRI": "OSRAM – CHLB Đức", "Flicker": "0,1%-0,2% Không nhấp nháy", "UGR": "~19 Hạn chế chói mắt", "duong_kinh_lo_khoet": "D90mm", "kich_thuoc": "Ø120×37 mm", "bao_ve_thi_luc": "Hạn chế ánh sáng xanh", "bao_hanh": "36 tháng", "thuong_hieu": "TLC LIGHTING", "chip_LED": "OSRAM – CHLB Đức"}</t>
         </is>
       </c>
       <c r="J17" t="n">
@@ -33400,7 +34345,7 @@
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>{"cong_suat": "09W", "anh_sang": "Trắng/Vàng/Trung tính", "flicker": "0,1%-0,2% Không nhấp nháy", "ugr": "~19 Hạn chế chói mắt", "duong_kinh_lo_khoet": "D90mm", "kich_thuoc": "Ø120×37 mm", "bao_ve_thi_luc": "Hạn chế ánh sáng xanh", "bao_hanh": "36 tháng", "chip_led": "OSRAM – CHLB Đức", "cri": "85-90Ra"}</t>
+          <t>{"cong_suat": "09W", "anh_sang": "Trắng/Vàng/Trung tính", "cri": "OSRAM – CHLB Đức", "flicker": "0,1%-0,2% Không nhấp nháy", "ugr": "~19 Hạn chế chói mắt", "duong_kinh_lo_khoet": "D90mm", "kich_thuoc": "Ø120×37 mm", "bao_ve_thi_luc": "Hạn chế ánh sáng xanh", "bao_hanh": "36 tháng", "chip_led": "OSRAM – CHLB Đức"}</t>
         </is>
       </c>
       <c r="J18" t="n">
@@ -33479,7 +34424,7 @@
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>{"cong_suat": "07W", "anh_sang": "Trắng/Vàng/Trung tính", "CRI": "85-90Ra", "Flicker": "0,1%-0,2% Không nhấp nháy", "UGR": "~19 Hạn chế chói mắt", "duong_kinh_lo_khoet": "D90mm", "kich_thuoc": "Ø120×37 mm", "bao_ve_thi_luc": "Hạn chế ánh sáng xanh", "bao_hanh": "36 tháng", "chip_LED": "OSRAM – CHLB Đức"}</t>
+          <t>{"cong_suat": "07W", "anh_sang": "Trắng/Vàng/Trung tính", "chip_led": "OSRAM – CHLB Đức", "cri": "0,1%-0,2% Không nhấp nháy", "ugr": "~19 Hạn chế chói mắt", "duong_kinh_lo_khoet": "D90mm", "kich_thuoc": "Ø120×37 mm", "bao_ve_thi_luc": "Hạn chế ánh sáng xanh", "bao_hanh": "36 tháng", "thuong_hieu": "TLC LIGHTING"}</t>
         </is>
       </c>
       <c r="J19" t="n">
@@ -33696,7 +34641,7 @@
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>{"cong_suat": "825W", "so_luong_bong": "03 bóng", "kich_thuoc": "490x250x245 mm", "mau_sac_anh_sang": "Ánh sáng trắng", "dien_ap": "220V – 50Hz", "tuoi_tho": "10.000h", "bao_hanh": "36 tháng", "so_bong": "3", "mau_anh_sang": "Trắng"}</t>
+          <t>{"cong_suat": "825W", "so_luong_bong": "03 bóng", "kich_thuoc": "490x250x245 mm", "mau_sac_anh_sang": "Ánh sáng trắng", "dien_ap": "220V – 50Hz", "tuoi_tho": "10.000h", "bao_hanh": "36 tháng", "so_bong": "3", "mau_anh_sang": "Trắng", "tuoi_tho_gio": "10.000 giờ"}</t>
         </is>
       </c>
       <c r="J2" t="n">
@@ -33940,7 +34885,7 @@
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>{"cong_suat": "275W x 2 Bóng", "so_luong_bong": "02 bóng", "kich_thuoc": "400x210x210 mm", "mau_sac_anh_sang": "Ánh sáng vàng", "dien_ap": "220V – 50Hz", "tuoi_tho": "10.000h", "bao_hanh": "36 tháng", "so_bong": "2", "mau_anh_sang": "Vàng"}</t>
+          <t>{"cong_suat": "550W", "so_luong_bong": "02 bóng", "kich_thuoc": "400x210x210 mm", "mau_sac_anh_sang": "Ánh sáng vàng", "dien_ap": "220V – 50Hz", "tuoi_tho": "10.000h", "bao_hanh": "36 tháng", "so_bong": "2", "mau_anh_sang": "Vàng"}</t>
         </is>
       </c>
       <c r="J5" t="n">
@@ -34022,7 +34967,7 @@
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>{"cong_suat": "550W", "so_luong_bong": "02 bóng", "kich_thuoc": "400x210x210 mm", "mau_sac_anh_sang": "Ánh sáng vàng", "dien_ap": "220V – 50Hz", "tuoi_tho": "10.000h", "bao_hanh": "36 tháng", "so_bong": "2", "mau_anh_sang": "Trắng", "tuoi_tho_gio": "10.000 giờ"}</t>
+          <t>{"cong_suat": "275W x 2 Bóng", "dien_ap": "AC 220V – 50Hz", "kich_thuoc": "400x210x210 mm", "so_bong": "2", "mau_anh_sang": "Trắng", "tuoi_tho": "10.000 giờ", "bao_hanh": "36 tháng"}</t>
         </is>
       </c>
       <c r="J6" t="n">
@@ -34111,7 +35056,7 @@
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>{"cong_suat": "825W", "so_luong_bong": "03 bóng", "kich_thuoc": "510x250x230 mm", "mau_sac_anh_sang": "Ánh sáng vàng", "dien_ap": "220V – 50Hz", "tuoi_tho": "10.000h", "bao_hanh": "36 tháng", "so_bong": "3", "mau_anh_sang": "Vàng", "tuoi_tho_don_vi_gio": "10.000 giờ"}</t>
+          <t>{"cong_suat": "825W", "so_luong_bong": "03 bóng", "kich_thuoc": "510x250x230 mm", "mau_sac_anh_sang": "Ánh sáng vàng", "dien_ap": "220V – 50Hz", "tuoi_tho": "10.000h", "bao_hanh": "36 tháng", "thuong_hieu": "TLC LIGHTING", "so_bong": "3", "mau_anh_sang": "Vàng"}</t>
         </is>
       </c>
       <c r="J7" t="n">
@@ -34189,6 +35134,11 @@
           <t>Đèn sưởi nhà tắm TLC LIGHTING - 3 Bóng trắng</t>
         </is>
       </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>TLC-SNT-BT03</t>
+        </is>
+      </c>
       <c r="F8" t="inlineStr">
         <is>
           <t>ĐÈN SƯỞI NHÀ TẮM</t>
@@ -34196,7 +35146,7 @@
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>{"cong_suat": "275W x 3 Bóng", "so_luong_bong": "03 bóng", "kich_thuoc": "510x250x230 mm", "mau_sac_anh_sang": "Ánh sáng vàng", "dien_ap": "220V – 50Hz", "tuoi_tho": "10.000h", "bao_hanh": "36 tháng"}</t>
+          <t>{"cong_suat": "825W", "so_luong_bong": "03 bóng", "kich_thuoc": "510x250x230 mm", "mau_sac_anh_sang": "Ánh sáng vàng", "dien_ap": "220V – 50Hz", "tuoi_tho": "10.000h", "bao_hanh": "36 tháng"}</t>
         </is>
       </c>
       <c r="J8" t="n">
@@ -34422,7 +35372,7 @@
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>{"cong_suat": "550W", "so_luong_bong": "02 bóng", "kich_thuoc": "430x225x220 mm", "mau_sac_anh_sang": "Ánh sáng trắng", "dien_ap": "220V – 50Hz", "tuoi_tho": "10.000h", "bao_hanh": "36 tháng", "thuong_hieu": "TLC LIGHTING", "so_bong": "2", "mau_anh_sang": "Trắng"}</t>
+          <t>{"cong_suat": "550W", "so_luong_bong": "02 bóng", "kich_thuoc": "430x225x220 mm", "mau_sac_anh_sang": "Ánh sáng trắng", "dien_ap": "220V – 50Hz", "tuoi_tho": "10.000h", "bao_hanh": "36 tháng", "so_bong": "2", "mau_anh_sang": "Trắng"}</t>
         </is>
       </c>
       <c r="J2" t="n">
@@ -34642,7 +35592,7 @@
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>{"cong_suat_dong_co": "100 W", "cong_suat": "AC 19/30/41/64/97 W", "sai_canh": "1400 (56”)", "chat_lieu_canh_quat": "Kim loại", "mau_sac": "Trắng", "so_canh_quat": "5", "so_toc_do_gio": "5", "bao_hanh": "24 tháng tại nhà", "thuong_hieu": "TLC LIGHTING", "luu_luong_gio": "90/120/140/208/286 m3/min"}</t>
+          <t>{"cong_suat": "100W", "dong_co": "AC 19/30/41/64/97 W", "sai_canh": "1400 (56”)", "chat_lieu_canh_quat": "Kim loại", "mau_sac": "Trắng", "so_canh_quat": "5", "so_toc_do_gio": "5", "luu_luong_gio": "90/120/140/208/286 m3/min", "bao_hanh": "24 Tháng tại nhà"}</t>
         </is>
       </c>
       <c r="J2" t="n">
@@ -34656,6 +35606,12 @@
       <c r="M2" t="inlineStr">
         <is>
           <t>https://tlclighting.com.vn/wp-content/uploads/2026/06/1-2.png</t>
+        </is>
+      </c>
+      <c r="P2" t="inlineStr">
+        <is>
+          <t>Biên dạng sải cánh lớn hơn 5%
+Bảo hành tại nhà 24 tháng</t>
         </is>
       </c>
       <c r="Q2" t="inlineStr">
@@ -34672,6 +35628,15 @@
 Bảo hành: 24 Tháng tại nhà</t>
         </is>
       </c>
+      <c r="T2" t="inlineStr">
+        <is>
+          <t>Đặc điểm nổi bật
+Biên dạng sải cánh lớn hơn 5%:
+Thiết kế đột phá với biên dạng sải cánh được mở rộng hơn 5% so với các dòng quạt thông thường. Sự cải tiến này giúp tối ưu hóa khí động học, mở rộng vùng làm mát và tăng cường lưu lượng gió vượt trội nhưng vẫn đảm bảo thiết bị vận hành êm ái, tiết kiệm điện năng.
+Bảo hành tại nhà 24 tháng:
+Chế độ bảo hành tại nhà lên đến 24 tháng chính là lời cam kết vàng cho chất lượng vượt trội của dòng quạt trần thế hệ mới. Không chỉ mang đến sản phẩm bền bỉ, chúng tôi còn đồng hành cùng sự an tâm của bạn bằng dịch vụ kỹ thuật chuyên nghiệp, xử lý nhanh chóng mọi sự cố ngay tại không gian sống mà bạn không cần tốn công tháo lắp hay di chuyển thiết bị.</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -34699,7 +35664,7 @@
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>{"cong_suat_dong_co": "80 W", "loai_dong_co": "AC", "duong_kinh_quat": "1500mm", "so_luong_canh": "5 cánh", "so_cap_toc_do": "5 cấp độ", "den_LED": "Không", "dien_ap": "AC 220V/ 50Hz", "bao_hanh": "5 năm", "cong_suat_toi_da": "80 W", "duong_kinh_canh_quat": "1500mm", "chat_lieu_canh_quat": "Kim loại", "mau_sac": "Màu đen", "so_canh_quat": "5", "so_toc_do_gio": "5", "dieu_khien": "Hộp số điều khiển", "dien_ap_AC": "AC 220V-50Hz", "dien_ap_": "220V – 50 Hz"}</t>
+          <t>{"cong_suat_dong_co": "80 W", "loai_dong_co": "AC", "duong_kinh_quat": "1500mm", "so_luong_canh": "5 cánh", "so_cap_toc_do": "5 cấp độ", "den_LED": "Không", "dien_ap": "AC 220V/ 50Hz", "bao_hanh": "5 năm", "thuong_hieu": "TLC LIGHTING", "cong_suat_toi_da": "80 W", "duong_kinh_canh_quat": "1500mm", "chat_lieu_canh_quat": "Kim loại", "mau_sac": "Màu đen", "so_canh_quat": "5", "so_toc_do_gio": "5", "dieu_khien": "Hộp số điều khiển", "dien_ap_AC": "AC 220V-50Hz"}</t>
         </is>
       </c>
       <c r="J3" t="n">
@@ -34782,7 +35747,7 @@
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>{"cong_suat_dong_co": "80W", "loai_dong_co": "AC", "duong_kinh_quat": "1500mm", "so_luong_canh": "5 cánh", "so_cap_toc_do": "5 cấp độ", "den_LED": "Không", "dien_ap": "AC 220V/ 50Hz", "bao_hanh": "5 năm", "thuong_hieu": "TLC LIGHTING", "cong_suat_toi_da": "80 W", "duong_kinh_canh_quat": "1500mm", "chat_lieu_canh_quat": "Kim loại", "mau_sac": "Màu trắng", "so_canh_quat": "5", "so_toc_do_gio": "5", "dieu_khien": "Hộp số điều khiển", "dien_ap_AC": "AC 220V-50Hz", "bao_hanh_dong_co": "5 năm"}</t>
+          <t>{"cong_suat_dong_co": "80W", "loai_dong_co": "AC", "duong_kinh_quat": "1500mm", "so_luong_canh": "5 cánh", "so_cap_toc_do": "5 cấp độ", "den_LED": "Không", "dien_ap": "AC 220V/ 50Hz", "bao_hanh": "5 năm", "thuong_hieu": "TLC LIGHTING", "cong_suat_toi_da": "80 W", "duong_kinh_canh_quat": "1500mm", "chat_lieu_canh_quat": "Kim loại", "mau_sac": "Màu trắng", "so_canh_quat": "5", "so_toc_do_gio": "5", "dieu_khien": "Hộp số điều khiển", "dien_ap_AC": "AC 220V-50Hz"}</t>
         </is>
       </c>
       <c r="J4" t="n">
@@ -34864,7 +35829,7 @@
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>{"cong_suat_dong_co": "56W", "loai_dong_co": "DC", "duong_kinh_quat": "1420mm", "so_luong_canh": "5 cánh", "so_cap_toc_do": "6 cấp độ", "den_LED": "Ba màu", "dien_ap": "AC 220V/ 50Hz", "bao_hanh": "5 năm", "thuong_hieu": "TLC LIGHTING", "cong_suat_toi_da": "56 W", "duong_kinh_canh_quat": "1420mm", "chat_lieu_canh_quat": "Nhựa ABS cao cấp", "mau_sac": "Màu bạc", "so_canh_quat": "5", "so_toc_do_gio": "6", "dieu_khien": "Điều khiển từ xa", "dien_ap_AC": "AC 220V-50Hz", "cong_suat": "56W", "chieu_dai_ti_quat": "25cm"}</t>
+          <t>{"cong_suat_dong_co": "56W", "loai_dong_co": "DC", "duong_kinh_quat": "1420mm", "so_luong_canh": "5 cánh", "so_cap_toc_do": "6 cấp độ", "den_LED": "Ba màu", "dien_ap": "AC 220V/ 50Hz", "bao_hanh": "5 năm", "cong_suat_toi_da": "56 W", "duong_kinh_canh_quat": "1420mm", "chat_lieu_canh_quat": "Nhựa ABS cao cấp", "mau_sac": "Màu bạc", "so_canh_quat": "5", "so_toc_do_gio": "6", "dien_ap_AC": "AC 220V-50Hz"}</t>
         </is>
       </c>
       <c r="J5" t="n">
@@ -34924,7 +35889,7 @@
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>{"cong_suat_dong_co": "80W", "loai_dong_co": "AC", "duong_kinh_quat": "1420mm", "so_luong_canh": "5 cánh", "so_cap_toc_do": "3 cấp độ", "den_LED": "Không", "dien_ap": "AC 220V/ 50Hz", "tuoi_tho": "100.000 giờ", "bao_hanh": "5 năm", "thuong_hieu": "TLC LIGHTING", "cong_suat_toi_da": "82 W", "duong_kinh_canh_quat": "1420mm", "chat_lieu_canh_quat": "Nhựa ABS", "mau_sac": "Màu bạc", "so_canh_quat": "5", "so_toc_do_gio": "3", "dieu_khien": "Điều khiển từ xa, chế độ hẹn giờ tắt", "dien_ap_AC": "50Hz, 220V", "cong_suat": "20W, 42W, 82W (công suất theo cấp độ gió)", "chinh_sach_bao_hanh": "miễn phí tại nhà", "bao_hanh_tai_nha": "hoàn toàn miễn phí 24 tháng", "bao_hanh_dong_co": "5 năm"}</t>
+          <t>{"cong_suat_dong_co": "80W", "loai_dong_co": "AC", "duong_kinh_quat": "1420mm", "so_luong_canh": "5 cánh", "so_cap_toc_do": "3 cấp độ", "den_LED": "Không", "dien_ap": "AC 220V/ 50Hz", "tuoi_tho": "100.000 giờ", "bao_hanh": "5 năm", "thuong_hieu": "TLC LIGHTING", "cong_suat_toi_da": "82 W", "duong_kinh_canh_quat": "1420mm", "chat_lieu_canh_quat": "Nhựa ABS", "mau_sac": "Màu bạc", "so_canh_quat": "5", "so_toc_do_gio": "3", "dieu_khien": "Điều khiển từ xa, chế độ hẹn giờ tắt", "dien_ap_AC": "50Hz, 220V", "dien_ap_": "220V – 50Hz"}</t>
         </is>
       </c>
       <c r="J6" t="n">
@@ -35021,7 +35986,7 @@
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>{"cong_suat_dong_co": "49W", "loai_dong_co": "DC", "duong_kinh_quat": "1370mm", "so_luong_canh": "5 cánh", "so_cap_toc_do": "5 cấp độ", "den_led": "Có", "dien_ap": "AC 220V/ 50Hz", "bao_hanh": "5 năm", "duong_kinh_canh_quat": "1370mm", "chat_lieu_canh_quat": "Nhựa ABS", "mau_sac": "Màu bạc", "so_canh_quat": "5", "so_toc_do_gio": "5", "dieu_khien": "Điều khiển từ xa, chế độ hẹn giờ tắt", "dien_ap_ac": "50Hz, 220V", "cong_suat": "6.3W đến 49W (công suất theo cấp độ gió)"}</t>
+          <t>{"cong_suat_dong_co": "49W", "loai_dong_co": "DC", "duong_kinh_quat": "1370mm", "so_luong_canh": "5 cánh", "so_cap_toc_do": "5 cấp độ", "den_LED": "Có", "dien_ap": "AC 220V/ 50Hz", "bao_hanh": "5 năm", "duong_kinh_canh_quat": "1370mm", "chat_lieu_canh_quat": "Nhựa ABS", "mau_sac": "Màu bạc", "so_canh_quat": "5", "so_toc_do_gio": "5", "dieu_khien": "Điều khiển từ xa, chế độ hẹn giờ tắt", "dien_ap_AC": "50Hz, 220V", "anh_sang": "3 màu trắng, vàng, trung tính"}</t>
         </is>
       </c>
       <c r="J7" t="n">
@@ -35119,7 +36084,7 @@
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>{"cong_suat_dong_co": "49W", "loai_dong_co": "DC", "duong_kinh_quat": "1370mm", "so_luong_canh": "5 cánh", "so_cap_toc_do": "5 cấp độ", "den_LED": "Có", "dien_ap": "AC 220V/ 50Hz", "tuoi_tho": "100.000 giờ", "bao_hanh": "5 năm", "thuong_hieu": "TLC LIGHTING", "duong_kinh_canh_quat": "1370mm", "chat_lieu_canh_quat": "Nhựa ABS", "mau_sac": "Vân gỗ", "so_canh_quat": "5", "so_toc_do_gio": "5", "dieu_khien": "Điều khiển từ xa, hẹn giờ tắt", "dien_ap_AC": "50Hz, 220V", "cong_suat": "6.3W đến 49W (công suất theo cấp độ gió)", "anh_sang": "3 màu trắng, vàng, trung tính"}</t>
+          <t>{"cong_suat_dong_co": "49W", "loai_dong_co": "DC", "duong_kinh_quat": "1370mm", "so_luong_canh": "5 cánh", "so_cap_toc_do": "5 cấp độ", "den_LED": "Có", "dien_ap": "AC 220V/ 50Hz", "tuoi_tho": "100.000 giờ", "bao_hanh": "5 năm", "duong_kinh_canh_quat": "1370mm", "chat_lieu_canh_quat": "Nhựa ABS", "mau_sac": "Vân gỗ", "so_canh_quat": "5", "so_toc_do_gio": "5", "dieu_khien": "Điều khiển từ xa, hẹn giờ tắt", "dien_ap_AC": "50Hz, 220V", "anh_sang": "trắng, vàng, trung tính"}</t>
         </is>
       </c>
       <c r="J8" t="n">
@@ -35311,7 +36276,7 @@
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>{"cong_suat_dong_co": "36W", "loai_dong_co": "DC", "duong_kinh_quat": "1500 mm", "so_luong_canh": "5 cánh", "so_cap_toc_do": "5 cấp độ", "den_LED": "15W, Ánh sáng Ba màu", "dien_ap": "AC 220V/ 50Hz", "bao_hanh": "10 năm", "thuong_hieu": "TLC LIGHTING", "cong_suat_toi_da": "36 W", "duong_kinh_canh_quat": "1500mm", "chat_lieu_canh_quat": "Nhựa ABS cao cấp", "mau_sac": "Màu bạc", "so_canh_quat": "5", "so_toc_do_gio": "5", "anh_sang": "3 màu", "dieu_khien": "Điều khiển từ xa", "dien_ap_AC": "AC 220V-50Hz"}</t>
+          <t>{"cong_suat_dong_co": "36W", "loai_dong_co": "DC", "duong_kinh_quat": "1500 mm", "so_luong_canh": "5 cánh", "so_cap_toc_do": "5 cấp độ", "den_LED": "15W, Ánh sáng Ba màu", "dien_ap": "AC 220V/ 50Hz", "bao_hanh": "10 năm", "thuong_hieu": "TLC LIGHTING", "cong_suat_toi_da": "36 W", "duong_kinh_canh_quat": "1500mm", "chat_lieu_canh_quat": "Nhựa ABS cao cấp", "mau_sac": "Màu bạc", "so_canh_quat": "5", "so_toc_do_gio": "5", "dieu_khien": "Điều khiển từ xa", "dien_ap_AC": "AC 220V-50Hz"}</t>
         </is>
       </c>
       <c r="J10" t="n">
@@ -35389,7 +36354,7 @@
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>{"cong_suat_dong_co": "38W", "sai_canh": "1420mm", "chat_lieu_canh_quat": "Nhựa ABS cao cấp", "mau_sac": "Bạc", "so_canh_quat": "5", "so_toc_do_gio": "8", "bao_hanh": "24 tháng tại nhà", "thuong_hieu": "TLC LIGHTING", "cong_suat": "38W", "loai_dong_co": "BLDC", "duong_kinh_quat": "1420mm", "den_LED": "23W-3 màu (T/V/TT)", "dieu_khien": "Điều khiển từ xa", "luu_luong_gio": "230m3/phút", "bao_hanh_tai_nha": "24 tháng"}</t>
+          <t>{"cong_suat_dong_co": "38W", "loai_dong_co": "BLDC", "sai_canh": "1420mm", "chat_lieu_canh_quat": "Nhựa ABS cao cấp", "mau_sac": "Bạc", "so_canh_quat": "5", "so_toc_do_gio": "8", "bao_hanh": "24 tháng tại nhà", "thuong_hieu": "TLC LIGHTING", "duong_kinh_quat": "1420mm", "den_LED": "23W-3 màu (T/V/TT)", "dieu_khien": "Điều khiển từ xa", "luu_luong_gio": "230m3/phút"}</t>
         </is>
       </c>
       <c r="J11" t="n">
@@ -35403,6 +36368,16 @@
       <c r="M11" t="inlineStr">
         <is>
           <t>https://tlclighting.com.vn/wp-content/uploads/2026/07/06-bạc.png</t>
+        </is>
+      </c>
+      <c r="P11" t="inlineStr">
+        <is>
+          <t>Công nghệ gió E-WIND:tạo gió tự nhiên, êm dịu, mô phỏng những làn gió tươi mát của những cánh đồng hoa. E-wind mang lại luồng gió nhẹ nhàng, giúp lưu thông không khí đồng đều mang đến cảm giác mát mẻ, chăm sóc sức khoẻ và nâng niu từng khoảnh khắc của tổ ấm.
+EV06 được trang bị hệ thống đèn LED công suất 23W, cung cấp nguồn sáng ổn định, đáp ứng tốt nhu cầu chiếu sáng trong mọi không gian. Đèn LED có tuổi thọ cao, tiết kiệm điện năng hạn chế việc thay thế bóng thường xuyên, từ đó giúp giảm chi phí sử dụng và góp phần bảo vệ môi trường.
+Sản phẩm Quạt trần EV06 sử dụng động cơ BLDC thế hệ mới với thiết kế nhỏ gọn, vận hành mạnh mẽ nhưng vẫn đảm bảo độ êm ái và ổn định. Động cơ giúp tiết kiệm đến 50% điện năng so với động cơ truyền thống, đồng thời giảm tiếng ồn, nâng cao tuổi thọ sản phẩm và mang đến trải nghiệm tối ưu cho người sử dụng.
+Thiết kế cánh quạt dạng cong 3D hiện đại giúp giảm lực cản và ma sát với không khí.Tạo lượng gió lớn và phân bổ đều khắp không gian đồng thời giảm thiểu tiếng ồn và rung lắc mang lại hiệu quả làm mát tối ưu.
+Chế độ an toàn :EV06 được trang bị dây treo an toàn cố định nhằm tăng cường khả năng bảo vệ trong quá trình sử dụng. Hệ thống này giúp ngăn ngừa nguy cơ quạt rơi khi ti treo, khớp nối hoặc một số bộ phận khác gặp sự cố, đảm bảo an toàn tối đa cho người sử dụng.
+Sản phẩm được trang bị điều khiển từ xa thông minh cho phép người dùng dễ dàng điều chỉnh tốc độ gió, bật/tắt đèn, lựa chọn chế độ gió hoặc cài đặt hẹn giờ mà không cần di chuyển mang đến sự tiện nghi trong quá trình sử dụng</t>
         </is>
       </c>
       <c r="Q11" t="inlineStr">
@@ -35421,6 +36396,17 @@
 Bảo hành: 24 Tháng tại nhà</t>
         </is>
       </c>
+      <c r="T11" t="inlineStr">
+        <is>
+          <t>Đặc điểm nổi bật
+–  Công nghệ gió E-WIND:tạo gió tự nhiên, êm dịu, mô phỏng những làn gió tươi mát của những cánh đồng hoa. E-wind mang lại luồng gió nhẹ nhàng, giúp lưu thông không khí đồng đều mang đến cảm giác mát mẻ, chăm sóc sức khoẻ và nâng niu từng khoảnh khắc của tổ ấm.
+– EV06 được trang bị hệ thống đèn LED công suất 23W, cung cấp nguồn sáng ổn định, đáp ứng tốt nhu cầu chiếu sáng trong mọi không gian. Đèn LED có tuổi thọ cao, tiết kiệm điện năng hạn chế việc thay thế bóng thường xuyên, từ đó giúp giảm chi phí sử dụng và góp phần bảo vệ môi trường.
+– Sản phẩm Quạt trần EV06 sử dụng động cơ BLDC thế hệ mới với thiết kế nhỏ gọn, vận hành mạnh mẽ nhưng vẫn đảm bảo độ êm ái và ổn định. Động cơ giúp tiết kiệm đến 50% điện năng so với động cơ truyền thống, đồng thời giảm tiếng ồn, nâng cao tuổi thọ sản phẩm và mang đến trải nghiệm tối ưu cho người sử dụng.
+– Thiết kế cánh quạt dạng cong 3D hiện đại giúp giảm lực cản và ma sát với không khí.Tạo lượng gió lớn và phân bổ đều khắp không gian đồng thời giảm thiểu tiếng ồn và rung lắc mang lại hiệu quả làm mát tối ưu.
+– Chế độ an toàn :EV06 được trang bị dây treo an toàn cố định nhằm tăng cường khả năng bảo vệ trong quá trình sử dụng. Hệ thống này giúp ngăn ngừa nguy cơ quạt rơi khi ti treo, khớp nối hoặc một số bộ phận khác gặp sự cố, đảm bảo an toàn tối đa cho người sử dụng.
+– Sản phẩm được trang bị điều khiển từ xa thông minh cho phép người dùng dễ dàng điều chỉnh tốc độ gió, bật/tắt đèn, lựa chọn chế độ gió hoặc cài đặt hẹn giờ mà không cần di chuyển mang đến sự tiện nghi trong quá trình sử dụng</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
@@ -35443,7 +36429,7 @@
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>{"cong_suat_dong_co": "38W", "loai_dong_co": "BLDC", "sai_canh": "1420mm", "chat_lieu_canh_quat": "Nhựa ABS cao cấp", "mau_sac": "3 màu: trắng, bạc, gỗ", "so_canh_quat": "5", "so_toc_do_gio": "8", "bao_hanh": "24 tháng tại nhà", "thuong_hieu": "TLC LIGHTING", "duong_kinh_quat": "1420mm", "den_LED": "23W-3 màu (T/V/TT)", "dieu_khien": "Điều khiển từ xa", "luu_luong_gio": "230m3/phút"}</t>
+          <t>{"cong_suat_dong_co": "38W", "sai_canh": "1420mm", "chat_lieu_canh_quat": "Nhựa ABS cao cấp", "mau_sac": "Bạc", "so_canh_quat": "5", "so_toc_do_gio": "8", "bao_hanh": "24 tháng tại nhà", "thuong_hieu": "TLC LIGHTING", "cong_suat": "38W", "loai_dong_co": "BLDC", "duong_kinh_quat": "1420mm", "mau_sac_2": "3 màu: trắng, bạc, gỗ", "den_LED": "23W-3 màu (T/V/TT)", "dieu_khien": "Điều khiển từ xa", "luu_luong_gio": "230m3/phút", "bao_hanh_2": "24 Tháng tại nhà"}</t>
         </is>
       </c>
       <c r="J12" t="n">
@@ -35457,6 +36443,16 @@
       <c r="M12" t="inlineStr">
         <is>
           <t>https://tlclighting.com.vn/wp-content/uploads/2026/07/06-trắng.png</t>
+        </is>
+      </c>
+      <c r="P12" t="inlineStr">
+        <is>
+          <t>Công nghệ gió E-WIND:tạo gió tự nhiên, êm dịu, mô phỏng những làn gió tươi mát của những cánh đồng hoa. E-wind mang lại luồng gió nhẹ nhàng, giúp lưu thông không khí đồng đều mang đến cảm giác mát mẻ, chăm sóc sức khoẻ và nâng niu từng khoảnh khắc của tổ ấm.
+EV06 được trang bị hệ thống đèn LED công suất 23W, cung cấp nguồn sáng ổn định, đáp ứng tốt nhu cầu chiếu sáng trong mọi không gian. Đèn LED có tuổi thọ cao, tiết kiệm điện năng hạn chế việc thay thế bóng thường xuyên, từ đó giúp giảm chi phí sử dụng và góp phần bảo vệ môi trường.
+Sản phẩm Quạt trần EV06 sử dụng động cơ BLDC thế hệ mới với thiết kế nhỏ gọn, vận hành mạnh mẽ nhưng vẫn đảm bảo độ êm ái và ổn định. Động cơ giúp tiết kiệm đến 50% điện năng so với động cơ truyền thống, đồng thời giảm tiếng ồn, nâng cao tuổi thọ sản phẩm và mang đến trải nghiệm tối ưu cho người sử dụng.
+Thiết kế cánh quạt dạng cong 3D hiện đại giúp giảm lực cản và ma sát với không khí.Tạo lượng gió lớn và phân bổ đều khắp không gian đồng thời giảm thiểu tiếng ồn và rung lắc mang lại hiệu quả làm mát tối ưu.
+Chế độ an toàn :EV06 được trang bị dây treo an toàn cố định nhằm tăng cường khả năng bảo vệ trong quá trình sử dụng. Hệ thống này giúp ngăn ngừa nguy cơ quạt rơi khi ti treo, khớp nối hoặc một số bộ phận khác gặp sự cố, đảm bảo an toàn tối đa cho người sử dụng.
+Sản phẩm được trang bị điều khiển từ xa thông minh cho phép người dùng dễ dàng điều chỉnh tốc độ gió, bật/tắt đèn, lựa chọn chế độ gió hoặc cài đặt hẹn giờ mà không cần di chuyển mang đến sự tiện nghi trong quá trình sử dụng</t>
         </is>
       </c>
       <c r="Q12" t="inlineStr">
@@ -35475,6 +36471,17 @@
 Bảo hành: 24 Tháng tại nhà</t>
         </is>
       </c>
+      <c r="T12" t="inlineStr">
+        <is>
+          <t>Đặc điểm nổi bật
+–  Công nghệ gió E-WIND:tạo gió tự nhiên, êm dịu, mô phỏng những làn gió tươi mát của những cánh đồng hoa. E-wind mang lại luồng gió nhẹ nhàng, giúp lưu thông không khí đồng đều mang đến cảm giác mát mẻ, chăm sóc sức khoẻ và nâng niu từng khoảnh khắc của tổ ấm.
+– EV06 được trang bị hệ thống đèn LED công suất 23W, cung cấp nguồn sáng ổn định, đáp ứng tốt nhu cầu chiếu sáng trong mọi không gian. Đèn LED có tuổi thọ cao, tiết kiệm điện năng hạn chế việc thay thế bóng thường xuyên, từ đó giúp giảm chi phí sử dụng và góp phần bảo vệ môi trường.
+– Sản phẩm Quạt trần EV06 sử dụng động cơ BLDC thế hệ mới với thiết kế nhỏ gọn, vận hành mạnh mẽ nhưng vẫn đảm bảo độ êm ái và ổn định. Động cơ giúp tiết kiệm đến 50% điện năng so với động cơ truyền thống, đồng thời giảm tiếng ồn, nâng cao tuổi thọ sản phẩm và mang đến trải nghiệm tối ưu cho người sử dụng.
+– Thiết kế cánh quạt dạng cong 3D hiện đại giúp giảm lực cản và ma sát với không khí.Tạo lượng gió lớn và phân bổ đều khắp không gian đồng thời giảm thiểu tiếng ồn và rung lắc mang lại hiệu quả làm mát tối ưu.
+– Chế độ an toàn :EV06 được trang bị dây treo an toàn cố định nhằm tăng cường khả năng bảo vệ trong quá trình sử dụng. Hệ thống này giúp ngăn ngừa nguy cơ quạt rơi khi ti treo, khớp nối hoặc một số bộ phận khác gặp sự cố, đảm bảo an toàn tối đa cho người sử dụng.
+– Sản phẩm được trang bị điều khiển từ xa thông minh cho phép người dùng dễ dàng điều chỉnh tốc độ gió, bật/tắt đèn, lựa chọn chế độ gió hoặc cài đặt hẹn giờ mà không cần di chuyển mang đến sự tiện nghi trong quá trình sử dụng</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
@@ -35497,7 +36504,7 @@
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>{"cong_suat_dong_co": "38W", "sai_canh": "1420mm", "chat_lieu_canh_quat": "Nhựa ABS cao cấp", "mau_sac": "Bạc, 3 màu: trắng, bạc, gỗ", "so_canh_quat": "5", "so_toc_do_gio": "8", "bao_hanh": "24 tháng tại nhà", "thuong_hieu": "TLC LIGHTING", "cong_suat": "38W", "loai_dong_co": "BLDC", "duong_kinh_quat": "1420mm", "den_led": "23W-3 màu (T/V/TT)", "dieu_khien": "Điều khiển từ xa", "luu_luong_gio": "230m3/phút"}</t>
+          <t>{"cong_suat_dong_co": "38W", "sai_canh": "1420mm", "chat_lieu_canh_quat": "Nhựa ABS cao cấp", "mau_sac": "Bạc", "so_canh_quat": "5", "so_toc_do_gio": "8", "bao_hanh": "24 tháng tại nhà", "thuong_hieu": "TLC LIGHTING", "cong_suat": "38W", "loai_dong_co": "BLDC", "duong_kinh_quat": "1420mm", "den_led": "23W-3 màu (T/V/TT)", "dieu_khien": "Điều khiển từ xa", "luu_luong_gio": "230m3/phút"}</t>
         </is>
       </c>
       <c r="J13" t="n">
@@ -35511,6 +36518,16 @@
       <c r="M13" t="inlineStr">
         <is>
           <t>https://tlclighting.com.vn/wp-content/uploads/2026/07/Thêm-tiêu-dề.png</t>
+        </is>
+      </c>
+      <c r="P13" t="inlineStr">
+        <is>
+          <t>Công nghệ gió E-WIND:tạo gió tự nhiên, êm dịu, mô phỏng những làn gió tươi mát của những cánh đồng hoa. E-wind mang lại luồng gió nhẹ nhàng, giúp lưu thông không khí đồng đều mang đến cảm giác mát mẻ, chăm sóc sức khoẻ và nâng niu từng khoảnh khắc của tổ ấm.
+EV06 được trang bị hệ thống đèn LED công suất 23W, cung cấp nguồn sáng ổn định, đáp ứng tốt nhu cầu chiếu sáng trong mọi không gian. Đèn LED có tuổi thọ cao, tiết kiệm điện năng hạn chế việc thay thế bóng thường xuyên, từ đó giúp giảm chi phí sử dụng và góp phần bảo vệ môi trường.
+Sản phẩm Quạt trần EV06 sử dụng động cơ BLDC thế hệ mới với thiết kế nhỏ gọn, vận hành mạnh mẽ nhưng vẫn đảm bảo độ êm ái và ổn định. Động cơ giúp tiết kiệm đến 50% điện năng so với động cơ truyền thống, đồng thời giảm tiếng ồn, nâng cao tuổi thọ sản phẩm và mang đến trải nghiệm tối ưu cho người sử dụng.
+Thiết kế cánh quạt dạng cong 3D hiện đại giúp giảm lực cản và ma sát với không khí.Tạo lượng gió lớn và phân bổ đều khắp không gian đồng thời giảm thiểu tiếng ồn và rung lắc mang lại hiệu quả làm mát tối ưu.
+Chế độ an toàn :EV06 được trang bị dây treo an toàn cố định nhằm tăng cường khả năng bảo vệ trong quá trình sử dụng. Hệ thống này giúp ngăn ngừa nguy cơ quạt rơi khi ti treo, khớp nối hoặc một số bộ phận khác gặp sự cố, đảm bảo an toàn tối đa cho người sử dụng.
+Sản phẩm được trang bị điều khiển từ xa thông minh cho phép người dùng dễ dàng điều chỉnh tốc độ gió, bật/tắt đèn, lựa chọn chế độ gió hoặc cài đặt hẹn giờ mà không cần di chuyển mang đến sự tiện nghi trong quá trình sử dụng</t>
         </is>
       </c>
       <c r="Q13" t="inlineStr">
@@ -35529,6 +36546,17 @@
 Bảo hành: 24 Tháng tại nhà</t>
         </is>
       </c>
+      <c r="T13" t="inlineStr">
+        <is>
+          <t>Đặc điểm nổi bật
+–  Công nghệ gió E-WIND:tạo gió tự nhiên, êm dịu, mô phỏng những làn gió tươi mát của những cánh đồng hoa. E-wind mang lại luồng gió nhẹ nhàng, giúp lưu thông không khí đồng đều mang đến cảm giác mát mẻ, chăm sóc sức khoẻ và nâng niu từng khoảnh khắc của tổ ấm.
+– EV06 được trang bị hệ thống đèn LED công suất 23W, cung cấp nguồn sáng ổn định, đáp ứng tốt nhu cầu chiếu sáng trong mọi không gian. Đèn LED có tuổi thọ cao, tiết kiệm điện năng hạn chế việc thay thế bóng thường xuyên, từ đó giúp giảm chi phí sử dụng và góp phần bảo vệ môi trường.
+– Sản phẩm Quạt trần EV06 sử dụng động cơ BLDC thế hệ mới với thiết kế nhỏ gọn, vận hành mạnh mẽ nhưng vẫn đảm bảo độ êm ái và ổn định. Động cơ giúp tiết kiệm đến 50% điện năng so với động cơ truyền thống, đồng thời giảm tiếng ồn, nâng cao tuổi thọ sản phẩm và mang đến trải nghiệm tối ưu cho người sử dụng.
+– Thiết kế cánh quạt dạng cong 3D hiện đại giúp giảm lực cản và ma sát với không khí.Tạo lượng gió lớn và phân bổ đều khắp không gian đồng thời giảm thiểu tiếng ồn và rung lắc mang lại hiệu quả làm mát tối ưu.
+– Chế độ an toàn :EV06 được trang bị dây treo an toàn cố định nhằm tăng cường khả năng bảo vệ trong quá trình sử dụng. Hệ thống này giúp ngăn ngừa nguy cơ quạt rơi khi ti treo, khớp nối hoặc một số bộ phận khác gặp sự cố, đảm bảo an toàn tối đa cho người sử dụng.
+– Sản phẩm được trang bị điều khiển từ xa thông minh cho phép người dùng dễ dàng điều chỉnh tốc độ gió, bật/tắt đèn, lựa chọn chế độ gió hoặc cài đặt hẹn giờ mà không cần di chuyển mang đến sự tiện nghi trong quá trình sử dụng</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
@@ -35551,7 +36579,7 @@
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>{"cong_suat_dong_co": "38W", "loai_dong_co": "BLDC", "sai_canh": "1420mm", "chat_lieu_canh_quat": "Nhựa ABS cao cấp", "mau_sac": "Bạc", "so_canh_quat": "5", "so_toc_do_gio": "8", "bao_hanh": "24 tháng tại nhà", "thuong_hieu": "TLC LIGHTING", "duong_kinh_quat": "1420mm", "mau_sac_tong_the": "trắng, bạc, gỗ, đen", "den_LED": "23W-3 màu (T/V/TT)", "dieu_khien": "Điều khiển từ xa", "luu_luong_gio": "230m3/phút", "bao_hanh_dong_co": "3 Năm"}</t>
+          <t>{"cong_suat_dong_co": "38W", "kieu_dong_co": "BLDC", "sai_canh": "1420mm", "chat_lieu_canh_quat": "Nhựa ABS cao cấp", "mau_sac": "Bạc", "so_canh_quat": "5", "so_toc_do_gio": "8", "bao_hanh": "24 tháng tại nhà", "thuong_hieu": "TLC LIGHTING", "cong_suat": "38W", "loai_dong_co": "BLDC", "duong_kinh_quat": "1420mm", "den_LED": "23W-3 màu (T/V/TT)", "dieu_khien": "Điều khiển từ xa", "luu_luong_gio": "230m3/phút", "bao_hanh_dong_co": "3 Năm"}</t>
         </is>
       </c>
       <c r="J14" t="n">
@@ -35565,6 +36593,14 @@
       <c r="M14" t="inlineStr">
         <is>
           <t>https://tlclighting.com.vn/wp-content/uploads/2026/07/06-trắng-1.png</t>
+        </is>
+      </c>
+      <c r="P14" t="inlineStr">
+        <is>
+          <t>Công nghệ gió E-WIND:tạo gió tự nhiên, êm dịu, mô phỏng những làn gió tươi mát của những cánh đồng hoa. E-wind mang lại luồng gió nhẹ nhàng, giúp lưu thông không khí đồng đều mang đến cảm giác mát mẻ, chăm sóc sức khoẻ và nâng niu từng khoảnh khắc của tổ ấm.
+EV09 sử dụng động cơ BLDC thế hệ mới với khả năng vận hành ổn định, tiết kiệm điện và giảm thiểu tiếng ồn. Thiết kế động cơ nhỏ gọn giúp quạt hoạt động bền bỉ, đồng thời nâng cao hiệu suất làm mát cho không gian
+Thiết kế cánh quạt dạng cong 3D hiện đại giúp giảm lực cản và ma sát với không khí.Tạo lượng gió lớn và phân bổ đều khắp không gian đồng thời giảm thiểu tiếng ồn và rung lắc mang lại hiệu quả làm mát tối ưu
+Đi kèm với sản phẩm là bộ điều khiển từ xa hiện đại, cho phép người dùng dễ dàng thao tác và điều chỉnh các chức năng của quạt một cách nhanh chóng và thuận tiện</t>
         </is>
       </c>
       <c r="Q14" t="inlineStr">
@@ -35584,6 +36620,15 @@
 Bảo hành động cơ: 3 Năm</t>
         </is>
       </c>
+      <c r="T14" t="inlineStr">
+        <is>
+          <t>Đặc điểm nổi bật
+–  Công nghệ gió E-WIND:tạo gió tự nhiên, êm dịu, mô phỏng những làn gió tươi mát của những cánh đồng hoa. E-wind mang lại luồng gió nhẹ nhàng, giúp lưu thông không khí đồng đều mang đến cảm giác mát mẻ, chăm sóc sức khoẻ và nâng niu từng khoảnh khắc của tổ ấm.
+– EV09 sử dụng động cơ BLDC thế hệ mới với khả năng vận hành ổn định, tiết kiệm điện và giảm thiểu tiếng ồn. Thiết kế động cơ nhỏ gọn giúp quạt hoạt động bền bỉ, đồng thời nâng cao hiệu suất làm mát cho không gian
+– Thiết kế cánh quạt dạng cong 3D hiện đại giúp giảm lực cản và ma sát với không khí.Tạo lượng gió lớn và phân bổ đều khắp không gian đồng thời giảm thiểu tiếng ồn và rung lắc mang lại hiệu quả làm mát tối ưu
+– Đi kèm với sản phẩm là bộ điều khiển từ xa hiện đại, cho phép người dùng dễ dàng thao tác và điều chỉnh các chức năng của quạt một cách nhanh chóng và thuận tiện</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
@@ -35606,7 +36651,7 @@
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>{"cong_suat_dong_co": "38W", "loai_dong_co": "BLDC", "sai_canh": "1420mm", "chat_lieu_canh_quat": "Nhựa ABS cao cấp", "mau_sac": "Đen", "so_canh_quat": "5", "so_toc_do_gio": "8", "bao_hanh": "24 tháng tại nhà", "thuong_hieu": "TLC LIGHTING", "duong_kinh_quat": "1420mm", "den_led": "23W-3 màu (T/V/TT)", "dieu_khien": "Điều khiển từ xa", "luu_luong_gio": "230m3/phút", "bao_hanh_dong_co": "3 Năm"}</t>
+          <t>{"cong_suat_dong_co": "38W", "kieu_dong_co": "BLDC", "sai_canh": "1420mm", "chat_lieu_canh_quat": "Nhựa ABS cao cấp", "mau_sac": "4 màu: trắng, bạc, gỗ, đen", "so_canh_quat": "5", "so_toc_do_gio": "8", "bao_hanh": "24 tháng tại nhà", "thuong_hieu": "TLC LIGHTING", "duong_kinh_quat": "1420mm", "den_LED": "23W-3 màu (T/V/TT)", "dieu_khien": "Điều khiển từ xa", "luu_luong_gio": "230m3/phút", "bao_hanh_dong_co": "3 Năm"}</t>
         </is>
       </c>
       <c r="J15" t="n">
@@ -35620,6 +36665,14 @@
       <c r="M15" t="inlineStr">
         <is>
           <t>https://tlclighting.com.vn/wp-content/uploads/2026/07/06-bạc-1.png</t>
+        </is>
+      </c>
+      <c r="P15" t="inlineStr">
+        <is>
+          <t>Công nghệ gió E-WIND:tạo gió tự nhiên, êm dịu, mô phỏng những làn gió tươi mát của những cánh đồng hoa. E-Wind mang lại luồng gió nhẹ nhàng, giúp lưu thông không khí đồng đều mang đến cảm giác mát mẻ, chăm sóc sức khoẻ và nâng niu từng khoảnh khắc của tổ ấm.
+EV09 sử dụng động cơ BLDC thế hệ mới với khả năng vận hành ổn định, tiết kiệm điện và giảm thiểu tiếng ồn. Thiết kế động cơ nhỏ gọn giúp quạt hoạt động bền bỉ, đồng thời nâng cao hiệu suất làm mát cho không gian
+Thiết kế cánh quạt dạng cong 3D hiện đại giúp giảm lực cản và ma sát với không khí. Tạo lượng gió lớn và phân bổ đều khắp không gian đồng thời giảm thiểu tiếng ồn và rung lắc mang lại hiệu quả làm mát tối ưu
+Đi kèm với sản phẩm là bộ điều khiển từ xa hiện đại, cho phép người dùng dễ dàng thao tác và điều chỉnh các chức năng của quạt một cách nhanh chóng và thuận tiện</t>
         </is>
       </c>
       <c r="Q15" t="inlineStr">
@@ -35639,6 +36692,15 @@
 Bảo hành động cơ: 3 Năm</t>
         </is>
       </c>
+      <c r="T15" t="inlineStr">
+        <is>
+          <t>Đặc điểm nổi bật
+–  Công nghệ gió E-WIND:tạo gió tự nhiên, êm dịu, mô phỏng những làn gió tươi mát của những cánh đồng hoa. E-Wind mang lại luồng gió nhẹ nhàng, giúp lưu thông không khí đồng đều mang đến cảm giác mát mẻ, chăm sóc sức khoẻ và nâng niu từng khoảnh khắc của tổ ấm.
+– EV09 sử dụng động cơ BLDC thế hệ mới với khả năng vận hành ổn định, tiết kiệm điện và giảm thiểu tiếng ồn. Thiết kế động cơ nhỏ gọn giúp quạt hoạt động bền bỉ, đồng thời nâng cao hiệu suất làm mát cho không gian
+– Thiết kế cánh quạt dạng cong 3D hiện đại giúp giảm lực cản và ma sát với không khí. Tạo lượng gió lớn và phân bổ đều khắp không gian đồng thời giảm thiểu tiếng ồn và rung lắc mang lại hiệu quả làm mát tối ưu
+– Đi kèm với sản phẩm là bộ điều khiển từ xa hiện đại, cho phép người dùng dễ dàng thao tác và điều chỉnh các chức năng của quạt một cách nhanh chóng và thuận tiện</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
@@ -35661,7 +36723,7 @@
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>{"cong_suat_dong_co": "38W", "sai_canh": "1420mm", "chat_lieu_canh_quat": "Nhựa ABS cao cấp", "mau_sac": "Vân gỗ", "so_canh_quat": "5", "so_toc_do_gio": "8", "bao_hanh": "24 tháng tại nhà", "thuong_hieu": "TLC LIGHTING", "cong_suat": "38W", "loai_dong_co": "BLDC", "duong_kinh_quat": "1420mm", "mau_sac_4_mau": "trắng, bạc, gỗ, đen", "den_LED": "23W-3 màu (T/V/TT)", "dieu_khien": "Điều khiển từ xa", "luu_luong_gio": "230m3/phút", "bao_hanh_dong_co": "3 Năm"}</t>
+          <t>{"cong_suat": "38W", "loai_dong_co": "BLDC", "duong_kinh_quat": "1420mm", "chat_lieu_canh_quat": "Nhựa ABS cao cấp", "mau_sac": "4 màu: trắng, bạc, gỗ, đen", "so_canh_quat": "5", "so_toc_do_gio": "8", "den_led": "23W-3 màu (T/V/TT)", "dieu_khien": "Điều khiển từ xa", "luu_luong_gio": "230m3/phút", "bao_hanh": "24 Tháng tại nhà", "bao_hanh_dong_co": "3 Năm"}</t>
         </is>
       </c>
       <c r="J16" t="n">
@@ -35675,6 +36737,14 @@
       <c r="M16" t="inlineStr">
         <is>
           <t>https://tlclighting.com.vn/wp-content/uploads/2026/07/3.png</t>
+        </is>
+      </c>
+      <c r="P16" t="inlineStr">
+        <is>
+          <t>Công nghệ gió E-WIND:tạo gió tự nhiên, êm dịu, mô phỏng những làn gió tươi mát của những cánh đồng hoa. E-wind mang lại luồng gió nhẹ nhàng, giúp lưu thông không khí đồng đều mang đến cảm giác mát mẻ, chăm sóc sức khoẻ và nâng niu từng khoảnh khắc của tổ ấm.
+EV09 sử dụng động cơ BLDC thế hệ mới với khả năng vận hành ổn định, tiết kiệm điện và giảm thiểu tiếng ồn. Thiết kế động cơ nhỏ gọn giúp quạt hoạt động bền bỉ, đồng thời nâng cao hiệu suất làm mát cho không gian
+Thiết kế cánh quạt dạng cong 3D hiện đại giúp giảm lực cản và ma sát với không khí.Tạo lượng gió lớn và phân bổ đều khắp không gian đồng thời giảm thiểu tiếng ồn và rung lắc mang lại hiệu quả làm mát tối ưu
+Đi kèm với sản phẩm là bộ điều khiển từ xa hiện đại, cho phép người dùng dễ dàng thao tác và điều chỉnh các chức năng của quạt một cách nhanh chóng và thuận tiện</t>
         </is>
       </c>
       <c r="Q16" t="inlineStr">
@@ -35694,6 +36764,15 @@
 Bảo hành động cơ: 3 Năm</t>
         </is>
       </c>
+      <c r="T16" t="inlineStr">
+        <is>
+          <t>Đặc điểm nổi bật
+–  Công nghệ gió E-WIND:tạo gió tự nhiên, êm dịu, mô phỏng những làn gió tươi mát của những cánh đồng hoa. E-wind mang lại luồng gió nhẹ nhàng, giúp lưu thông không khí đồng đều mang đến cảm giác mát mẻ, chăm sóc sức khoẻ và nâng niu từng khoảnh khắc của tổ ấm.
+– EV09 sử dụng động cơ BLDC thế hệ mới với khả năng vận hành ổn định, tiết kiệm điện và giảm thiểu tiếng ồn. Thiết kế động cơ nhỏ gọn giúp quạt hoạt động bền bỉ, đồng thời nâng cao hiệu suất làm mát cho không gian
+– Thiết kế cánh quạt dạng cong 3D hiện đại giúp giảm lực cản và ma sát với không khí.Tạo lượng gió lớn và phân bổ đều khắp không gian đồng thời giảm thiểu tiếng ồn và rung lắc mang lại hiệu quả làm mát tối ưu
+– Đi kèm với sản phẩm là bộ điều khiển từ xa hiện đại, cho phép người dùng dễ dàng thao tác và điều chỉnh các chức năng của quạt một cách nhanh chóng và thuận tiện</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
@@ -35716,7 +36795,7 @@
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>{"cong_suat_dong_co": "38W", "loai_dong_co": "BLDC", "duong_kinh_quat": "1420mm", "chat_lieu_canh_quat": "Nhựa ABS cao cấp", "mau_sac": "Trắng", "so_canh_quat": "5", "so_toc_do_gio": "8", "bao_hanh": "24 tháng tại nhà", "thuong_hieu": "TLC LIGHTING", "cong_suat": "38W", "den_led": "23W-3 màu (T/V/TT)", "dieu_khien": "Điều khiển từ xa", "luu_luong_gio": "230m3/phút", "bao_hanh_dong_co": "3 Năm"}</t>
+          <t>{"cong_suat_dong_co": "38W", "loai_dong_co": "BLDC", "duong_kinh_quat": "1420mm", "chat_lieu_canh_quat": "Nhựa ABS cao cấp", "mau_sac": "Trắng", "so_canh_quat": "5", "so_toc_do_gio": "8", "bao_hanh": "24 tháng tại nhà", "thuong_hieu": "TLC LIGHTING", "den_LED": "23W-3 màu (T/V/TT)", "dieu_khien": "Điều khiển từ xa", "luu_luong_gio": "230m3/phút", "bao_hanh_dong_co": "3 Năm"}</t>
         </is>
       </c>
       <c r="J17" t="n">
@@ -35730,6 +36809,14 @@
       <c r="M17" t="inlineStr">
         <is>
           <t>https://tlclighting.com.vn/wp-content/uploads/2026/07/4.png</t>
+        </is>
+      </c>
+      <c r="P17" t="inlineStr">
+        <is>
+          <t>Công nghệ gió E-WIND:tạo gió tự nhiên, êm dịu, mô phỏng những làn gió tươi mát của những cánh đồng hoa. E-Wind mang lại luồng gió nhẹ nhàng, giúp lưu thông không khí đồng đều mang đến cảm giác mát mẻ, chăm sóc sức khoẻ và nâng niu từng khoảnh khắc của tổ ấm.
+EV09 sử dụng động cơ BLDC thế hệ mới với khả năng vận hành ổn định, tiết kiệm điện và giảm thiểu tiếng ồn. Thiết kế động cơ nhỏ gọn giúp quạt hoạt động bền bỉ, đồng thời nâng cao hiệu suất làm mát cho không gian
+Thiết kế cánh quạt dạng cong 3D hiện đại giúp giảm lực cản và ma sát với không khí. Tạo lượng gió lớn và phân bổ đều khắp không gian đồng thời giảm thiểu tiếng ồn và rung lắc mang lại hiệu quả làm mát tối ưu
+Đi kèm với sản phẩm là bộ điều khiển từ xa hiện đại, cho phép người dùng dễ dàng thao tác và điều chỉnh các chức năng của quạt một cách nhanh chóng và thuận tiện</t>
         </is>
       </c>
       <c r="Q17" t="inlineStr">
@@ -35749,6 +36836,15 @@
 Bảo hành động cơ: 3 Năm</t>
         </is>
       </c>
+      <c r="T17" t="inlineStr">
+        <is>
+          <t>Đặc điểm nổi bật
+–  Công nghệ gió E-WIND:tạo gió tự nhiên, êm dịu, mô phỏng những làn gió tươi mát của những cánh đồng hoa. E-Wind mang lại luồng gió nhẹ nhàng, giúp lưu thông không khí đồng đều mang đến cảm giác mát mẻ, chăm sóc sức khoẻ và nâng niu từng khoảnh khắc của tổ ấm.
+– EV09 sử dụng động cơ BLDC thế hệ mới với khả năng vận hành ổn định, tiết kiệm điện và giảm thiểu tiếng ồn. Thiết kế động cơ nhỏ gọn giúp quạt hoạt động bền bỉ, đồng thời nâng cao hiệu suất làm mát cho không gian
+– Thiết kế cánh quạt dạng cong 3D hiện đại giúp giảm lực cản và ma sát với không khí. Tạo lượng gió lớn và phân bổ đều khắp không gian đồng thời giảm thiểu tiếng ồn và rung lắc mang lại hiệu quả làm mát tối ưu
+– Đi kèm với sản phẩm là bộ điều khiển từ xa hiện đại, cho phép người dùng dễ dàng thao tác và điều chỉnh các chức năng của quạt một cách nhanh chóng và thuận tiện</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
@@ -35771,7 +36867,7 @@
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>{"cong_suat_quat_dong_co": "65 W", "sai_canh": "1535 mm", "chat_lieu_canh_quat": "Nhựa ABS cao cấp", "mau_sac": "Vân gỗ", "so_canh_quat": "8", "so_toc_do_gio": "9", "bao_hanh": "24 tháng tại nhà", "thuong_hieu": "TLC LIGHTING", "cong_suat_quat": "65W", "cong_suat_den": "24W – 3 màu (T-V-TT)", "loai_dong_co": "BLDC", "dieu_khien": "Điều khiển từ xa màn LED", "luu_luong_gio": "320m3/phút", "bao_hanh_dong_co": "3 Năm"}</t>
+          <t>{"cong_suat_quat_dong_co_sai_canh_chat_lieu_canh_quat_mau_sac_so_canh_quat_so_toc_do_gio_bao_hanh": "65 W : BLDC : 1535 mm : Nhựa ABS cao cấp : Vân gỗ : 8 : 9 : 24 tháng tại nhà", "thuong_hieu": "TLC LIGHTING", "cong_suat_quat": "65W", "cong_suat_den": "24W – 3 màu (T-V-TT)", "loai_dong_co": "BLDC", "sai_canh": "1535mm", "chat_lieu_canh_quat": "Nhựa ABS cao cấp", "mau_sac": "Vân gỗ", "so_canh_quat": "8", "so_toc_do_gio": "9", "dieu_khien": "Điều khiển từ xa màn LED", "luu_luong_gio": "320m3/phút", "bao_hanh": "24 Tháng tại nhà", "bao_hanh_dong_co": "3 Năm"}</t>
         </is>
       </c>
       <c r="J18" t="n">
@@ -35785,6 +36881,14 @@
       <c r="M18" t="inlineStr">
         <is>
           <t>https://tlclighting.com.vn/wp-content/uploads/2026/08/06-bạc-scaled.jpg</t>
+        </is>
+      </c>
+      <c r="P18" t="inlineStr">
+        <is>
+          <t>Công nghệ gió E-WIND: tạo gió tự nhiên, êm dịu, mô phỏng những làn gió tươi mát của những cánh đồng hoa. E-wind mang lại luồng gió nhẹ nhàng, giúp lưu thông không khí đồng đều mang đến cảm giác mát mẻ, chăm sóc sức khoẻ và nâng niu từng khoảnh khắc của tổ ấm.
+EV11 sử dụng động cơ BLDC thế hệ mới với khả năng vận hành ổn định, tiết kiệm điện và giảm thiểu tiếng ồn. Thiết kế động cơ nhỏ gọn giúp quạt hoạt động bền bỉ, đồng thời nâng cao hiệu suất làm mát cho không gian
+Thiết kế cánh quạt dạng cong 3D hiện đại giúp giảm lực cản và ma sát với không khí.Tạo lượng gió lớn và phân bổ đều khắp không gian đồng thời giảm thiểu tiếng ồn và rung lắc mang lại hiệu quả làm mát tối ưu
+Đi kèm với sản phẩm là bộ điều khiển từ xa hiện đại, cho phép người dùng dễ dàng thao tác và điều chỉnh các chức năng của quạt một cách nhanh chóng và thuận tiện</t>
         </is>
       </c>
       <c r="Q18" t="inlineStr">
@@ -35804,6 +36908,15 @@
 Bảo hành động cơ: 3 Năm</t>
         </is>
       </c>
+      <c r="T18" t="inlineStr">
+        <is>
+          <t>Đặc điểm nổi bật
+–  Công nghệ gió E-WIND: tạo gió tự nhiên, êm dịu, mô phỏng những làn gió tươi mát của những cánh đồng hoa. E-wind mang lại luồng gió nhẹ nhàng, giúp lưu thông không khí đồng đều mang đến cảm giác mát mẻ, chăm sóc sức khoẻ và nâng niu từng khoảnh khắc của tổ ấm.
+– EV11 sử dụng động cơ BLDC thế hệ mới với khả năng vận hành ổn định, tiết kiệm điện và giảm thiểu tiếng ồn. Thiết kế động cơ nhỏ gọn giúp quạt hoạt động bền bỉ, đồng thời nâng cao hiệu suất làm mát cho không gian
+– Thiết kế cánh quạt dạng cong 3D hiện đại giúp giảm lực cản và ma sát với không khí.Tạo lượng gió lớn và phân bổ đều khắp không gian đồng thời giảm thiểu tiếng ồn và rung lắc mang lại hiệu quả làm mát tối ưu
+– Đi kèm với sản phẩm là bộ điều khiển từ xa hiện đại, cho phép người dùng dễ dàng thao tác và điều chỉnh các chức năng của quạt một cách nhanh chóng và thuận tiện</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="n">
@@ -35831,7 +36944,7 @@
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>{"cong_suat_dong_co": "56W", "loai_dong_co": "DC", "duong_kinh_quat": "1420mm", "so_luong_canh": "5 cánh", "dien_ap": "AC 220V/ 50Hz", "thuong_hieu": "TLC LIGHTING", "cong_suat_toi_da": "56 W", "duong_kinh_canh_quat": "1420mm", "chat_lieu_canh_quat": "Nhựa ABS cao cấp", "mau_sac": "Màu bạc", "so_canh_quat": "5", "so_toc_do_gio": "6", "dieu_khien": "Điều khiển từ xa", "dien_ap_(AC)": "AC 220V-50Hz", "chat_lieu": "ABS", "kich_thuoc_sai_canh_quat_tran": "58inches/1400mm", "chieu_dai_ti_quat": "25cm", "cong_suat": "18W"}</t>
+          <t>{"cong_suat_dong_co": "56W", "loai_dong_co": "DC", "duong_kinh_quat": "1420mm", "so_luong_canh": "5 cánh", "dien_ap": "AC 220V/ 50Hz", "cong_suat_toi_da": "56 W", "duong_kinh_canh_quat": "1420mm", "mau_sac": "Màu bạc", "so_canh_quat": "5", "so_toc_do_gio": "6", "den_LED_chi_tiet": "Ba màu ( trắng, vàng, trung tính )", "dieu_khien": "Điều khiển từ xa", "dien_ap_AC": "AC 220V-50Hz", "bao_hanh_chi_tiet": "05 năm", "chat_lieu": "ABS", "kich_thuoc_sai_canh_quat_tran": "58inches/1400mm", "che_do_den_LED": "trắng, vàng và trung tính", "cong_suat_den_LED": "18W", "che_do_mau": "Trắng – Vàng – Trung tính", "chieu_dai_ti_quat": "25cm"}</t>
         </is>
       </c>
       <c r="J19" t="n">
@@ -35915,7 +37028,7 @@
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t>{"cong_suat_dong_co": "56W", "loai_dong_co": "DC", "duong_kinh_quat": "1420mm", "so_luong_canh": "5 cánh", "so_cap_toc_do": "6 cấp độ", "den_LED": "Ba màu", "dien_ap": "AC 220V/ 50Hz", "bao_hanh": "5 năm", "cong_suat_toi_da": "56 W", "duong_kinh_canh_quat": "1420mm", "chat_lieu_canh_quat": "Nhựa ABS cao cấp", "mau_sac": "Màu bạc", "so_canh_quat": "5", "so_toc_do_gio": "6", "dieu_khien": "Điều khiển từ xa", "dien_ap_AC": "AC 220V-50Hz", "cong_suat_LED": "18W", "che_do_mau_LED": "Trắng, Vàng, Trung tính", "chieu_dai_ti_quat": "25cm"}</t>
+          <t>{"cong_suat_dong_co": "56W", "loai_dong_co": "DC", "duong_kinh_quat": "1420mm", "so_luong_canh": "5 cánh", "so_cap_toc_do": "6 cấp độ", "den_LED": "Ba màu", "dien_ap": "AC 220V/ 50Hz", "bao_hanh": "5 năm", "thuong_hieu": "TLC LIGHTING", "cong_suat_toi_da": "56 W", "duong_kinh_canh_quat": "1420mm", "chat_lieu_canh_quat": "Nhựa ABS cao cấp", "mau_sac": "Màu bạc", "so_canh_quat": "5", "so_toc_do_gio": "6", "dieu_khien": "Điều khiển từ xa", "dien_ap_AC": "AC 220V-50Hz", "cong_suat": "56W", "kich_thuoc": "58inches/1400mm", "cong_suat_LED": "18W", "che_do_mau": "Trắng, Vàng, Trung tính", "chieu_dai_phan_ti_quat": "25cm"}</t>
         </is>
       </c>
       <c r="J20" t="n">
@@ -36136,7 +37249,7 @@
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>{"cong_suat_chiu_tai": "3000W", "dien_ap_hoat_dong": "250V/12A", "chieu_dai_day": "Không kèm dây", "chat_lieu_vo": "Nhựa ABS", "so_lo_cam": "3 lỗ cắm 2 chấu", "mau_sac": "Trắng – Đen", "kich_thuoc": "106x52x31", "chat_lieu": "Vỏ nhựa ABS, chấu điện đồng nhập khẩu", "kich_thuoc_DxRxC": "106x52x31"}</t>
+          <t>{"cong_suat_chiu_tai": "3000W", "dien_ap_hoat_dong": "250V/12A", "chieu_dai_day": "Không kèm dây", "chat_lieu_vo": "Nhựa ABS", "so_lo_cam": "3 lỗ cắm 2 chấu", "mau_sac": "Trắng – Đen", "kich_thuoc": "106x52x31", "chat_lieu": "Vỏ nhựa ABS, chấu điện đồng nhập khẩu", "kich_thuoc_dxrxc": "106x52x31"}</t>
         </is>
       </c>
       <c r="L2" t="inlineStr">
@@ -36212,7 +37325,7 @@
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>{"cong_suat_chiu_tai": "2500W", "dien_ap_hoat_dong": "250V/12A", "chieu_dai_dây": "2.5 mét", "chat_lieu_vo": "Nhựa ABS", "so_lo_cam": "3 lỗ 2 chấu, 1 lỗ 3 chấu", "mau_sac": "Trắng", "thuong_hieu": "TLC", "xuat_xu": "Việt Nam", "chat_lieu": "Vỏ nhựa ABS, chấu điện đồng nhập khẩu"}</t>
+          <t>{"cong_suat_chiu_tai": "2500W", "dien_ap_hoat_dong": "250V/12A", "chieu_dai_day": "2.5 mét", "chat_lieu_vo": "Nhựa ABS", "so_lo_cam": "3 lỗ 2 chấu, 1 lỗ 3 chấu", "mau_sac": "Trắng", "thuong_hieu": "TLC", "xuat_xu": "Việt Nam", "chat_lieu": "Vỏ nhựa ABS, chấu điện đồng nhập khẩu"}</t>
         </is>
       </c>
       <c r="L3" t="inlineStr">
@@ -36372,7 +37485,7 @@
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>{"cong_suat_chiu_tai": "2500W", "dien_ap_hoat_dong": "250V/12A", "chieu_dai_day": "4.5 mét", "chat_lieu_vo": "Nhựa ABS", "so_lo_cam": "3 lỗ 2 chấu, 1 lỗ 3 chấu", "mau_sac": "Trắng", "thuong_hieu": "TLC", "xuat_xu": "Việt Nam", "cong_suat_chiu_tai_toi_da": "2500W", "chat_lieu": "Vỏ nhựa ABS, chấu điện đồng nhập khẩu"}</t>
+          <t>{"cong_suat_chiu_tai": "2500W", "dien_ap_hoat_dong": "250V/12A", "chieu_dai_day": "4.5 mét", "chat_lieu_vo": "Nhựa ABS", "so_lo_cam": "3 lỗ 2 chấu, 1 lỗ 3 chấu", "mau_sac": "Trắng", "thuong_hieu": "TLC", "xuat_xu": "Việt Nam"}</t>
         </is>
       </c>
       <c r="L5" t="inlineStr">
@@ -36454,7 +37567,7 @@
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>{"cong_suat_chiu_tai": "6500W", "dien_ap_hoat_dong": "250V/30A", "chieu_dai_day": "Không kèm dây", "chat_lieu_vo": "Nhựa ABS", "so_lo_cam": "2 lỗ 2 chấu, 1 lỗ 3 chấu", "mau_sac": "Vàng – Cam", "kich_thuoc_mm": "175x60x35", "thuong_hieu": "TLC", "xuat_xu": "Việt Nam", "so_lo_cam_khac": "2 lỗ cắm 2 chấu, 1 lỗ cắm 3 chấy", "chat_lieu": "Vỏ nhựa ABS, chấu điện đồng nhập khẩu, mặt ổ nhựa PBT", "kich_thuoc_dxrxc": "175x60x35mm"}</t>
+          <t>{"cong_suat_chiu_tai": "6500W", "dien_ap_hoat_dong": "250V/30A", "chieu_dai_day": "Không kèm dây", "chat_lieu_vo": "Nhựa ABS", "so_lo_cam": "2 lỗ 2 chấu, 1 lỗ 3 chấu", "mau_sac": "Vàng – Cam", "kich_thuoc_mm": "175x60x35", "thuong_hieu": "TLC", "xuat_xu": "Việt Nam", "chat_lieu": "Vỏ nhựa ABS, chấu điện đồng nhập khẩu, mặt ổ nhựa PBT", "kich_thuoc_DxRxC": "175x60x35mm"}</t>
         </is>
       </c>
       <c r="L6" t="inlineStr">
@@ -36535,7 +37648,7 @@
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>{"cong_suat_chiu_tai": "6500W", "dien_ap_hoat_dong": "250V/30A", "chieu_dai_day": "Không kèm dây", "chat_lieu_vo": "Nhựa ABS, Nhựa BPT", "so_lo_cam": "3 lỗ cắm 2 chấu, 1 lỗ cắm 3 chấu", "mau_sac": "Vàng – Cam", "kich_thuoc": "215x60x40", "thuong_hieu": "TLC", "xuat_xu": "Việt Nam", "chat_lieu": "Vỏ nhựa ABS, chấu điện đồng nhập khẩu", "kich_thuoc_dxrxc": "215mmx60mmx40mm"}</t>
+          <t>{"cong_suat_chiu_tai": "6500W", "dien_ap_hoat_dong": "250V/30A", "chieu_dai_dây": "Không kèm dây", "chat_lieu_vo": "Nhựa ABS, Nhựa BPT", "so_lo_cam": "3 lỗ cắm 2 chấu, 1 lỗ cắm 3 chấu", "mau_sac": "Vàng – Cam", "kich_thuoc": "215x60x40", "thuong_hieu": "TLC", "xuat_xu": "Việt Nam", "cong_suat_chiu_tai_toi_da": "6500W", "chat_lieu": "Vỏ nhựa ABS, chấu điện đồng nhập khẩu", "kich_thuoc_dxrxc": "215mmx60mmx40mm"}</t>
         </is>
       </c>
       <c r="L7" t="inlineStr">
@@ -36616,7 +37729,7 @@
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>{"cong_suat_chiu_tai": "3500W", "dien_ap_hoat_dong": "250V/16A", "chieu_dai_day": "3 mét", "chat_lieu_vo": "Nhựa ABS, Nhựa BPT", "so_lo_cam": "2 lỗ 2 chấu, 1 lỗ 3 chấu", "mau_sac": "Vàng – Cam", "kich_thuoc_o_cam": "170x60x35", "cong_suat_chiu_tai_toi_da": "3500W", "dien_ap_hoat_dong_2": "250V/16A", "so_lo_cam_2": "2 lỗ cắm 2 chấu, 1 lỗ cắm 3 chấu", "chieu_dai_day_2": "3m", "chat_lieu": "Vỏ nhựa ABS, mặt ổ nhựa BPT, chấu điện đồng nhập khẩu", "kich_thuoc_o_cam_dxrxc": "175x60x35"}</t>
+          <t>{"cong_suat_chiu_tai": "3500W", "dien_ap_hoat_dong": "250V/16A", "chieu_dai_dây": "3 mét", "chat_lieu_vo": "Nhựa ABS, Nhựa BPT", "so_lo_cam": "2 lỗ 2 chấu, 1 lỗ 3 chấu", "mau_sac": "Vàng – Cam", "kich_thuoc_o_cam": "170x60x35", "thuong_hieu": "TLC", "xuat_xu": "Việt Nam", "cong_suat_chiu_tai_toi_da": "3500W", "chieu_dai_day": "3m", "chat_lieu": "Vỏ nhựa ABS, mặt ổ nhựa BPT, chấu điện đồng nhập khẩu", "kich_thuoc_o_cam_DxRxC": "175x60x35"}</t>
         </is>
       </c>
       <c r="L8" t="inlineStr">
@@ -36698,7 +37811,7 @@
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>{"cong_suat_chiu_tai": "3500W", "dien_ap_hoat_dong": "250V/16A", "chieu_dai_day": "5 mét", "chat_lieu_vo": "Nhựa ABS, Nhựa BPT", "so_lo_cam": "2 lỗ 2 chấu, 1 lỗ 3 chấu", "mau_sac": "Vàng – Cam", "kich_thuoc": "155x65x35", "cong_suat_chiu_tai_toi_da": "3500W", "dien_ap_hoat_dong_2": "250V/16A", "so_lo_cam_2": "2 lỗ cắm 2 chấu, 1 lỗ cắm 3 chấu", "chieu_dai_day_2": "5m", "chat_lieu": "Vỏ nhựa ABS, mặt ổ nhựa BPT, chấu điện đồng nhập khẩu", "kich_thuoc_dxrxc": "106x52x31", "mau_sac_2": "Vàng – Cam"}</t>
+          <t>{"cong_suat_chiu_tai": "3500W", "dien_ap_hoat_dong": "250V/16A", "chieu_dai_day": "5 mét", "chat_lieu_vo": "Nhựa ABS, Nhựa BPT", "so_lo_cam": "2 lỗ 2 chấu, 1 lỗ 3 chấu", "mau_sac": "Vàng – Cam", "kich_thuoc": "155x65x35", "cong_suat_chiu_tai_toi_da": "3500W", "so_lo_cam_thong_so": "2 lỗ cắm 2 chấu, 1 lỗ cắm 3 chấu", "chieu_dai_day_thong_so": "5m", "chat_lieu": "Vỏ nhựa ABS, mặt ổ nhựa BPT, chấu điện đồng nhập khẩu", "kich_thuoc_DxRxC": "106x52x31", "thuong_hieu": "TLC", "xuat_xu": "Việt Nam"}</t>
         </is>
       </c>
       <c r="L9" t="inlineStr">
@@ -36780,7 +37893,7 @@
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>{"cong_suat_chiu_tai": "3500W", "dien_ap_hoat_dong": "250V/16A", "chieu_dai_day": "3 mét", "chat_lieu_vo": "Nhựa ABS, Nhựa BPT", "so_lo_cam": "2 lỗ 2 chấu, 1 lỗ 3 chấu", "mau_sac": "Vàng – Cam", "cong_suat_chiu_tai_toi_da": "3500W", "chat_lieu": "Vỏ nhựa ABS, mặt ổ nhựa BPT, chấu điện đồng nhập khẩu", "chieu_dai_day_dien": "3m"}</t>
+          <t>{"cong_suat_chiu_tai": "3500W", "dien_ap_hoat_dong": "250V/16A", "chieu_dai_day": "3 mét", "chat_lieu_vo": "Nhựa ABS, Nhựa BPT", "so_lo_cam": "2 lỗ 2 chấu, 1 lỗ 3 chấu", "mau_sac": "Vàng – Cam", "cong_suat_chiu_tai_toi_da": "3500W", "chat_lieu": "Vỏ nhựa ABS, mặt ổ nhựa BPT, chấu điện đồng nhập khẩu", "thuong_hieu": "TLC", "xuat_xu": "Việt Nam"}</t>
         </is>
       </c>
       <c r="L10" t="inlineStr">
@@ -36863,7 +37976,7 @@
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>{"cong_suat_chiu_tai": "3500W", "dien_ap_hoat_dong": "250V/16A", "chieu_dai_day": "5m", "chat_lieu_vo": "Nhựa ABS, Nhựa BPT", "so_lo_cam": "3 lỗ cắm 2 chấu, 1 lỗ cắm 3 chấu", "mau_sac": "Vàng – Cam", "cong_suat_chiu_tai_toi_da": "3500W", "chat_lieu": "Vỏ nhựa ABS, mặt ổ nhựa BPT, chấu điện đồng nhập khẩu"}</t>
+          <t>{"cong_suat_chiu_tai_toi_da": "3500W", "dien_ap_hoat_dong": "250V/16A", "so_lo_cam": "3 lỗ cắm 2 chấu, 1 lỗ cắm 3 chấu", "chieu_dai_day": "5m", "chat_lieu": "Vỏ nhựa ABS, mặt ổ nhựa BPT, chấu điện đồng nhập khẩu", "mau_sac": "Vàng – Cam", "thuong_hieu": "TLC", "xuat_xu": "Việt Nam"}</t>
         </is>
       </c>
       <c r="L11" t="inlineStr">
@@ -37185,7 +38298,7 @@
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>{"cong_suat": "40W", "anh_sang": "Ba màu(Trắng/ Vàng/trung tính), Ba màu(Trắng/vàng/trung tính)", "nhiet_do_mau": "3500K/6500K", "kich_thuoc": "Φ 420×62", "chip_led": "Chip Bridgelux", "hieu_suat_quang": "110-120 Lm/w, 110~120Lm/w", "chi_so_hoan_mau": "CRI≥85", "dien_ap": "85-265V", "thuong_hieu": "TLC LIGHTING", "tuoi_tho": "40.000h", "quang_thong": "4600Lm", "do_hoan_mau": "&gt;85", "dien_ap_ac": "85-265V", "tuoi_tho_chip_led": "40.000 giờ", "bao_hanh": "24 tháng"}</t>
+          <t>{"cong_suat": "40W", "anh_sang": "Ba màu(Trắng/ Vàng/trung tính)", "nhiet_do_mau": "3500K/6500K", "kich_thuoc": "Φ 420×62", "chip_led": "Chip Bridgelux", "hieu_suat_quang": "110-120 Lm/w, 110~120Lm/w", "chi_so_hoan_mau": "CRI≥85", "dien_ap": "85-265V", "thuong_hieu": "TLC LIGHTING", "tuoi_tho": "40.000h", "bao_hanh": "24 tháng", "quang_thong": "4600Lm", "do_hoan_mau": "&gt;85", "dien_ap_ac": "85-265V", "tuoi_tho_chip_led": "40.000 giờ"}</t>
         </is>
       </c>
       <c r="J3" t="n">
@@ -37199,6 +38312,16 @@
       <c r="M3" t="inlineStr">
         <is>
           <t>https://tlclighting.com.vn/wp-content/uploads/2018/12/Untitled-11.jpg</t>
+        </is>
+      </c>
+      <c r="P3" t="inlineStr">
+        <is>
+          <t>Đèn có thiết kế sang trọng – đẳng cấp, tính thẩm mỹ cao
+Cấu tạo từ những linh kiện cao cấp: Sử dụng Chip LED Bridgelux – Mỹ với hiệu suất quang lên tới 120 Lm/W, bộ nguồn chịu nhiệt tốt.
+Tuổi thọ bóng đèn lên tới 40.000 giờ chiếu sáng
+Ngoài khả năng chiếu sáng vượt trội, đèn được ứng dụng như đèn trang trí cao cấp
+Chế độ bảo hành đổi mới: 24 tháng nếu có lỗi từ nhà sản xuất
+Đèn dễ dàng lắp đặt và tháo dỡ, ứng dụng chủ yếu cho các chung cư, nhà ở, nhà hàng, khách sạn cao cấp.</t>
         </is>
       </c>
       <c r="Q3" t="inlineStr">
@@ -37227,6 +38350,27 @@
 Chip LED: Chip Bridgelux
 Tuổi thọ chip LED: 40.000 giờ
 Bảo hành: 24 tháng</t>
+        </is>
+      </c>
+      <c r="T3" t="inlineStr">
+        <is>
+          <t>Đặc điểm
+Đèn Led
+ốp trần galaxy plus có công suất 40w được tích hợp chế độ ECO 20w, giúp tiết kiệm 50% lượng điện năng tiêu thụ, tiết kiệm điện lên đến 90% so với dòng đèn trang trí thông thường.
+Về mặt thẩm mĩ, chiếc đèn được thiết kế dựa trên mô phỏng dải ngân hà giúp tạo ấn tượng cho khách hàng ngay từ cái nhìn đầu tiên. Không chỉ có công dụng chiếu sáng, chiếc đèn
+ốp trần galaxy plus 40w
+còn là vật dụng dùng trang trí cho căn phòng hiện đại.
+Đèn LED ốp trần Galaxy Plus
+Đèn ốp nổi Galaxy Plus 40w ứng dụng công nghệ ECO
+Ngoài ra, đèn Led
+ốp trần galaxy plus 40w
+còn có những đặc điểm sau:
+Đèn có thiết kế sang trọng – đẳng cấp, tính thẩm mỹ cao
+Cấu tạo từ những linh kiện cao cấp: Sử dụng Chip LED Bridgelux – Mỹ với hiệu suất quang lên tới 120 Lm/W, bộ nguồn chịu nhiệt tốt.
+Tuổi thọ bóng đèn lên tới 40.000 giờ chiếu sáng
+Ngoài khả năng chiếu sáng vượt trội, đèn được ứng dụng như đèn trang trí cao cấp
+Chế độ bảo hành đổi mới: 24 tháng nếu có lỗi từ nhà sản xuất
+Đèn dễ dàng lắp đặt và tháo dỡ, ứng dụng chủ yếu cho các chung cư, nhà ở, nhà hàng, khách sạn cao cấp.</t>
         </is>
       </c>
     </row>
@@ -37566,7 +38710,7 @@
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>{"cong_suat_chiu_tai": "4500W", "dien_ap_hoat_dong": "20A/250V", "kich_thuoc_chan_cam": "4.5mm", "chat_lieu_chan_phich": "Đồng Hàn Quốc", "chat_lieu_vo": "Nhựa PC", "thuong_hieu": "TLC", "xuat_xu": "Việt Nam", "cong_suat_chiu_tai_toi_da": "4500W", "dien_ap_toi_da": "20A/250V", "mau_sac": "Cam", "chat_lieu": "Vỏ nhựa PC, Chân phích đồng", "chat_lieu_vo_phich": "nhựa ABS", "chat_lieu_chau_phich_cam": "đồng lá nguyên chất", "loi_phich_cam_dien_chiu_tai": "nhựa PC", "do_an_toan_cao": "Phích cắm cái đạt các tiêu chuẩn ISO 9001:2015, phần vỏ làm từ nhựa ABS cách điện tuyệt đối, chịu nhiệt lên tới 140 độ C"}</t>
+          <t>{"cong_suat_chiu_tai": "4500W", "dien_ap_hoat_dong": "20A/250V", "kich_thuoc_chan_cam": "4.5mm", "chat_lieu_chan_phich": "Đồng Hàn Quốc", "chat_lieu_vo": "Nhựa PC", "cong_suat_chiu_tai_toi_da": "4500W", "dien_ap_toi_da": "20A/250V", "mau_sac": "Cam", "chat_lieu": "Vỏ nhựa PC, Chân phích đồng", "chat_lieu_vo_phich": "nhựa ABS", "chat_lieu_chaus_phich_cam": "đồng lá nguyên chất", "chat_lieu_loi_phich_cam_dien_chiu_tai": "nhựa PC"}</t>
         </is>
       </c>
       <c r="L3" t="inlineStr">
@@ -37577,6 +38721,15 @@
       <c r="M3" t="inlineStr">
         <is>
           <t>https://tlclighting.com.vn/wp-content/uploads/2023/02/phich-cam-cai-1.png</t>
+        </is>
+      </c>
+      <c r="P3" t="inlineStr">
+        <is>
+          <t>Độ an toàn cao
+Chịu tải lớn
+Phù hợp với mọi loại phích cắm
+Thiết kế tiện lợi
+Độ bền cao</t>
         </is>
       </c>
       <c r="Q3" t="inlineStr">
@@ -37598,6 +38751,21 @@
 Bảo hành: </t>
         </is>
       </c>
+      <c r="T3" t="inlineStr">
+        <is>
+          <t>Tại sao nên sử dụng phích cắm cái chịu tải 4500W
+Độ an toàn cao:
+Phích cắm cái đạt các tiêu chuẩn ISO 9001:2015, phần vỏ làm từ nhựa ABS cách điện tuyệt đối, chịu nhiệt lên tới 140 độ C an toàn cho người sử dụng.
+Chịu tải lớn:
+Công suất chịu tải 4500W, phù hợp sử dụng cho các máy chuyên dùng, thiết bị công nghiệp có công suất lớn.
+Phù hợp với mọi loại phích cắm:
+Thiết kế thông mình phù hợp với các loại phích chân tròn và chân dẹt.
+Thiết kế tiện lợi:
+kích thước nhỏ gọn, dễ dàng đấu nối, tháo lắp cho người sử dụng
+Độ bền cao:
+Vỏ ngoài làm từ nhựa ABS chống va đập, lõi phích cắm cái sử dụng nhựa PC chịu nhiệt cùng chấu phích đồng lá giúp phích cắm có tuổi thọ lên tới 50.000 lần sử dụng</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -37651,6 +38819,17 @@
 Bảo hành: </t>
         </is>
       </c>
+      <c r="T4" t="inlineStr">
+        <is>
+          <t>Tại sao nên sử dụng phích cắm điện 2 chấu TLC
+Độ an toàn cao: Vỏ nhựa ABS cách điện chống nước chịu va đập cao, an toàn cho người sử dụng.
+Chịu tải lớn: Công suất chịu tải lên tới 2500W phù hợp với đa số thiết bị điện trong gia đình.
+Phù hợp với mọi loại ổ cắm: Chân phích cắm điện chịu tải có dạng tròn đường kính 4,5mm tiêu chuẩn phù hợp với các loại ổ cắm lỗ tròn trên thị trường.
+Thiết kế tiện lợi: Thiết kế dạng tròn, nhỏ gọn, kiểu cắm đứng dễ dàng cắm – tháo khỏi ổ cắm
+Độ bền cao:
+Vỏ ngoài làm từ nhựa ABS chống va đập, chân phích được đúc từ đồng giúp phích cắm có tuổi thọ lên tới 50.000 lần sử dụng.</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -37678,7 +38857,7 @@
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>{"cong_suat_chiu_tai": "2500W", "dien_ap_hoat_dong": "10A/250V", "kich_thuoc_chan_cam": "4.5mm", "chat_lieu_chan_phich": "Đồng Hàn Quốc", "chat_lieu_vo": "Nhựa ABS", "thuong_hieu": "TLC", "xuat_xu": "Việt Nam", "cong_suat_chiu_tai_toi_da": "2500W", "dien_ap_toi_da": "10A/250V", "mau_sac": "Trắng", "chat_lieu": "Vỏ nhựa ABS, Chân phích đồng"}</t>
+          <t>{"cong_suat_chiu_tai": "2500W", "dien_ap_hoat_dong": "10A/250V", "kich_thuoc_chan_cam": "4.5mm", "chat_lieu_chan_phich": "Đồng Hàn Quốc", "chat_lieu_vo": "Nhựa ABS", "thuong_hieu": "TLC", "xuat_xu": "Việt Nam", "cong_suat_chiu_tai_toi_da": "2500W", "dien_ap_toi_da": "10A/250V", "mau_sac": "Trắng", "chat_lieu": "Vỏ nhựa ABS, Chân phích đồng", "tuoi_tho": "50.000 lần sử dụng"}</t>
         </is>
       </c>
       <c r="L5" t="inlineStr">
@@ -37689,6 +38868,15 @@
       <c r="M5" t="inlineStr">
         <is>
           <t>https://tlclighting.com.vn/wp-content/uploads/2023/07/phich-cam-duong.jpg</t>
+        </is>
+      </c>
+      <c r="P5" t="inlineStr">
+        <is>
+          <t>Độ an toàn cao
+Phù hợp với mọi loại ổ cắm
+Thiết kế tiện lợi
+Độ bền cao
+Giá thành rẻ</t>
         </is>
       </c>
       <c r="Q5" t="inlineStr">
@@ -37710,6 +38898,21 @@
 Bảo hành: </t>
         </is>
       </c>
+      <c r="T5" t="inlineStr">
+        <is>
+          <t>Tại sao nên sử dụng phích cắm dương 10A-250V TLC
+Độ an toàn cao:
+Lớp vỏ phích cắm được làm từ nhựa ABS độ bền cao, cách điện tốt đảm bảo an toàn trong quá trình sử dụng cho người dùng.
+Phù hợp với mọi loại ổ cắm:
+Chân phích cắm dương TLC có dạng tròn đường kính 4,5mm tiêu chuẩn phù hợp với các loại ổ cắm lỗ tròn trên thị trường.
+Thiết kế tiện lợi:
+Thiết kế dạng tròn, nhỏ gọn, kiểu cắm đứng dễ dàng cắm – tháo khỏi ổ cắm.
+Độ bền cao:
+Vỏ ngoài làm từ nhựa ABS chống va đập, chân phích được đúc từ đồng giúp phích cắm có tuổi thọ lên tới 50.000 lần sử dụng.
+Giá thành rẻ:
+Phích cắm TLC LIGHTING là sản phẩm phổ thông chất lượng tốt với mức giá phải chăng. Phù hợp với mọi nhu cầu kết nối điện trong gia đình.</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -37737,7 +38940,7 @@
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>{"cong_suat_chiu_tai": "4500W", "dien_ap_hoat_dong": "20A/250V", "kich_thuoc_chan_cam": "4.5mm", "chat_lieu_chan_phich": "Đồng Hàn Quốc", "chat_lieu_vo": "Nhựa PC", "thuong_hieu": "TLC", "xuat_xu": "Việt Nam", "cong_suat_chiu_tai_toi_da": "4500W", "dien_ap_toi_da": "20A/250V", "mau_sac": "Cam", "chat_lieu": "Vỏ nhựa PC, Chân phích đồng", "loi_phich_cam_dien_chiu_tai": "Nhựa PC", "loi_phich_cam_dien_chiu_tai_chiu_nhiet": "140 độ C", "chan_phich_cam_dien_chiu_tai_duong_kinh": "4,5mm"}</t>
+          <t>{"cong_suat_chiu_tai": "4500W", "dien_ap_hoat_dong": "20A/250V", "kich_thuoc_chan_cam": "4.5mm", "chat_lieu_chan_phich": "Đồng Hàn Quốc", "chat_lieu_vo": "Nhựa PC", "thuong_hieu": "TLC", "xuat_xu": "Việt Nam", "dien_ap_toi_da": "20A/250V", "mau_sac": "Cam", "chat_lieu": "Vỏ nhựa PC, Chân phích đồng"}</t>
         </is>
       </c>
       <c r="L6" t="inlineStr">
@@ -37761,6 +38964,17 @@
 Màu sắc: Cam
 Chất liệu: Vỏ nhựa PC, Chân phích đồng
 Bảo hành: </t>
+        </is>
+      </c>
+      <c r="T6" t="inlineStr">
+        <is>
+          <t>Tại sao nên sử dụng phích cắm điện chịu tải 4500W
+Độ an toàn cao: Vỏ nhựa ABS cách điện chống nước chịu va đập cao, an toàn cho người sử dụng. Lõi phíc cắm điện chịu tải làm từ nhựa PC chịu nhiệt lên đến 140 độ C chống cháy dù trong điều kiện hoạt động kéo dài.
+Chịu tải lớn: Công suất chịu tải lên tới 4500W phù hợp với tất cả thiết bị điện dân dụng, thiết bị công nghiệp, thiết bị chuyên dùng được các thợ điện khuyên dùng.
+Phù hợp với mọi loại ổ cắm: Chân phích cắm điện chịu tải có dạng tròn đường kính 4,5mm tiêu chuẩn phù hợp với các loại ổ cắm lỗ tròn trên thị trường.
+Thiết kế tiện lợi: Thiết kế dạng tròn, nhỏ gọn, kiểu cắm đứng dễ dàng cắm – tháo khỏi ổ cắm
+Độ bền cao:
+Vỏ ngoài làm từ nhựa ABS chống va đập, lõi phích cắm điện chịu tải sử dụng nhựa PC chịu nhiệt cùng chân phích được đúc từ đồng giúp phích cắm có tuổi thọ lên tới 50.000 lần sử dụng.</t>
         </is>
       </c>
     </row>
@@ -37918,7 +39132,7 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>TLC-SAL-30×30</t>
+          <t>TLC-SAL-30x30</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
@@ -37928,7 +39142,7 @@
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>{"cong_suat_suoi_am": "1250/ 2500W", "cong_suat_quat": "36W", "cong_suat_den_LED": "11W", "kich_thuoc": "300x300x130 mm", "dieu_khien": "Điều khiển cảm ứng từ xa, Điều khiển từ xa cảm ứng gắn tường", "dien_ap": "AC 220V/ 50Hz, 50Hz, 220V", "tuoi_tho": "30.000 giờ", "bao_hanh": "3 năm, 03 năm, 36 tháng", "thuong_hieu": "TLC LIGHTING", "chat_lieu": "Nhựa ABS, Nhựa ABS cao cấp", "mau_sac_anh_sang": "Trắng", "cong_nghe_suoi_am": "Sưởi gốm Ceramic", "nhiet_do_mau": "6000K"}</t>
+          <t>{"cong_suat_suoi_am": "1250/ 2500W", "cong_suat_quat": "36W", "cong_suat_den_LED": "11W", "kich_thuoc": "300x300x130 mm", "dieu_khien": "Điều khiển cảm ứng từ xa", "dien_ap": "AC 220V/ 50Hz", "tuoi_tho": "30.000 giờ", "bao_hanh": "3 năm", "thuong_hieu": "TLC LIGHTING", "chat_lieu": "Nhựa ABS", "mau_sac_anh_sang": "Trắng", "cong_nghe_suoi_am": "Sưởi gốm Ceramic", "dien_ap_AC": "50Hz, 220V"}</t>
         </is>
       </c>
       <c r="J2" t="n">
@@ -38001,7 +39215,7 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>TLC-SAUV- 60×30</t>
+          <t>TLC-SAUV-60×30</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
@@ -38011,7 +39225,7 @@
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>{"cong_suat_den_LED": "16W", "kich_thuoc": "600x300x120mm", "cong_suat_quat_va_thong_gio": "46W", "suoi_am_1": "1400W", "suoi_am_2": "2600W", "dien_ap": "AC 220V/ 50Hz", "bao_hanh_tai_nha": "24 tháng", "dien_ap_AC": "50Hz, 220V", "nhiet_do_mau": "6000K"}</t>
+          <t>{"cong_suat_den_LED": "16W", "kich_thuoc": "600x300x120mm", "cong_suat_quat_va_thong_gio": "46W", "suoi_am_1": "1400W", "suoi_am_2": "2600W", "dien_ap": "AC 220V/ 50Hz", "bao_hanh_tai_nha": "24 tháng", "thuong_hieu": "TLC LIGHTING", "dien_ap_AC": "50Hz, 220V"}</t>
         </is>
       </c>
       <c r="J3" t="n">
@@ -38098,7 +39312,7 @@
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>{"cong_suat_suoi_am": "1300/ 2600W", "cong_suat_quat_gio": "46W", "cong_suat_den_LED": "16W", "kich_thuoc": "600x300x130 mm", "dieu_khien": "Điều khiển cảm ứng từ xa", "dien_ap": "AC 220V/ 50Hz", "tuoi_tho": "30.000 giờ", "bao_hanh": "3 năm", "thuong_hieu": "TLC LIGHTING", "cong_suat_quat": "46W", "chat_lieu": "Nhựa ABS", "mau_sac_anh_sang": "Trắng", "cong_nghe_suoi_am": "Sưởi gốm Ceramic", "dien_ap_AC": "50Hz, 220V"}</t>
+          <t>{"cong_suat_suoi_am": "1300/ 2600W", "cong_suat_quat_gio": "46W", "cong_suat_den_LED": "16W", "kich_thuoc": "600x300x130 mm", "dieu_khien": "Điều khiển cảm ứng từ xa", "dien_ap": "AC 220V/ 50Hz", "tuoi_tho": "30.000 giờ", "bao_hanh": "3 năm", "thuong_hieu": "TLC LIGHTING", "cong_suat_quat": "46W", "chat_lieu": "Nhựa ABS", "mau_sac_anh_sang": "Trắng", "cong_nghe_suoi_am": "Sưởi gốm Ceramic", "dien_ap_ac": "50Hz, 220V"}</t>
         </is>
       </c>
       <c r="J4" t="n">
@@ -38320,7 +39534,7 @@
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>{"cong_suat": "07W", "anh_sang": "3 màu", "CRI": "OSRAM – CHLB Đức", "Flicker": "0,1%-0,2% Không nhấp nháy", "UGR": "~19 Hạn chế chói mắt", "duong_kinh_lo_khoet": "D90mm", "kich_thuoc": "Ø120×35 mm", "bao_ve_thi_luc": "Hạn chế ánh sáng xanh", "bao_hanh": "30 tháng", "chip_LED": "OSRAM – CHLB Đức"}</t>
+          <t>{"cong_suat": "07W, 7W", "anh_sang": "3 màu", "cri": "OSRAM – CHLB Đức, 85-90Ra", "flicker": "0,1%-0,2% Không nhấp nháy", "ugr": "~19 Hạn chế chói mắt", "duong_kinh_lo_khoet": "D90mm", "kich_thuoc": "Ø120×35 mm", "bao_ve_thi_luc": "Hạn chế ánh sáng xanh", "bao_hanh": "30 tháng", "thuong_hieu": "TLC LIGHTING", "chip_led": "OSRAM – CHLB Đức"}</t>
         </is>
       </c>
       <c r="J2" t="n">
@@ -38409,7 +39623,7 @@
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>{"cong_suat": "07W", "anh_sang": "Trắng/Vàng/Trung tính", "cri": "OSRAM – CHLB Đức", "flicker": "0,1%-0,2% Không nhấp nháy", "ugr": "~19 Hạn chế chói mắt", "duong_kinh_lo_khoet": "D90mm", "kich_thuoc": "Ø120×35 mm", "bao_ve_thi_luc": "Hạn chế ánh sáng xanh", "bao_hanh": "30 tháng"}</t>
+          <t>{"cong_suat": "07W", "anh_sang": "Trắng/Vàng/Trung tính", "CRI": "OSRAM – CHLB Đức", "Flicker": "0,1%-0,2% Không nhấp nháy", "UGR": "~19 Hạn chế chói mắt", "duong_kinh_lo_khoet": "D90mm", "kich_thuoc": "Ø120×35 mm", "bao_ve_thi_luc": "Hạn chế ánh sáng xanh", "bao_hanh": "30 tháng", "chip_LED": "OSRAM – CHLB Đức"}</t>
         </is>
       </c>
       <c r="J3" t="n">
@@ -38498,7 +39712,7 @@
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>{"cong_suat": "07W", "anh_sang": "3 màu", "cri": "85-90Ra", "flicker": "0,1%-0,2% Không nhấp nháy", "ugr": "~19 Hạn chế chói mắt", "duong_kinh_lo_khoet": "D90mm", "kich_thuoc": "Ø120×35 mm", "bao_ve_thi_luc": "Hạn chế ánh sáng xanh", "bao_hanh": "30 tháng", "chip_led": "OSRAM – CHLB Đức"}</t>
+          <t>{"cong_suat": "07W", "anh_sang": "3 màu", "cri": "OSRAM – CHLB Đức, 85-90Ra", "flicker": "0,1%-0,2% Không nhấp nháy", "ugr": "~19 Hạn chế chói mắt", "duong_kinh_lo_khoet": "D90mm", "kich_thuoc": "Ø120×35 mm", "bao_ve_thi_luc": "Hạn chế ánh sáng xanh", "bao_hanh": "30 tháng", "thuong_hieu": "TLC LIGHTING", "chip_led": "OSRAM – CHLB Đức"}</t>
         </is>
       </c>
       <c r="J4" t="n">
@@ -38587,7 +39801,7 @@
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>{"cong_suat": "9W", "anh_sang": "3 màu", "CRI": "OSRAM – CHLB Đức, 85-90Ra", "Flicker": "0,1%-0,2% Không nhấp nháy", "UGR": "~19 Hạn chế chói mắt", "duong_kinh_lo_khoet": "D90mm", "kich_thuoc": "Ø120×35 mm", "bao_ve_thi_luc": "Hạn chế ánh sáng xanh", "bao_hanh": "30 tháng", "thuong_hieu": "TLC LIGHTING", "chip_LED": "OSRAM – CHLB Đức"}</t>
+          <t>{"cong_suat": "9W", "anh_sang": "3 màu", "cri": "OSRAM – CHLB Đức, 85-90Ra", "flicker": "0,1%-0,2% Không nhấp nháy", "ugr": "~19 Hạn chế chói mắt", "duong_kinh_lo_khoet": "D90mm", "kich_thuoc": "Ø120×35 mm", "bao_ve_thi_luc": "Hạn chế ánh sáng xanh", "bao_hanh": "30 tháng", "thuong_hieu": "TLC LIGHTING", "chip_led": "OSRAM – CHLB Đức"}</t>
         </is>
       </c>
       <c r="J5" t="n">
@@ -38676,7 +39890,7 @@
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>{"cong_suat": "9W", "anh_sang": "Trắng/Vàng/Trung tính", "cri": "85-90Ra", "flicker": "0,1%-0,2% Không nhấp nháy", "ugr": "~19 Hạn chế chói mắt", "duong_kinh_lo_khoet": "D90mm", "kich_thuoc": "Ø120×35 mm", "bao_ve_thi_luc": "Hạn chế ánh sáng xanh", "bao_hanh": "30 tháng", "chip_led": "OSRAM – CHLB Đức", "thuong_hieu": "TLC LIGHTING"}</t>
+          <t>{"cong_suat": "9W", "anh_sang": "Trắng/Vàng/Trung tính", "CRI": "OSRAM – CHLB Đức, 85-90Ra", "Flicker": "0,1%-0,2% Không nhấp nháy", "UGR": "~19 Hạn chế chói mắt", "duong_kinh_lo_khoet": "D90mm", "kich_thuoc": "Ø120×35 mm", "bao_ve_thi_luc": "Hạn chế ánh sáng xanh", "bao_hanh": "30 tháng", "thuong_hieu": "TLC LIGHTING", "chip_LED": "OSRAM – CHLB Đức"}</t>
         </is>
       </c>
       <c r="J6" t="n">
@@ -38765,7 +39979,7 @@
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>{"cong_suat": "9W", "anh_sang": "3 màu", "cri": "OSRAM – CHLB Đức, 85-90Ra", "flicker": "0,1%-0,2% Không nhấp nháy", "ugr": "~19 Hạn chế chói mắt", "duong_kinh_lo_khoet": "D90mm", "kich_thuoc": "Ø120×35 mm", "bao_ve_thi_luc": "Hạn chế ánh sáng xanh", "bao_hanh": "30 tháng", "thuong_hieu": "TLC LIGHTING", "chip_led": "OSRAM – CHLB Đức"}</t>
+          <t>{"cong_suat": "9W", "anh_sang": "3 màu", "CRI": "OSRAM – CHLB Đức, 85-90Ra", "Flicker": "0,1%-0,2% Không nhấp nháy", "UGR": "~19 Hạn chế chói mắt", "duong_kinh_lo_khoet": "D90mm", "kich_thuoc": "Ø120×35 mm", "bao_ve_thi_luc": "Hạn chế ánh sáng xanh", "bao_hanh": "30 tháng", "thuong_hieu": "TLC LIGHTING", "chip_LED": "OSRAM – CHLB Đức"}</t>
         </is>
       </c>
       <c r="J7" t="n">
@@ -39170,7 +40384,7 @@
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>{"cong_suat": "08W", "anh_sang": "3 màu", "CRI": "OSRAM – CHLB Đức, 85-90Ra, 90, 97/100", "Flicker": "0,1%-0,2% Không nhấp nháy", "UGR": "~ 16 Hạn chế chói mắt", "duong_kinh_lo_khoet": "D90mm", "kich_thuoc": "Ø112×54 mm", "bao_ve_thi_luc": "Hạn chế ánh sáng xanh", "bao_hanh": "36 tháng, 30-36 tháng, 2 năm", "thuong_hieu": "TLC LIGHTING", "Chip LED": "OSRAM – CHLB Đức", "do_ben_sang": "L70-50.000h", "nhiet_do_mau_Kelvin": "3000-6000K"}</t>
+          <t>{"cong_suat": "08W", "anh_sang": "3 màu", "CRI": "OSRAM – CHLB Đức", "Flicker": "0,1%-0,2% Không nhấp nháy", "UGR": "~ 16 Hạn chế chói mắt", "duong_kinh_lo_khoet": "D90mm", "kich_thuoc": "Ø112×54 mm", "bao_ve_thi_luc": "Hạn chế ánh sáng xanh", "bao_hanh": "36 tháng", "thuong_hieu": "TLC LIGHTING", "chip_LED": "OSRAM – CHLB Đức", "CRI_chip_led": "85-90Ra"}</t>
         </is>
       </c>
       <c r="J2" t="n">
@@ -39259,7 +40473,7 @@
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>{"cong_suat": "08W", "anh_sang": "Trắng/Vàng/Trung tính", "chip_led": "OSRAM – CHLB Đức", "cri": "85-90Ra", "flicker": "0,1%-0,2% Không nhấp nháy", "ugr": "~ 16 Hạn chế chói mắt", "duong_kinh_lo_khoet": "D90mm", "kich_thuoc": "Ø112×54 mm", "bao_ve_thi_luc": "Hạn chế ánh sáng xanh", "bao_hanh": "36 tháng", "thuong_hieu": "TLC LIGHTING"}</t>
+          <t>{"cong_suat": "8W", "anh_sang": "Trắng/Vàng/Trung tính", "cri": "85-90Ra", "flicker": "0,1%-0,2% Không nhấp nháy", "ugr": "~ 16 Hạn chế chói mắt", "duong_kinh_lo_khoet": "D90mm", "kich_thuoc": "Ø112×54 mm", "bao_ve_thi_luc": "Hạn chế ánh sáng xanh", "bao_hanh": "36 tháng"}</t>
         </is>
       </c>
       <c r="J3" t="n">
@@ -39476,7 +40690,7 @@
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>{"cong_suat": "20W", "anh_sang": "Trắng", "kich_thuoc": "1200 mm", "chip_led": "SMD", "dien_ap": "AC 120-265", "thuong_hieu": "TLC LIGHTING", "tuoi_tho": "40.000h", "bao_hanh": "24 tháng", "chung_loai": "Bộ tuýp LED thủy tinh", "quang_thong": "2400 lm", "dien_ap_ac": "AC 120-265", "tuoi_tho_chip_led": "40.000 giờ", "hieu_suat_phat_quang": "90-100 Lm/w", "chi_so_hoan_mau": "Ra&gt; 85"}</t>
+          <t>{"cong_suat": "20W", "anh_sang": "Trắng", "kich_thuoc": "1200 mm, 1.2 m", "chip_led": "SMD", "dien_ap": "AC 120-265", "thuong_hieu": "TLC LIGHTING", "tuoi_tho": "40.000h", "bao_hanh": "24 tháng", "chung_loai": "Bộ tuýp LED thủy tinh", "quang_thong": "2400 lm", "tuoi_tho_chip_led": "40.000 giờ"}</t>
         </is>
       </c>
       <c r="J2" t="n">
@@ -39550,7 +40764,7 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>TLC-BTT-28W, TLC-TTT-28W</t>
+          <t>TLC-BTT-28W</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
@@ -39560,7 +40774,7 @@
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>{"cong_suat": "28W", "anh_sang": "Trắng", "kich_thuoc": "1200 mm, 1.2 m", "chip_led": "SMD", "dien_ap": "AC 120-265", "thuong_hieu": "TLC LIGHTING", "tuoi_tho": "40.000h, 40.000 giờ", "bao_hanh": "24 tháng", "quang_thong": "2660 lm", "chu_loai": "Tuýp LED thủy tinh"}</t>
+          <t>{"cong_suat": "28W", "anh_sang": "Trắng", "kich_thuoc": "1.2m", "chip_led": "SMD", "dien_ap": "AC 120-265", "thuong_hieu": "TLC LIGHTING", "tuoi_tho": "40.000h", "bao_hanh": "24 tháng", "chung_loai": "Tuýp LED thủy tinh", "quang_thong": "2660 lm", "dien_ap_ac": "AC 120-265", "tuoi_tho_chip_led": "40.000 giờ"}</t>
         </is>
       </c>
       <c r="J3" t="n">
@@ -39727,7 +40941,7 @@
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>{"cong_suat": "28W", "anh_sang": "Trắng", "kich_thuoc": "1200 mm", "chip_led": "SMD", "dien_ap": "AC 120-265", "thuong_hieu": "TLC LIGHTING", "tuoi_tho": "40.000h", "bao_hanh": "24 tháng", "chung_loai": "Tuýp LED thủy tinh", "quang_thong": "2660 lm", "dien_ap_ac": "AC 120-265", "tuoi_tho_chip_led": "40.000 giờ", "hieu_suat_phat_quang": "90-100 Lm/w", "chi_so_hoan_mau": "Ra&gt; 85"}</t>
+          <t>{"cong_suat": "28W", "anh_sang": "Trắng", "kich_thuoc": "1.2 m", "chip_led": "SMD", "dien_ap": "AC 120-265", "thuong_hieu": "TLC LIGHTING", "tuoi_tho": "40.000h", "bao_hanh": "24 tháng", "chung_loai": "Tuýp LED thủy tinh", "quang_thong": "2660 lm", "dien_ap_ac": "AC 120-265", "tuoi_tho_chip_led": "40.000 giờ"}</t>
         </is>
       </c>
       <c r="J5" t="n">
@@ -40168,7 +41382,7 @@
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>{"cong_suat": "18W", "anh_sang": "Trắng, vàng", "kich_thuoc": "600", "hieu_suat_quang": "95 Lm/w, 95 Lm/W", "chi_so_hoan_mau": "CRI≥80, Ra &gt; 80", "dien_ap": "85-265V", "chat_lieu": "Nhựa, nhôm cao cấp", "thuong_hieu": "TLC LIGHTING", "tuoi_tho": "40.000h, 50.000 giờ", "bao_hanh": "24 tháng", "quang_thong": "1710Lm", "che_do_chieu_sang": "Chống chói", "nhiet_do_hoat_dong": "-10oC~40oC", "nhiet_do_ben_ngoai": "≤40oC", "nhiet_do_mau": "6500K"}</t>
+          <t>{"cong_suat": "18W", "anh_sang": "Trắng, vàng", "kich_thuoc": "600", "hieu_suat_quang": "95 Lm/w", "chi_so_hoan_mau": "CRI≥80", "dien_ap": "85-265V", "chat_lieu": "Nhựa, nhôm cao cấp", "thuong_hieu": "TLC LIGHTING", "tuoi_tho": "40.000h", "bao_hanh": "24 tháng", "quang_thong": "1710Lm", "che_do_chieu_sang": "Chống chói", "nhiet_do_hoat_dong": "-10oC~40oC", "nhiet_do_ben_ngoai": "≤40oC"}</t>
         </is>
       </c>
       <c r="J10" t="n">
@@ -40354,7 +41568,7 @@
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>{"cong_suat": "27W", "anh_sang": "Trắng/vàng", "kich_thuoc": "2565", "hieu_suat_quang": "95 Lm/w, 95 Lm/W", "chi_so_hoan_mau": "CRI≥80, Ra &gt; 80", "dien_ap": "85-265V", "chat_lieu": "Nhôm, nhựa cao cấp", "thuong_hieu": "TLC LIGHTING", "tuoi_tho": "40.000h, &gt; 40.000 giờ, 40.000 giờ", "bao_hanh": "24 tháng", "che_do_chieu_sang": "Chống chói", "nhiet_do_hoat_dong": "-10oC~40oC", "nhiet_do_ben_ngoai": "≤40oC"}</t>
+          <t>{"cong_suat": "27W", "anh_sang": "Trắng/vàng", "kich_thuoc": "2565", "hieu_suat_quang": "95 Lm/w", "chi_so_hoan_mau": "CRI≥80", "dien_ap": "85-265V", "chat_lieu": "Nhôm, nhựa cao cấp", "thuong_hieu": "TLC LIGHTING", "tuoi_tho": "40.000h", "bao_hanh": "24 tháng", "che_do_chieu_sang": "Chống chói", "nhiet_do_hoat_dong": "-10oC~40oC", "nhiet_do_ben_ngoai": "≤40oC"}</t>
         </is>
       </c>
       <c r="J12" t="n">
@@ -40524,7 +41738,7 @@
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>{"cong_suat": "20W", "anh_sang": "Trắng/ Vàng", "kich_thuoc": "600 mm", "dien_ap": "AC 120-265V", "thuong_hieu": "TLC LIGHTING", "tuoi_tho": "40.000h", "bao_hanh": "24 tháng", "quang_thong": "2000 Lm", "dien_ap_ac": "AC 120-265", "tuoi_tho_chip_led": "40.000 giờ", "chi_so_hoan_mau": "cao trên 80 Ra"}</t>
+          <t>{"cong_suat": "20W", "anh_sang": "Trắng/ Vàng", "kich_thuoc": "600 mm", "dien_ap": "AC 120-265V", "thuong_hieu": "TLC LIGHTING", "tuoi_tho": "40.000h", "bao_hanh": "24 tháng", "quang_thong": "2000 Lm", "dien_ap_ac": "AC 120-265", "tuoi_tho_chip_led": "40.000 giờ", "chi_so_hoan_mau_cri": "cao trên 80 Ra"}</t>
         </is>
       </c>
       <c r="J14" t="n">
@@ -40603,7 +41817,7 @@
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>{"cong_suat": "52W", "anh_sang": "Trắng", "kich_thuoc": "1200 mm", "dien_ap": "AC 120-265", "thuong_hieu": "TLC LIGHTING", "tuoi_tho": "40.000h", "bao_hanh": "24 tháng", "quang_thong": "6240 Lm", "chat_lieu_vo_den": "Nhựa PC", "cong_nghe": "Đúc nguyên khối, không phân lớp"}</t>
+          <t>{"cong_suat": "52W", "anh_sang": "Trắng", "kich_thuoc": "1200 mm", "dien_ap": "AC 120-265", "thuong_hieu": "TLC LIGHTING", "tuoi_tho": "40.000h", "bao_hanh": "24 tháng", "dien_ap_ac": "160-265V", "quang_thong": "6240 Lm", "kich_thuoc_den": "1200mm", "chat_lieu_vo_den": "Nhựa PC", "cong_nghe": "Đúc nguyên khối, không phân lớp", "tuoi_tho_chip_led": "40.000 giờ", "hieu_suat_chieu_sang": "120 Lm/W", "goc_chieu": "180°"}</t>
         </is>
       </c>
       <c r="J15" t="n">
@@ -40689,7 +41903,7 @@
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>{"cong_suat": "18W", "anh_sang": "Trắng/Vàng", "kich_thuoc": "1200mm", "hieu_suat_quang": "120 Lm/w", "chi_so_hoan_mau": "CRI≥80", "dien_ap": "85-265V", "chat_lieu": "Mica cao cấp", "thuong_hieu": "TLC LIGHTING", "tuoi_tho": "40.000h", "bao_hanh": "24 tháng", "quang_thong": "1530Lm", "ra": "&gt; 80", "che_do_chieu_sang": "Chống chói", "nhiet_do_hoat_dong": "-10oC~40oC", "nhiet_do_ben_ngoai": "≤40oC"}</t>
+          <t>{"cong_suat": "18W", "anh_sang": "Trắng/Vàng", "kich_thuoc": "1200mm", "hieu_suat_quang": "120 Lm/w", "chi_so_hoan_mau": "CRI≥80", "dien_ap": "85-265V", "chat_lieu": "Mica cao cấp", "thuong_hieu": "TLC LIGHTING", "tuoi_tho": "40.000h", "bao_hanh": "24 tháng", "quang_thong": "1530Lm", "che_do_chieu_sang": "Chống chói", "nhiet_do_hoat_dong": "-10oC~40oC", "nhiet_do_ben_ngoai": "≤40oC"}</t>
         </is>
       </c>
       <c r="J16" t="n">
@@ -40877,7 +42091,7 @@
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>{"cong_suat": "11W", "anh_sang": "Trắng", "kich_thuoc": "600 mm", "chip_led": "SMD", "dien_ap": "AC 120-265", "thuong_hieu": "TLC LIGHTING", "tuoi_tho": "40.000h", "bao_hanh": "24 tháng", "chung_loai": "Bóng thủy tinh", "quang_thong": "1045 lm", "dien_ap_ac": "AC 120-265", "tuoi_tho_chip_led": "40.000 giờ"}</t>
+          <t>{"cong_suat": "11W", "anh_sang": "Trắng", "kich_thuoc": "600 mm", "chip_led": "SMD", "dien_ap": "AC 120-265", "thuong_hieu": "TLC LIGHTING", "tuoi_tho": "40.000h", "bao_hanh": "24 tháng", "chung_loai": "Bóng thủy tinh", "quang_thong": "1045 lm", "kich_thuoc_": "0.6m", "dien_ap_ac": "AC 120-265", "tuoi_tho_chip_led": "40.000 giờ"}</t>
         </is>
       </c>
       <c r="J18" t="n">
@@ -40932,11 +42146,7 @@
 Tuýp thủy tinh có
 mức giá
 thành phù hợp với khả năng chi trả của khách hàng
-Bảo hành 24 tháng
-5. Ứng dụng của đèn LED tuýp thủy tinh
-Với những ưu điểm vượt trội cùng thương hiệu TLC Lighting uy tín đèn LED tuýp thủy tinh 0.6W của TLC LIGHTING được ứng dụng rộng rãi trong chiếu sáng phòng khách, phòng ngủ, phòng ăn, phòng đọc sách, phòng bếp…
-Đèn tuýp LED chiếu sáng siêu thị
-Đèn tuýp LED chiếu sáng hầm gửi xe</t>
+Bảo hành 24 tháng</t>
         </is>
       </c>
     </row>
@@ -40966,7 +42176,7 @@
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>{"cong_suat": "40W", "anh_sang": "Trắng, Vàng", "kich_thuoc": "1200 mm, 1.2 m", "chip_led": "SMD", "dien_ap": "AC 180-265", "thuong_hieu": "TLC LIGHTING", "tuoi_tho": "40.000h, 40.000 giờ", "bao_hanh": "24 tháng", "chung_loai": "Tuýp LED thủy tinh", "quang_thong": "4800 Lm", "hieu_suat_phat_quang": "120Lm/W", "chi_so_hoan_mau": "CRI &gt; 85"}</t>
+          <t>{"cong_suat": "40W", "anh_sang": "Trắng/ Vàng", "kich_thuoc": "1200 mm", "chip_led": "SMD", "dien_ap": "AC 180-265", "thuong_hieu": "TLC LIGHTING", "tuoi_tho": "40.000h", "bao_hanh": "24 tháng", "chung_loai": "Tuýp LED thủy tinh", "quang_thong": "4800 Lm", "tuoi_tho_chip_led": "40.000 giờ", "hieu_suat_phat_quang": "120Lm/W", "chi_so_hoan_mau": "CRI &gt; 85"}</t>
         </is>
       </c>
       <c r="J19" t="n">
@@ -41059,7 +42269,7 @@
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t>{"cong_suat": "11W", "anh_sang": "Trắng", "kich_thuoc": "600 mm", "chip_led": "SMD", "dien_ap": "AC 120-265", "thuong_hieu": "TLC LIGHTING", "tuoi_tho": "40.000h", "bao_hanh": "24 tháng", "chung_loai": "Bộ đèn tuýp thủy tinh", "quang_thong": "1045 lm", "dien_ap_ac": "AC 120-265", "tuoi_tho_chip_led": "40.000 giờ"}</t>
+          <t>{"cong_suat": "11W", "anh_sang": "Trắng", "kich_thuoc": "600 mm", "chip_led": "SMD", "dien_ap": "AC 120-265", "thuong_hieu": "TLC LIGHTING", "tuoi_tho": "40.000h", "bao_hanh": "24 tháng", "chung_loai": "Bộ đèn tuýp thủy tinh", "quang_thong": "1045 lm", "tuoi_tho_chip_led": "40.000 giờ", "hieu_suat_quang": "cao", "chi_so_hoan_mau": "Ra &gt; 80"}</t>
         </is>
       </c>
       <c r="J20" t="n">
@@ -41115,11 +42325,7 @@
 Tuýp thủy tinh có
 mức giá
 thành phù hợp với khả năng chi trả của khách hàng
-Bảo hành 24 tháng
-5. Ứng dụng của bộ đèn LED tuýp thủy tinh
-Với những ưu điểm vượt trội cùng thương hiệu TLC Lighting uy tín đèn LED tuýp thủy tinh 0.6W của TLC LIGHTING được ứng dụng rộng rãi trong chiếu sáng phòng khách, phòng ngủ, phòng ăn, phòng đọc sách, phòng bếp…
-Đèn tuýp LED chiếu sáng siêu thị
-Đèn tuýp LED chiếu sáng phòng ngủ</t>
+Bảo hành 24 tháng</t>
         </is>
       </c>
     </row>
@@ -41149,7 +42355,7 @@
       </c>
       <c r="I21" t="inlineStr">
         <is>
-          <t>{"cong_suat": "10W", "anh_sang": "Trắng, vàng", "kich_thuoc": "300", "hieu_suat_quang": "95 Lm/w", "chi_so_hoan_mau": "CRI≥80", "dien_ap": "85-265V", "chat_lieu": "Nhựa cao cấp, nhôm tĩnh điện", "thuong_hieu": "TLC LIGHTING", "tuoi_tho": "40.000h", "bao_hanh": "24 tháng", "quang_thong": "950 Lm", "che_do_chieu_sang": "Chống chói", "nhiet_do_hoat_dong": "-10oC~40oC", "nhiet_do_ben_ngoai": "≤40oC"}</t>
+          <t>{"cong_suat": "10W", "anh_sang": "Trắng, vàng", "kich_thuoc": "300", "hieu_suat_quang": "95 Lm/w", "chi_so_hoan_mau": "CRI≥80", "dien_ap": "85-265V", "chat_lieu": "Nhựa cao cấp, nhôm tĩnh điện", "thuong_hieu": "TLC LIGHTING", "tuoi_tho": "40.000h", "bao_hanh": "24 tháng", "quang_thong": "950 Lm", "ra": "&gt; 80", "che_do_chieu_sang": "Chống chói", "nhiet_do_hoat_dong": "-10oC~40oC", "nhiet_do_ben_ngoai": "≤40oC"}</t>
         </is>
       </c>
       <c r="J21" t="n">
@@ -41247,7 +42453,7 @@
       </c>
       <c r="I22" t="inlineStr">
         <is>
-          <t>{"cong_suat": "10W", "anh_sang": "Trắng/vàng", "kich_thuoc": "600 mm", "chip_led": "SMD", "dien_ap": "AC 85-265", "thuong_hieu": "TLC LIGHTING", "tuoi_tho": "40.000h", "bao_hanh": "24 tháng", "hang_san_xuat": "TLC LIGHTING", "xuat_xu": "Việt Nam", "chung_loai": "Tuýp LED T8", "quang_thong": "850 lm", "tuoi_tho_chip_led": "40.000 giờ"}</t>
+          <t>{"cong_suat": "10W", "anh_sang": "Trắng/vàng", "kich_thuoc": "600 mm", "chip_led": "SMD", "dien_ap": "AC 85-265", "thuong_hieu": "TLC LIGHTING", "tuoi_tho": "40.000h", "bao_hanh": "24 tháng", "hang_san_xuat": "TLC LIGHTING", "xuat_xu": "Việt Nam", "chung_loai": "Tuýp LED T8", "quang_thong": "850 lm", "dien_ap_ac": "AC 85-265", "tuoi_tho_chip_led": "40.000 giờ"}</t>
         </is>
       </c>
       <c r="J22" t="n">
@@ -41349,6 +42555,17 @@
           <t>https://tlclighting.com.vn/wp-content/uploads/2019/09/Untitled-1-Copy.jpg</t>
         </is>
       </c>
+      <c r="P23" t="inlineStr">
+        <is>
+          <t>Tiết kiệm điện năng tiêu thụ: Đèn LED tuýp T8 được dùng để thay thế hoàn toàn bóng đèn huỳnh quang hay compact bởi khả năng tiết kiệm điện từ 50-80%. Do vậy, người tiêu dùng có thể tiết kiệm khoản chi phí lớn dành cho điện
+Đa dạng kích thước (0.6m và 1,2m); công suất (10w, 18w, 24w); màu sắc ánh sáng ( màu trắng, màu vàng) giúp người tiêu dùng có thể ứng dụng được ở nhiều vị trí khác nhau cho công trình.
+Đèn không chứa các các độc hại như lưu huỳnh, bột huỳnh quang. Khi phát sáng đèn không phát ra các tia có hại như: tia cực tím, tia hồng ngoại,…
+Tuổi thọ của đèn cao, lên tới 40.000 giờ chiếu sáng. Riêng đối với đèn T8 công suất 24w chuyên dụng cho công trình có thể hoạt động trong 3 ca liên tục mà vẫn đảm bảo về tuổi thọ và độ bền của đèn
+Ánh sáng của đèn có chỉ số hoàn màu cao, ánh sáng tự nhiên, đồng đều, tốt cho mắt, bảo vệ mắt theo tiêu chuẩn Châu Âu.
+Chính sách bảo hành sản phẩm lên tới 24 tháng
+Đèn dễ dàng lắp đặt, thay thế.</t>
+        </is>
+      </c>
       <c r="Q23" t="inlineStr">
         <is>
           <t>Mã sản phẩm: TLC-TT8-18W
@@ -41364,6 +42581,20 @@
 Bảo hành: 24 tháng</t>
         </is>
       </c>
+      <c r="T23" t="inlineStr">
+        <is>
+          <t>4. Ưu điểm đèn tuýp LED 1.2m công suất 18W
+Đèn LED tuýp T8 của TLC Lighting được đánh giá là là một trong những sản phẩm LED tuýp được khách hàng ưa chuộng và tin dùng. Vì sao lại như vậy? Đèn đem lại những lợi ích gì cho người tiêu dùng, chúng ta hãy cùng tìm hiểu những ưu điểm của đèn LED tuýp T8 nhé!
+Tiết kiệm điện năng tiêu thụ: Đèn LED tuýp T8 được dùng để thay thế hoàn toàn bóng đèn huỳnh quang hay compact bởi khả năng tiết kiệm điện từ 50-80%. Do vậy, người tiêu dùng có thể tiết kiệm khoản chi phí lớn dành cho điện
+Đa dạng kích thước (0.6m và 1,2m); công suất (10w, 18w, 24w); màu sắc ánh sáng ( màu trắng, màu vàng) giúp người tiêu dùng có thể ứng dụng được ở nhiều vị trí khác nhau cho công trình.
+Đèn LED tuýp T8 TLC Lighting
+Đèn không chứa các các độc hại như lưu huỳnh, bột huỳnh quang. Khi phát sáng đèn không phát ra các tia có hại như: tia cực tím, tia hồng ngoại,…
+Tuổi thọ của đèn cao, lên tới 40.000 giờ chiếu sáng. Riêng đối với đèn T8 công suất 24w chuyên dụng cho công trình có thể hoạt động trong 3 ca liên tục mà vẫn đảm bảo về tuổi thọ và độ bền của đèn
+Ánh sáng của đèn có chỉ số hoàn màu cao, ánh sáng tự nhiên, đồng đều, tốt cho mắt, bảo vệ mắt theo tiêu chuẩn Châu Âu.
+Chính sách bảo hành sản phẩm lên tới 24 tháng
+Đèn dễ dàng lắp đặt, thay thế.</t>
+        </is>
+      </c>
     </row>
     <row r="24">
       <c r="A24" t="n">
@@ -41457,7 +42688,7 @@
       </c>
       <c r="I25" t="inlineStr">
         <is>
-          <t>{"cong_suat": "52W", "anh_sang": "Trắng/ Vàng", "kich_thuoc": "1200 mm", "chip_led": "SMD", "dien_ap": "AC 120-265", "thuong_hieu": "TLC LIGHTING", "tuoi_tho": "40.000h", "bao_hanh": "24 tháng", "quang_thong": "5200 Lm", "dien_ap_ac": "AC 120-265", "tuoi_tho_chip_led": "40.000 giờ", "cri": "&gt;85"}</t>
+          <t>{"cong_suat": "52W", "anh_sang": "Trắng/ Vàng", "kich_thuoc": "1200 mm", "chip_led": "SMD", "dien_ap": "AC 120-265", "thuong_hieu": "TLC LIGHTING", "tuoi_tho": "40.000h", "bao_hanh": "24 tháng", "quang_thong": "5200 Lm", "dien_ap_ac": "AC 120-265", "tuoi_tho_chip_led": "40.000 giờ", "chi_so_hoan_mau": "CRI&gt;85"}</t>
         </is>
       </c>
       <c r="J25" t="n">
@@ -41543,7 +42774,7 @@
       </c>
       <c r="I26" t="inlineStr">
         <is>
-          <t>{"cong_suat": "10W", "anh_sang": "Trắng/Vàng", "kich_thuoc": "600mm", "hieu_suat_quang": "120 Lm/w, 95 Lm/W", "chi_so_hoan_mau": "CRI≥80, Ra &gt; 80", "dien_ap": "85-265V", "chat_lieu": "Nhựa mica cao cấp", "thuong_hieu": "TLC LIGHTING", "tuoi_tho": "40.000h, 40,000h", "bao_hanh": "24 tháng", "quang_thong": "850Lm", "che_do_chieu_sang": "Chống chói"}</t>
+          <t>{"cong_suat": "10W", "anh_sang": "Trắng/Vàng", "kich_thuoc": "600mm", "hieu_suat_quang": "120 Lm/w", "chi_so_hoan_mau": "CRI≥80", "dien_ap": "85-265V", "chat_lieu": "Nhựa mica cao cấp", "thuong_hieu": "TLC LIGHTING", "tuoi_tho": "40.000h", "bao_hanh": "24 tháng", "quang_thong": "850Lm", "che_do_chieu_sang": "Chống chói"}</t>
         </is>
       </c>
       <c r="J26" t="n">
@@ -41720,7 +42951,7 @@
       </c>
       <c r="I28" t="inlineStr">
         <is>
-          <t>{"cong_suat": "54W", "anh_sang": "Trắng, vàng", "kich_thuoc": "5130, 1200", "hieu_suat_quang": "95 Lm/w", "chi_so_hoan_mau": "CRI≥80, Ra &gt; 80", "dien_ap": "85-265V", "chat_lieu": "Nhựa, nhôm cao cấp, hợp kim nhôm, nhựa PC", "thuong_hieu": "TLC LIGHTING", "tuoi_tho": "40.000h", "bao_hanh": "24 tháng", "che_do_chieu_sang": "Chống chói", "nhiet_do_hoat_dong": "-10oC~40oC", "nhiet_do_ben_ngoai": "≤40oC"}</t>
+          <t>{"cong_suat": "54W", "anh_sang": "Trắng, vàng", "hieu_suat_quang": "95 Lm/w", "chi_so_hoan_mau": "CRI≥80", "dien_ap": "85-265V", "chat_lieu": "Nhựa, nhôm cao cấp", "thuong_hieu": "TLC LIGHTING", "tuoi_tho": "40.000h", "bao_hanh": "24 tháng", "che_do_chieu_sang": "Chống chói", "nhiet_do_hoat_dong": "-10oC~40oC", "nhiet_do_ben_ngoai": "≤40oC"}</t>
         </is>
       </c>
       <c r="J28" t="n">
@@ -41941,7 +43172,7 @@
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>{"cong_suat": "20W", "anh_sang": "Trắng/ Vàng, Trắng, Vàng", "nhiet_do_mau": "3500K/6500K", "kich_thuoc": "ø80x129mm, 80x150mm", "hieu_suat_quang": "110-120 Lm/w, 120~110Lm/w", "chi_so_hoan_mau": "CRI≥85, Ra&gt;85", "dien_ap": "85-265V", "tuoi_tho": "40.000h, 40.000 giờ", "bao_hanh": "24 tháng", "thuong_hieu": "TLC LIGHTING", "dien_ap_ac": "85-265V", "che_do_anh_sang": "Chống chói", "chat_lieu": "Hợp kim nhôm sơn tĩnh điện"}</t>
+          <t>{"cong_suat": "20W", "anh_sang": "Trắng/ Vàng, Trắng, Vàng", "nhiet_do_mau": "3500K/6500K", "kich_thuoc": "ø80x129mm, 80x150mm", "hieu_suat_quang": "110-120 Lm/w, 120~110Lm/w", "chi_so_hoan_mau": "CRI≥85", "dien_ap": "85-265V", "tuoi_tho": "40.000h, 40.000 giờ", "bao_hanh": "24 tháng", "thuong_hieu": "TLC LIGHTING", "dien_ap_ac": "85-265V", "do_hoan_mau": "Ra&gt;85", "che_do_anh_sang": "Chống chói", "chat_lieu": "Hợp kim nhôm sơn tĩnh điện"}</t>
         </is>
       </c>
       <c r="J2" t="n">
@@ -42042,7 +43273,7 @@
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>{"cong_suat": "20W", "anh_sang": "Trắng/ Vàng", "nhiet_do_mau": "3500K/6500K", "kich_thuoc": "ø80x129mm", "hieu_suat_quang": "110-120 Lm/w", "chi_so_hoan_mau": "CRI≥85", "dien_ap": "85-265V", "tuoi_tho": "40.000h", "bao_hanh": "24 tháng", "thuong_hieu": "TLC LIGHTING", "dien_ap_ac": "85-265V", "do_hoan_mau": "Ra&gt;85", "che_do_anh_sang": "Chống chói", "chat_lieu": "Hợp kim nhôm sơn tĩnh điện", "tuoi_tho_gio": "40.000 giờ", "dui_bong": "E27"}</t>
+          <t>{"cong_suat": "20W", "anh_sang": "Trắng/ Vàng, Trắng, Vàng", "nhiet_do_mau": "3500K/6500K", "kich_thuoc": "ø80x129mm, 80x150mm, 80x129mm", "hieu_suat_quang": "110-120 Lm/w, 120~110Lm/w", "chi_so_hoan_mau": "CRI≥85", "dien_ap": "85-265V", "tuoi_tho": "40.000h, 40.000 giờ", "bao_hanh": "24 tháng", "thuong_hieu": "TLC LIGHTING", "dien_ap_ac": "85-265V", "do_hoan_mau": "Ra&gt;85", "che_do_anh_sang": "Chống chói", "chat_lieu": "Hợp kim nhôm sơn tĩnh điện", "dui_bong": "E27"}</t>
         </is>
       </c>
       <c r="J3" t="n">
@@ -42148,7 +43379,7 @@
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>{"cong_suat": "30W", "anh_sang": "Trắng, Vàng", "nhiet_do_mau": "3500K/6500K", "kich_thuoc": "ø100x182mm", "hieu_suat_quang": "110-120 Lm/w", "chi_so_hoan_mau": "CRI≥85", "dien_ap": "85-265V", "tuoi_tho": "40.000h", "bao_hanh": "24 tháng", "thuong_hieu": "TLC LIGHTING", "dien_ap_ac": "85-265V", "do_hoan_mau": "&gt;85Ra", "che_do_anh_sang": "Chống chói", "chat_lieu": "Hợp kim nhôm sơn tĩnh điện"}</t>
+          <t>{"cong_suat": "30W", "anh_sang": "Trắng, Vàng", "nhiet_do_mau": "3500K/6500K", "kich_thuoc": "ø100x182mm", "hieu_suat_quang": "110-120 Lm/w", "chi_so_hoan_mau": "CRI≥85", "dien_ap": "85-265V", "tuoi_tho": "40.000h", "bao_hanh": "24 tháng", "thuong_hieu": "TLC LIGHTING", "dien_ap_ac": "85-265V", "do_hoan_mau": "&gt;85Ra", "che_do_anh_sang": "Chống chói", "chat_lieu": "Hợp kim nhôm sơn tĩnh điện", "tuoi_tho_gio": "40.000 giờ"}</t>
         </is>
       </c>
       <c r="J4" t="n">
@@ -42252,7 +43483,7 @@
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>{"cong_suat": "15W", "anh_sang": "Trắng/ Vàng, Trắng, Vàng", "nhiet_do_mau": "3500K/6500K", "kich_thuoc": "ø70×132 mm, 70×132 mm", "hieu_suat_quang": "110 Lm/w, 110 Lm/W", "chi_so_hoan_mau": "Ra ≥ 85, Ra &gt; 85, CRI &gt;85 Ra", "dien_ap": "85-265V", "tuoi_tho": "40.000h, 40.000 giờ", "bao_hanh": "24 tháng", "thuong_hieu": "TLC LIGHTING", "quang_thong": "1650 Lm", "che_do_anh_sang": "Chống chói", "chat_lieu": "Nhôm, nhựa", "duoi_den": "E27"}</t>
+          <t>{"cong_suat": "15W", "anh_sang": "Trắng/ Vàng", "nhiet_do_mau": "3500K/6500K", "kich_thuoc": "ø70×132 mm", "hieu_suat_quang": "110 Lm/w", "chi_so_hoan_mau": "Ra ≥ 85", "dien_ap": "85-265V", "tuoi_tho": "40.000h", "bao_hanh": "24 tháng", "thuong_hieu": "TLC LIGHTING", "quang_thong": "1650 Lm", "do_hoan_mau": "Ra &gt; 85", "dien_ap_ac": "85-265V", "che_do_anh_sang": "Chống chói", "chat_lieu": "Nhôm, nhựa", "tuoi_tho_chip_led": "40.000 giờ", "dui_den": "E27"}</t>
         </is>
       </c>
       <c r="J5" t="n">
@@ -42361,7 +43592,7 @@
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>{"cong_suat": "20W", "anh_sang": "Trắng/ Vàng, Trắng, Vàng", "nhiet_do_mau": "3500K/6500K", "kich_thuoc": "ø80×152 mm, 80×152 mm", "hieu_suat_quang": "110 Lm/w, 110 Lm/W", "chi_so_hoan_mau": "Ra ≥ 85, Ra &gt; 85", "dien_ap": "85-265V", "tuoi_tho": "40.000h", "bao_hanh": "24 tháng", "thuong_hieu": "TLC LIGHTING", "quang_thong": "1650 Lm", "dien_ap_ac": "85-265V", "che_do_anh_sang": "Chống chói", "chat_lieu": "Nhôm, nhựa", "tuoi_tho_chip_led": "40.000 giờ", "doi_bong": "E27"}</t>
+          <t>{"cong_suat": "20W", "anh_sang": "Trắng/ Vàng, Trắng, Vàng", "nhiet_do_mau": "3500K/6500K", "kich_thuoc": "ø80×152 mm, 80×152 mm", "hieu_suat_quang": "110 Lm/w, 110 Lm/W", "chi_so_hoan_mau": "Ra ≥ 85", "dien_ap": "85-265V", "tuoi_tho": "40.000h", "bao_hanh": "24 tháng", "thuong_hieu": "TLC LIGHTING", "quang_thong": "1650 Lm", "do_hoan_mau": "Ra &gt; 85", "dien_ap_ac": "85-265V", "che_do_anh_sang": "Chống chói", "chat_lieu": "Nhôm, nhựa", "tuoi_tho_chip_led": "40.000 giờ"}</t>
         </is>
       </c>
       <c r="J6" t="n">
@@ -42470,7 +43701,7 @@
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>{"cong_suat": "30W", "anh_sang": "Trắng/ Vàng, Trắng, Vàng", "nhiet_do_mau": "3500K/6500K", "kich_thuoc": "ø100×182 mm, 100×182 mm", "hieu_suat_quang": "110 Lm/w, 110 Lm/W", "chi_so_hoan_mau": "Ra ≥ 85, Ra &gt; 85, CRI &gt;85 Ra", "dien_ap": "85-265V", "tuoi_tho": "40.000h", "bao_hanh": "24 tháng", "thuong_hieu": "TLC LIGHTING", "quang_thong": "1650 Lm", "dien_ap_ac": "85-265V", "che_do_anh_sang": "Chống chói", "chat_lieu": "Nhôm, nhựa", "tuoi_tho_chip_led": "40.000 giờ", "dui_den": "E27"}</t>
+          <t>{"cong_suat": "30W", "anh_sang": "Trắng/ Vàng", "nhiet_do_mau": "3500K/6500K", "kich_thuoc": "ø100×182 mm", "hieu_suat_quang": "110 Lm/w", "chi_so_hoan_mau": "Ra ≥ 85", "dien_ap": "85-265V", "tuoi_tho": "40.000h", "bao_hanh": "24 tháng", "thuong_hieu": "TLC LIGHTING", "quang_thong": "1650 Lm", "do_hoan_mau": "Ra &gt; 85", "dien_ap_ac": "85-265V", "che_do_anh_sang": "Chống chói", "chat_lieu": "Nhôm, nhựa", "tuoi_tho_chip_led": "40.000 giờ", "chip_led": "OSRAM nhập khẩu từ Đức", "hieu_suat_anh_sang": "110Lm/W", "cri": "&gt;85 Ra", "chao_den": "nhựa PC cao cấp", "he_so_thau_quang": "92%", "dui_den": "E27, IP44"}</t>
         </is>
       </c>
       <c r="J7" t="n">
@@ -42570,7 +43801,7 @@
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>{"cong_suat": "13W", "anh_sang": "Trắng/ Vàng", "nhiet_do_mau": "3500K/6500K", "kich_thuoc": "Φ 75 x 149", "chip_led": "Osram", "hieu_suat_quang": "110-120 Lm/w", "chi_so_hoan_mau": "CRI≥85", "dien_ap": "85-265V", "thuong_hieu": "TLC LIGHTING", "tuoi_tho": "50.000h", "bao_hanh": "30 tháng", "dien_ap_ac": "85-265V", "do_hoan_mau": "&gt;85 Ra", "che_do_anh_sang": "Chống chói", "khi_thai": "E27"}</t>
+          <t>{"cong_suat": "13W", "anh_sang": "Trắng/ Vàng", "nhiet_do_mau": "3500K/6500K", "kich_thuoc": "Φ 75 x 149", "chip_led": "Osram", "hieu_suat_quang": "110-120 Lm/w", "chi_so_hoan_mau": "CRI≥85", "dien_ap": "85-265V", "thuong_hieu": "TLC LIGHTING", "tuoi_tho": "50.000h", "bao_hanh": "30 tháng", "dien_ap_ac": "85-265V", "do_hoan_mau": "&gt;85 Ra", "che_do_anh_sang": "Chống chói", "kich_thuoc_2": "75x149mm", "tuoi_tho_2": "50.000 giờ"}</t>
         </is>
       </c>
       <c r="J8" t="n">
@@ -42669,7 +43900,7 @@
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>{"cong_suat": "3W", "anh_sang": "Trắng/ Vàng", "nhiet_do_mau": "3500K/6500K", "kich_thuoc": "Φ 45 x 84", "chip_led": "Osram", "hieu_suat_quang": "110-120 Lm/w", "chi_so_hoan_mau": "CRI≥85", "dien_ap": "85-265V", "chat_lieu": "Hợp kim nhôm, sơn tĩnh điện", "thuong_hieu": "TLC LIGHTING", "tuoi_tho": "40.000h", "bao_hanh": "24 tháng", "duong_kinh": "45x84mm", "dui_bong": "E27"}</t>
+          <t>{"cong_suat": "3W", "anh_sang": "Trắng/ Vàng", "nhiet_do_mau": "3500K/6500K", "kich_thuoc": "Φ 45 x 84", "chip_led": "Osram", "hieu_suat_quang": "110-120 Lm/w", "chi_so_hoan_mau": "CRI≥85", "dien_ap": "85-265V", "chat_lieu": "Hợp kim nhôm, sơn tĩnh điện", "thuong_hieu": "TLC LIGHTING", "tuoi_tho": "40.000h", "bao_hanh": "24 tháng", "dui_bong": "E27"}</t>
         </is>
       </c>
       <c r="J9" t="n">
@@ -42766,7 +43997,7 @@
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>{"cong_suat": "8W", "anh_sang": "Trắng/ Vàng, Trắng, Vàng", "nhiet_do_mau": "3500K/6500K", "kich_thuoc": "Φ 60 x 118, 60x118mm", "chip_led": "Osram", "hieu_suat_quang": "110-120 Lm/w, 120~110Lm/w", "chi_so_hoan_mau": "CRI≥85", "dien_ap": "85-265V", "chat_lieu": "Hợp kim nhôm, sơn tĩnh điện, Hợp kim nhôm sơn tĩnh điện", "thuong_hieu": "TLC LIGHTING", "tuoi_tho": "50.000h, 50.000 giờ, 40.000 giờ", "bao_hanh": "24 tháng, 30 tháng", "dien_ap_ac": "85-265V", "do_hoan_mau": "&gt;85Ra", "che_do_anh_sang": "Chống chói", "duoi_bong": "E27"}</t>
+          <t>{"cong_suat": "8W", "anh_sang": "Trắng/ Vàng, Trắng, Vàng", "nhiet_do_mau": "3500K/6500K", "kich_thuoc": "Φ 60 x 118, 60x118mm", "chip_led": "Osram", "hieu_suat_quang": "110-120 Lm/w, 120~110Lm/w", "chi_so_hoan_mau": "CRI≥85", "dien_ap": "85-265V", "chat_lieu": "Hợp kim nhôm, sơn tĩnh điện, Hợp kim nhôm sơn tĩnh điện", "thuong_hieu": "TLC LIGHTING", "tuoi_tho": "50.000h, 50.000 giờ", "bao_hanh": "24 tháng, 30 tháng", "dien_ap_ac": "85-265V", "do_hoan_mau": "&gt;85Ra", "che_do_anh_sang": "Chống chói", "dui_bong": "E27"}</t>
         </is>
       </c>
       <c r="J10" t="n">
@@ -42866,7 +44097,7 @@
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>{"cong_suat": "10W", "anh_sang": "Trắng/ Vàng", "nhiet_do_mau": "3500K/6500K", "kich_thuoc": "Φ 65 x 137", "chip_led": "Osram", "hieu_suat_quang": "110-120 Lm/w", "chi_so_hoan_mau": "CRI≥85", "dien_ap": "85-265V", "thuong_hieu": "TLC LIGHTING", "tuoi_tho": "50.000h", "bao_hanh": "30 tháng", "quang_thong": "1150 Lm", "che_do_chieu_sang": "Chống chói", "nhiet_do_hoat_dong": "-10oC~40oC", "nhiet_do_ben_ngoai": "≤40oC", "dui_bong": "E27"}</t>
+          <t>{"cong_suat": "10W", "anh_sang": "Trắng/ Vàng, Trắng, vàng", "nhiet_do_mau": "3500K/6500K", "kich_thuoc": "Φ 65 x 137", "chip_led": "Osram", "hieu_suat_quang": "110-120 Lm/w, 110 -120 Lm/W", "chi_so_hoan_mau": "CRI≥85, Ra &gt; 85", "dien_ap": "85-265V", "thuong_hieu": "TLC LIGHTING", "tuoi_tho": "50.000h, 50.000 giờ", "bao_hanh": "30 tháng", "quang_thong": "1150 Lm", "che_do_chieu_sang": "Chống chói", "nhiet_do_hoat_dong": "-10oC~40oC", "nhiet_do_ben_ngoai": "≤40oC", "dui_bong": "E27"}</t>
         </is>
       </c>
       <c r="J11" t="n">
@@ -42961,7 +44192,7 @@
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>{"cong_suat": "6W", "anh_sang": "Trắng/ Vàng", "nhiet_do_mau": "3500K/6500K", "kich_thuoc": "Φ 55 x 110", "chip_led": "Osram", "hieu_suat_quang": "110-120 Lm/w", "chi_so_hoan_mau": "CRI≥85", "dien_ap": "85-265V", "chat_lieu": "Hợp kim nhôm, sơn tĩnh điện", "thuong_hieu": "TLC LIGHTING", "tuoi_tho": "50.000h", "bao_hanh": "30 tháng", "xuat_xu": "Việt Nam", "dien_ap_ac": "85-265V", "do_hoan_mau": "&gt;85Ra", "che_do_anh_sang": "Chống chói", "kich_thuoc_mm": "55x110mm", "tuoi_tho_gio": "50.000 giờ", "dui_bong": "E27"}</t>
+          <t>{"cong_suat": "6W", "anh_sang": "Trắng/ Vàng", "nhiet_do_mau": "3500K/6500K", "kich_thuoc": "Φ 55 x 110", "chip_led": "Osram", "hieu_suat_quang": "110-120 Lm/w", "chi_so_hoan_mau": "CRI≥85", "dien_ap": "85-265V", "chat_lieu": "Hợp kim nhôm, sơn tĩnh điện", "thuong_hieu": "TLC LIGHTING", "tuoi_tho": "50.000h", "bao_hanh": "30 tháng", "xuat_xu": "Việt Nam", "do_hoan_mau": "&gt;85Ra", "che_do_anh_sang": "Chống chói", "khi_kich_thuoc": "55x110mm", "chat_lieu_khac": "Hợp kim nhôm sơn tĩnh điện", "tuoi_tho_khac": "50.000 giờ", "dui_bong": "E27"}</t>
         </is>
       </c>
       <c r="J12" t="n">
@@ -43059,7 +44290,7 @@
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>{"cong_suat": "30W", "anh_sang": "Trắng/ Vàng", "nhiet_do_mau": "3500K/6500K", "kich_thuoc": "ø100×195 mm", "chi_so_hoan_mau": "Ra ≥ 85", "dien_ap": "85-265V", "tuoi_tho": "40.000h", "bao_hanh": "24 tháng", "quang_thong": "3300Lm", "do_hoan_mau": "Ra &gt; 85", "dien_ap_ac": "85-265V", "tuoi_tho_chip_led": "40.000 giờ"}</t>
+          <t>{"cong_suat": "30W", "anh_sang": "Trắng/ Vàng", "nhiet_do_mau": "3500K/6500K", "kich_thuoc": "ø100×195 mm", "chi_so_hoan_mau": "Ra ≥ 85", "dien_ap": "85-265V", "tuoi_tho": "40.000h", "bao_hanh": "24 tháng", "thuong_hieu": "TLC LIGHTING", "quang_thong": "3300Lm", "do_hoan_mau": "Ra &gt; 85", "dien_ap_ac": "85-265V", "tuoi_tho_chip_led": "40.000 giờ"}</t>
         </is>
       </c>
       <c r="L13" t="inlineStr">
@@ -43151,7 +44382,7 @@
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>{"cong_suat": "40W", "anh_sang": "Trắng/ Vàng", "nhiet_do_mau": "3500K/6500K", "kich_thuoc": "ø125×227 mm", "hieu_suat_quang": "110 Lm/w", "chi_so_hoan_mau": "Ra ≥ 85", "dien_ap": "85-265V", "tuoi_tho": "40.000h", "bao_hanh": "24 tháng", "thuong_hieu": "TLC LIGHTING", "quang_thong": "1650 Lm", "do_hoan_mau": "Ra &gt; 85", "dien_ap_ac": "85-265V", "che_do_anh_sang": "Chống chói", "chat_lieu": "Nhôm, nhựa", "tuoi_tho_chip_led": "40.000 giờ", "dui_bong": "E27"}</t>
+          <t>{"cong_suat": "40W", "anh_sang": "Trắng/ Vàng", "nhiet_do_mau": "3500K/6500K", "kich_thuoc": "ø125×227 mm", "hieu_suat_quang": "110 Lm/w", "chi_so_hoan_mau": "Ra ≥ 85", "dien_ap": "85-265V", "tuoi_tho": "40.000h", "bao_hanh": "24 tháng", "quang_thong": "1650 Lm", "do_hoan_mau": "Ra &gt; 85", "dien_ap_ac": "85-265V", "che_do_anh_sang": "Chống chói", "chat_lieu": "Nhôm, nhựa", "tuoi_tho_chip_led": "40.000 giờ"}</t>
         </is>
       </c>
       <c r="J14" t="n">
@@ -43257,7 +44488,7 @@
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>{"cong_suat": "50W", "anh_sang": "Trắng/ Vàng, Trắng, Vàng", "nhiet_do_mau": "3500K/6500K", "kich_thuoc": "ø135×248 mm, 135×248 mm", "hieu_suat_quang": "110 Lm/w, 110 Lm/W", "chi_so_hoan_mau": "Ra ≥ 85, Ra &gt; 85, CRI &gt;85 Ra", "dien_ap": "85-265V", "tuoi_tho": "40.000h, 40.000 giờ", "bao_hanh": "24 tháng", "thuong_hieu": "TLC LIGHTING", "quang_thong": "1650 Lm", "dien_ap_ac": "85-265V", "che_do_anh_sang": "Chống chói", "chat_lieu": "Nhôm, nhựa", "tuoi_tho_chip_led": "40.000 giờ", "dui_den": "E27"}</t>
+          <t>{"cong_suat": "50W", "anh_sang": "Trắng/ Vàng, Trắng, Vàng", "nhiet_do_mau": "3500K/6500K", "kich_thuoc": "ø135×248 mm, 135×248 mm", "hieu_suat_quang": "110 Lm/w, 110 Lm/W", "chi_so_hoan_mau": "Ra ≥ 85, Ra &gt; 85", "dien_ap": "85-265V", "tuoi_tho": "40.000h", "bao_hanh": "24 tháng", "thuong_hieu": "TLC LIGHTING", "quang_thong": "1650 Lm", "dien_ap_ac": "85-265V", "che_do_anh_sang": "Chống chói", "chat_lieu": "Nhôm, nhựa", "tuoi_tho_chip_led": "40.000 giờ", "dui_den": "E27"}</t>
         </is>
       </c>
       <c r="J15" t="n">
@@ -43271,6 +44502,16 @@
       <c r="M15" t="inlineStr">
         <is>
           <t>https://tlclighting.com.vn/wp-content/uploads/2021/03/50W.png</t>
+        </is>
+      </c>
+      <c r="P15" t="inlineStr">
+        <is>
+          <t>Ánh sáng chất lượng cao
+Tuổi thọ cao
+Tiết kiệm điện năng
+An toàn với người sử dụng
+Giá thành hợp lý
+Tính thẩm mỹ cao</t>
         </is>
       </c>
       <c r="Q15" t="inlineStr">
@@ -43300,6 +44541,30 @@
 Bảo hành: 24 tháng</t>
         </is>
       </c>
+      <c r="T15" t="inlineStr">
+        <is>
+          <t>6 LÝ DO nên chọn đèn LED Bulb 50W DOS
+Được đánh giá là bóng đèn LED sáng nhất thị trường. Bên cạnh hiệu năng chiếu sáng, bóng
+đèn LED Bulb 50W
+DOS
+còn có nhiều ưu điểm vượt trội được người tiêu dùng đánh giá cao. Có thể điểm đến những 6 ưu điểm nổi bật sau.
+Ưu điểm của đèn LED Búp 50W DOS TLC LIGHTING
+Ánh sáng chất lượng cao
+:
+Đèn LED Bulb 50W DOS
+có hiệu suất phát quang lên tới 110Lm/W sáng nhất thị trường nhờ sử dụng chip LED OSRAM – thương hiệu hàng đầu CHLB Đức. Chip LED là linh kiện quan trọng nhất trong bóng đèn, quyết định độ sáng của sản phẩm.
+Tuổi thọ cao
+: Ứng dụng công nghệ DOB giúp phần sản phẩm tản nhiệt nhanh hơn, tăng tuổi thọ của nguồn đèn và chip LED giúp sản phẩm có tuổi thọ lên tới 40.000 giờ tương đương 10 năm sử dụng.
+Tiết kiệm điện năng
+: Ngoài chất lượng ánh sáng cao, bóng đèn LED Bulb 50W DOS còn đảm bảo tiêu chí tiết kiệm điện. Sản phẩm tiết kiệm đến 90% điện năng tiêu thụ so với các sản phẩm đèn sợi đốt, huỳnh quang thông thường.
+An toàn với người sử dụng
+: Sản phẩm đạt chỉ số hoàn màu CRI &gt; 85Ra đảm bảo chất lượng ánh sáng chân thực, an toàn cho mắt người sử dụng. Không chứa các chất độc hại (thủy ngân, lưu huỳnh,…), không phát ra tia cực tím.
+Giá thành hợp lý
+: Bóng đèn LED búp trụ DOS công suất 50W có tuổi thọ lên tới 40.000 giờ (tương đương 10 năm sử dụng), bảo hành 24 tháng. Với cam kết về tuổi thọ và chính sách bảo hành, quý khách hàng có thể yên tâm về giá thành sản phẩm phù hợp với chất lượng.
+Tính thẩm mỹ cao:
+Lấy cảm hứng từ thiết kế mang tính thông dụng nhưng vẫn có đường nét hiện đại, đèn LED Bulb 50W có thể phù hợp với nhiều vị trí lắp đặt nội ngoại thất.</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
@@ -43327,7 +44592,7 @@
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>{"cong_suat": "80W", "anh_sang": "Trắng/ Vàng", "nhiet_do_mau": "3500K/6500K", "kich_thuoc": "ø138x270mm", "hieu_suat_quang": "110-120 Lm/w", "chi_so_hoan_mau": "CRI≥85", "dien_ap": "85-265V", "chat_lieu": "Hợp kim nhôm, sơn tĩnh điện", "thuong_hieu": "TLC LIGHTING", "tuoi_tho": "40.000h", "bao_hanh": "24 tháng", "quang_thong": "9000 Lm", "do_hoan_mau": "Ra&gt;85", "dien_ap_ac": "85-265V", "che_do_anh_sang": "Chống chói", "tuoi_tho_chip_led": "40.000 giờ", "dui_den": "E27"}</t>
+          <t>{"cong_suat": "80W", "anh_sang": "Trắng/ Vàng, Trắng, Vàng", "nhiet_do_mau": "3500K/6500K", "kich_thuoc": "ø138x270mm, 138x270mm", "hieu_suat_quang": "110-120 Lm/w, 110~120Lm/w", "chi_so_hoan_mau": "CRI≥85", "dien_ap": "85-265V", "chat_lieu": "Hợp kim nhôm, sơn tĩnh điện, Hợp kim nhôm sơn tĩnh điện", "thuong_hieu": "TLC LIGHTING", "tuoi_tho": "40.000h", "bao_hanh": "24 tháng", "quang_thong": "9000 Lm", "do_hoan_mau": "Ra&gt;85", "dien_ap_ac": "85-265V", "che_do_anh_sang": "Chống chói", "tuoi_tho_chip_led": "40.000 giờ", "du_bong": "E27"}</t>
         </is>
       </c>
       <c r="J16" t="n">
@@ -43436,7 +44701,7 @@
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>{"cong_suat": "20W", "anh_sang": "Trắng/ Vàng, Trắng, Vàng", "nhiet_do_mau": "3500K/6500K", "kich_thuoc": "ø81×163 mm, 81×163 mm", "chi_so_hoan_mau": "Ra ≥ 85", "dien_ap": "85-265V", "tuoi_tho": "40.000h", "bao_hanh": "24 tháng", "thuong_hieu": "TLC LIGHTING", "quang_thong": "2200Lm", "do_hoan_mau": "Ra &gt; 85", "dien_ap_ac": "85-265V", "tuoi_tho_chip_led": "40.000 giờ", "hieu_suat_quang": "110Lm/W", "cri": "&gt;85 RA"}</t>
+          <t>{"cong_suat": "20W", "anh_sang": "Trắng/ Vàng, Trắng, Vàng", "nhiet_do_mau": "3500K/6500K", "kich_thuoc": "ø81×163 mm, 81×163 mm", "chi_so_hoan_mau": "Ra ≥ 85, Ra &gt; 85, CRI &gt;85 RA", "dien_ap": "85-265V", "tuoi_tho": "40.000h", "bao_hanh": "24 tháng", "thuong_hieu": "TLC LIGHTING", "quang_thong": "2200Lm", "dien_ap_ac": "85-265V", "tuoi_tho_chip_led": "40.000 giờ", "hieu_suat_quang": "110Lm/W", "dui_den": "E27"}</t>
         </is>
       </c>
       <c r="L17" t="inlineStr">
@@ -43527,7 +44792,7 @@
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>{"cong_suat": "40W", "anh_sang": "Trắng/ Vàng", "nhiet_do_mau": "3500K/6500K", "kich_thuoc": "ø116×222 mm", "chi_so_hoan_mau": "Ra ≥ 85", "dien_ap": "85-265V", "tuoi_tho": "40.000h", "bao_hanh": "24 tháng", "thuong_hieu": "TLC LIGHTING", "quang_thong": "4400Lm", "do_hoan_mau": "Ra &gt; 85", "dien_ap_ac": "85-265V", "tuoi_tho_chip_led": "40.000 giờ"}</t>
+          <t>{"cong_suat": "40W", "anh_sang": "Trắng/ Vàng, Trắng, Vàng", "nhiet_do_mau": "3500K/6500K", "kich_thuoc": "ø116×222 mm, 116×222 mm", "chi_so_hoan_mau": "Ra ≥ 85", "dien_ap": "85-265V", "tuoi_tho": "40.000h", "bao_hanh": "24 tháng", "quang_thong": "4400Lm", "do_hoan_mau": "Ra &gt; 85", "dien_ap_ac": "85-265V", "tuoi_tho_chip_led": "40.000 giờ"}</t>
         </is>
       </c>
       <c r="L18" t="inlineStr">
@@ -43616,7 +44881,7 @@
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>{"cong_suat": "50W", "anh_sang": "Trắng/ Vàng", "nhiet_do_mau": "3500K/6500K", "kich_thuoc": "ø126×242 mm", "chi_so_hoan_mau": "Ra ≥ 85", "dien_ap": "85-265V", "tuoi_tho": "40.000h", "bao_hanh": "24 tháng", "quang_thong": "5500Lm", "dien_ap_ac": "85-265V", "tuoi_tho_chip_led": "40.000 giờ"}</t>
+          <t>{"cong_suat": "50W", "anh_sang": "Trắng/ Vàng", "nhiet_do_mau": "3500K/6500K", "kich_thuoc": "ø126×242 mm", "chi_so_hoan_mau": "Ra ≥ 85", "dien_ap": "85-265V", "tuoi_tho": "40.000h", "bao_hanh": "24 tháng", "thuong_hieu": "TLC LIGHTING", "quang_thong": "5500Lm", "do_hoan_mau": "Ra &gt; 85", "dien_ap_ac": "85-265V", "tuoi_tho_chip_led": "40.000 giờ"}</t>
         </is>
       </c>
       <c r="L19" t="inlineStr">
@@ -43703,7 +44968,7 @@
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t>{"cong_suat": "80W", "anh_sang": "Trắng/ Vàng, Trắng, Vàng", "nhiet_do_mau": "3500K/6500K", "kich_thuoc": "ø150×250 mm, 150x250mm", "quang_thong": "7200 Lm", "chi_so_hoan_mau": "Ra ≥ 85", "dien_ap": "185-265V", "bao_hanh": "24 tháng", "thuong_hieu": "TLC LIGHTING", "do_hoan_mau": "Ra &gt; 85, CRI&gt;= 80, CRI&gt;85", "dien_ap_AC": "185-265V", "chat_lieu": "Nhôm, nhựa", "hieu_suat_quang": "110Lm/W", "thoi_gian_chieu_sang": "40,000 giờ", "tuoi_tho": "40.000 giờ", "dui_den": "E27"}</t>
+          <t>{"cong_suat": "80W", "anh_sang": "Trắng/ Vàng", "nhiet_do_mau": "3500K/6500K", "kich_thuoc": "ø150×250 mm", "quang_thong": "7200 Lm", "chi_so_hoan_mau": "Ra ≥ 85", "dien_ap": "185-265V", "bao_hanh": "24 tháng", "thuong_hieu": "TLC LIGHTING", "do_hoan_mau": "Ra &gt; 85", "dien_ap_ac": "185-265V", "chat_lieu": "Nhôm, nhựa"}</t>
         </is>
       </c>
       <c r="J20" t="n">
@@ -43794,7 +45059,7 @@
       </c>
       <c r="I21" t="inlineStr">
         <is>
-          <t>{"cong_suat": "15W", "anh_sang": "Trắng/ Vàng, Trắng, Vàng", "nhiet_do_mau": "3500K/6500K", "kich_thuoc": "ø70x129mm, 70x129mm", "hieu_suat_quang": "110-120 Lm/w, 110~120Lm/w", "chi_so_hoan_mau": "Ra ≥ 85, Ra &gt; 85", "dien_ap": "85-265V", "tuoi_tho": "40.000h", "bao_hanh": "24 tháng", "thuong_hieu": "TLC LIGHTING", "quang_thong": "1695 Lm", "dien_ap_ac": "85-265V", "che_do_anh_sang": "Chống chói", "chat_lieu": "Hợp kim nhôm sơn tĩnh điện", "tuoi_tho_chip_led": "40.000 giờ"}</t>
+          <t>{"cong_suat": "15W", "anh_sang": "Trắng/ Vàng", "nhiet_do_mau": "3500K/6500K", "kich_thuoc": "ø70x129mm", "hieu_suat_quang": "110-120 Lm/w", "chi_so_hoan_mau": "Ra ≥ 85", "dien_ap": "85-265V", "tuoi_tho": "40.000h", "bao_hanh": "24 tháng", "thuong_hieu": "TLC LIGHTING", "quang_thong": "1695 Lm", "do_hoan_mau": "Ra &gt; 85", "dien_ap_ac": "85-265V", "che_do_anh_sang": "Chống chói", "chat_lieu": "Hợp kim nhôm sơn tĩnh điện", "tuoi_tho_chip_led": "40.000 giờ"}</t>
         </is>
       </c>
       <c r="J21" t="n">
@@ -43896,7 +45161,7 @@
       </c>
       <c r="I22" t="inlineStr">
         <is>
-          <t>{"cong_suat": "40W", "anh_sang": "Trắng/ Vàng", "nhiet_do_mau": "3500K/6500K", "kich_thuoc": "ø118x207mm", "hieu_suat_quang": "110-120 Lm/w", "chi_so_hoan_mau": "CRI≥85", "dien_ap": "85-265V", "tuoi_tho": "40.000h", "bao_hanh": "24 tháng", "dien_ap_ac": "85-265V", "do_hoan_mau": "&gt;85Ra", "che_do_anh_sang": "Chống chói", "chat_lieu": "Hợp kim nhôm sơn tĩnh điện", "tuy_tho": "40.000 giờ"}</t>
+          <t>{"cong_suat": "40W", "anh_sang": "Trắng/ Vàng", "nhiet_do_mau": "3500K/6500K", "kich_thuoc": "ø118x207mm", "hieu_suat_quang": "110-120 Lm/w", "chi_so_hoan_mau": "CRI≥85", "dien_ap": "85-265V", "tuoi_tho": "40.000h", "bao_hanh": "24 tháng", "thuong_hieu": "TLC LIGHTING", "dien_ap_ac": "85-265V", "do_hoan_mau": "&gt;85Ra", "che_do_anh_sang": "Chống chói", "chat_lieu": "Hợp kim nhôm sơn tĩnh điện", "tuoi_tho_gio": "40.000 giờ"}</t>
         </is>
       </c>
       <c r="J22" t="n">
@@ -43989,7 +45254,7 @@
       </c>
       <c r="I23" t="inlineStr">
         <is>
-          <t>{"cong_suat": "10W", "anh_sang": "Trắng/ Vàng, Trắng, Vàng", "nhiet_do_mau": "3500K/6500K", "kich_thuoc": "ø60x129mm, 60x129mm", "hieu_suat_quang": "110-120 Lm/w, 110~120Lm/w", "chi_so_hoan_mau": "CRI≥85, &gt;85", "dien_ap": "85-265V", "chat_lieu": "Hợp kim nhôm, sơn tĩnh điện, Hợp kim nhôm sơn tĩnh điện", "thuong_hieu": "TLC LIGHTING", "tuoi_tho": "40.000h", "bao_hanh": "24 tháng", "quang_thong": "1130 Lm", "dien_ap_ac": "85-265V", "che_do_anh_sang": "Chống chói", "tuoi_tho_chip_led": "40.000 giờ"}</t>
+          <t>{"cong_suat": "10W", "anh_sang": "Trắng/ Vàng, Trắng, Vàng", "nhiet_do_mau": "3500K/6500K", "kich_thuoc": "ø60x129mm, 60x129mm", "hieu_suat_quang": "110-120 Lm/w, 110~120Lm/w", "chi_so_hoan_mau": "CRI≥85", "dien_ap": "85-265V", "chat_lieu": "Hợp kim nhôm, sơn tĩnh điện, Hợp kim nhôm sơn tĩnh điện", "thuong_hieu": "TLC LIGHTING", "tuoi_tho": "40.000h", "bao_hanh": "24 tháng", "quang_thong": "1130 Lm", "do_hoan_mau": "&gt;85", "dien_ap_ac": "85-265V", "che_do_anh_sang": "Chống chói", "tuoi_tho_chip_led": "40.000 giờ", "chip_led": "Hiệu suất quang 110-120 Lm/w. Ngoài ra, chip LED giúp đèn có khả năng tiết kiệm điện hiệu quả. Chỉ số hoàn màu của chip LED đạt Ra &gt; 85 giúp đèn cho ánh sáng trung thực, không gây chói và bảo vệ mắt.", "nguon_den": "Được cấu tạo từ những linh kiện cao cấp giúp đèn hoạt động ổn định, duy trì tuổi thọ của đèn", "choa_den": "được thiết kế từ mica trắng mờ với PC thấu quang 82%, góc chiếu 270 độ, cho ánh sáng mờ, đồng đều, rõ nét và tốt cho mắt.", "tan_nhiet": "của đèn được cấu tạo từ nhôm nguyên khối với cấu tạo nhiều cánh tản nhiệt đa chiều, giúp hiệu quả tản nhiệt tốt hơn 20% so với các dòng đèn LED thông thường, duy trì tuổi thọ của đèn.", "dui_den": "Đèn được thiết kế đui E27 phổ thông dạng xoắn giúp lắp đặt nhanh và tiện dụng hơn."}</t>
         </is>
       </c>
       <c r="J23" t="n">
@@ -44178,7 +45443,7 @@
       </c>
       <c r="I25" t="inlineStr">
         <is>
-          <t>{"chip_led": "Epistar", "cong_suat": "3W, 5w, 7w, 9w, 12w", "hieu_suat_quang": "80 Lm/w", "mau_sac": "trắng/vàng", "dien_ap": "AC 85-265", "tuoi_tho": "40.000 giờ", "bao_hanh": "24 tháng", "goc_chieu": "260 độ", "dui": "E27 crom"}</t>
+          <t>{"ten_san_pham": "Đèn LED búp sứ siêu sáng", "chip_led": "Epistar", "cong_suat": "3W, 5w, 7w, 9w, 12w", "hieu_suat_quang": "80 Lm/w", "mau_sac": "trắng/vàng. Bóng LED màu đỏ, xanh lá, xanh dương chỉ có loại công suất 3W", "dien_ap": "AC 85-265", "tuoi_tho": "40.000 giờ", "bao_hanh": "24 tháng", "goc_chieu_anh_sang": "260 độ", "dui": "E27 crom"}</t>
         </is>
       </c>
       <c r="L25" t="inlineStr">
@@ -44256,7 +45521,7 @@
       </c>
       <c r="I26" t="inlineStr">
         <is>
-          <t>{"cong_suat": "30W", "anh_sang": "Trắng/ Vàng", "nhiet_do_mau": "3500K/6500K", "kich_thuoc": "ø100x182mm", "hieu_suat_quang": "110-120 Lm/w", "chi_so_hoan_mau": "CRI≥85", "dien_ap": "85-265V", "tuoi_tho": "40.000h", "bao_hanh": "24 tháng", "thuong_hieu": "TLC LIGHTING", "dien_ap_ac": "85-265V", "do_hoan_mau": "&gt;85Ra", "che_do_anh_sang": "Chống chói", "chat_lieu": "Hợp kim nhôm sơn tĩnh điện"}</t>
+          <t>{"cong_suat": "30W", "anh_sang": "Trắng/ Vàng", "nhiet_do_mau": "3500K/6500K", "kich_thuoc": "ø100x182mm", "hieu_suat_quang": "110-120 Lm/w", "chi_so_hoan_mau": "CRI≥85", "dien_ap": "85-265V", "tuoi_tho": "40.000h", "bao_hanh": "24 tháng", "dien_ap_ac": "85-265V", "do_hoan_mau": "&gt;85Ra", "che_do_anh_sang": "Chống chói", "chat_lieu": "Hợp kim nhôm sơn tĩnh điện", "tuoi_tho_gio": "40.000 giờ"}</t>
         </is>
       </c>
       <c r="J26" t="n">
@@ -44611,7 +45876,7 @@
       </c>
       <c r="I30" t="inlineStr">
         <is>
-          <t>{"cong_suat": "50W", "anh_sang": "Trắng/ Vàng, Trắng, Vàng", "nhiet_do_mau": "3500K/6500K", "kich_thuoc": "ø138x248mm, 138x248mm", "hieu_suat_quang": "110-120 Lm/w", "chi_so_hoan_mau": "CRI≥85", "dien_ap": "85-265V", "chat_lieu": "Hợp kim nhôm, sơn tĩnh điện, Hợp kim nhôm sơn tĩnh điện", "tuoi_tho": "40.000h", "bao_hanh": "24 tháng", "thuong_hieu": "TLC LIGHTING", "quang_thong": "5650 Lm", "do_hoan_mau": "Ra&gt;85", "dien_ap_ac": "85-265V", "che_do_anh_sang": "Chống chói", "tuoi_tho_chip_led": "40.000 giờ", "dui_bong": "E27"}</t>
+          <t>{"cong_suat": "50W", "anh_sang": "Trắng/ Vàng", "nhiet_do_mau": "3500K/6500K", "kich_thuoc": "ø138x248mm", "hieu_suat_quang": "110-120 Lm/w", "chi_so_hoan_mau": "CRI≥85", "dien_ap": "85-265V", "chat_lieu": "Hợp kim nhôm, sơn tĩnh điện", "tuoi_tho": "40.000h", "bao_hanh": "24 tháng", "thuong_hieu": "TLC LIGHTING", "quang_thong": "5650 Lm", "do_hoan_mau": "Ra&gt;85", "dien_ap_ac": "85-265V", "che_do_anh_sang": "Chống chói", "chat_lieu_2": "Hợp kim nhôm sơn tĩnh điện", "tuoi_tho_chip_led": "40.000 giờ"}</t>
         </is>
       </c>
       <c r="J30" t="n">
@@ -44848,7 +46113,7 @@
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>{"cong_suat": "7W", "anh_sang": "Trắng/vàng", "nhiet_do_mau": "3500K/6500K", "kich_thuoc": "ø120x38mm", "lo_khoet": "ø90mm", "chip_led": "OSRAM", "hieu_suat_quang": "110-120 Lm/w", "chi_so_hoan_mau": "CRI≥85", "dien_ap": "85-265V", "thuong_hieu": "TLC LIGHTING", "tuoi_tho": "40.000h", "bao_hanh": "24 tháng", "dien_ap_ac": "85-265V", "do_hoan_mau": "&gt;85Ra", "che_do_anh_sang": "Chống chói", "duong_kinh_lo_khoet": "D90mm", "duong_kinh_mat": "D120mm", "chieu_day": "38mm", "chat_lieu": "Hợp kim nhôm"}</t>
+          <t>{"cong_suat": "7W", "anh_sang": "Trắng/vàng", "nhiet_do_mau": "3500K/6500K", "kich_thuoc": "ø120x38mm", "lo_khoet": "ø90mm", "chip_led": "OSRAM", "hieu_suat_quang": "110-120 Lm/w", "chi_so_hoan_mau": "CRI≥85", "dien_ap": "85-265V", "thuong_hieu": "TLC LIGHTING", "tuoi_tho": "40.000h", "bao_hanh": "24 tháng", "dien_ap_ac": "85-265V", "hieu_suat_quang_2": "~110Lm/w", "do_hoan_mau": "&gt;85Ra", "che_do_anh_sang": "Chống chói", "duong_kinh_lo_khoet": "D90mm", "duong_kinh_mat": "D120mm", "chieu_day": "38mm", "chat_lieu": "Hợp kim nhôm", "tuoi_tho_2": "40.000 giờ"}</t>
         </is>
       </c>
       <c r="J2" t="n">
@@ -45031,7 +46296,7 @@
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>{"cong_suat": "5W", "anh_sang": "Ba màu", "nhiet_do_mau": "3500K/6500K", "kich_thuoc": "Ø110×35", "hieu_suat_quang": "110-120 Lm/w, 80 Lm/w", "chi_so_hoan_mau": "CRI≥85, &gt;85Ra", "dien_ap": "85-265V", "lo_khoet": "Ø76", "thuong_hieu": "TLC LIGHTING", "tuoi_tho": "40.000h, 40.000 giờ", "bao_hanh": "24 tháng, 2 năm", "quang_thong": "400Lm"}</t>
+          <t>{"cong_suat": "5W", "anh_sang": "Ba màu", "nhiet_do_mau": "3500K/6500K", "kich_thuoc": "Ø110×35", "hieu_suat_quang": "110-120 Lm/w, 80 Lm/w", "chi_so_hoan_mau": "CRI≥85, &gt;85Ra", "dien_ap": "85-265V", "lo_khoet": "Ø76", "thuong_hieu": "TLC LIGHTING", "tuoi_tho": "40.000h, 40.000 giờ", "bao_hanh": "24 tháng, 2 năm", "dien_ap_ac": "85-265V", "quang_thong": "400Lm"}</t>
         </is>
       </c>
       <c r="J4" t="n">
@@ -45201,7 +46466,7 @@
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>{"cong_suat": "5W", "anh_sang": "Trắng, Vàng", "nhiet_do_mau": "3500K/6500K", "kich_thuoc": "Ø110×35", "hieu_suat_quang": "110-120 Lm/w", "chi_so_hoan_mau": "CRI≥85", "dien_ap": "85-265V", "lo_khoet": "Ø76", "thuong_hieu": "TLC LIGHTING", "tuoi_tho": "40.000h", "bao_hanh": "24 tháng", "do_hoan_mau": "&gt;85Ra", "quang_thong": "400Lm", "dien_ap_ac": "85-265V"}</t>
+          <t>{"cong_suat": "5W", "anh_sang": "Trắng/ Vàng", "nhiet_do_mau": "3500K/6500K", "kich_thuoc": "Ø110×35", "hieu_suat_quang": "110-120 Lm/w", "chi_so_hoan_mau": "CRI≥85", "dien_ap": "85-265V", "lo_khoet": "Ø76", "thuong_hieu": "TLC LIGHTING", "tuoi_tho": "40.000h", "bao_hanh": "24 tháng", "dien_ap_ac": "85-265V", "do_hoan_mau": "&gt;85Ra", "quang_thong": "400Lm", "tuoi_tho_gio": "40.000 giờ"}</t>
         </is>
       </c>
       <c r="J6" t="n">
@@ -45215,6 +46480,15 @@
       <c r="M6" t="inlineStr">
         <is>
           <t>https://tlclighting.com.vn/wp-content/uploads/2019/11/IMG_2428.jpg</t>
+        </is>
+      </c>
+      <c r="P6" t="inlineStr">
+        <is>
+          <t>Khả năng tiết kiệm điện năng hiệu quả: Tiết kiệm điện gấp 2 lần đèn huỳnh quang, compact và gấp 10 lần so với đèn sợi đốt nhờ sử dụng chip LED thế hệ mới.
+Đèn có dòng mặt vàng với công suất 5w thông dụng giúp người dùng có thể tùy ý lựa chọn phù hợp với không gian. Mang lại vẻ sang trọng và tinh tế.
+Đèn có đế mỏng, phù hợp với tất cả các loại trần, kể cả trần thạch cao, trần gỗ…
+Chỉ số hoàn màu của đèn cao Ra &gt; 85 kết hợp với chóa đèn từ mica sần mờ giúp mang lại ánh sáng đồng đều, trung thực giúp chống lóa mắt, mỏi mắt, bảo vệ mắt hiệu quả theo tiêu chuẩn Châu Âu.
+Tuổi thọ đèn cao, đạt 40.000 giờ chiếu sáng. Chế độ bảo hành đèn 24 tháng trên toàn quốc giúp người dùng tiết kiệm chi phí thay thế, đổi mới.</t>
         </is>
       </c>
       <c r="Q6" t="inlineStr">
@@ -45238,6 +46512,19 @@
 3 màu: Tham khảo tại đây</t>
         </is>
       </c>
+      <c r="T6" t="inlineStr">
+        <is>
+          <t>Ưu đặc điểm đèn downlight 5W đế mỏng viền vàng
+Khả năng tiết kiệm điện năng hiệu quả: Tiết kiệm điện gấp 2 lần đèn huỳnh quang, compact và gấp 10 lần so với đèn sợi đốt nhờ sử dụng chip LED thế hệ mới.
+Đèn có dòng mặt vàng với công suất 5w thông dụng giúp người dùng có thể tùy ý lựa chọn phù hợp với không gian. Mang lại vẻ sang trọng và tinh tế.
+Đèn có đế mỏng, phù hợp với tất cả các loại trần, kể cả trần thạch cao, trần gỗ…
+Chỉ số hoàn màu của đèn cao Ra &gt; 85 kết hợp với chóa đèn từ mica sần mờ giúp mang lại ánh sáng đồng đều, trung thực giúp chống lóa mắt, mỏi mắt, bảo vệ mắt hiệu quả theo tiêu chuẩn Châu Âu.
+Tuổi thọ đèn cao, đạt 40.000 giờ chiếu sáng. Chế độ bảo hành đèn 24 tháng trên toàn quốc giúp người dùng tiết kiệm chi phí thay thế, đổi mới.
+Các mẫu
+đèn LED âm trần màu vàng
+được ưa chuộng nhất</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -45265,7 +46552,7 @@
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>{"cong_suat": "7W", "anh_sang": "Ba màu", "nhiet_do_mau": "3500K/6500K", "kich_thuoc": "Ø120×35", "hieu_suat_quang": "110-120 Lm/w", "chi_so_hoan_mau": "CRI≥85", "dien_ap": "85-265V", "lo_khoet": "Ø90", "thuong_hieu": "TLC LIGHTING", "tuoi_tho": "40.000h", "bao_hanh": "24 tháng", "dien_ap_ac": "85-265V", "do_hoan_mau": "&gt;85Ra", "quang_thong": "560Lm", "tuoi_tho_gio": "40.000 giờ"}</t>
+          <t>{"cong_suat": "7W", "anh_sang": "Ba màu", "nhiet_do_mau": "3500K/6500K", "kich_thuoc": "Ø120×35", "hieu_suat_quang": "110-120 Lm/w", "chi_so_hoan_mau": "CRI≥85", "dien_ap": "85-265V", "lo_khoet": "Ø90", "thuong_hieu": "TLC LIGHTING", "tuoi_tho": "40.000h", "bao_hanh": "24 tháng", "do_hoan_mau": "&gt;85Ra", "quang_thong": "560Lm", "tuoi_tho_den": "40.000 giờ"}</t>
         </is>
       </c>
       <c r="J7" t="n">
@@ -45279,6 +46566,16 @@
       <c r="M7" t="inlineStr">
         <is>
           <t>https://tlclighting.com.vn/wp-content/uploads/2019/07/IMG_2619-min.jpg</t>
+        </is>
+      </c>
+      <c r="P7" t="inlineStr">
+        <is>
+          <t>Đèn âm trần 7w đế mỏng có thiết kế mặt đèn đẹp, với điểm nhấn viền kim loại màu trắng hoặc vàng, đảm bảo về tính thẩm mỹ cho không gian sống. Hơn nữa, mặt đèn được sơn bóng chống trầy xước, đảm bảo duy trì vẻ đẹp của đèn trong thời gian dài.
+Đèn có thiết kế độ dày chỉ 35mm, thích hợp lắp đặt cho tất cả các loại trần cho đa dạng các công trình
+Chip LED được sử dụng là dòng chip LED 5730 siêu sáng, cho hiệu suất phát quang đạt 80 Lm/w, sáng hơn gấp 2 lần so với đèn compact, huỳnh quang, 10 lần so với đèn sợ đốt
+Chóa đèn được cấu tạo từ Mica sần với độ thấu quang 92% cho ánh sáng trung thực, tốt cho mắt, chống lóa, mỏi mắt, bảo vệ mắt hiệu quả theo tiêu chuẩn Châu Âu
+Tuổi thọ đèn cao, lên tới 40.000 giờ, hạn chế chi phí thay mới, sửa chữa
+Nguồn đèn được cấu tạo từ những linh kiện cao cấp cho hiệu quả chiếu sáng ổn định, hạn chế các hiện tượng chập, cháy</t>
         </is>
       </c>
       <c r="Q7" t="inlineStr">
@@ -45302,6 +46599,17 @@
 3 màu: Tham khảo tại đây</t>
         </is>
       </c>
+      <c r="T7" t="inlineStr">
+        <is>
+          <t>Đặc điểm của đèn Led âm trần 7w đế mỏng viền trắng (3 màu)
+Đèn âm trần 7w đế mỏng có thiết kế mặt đèn đẹp, với điểm nhấn viền kim loại màu trắng hoặc vàng, đảm bảo về tính thẩm mỹ cho không gian sống. Hơn nữa, mặt đèn được sơn bóng chống trầy xước, đảm bảo duy trì vẻ đẹp của đèn trong thời gian dài.
+Đèn có thiết kế độ dày chỉ 35mm, thích hợp lắp đặt cho tất cả các loại trần cho đa dạng các công trình
+Chip LED được sử dụng là dòng chip LED 5730 siêu sáng, cho hiệu suất phát quang đạt 80 Lm/w, sáng hơn gấp 2 lần so với đèn compact, huỳnh quang, 10 lần so với đèn sợ đốt
+Chóa đèn được cấu tạo từ Mica sần với độ thấu quang 92% cho ánh sáng trung thực, tốt cho mắt, chống lóa, mỏi mắt, bảo vệ mắt hiệu quả theo tiêu chuẩn Châu Âu
+Tuổi thọ đèn cao, lên tới 40.000 giờ, hạn chế chi phí thay mới, sửa chữa
+Nguồn đèn được cấu tạo từ những linh kiện cao cấp cho hiệu quả chiếu sáng ổn định, hạn chế các hiện tượng chập, cháy</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -45329,7 +46637,7 @@
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>{"cong_suat": "7W", "anh_sang": "Trắng/ Vàng, Trắng, Vàng", "nhiet_do_mau": "3500K/6500K", "kich_thuoc": "Ø120×35", "hieu_suat_quang": "110-120 Lm/w, 80 Lm/w", "chi_so_hoan_mau": "CRI≥85, &gt;85Ra", "dien_ap": "85-265V", "lo_khoet": "Ø90", "thuong_hieu": "TLC LIGHTING", "tuoi_tho": "40.000h, 40.000 giờ", "bao_hanh": "24 tháng, 2 năm", "dien_ap_ac": "85-265V", "do_hoan_mau": "&gt;85Ra", "quang_thong": "560Lm"}</t>
+          <t>{"cong_suat": "7W", "anh_sang": "Trắng/ Vàng", "nhiet_do_mau": "3500K/6500K", "kich_thuoc": "Ø120×35", "hieu_suat_quang": "110-120 Lm/w", "chi_so_hoan_mau": "CRI≥85", "dien_ap": "85-265V", "lo_khoet": "Ø90", "thuong_hieu": "TLC LIGHTING", "tuoi_tho": "40.000h", "bao_hanh": "24 tháng", "do_hoan_mau": "&gt;85Ra", "quang_thong": "560Lm"}</t>
         </is>
       </c>
       <c r="J8" t="n">
@@ -45415,7 +46723,7 @@
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>{"cong_suat": "7W", "anh_sang": "Ba màu", "nhiet_do_mau": "3500K/6500K", "kich_thuoc": "Ø120×35", "hieu_suat_quang": "110-120 Lm/w", "chi_so_hoan_mau": "CRI≥85", "dien_ap": "85-265V", "lo_khoet": "Ø90", "thuong_hieu": "TLC LIGHTING", "tuoi_tho": "40.000h", "bao_hanh": "24 tháng", "dien_ap_ac": "85-265V", "do_hoan_mau": "&gt;85Ra", "quang_thong": "560Lm", "tuoi_tho_gio": "40.000 giờ", "bao_hanh_nam": "2 năm"}</t>
+          <t>{"cong_suat": "7W", "anh_sang": "Ba màu", "nhiet_do_mau": "3500K/6500K", "kich_thuoc": "Ø120×35", "hieu_suat_quang": "110-120 Lm/w", "chi_so_hoan_mau": "CRI≥85", "dien_ap": "85-265V", "lo_khoet": "Ø90", "thuong_hieu": "TLC LIGHTING", "tuoi_tho": "40.000h", "bao_hanh": "24 tháng", "dien_ap_ac": "85-265V", "do_hoan_mau": "&gt;85Ra", "quang_thong": "560Lm", "tuoi_tho_gio": "40.000 giờ"}</t>
         </is>
       </c>
       <c r="J9" t="n">
@@ -45500,7 +46808,7 @@
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>{"cong_suat": "7W", "anh_sang": "Trắng/ Vàng", "nhiet_do_mau": "3500K/6500K", "kich_thuoc": "Ø120×35", "hieu_suat_quang": "110-120 Lm/w", "chi_so_hoan_mau": "CRI≥85", "dien_ap": "85-265V", "lo_khoet": "Ø90", "thuong_hieu": "TLC LIGHTING", "tuoi_tho": "40.000h", "bao_hanh": "24 tháng", "do_hoan_mau": "&gt;85Ra", "quang_thong": "560Lm"}</t>
+          <t>{"cong_suat": "7W", "anh_sang": "Trắng/ Vàng", "nhiet_do_mau": "3500K/6500K", "kich_thuoc": "Ø120×35", "hieu_suat_quang": "110-120 Lm/w", "chi_so_hoan_mau": "CRI≥85", "dien_ap": "85-265V", "lo_khoet": "Ø90", "thuong_hieu": "TLC LIGHTING", "tuoi_tho": "40.000h", "bao_hanh": "24 tháng", "do_hoan_mau": "&gt;85Ra", "quang_thong": "560Lm", "dien_ap_ac": "85-265V"}</t>
         </is>
       </c>
       <c r="J10" t="n">
@@ -45514,6 +46822,15 @@
       <c r="M10" t="inlineStr">
         <is>
           <t>https://tlclighting.com.vn/wp-content/uploads/2019/11/IMG_2428.jpg</t>
+        </is>
+      </c>
+      <c r="P10" t="inlineStr">
+        <is>
+          <t>Thiết kế tinh tế với điểm nhấn viền kim loại sang trọng, tinh tế, đem lại không gian thẩm mỹ cho không gian sống
+Phần đế mỏng khoảng 35mm, phù hợp với đa dạng các loại trần: trần nhựa, trần thạch cao, trần bê tông, trần nhôm
+Ánh sáng: trắng, vàng phù hợp với yêu cầu của người tiêu dùng
+Đèn LED âm trần chống chói có khả năng tiết kiệm điện năng hiệu quả, hiệu suất phát quang lên tới 110-120 Lm/w. Chỉ số hoàn màu ánh sáng Ra&gt; 85, cho ánh sáng trung thực, bảo vệ mắt hiệu quả theo tiêu chuẩn Châu Âu, chống lóa – mỏi mắt.
+Tuổi thọ của đèn cao lên đến 40.000 giờ giúp hạn chế chi phí thay mới, bảo trì, bảo dưỡng.</t>
         </is>
       </c>
       <c r="Q10" t="inlineStr">
@@ -45537,6 +46854,17 @@
 3 màu: Tham khảo tại đâ</t>
         </is>
       </c>
+      <c r="T10" t="inlineStr">
+        <is>
+          <t>Đặc điểm của đèn LED âm trần 7w đế mỏng viền vàng
+Đèn LED âm trần 7W đế mỏng viền vàng đơn sắc có những đặc điểm sau:
+Thiết kế tinh tế với điểm nhấn viền kim loại sang trọng, tinh tế, đem lại không gian thẩm mỹ cho không gian sống
+Phần đế mỏng khoảng 35mm, phù hợp với đa dạng các loại trần: trần nhựa, trần thạch cao, trần bê tông, trần nhôm
+Ánh sáng: trắng, vàng phù hợp với yêu cầu của người tiêu dùng
+Đèn LED âm trần chống chói có khả năng tiết kiệm điện năng hiệu quả, hiệu suất phát quang lên tới 110-120 Lm/w. Chỉ số hoàn màu ánh sáng Ra&gt; 85, cho ánh sáng trung thực, bảo vệ mắt hiệu quả theo tiêu chuẩn Châu Âu, chống lóa – mỏi mắt.
+Tuổi thọ của đèn cao lên đến 40.000 giờ giúp hạn chế chi phí thay mới, bảo trì, bảo dưỡng.</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
@@ -45554,7 +46882,7 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>TLC-ACM-VV-07W</t>
+          <t>TLC–ACM–VT–05W</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
@@ -45650,7 +46978,7 @@
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>{"cong_suat": "9W", "anh_sang": "Đơn sắc, Trắng, Vàng", "nhiet_do_mau": "3500K/6500K", "kich_thuoc": "Ø120×35, 148×35mm", "hieu_suat_quang": "110-120 Lm/w", "chi_so_hoan_mau": "CRI≥85, &gt;85Ra", "dien_ap": "85-265V", "lo_khoet": "Ø90, Ø105", "thuong_hieu": "TLC LIGHTING, Việt Nam", "tuoi_tho": "40.000h, 40.000 giờ", "bao_hanh": "24 tháng, 2 năm", "quang_thong": "720 Lm"}</t>
+          <t>{"cong_suat": "9W", "anh_sang": "Đơn sắc", "nhiet_do_mau": "3500K/6500K", "kich_thuoc": "Ø120×35", "hieu_suat_quang": "110-120 Lm/w", "chi_so_hoan_mau": "CRI≥85", "dien_ap": "85-265V", "lo_khoet": "Ø90", "thuong_hieu": "TLC LIGHTING", "tuoi_tho": "40.000h", "bao_hanh": "24 tháng"}</t>
         </is>
       </c>
       <c r="J12" t="n">
@@ -45737,7 +47065,7 @@
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>{"cong_suat": "5W", "anh_sang": "Trắng/ Vàng", "nhiet_do_mau": "3500K/6500K", "kich_thuoc": "Ø110×35", "hieu_suat_quang": "110-120 Lm/w", "chi_so_hoan_mau": "CRI≥85", "dien_ap": "85-265V", "lo_khoet": "Ø76", "thuong_hieu": "TLC LIGHTING", "tuoi_tho": "40.000h", "bao_hanh": "24 tháng", "do_hoan_mau": "&gt;85Ra", "quang_thong": "400 Lm"}</t>
+          <t>{"cong_suat": "5W", "anh_sang": "Trắng/ Vàng, Trắng, Vàng", "nhiet_do_mau": "3500K/6500K", "kich_thuoc": "Ø110×35", "hieu_suat_quang": "110-120 Lm/w", "chi_so_hoan_mau": "CRI≥85", "dien_ap": "85-265V", "lo_khoet": "Ø76", "thuong_hieu": "TLC LIGHTING", "tuoi_tho": "40.000h, 40.000 giờ", "bao_hanh": "24 tháng, 2 năm", "do_hoan_mau": "&gt;85Ra", "quang_thong": "400 Lm"}</t>
         </is>
       </c>
       <c r="J13" t="n">
@@ -45824,7 +47152,7 @@
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>{"cong_suat": "7W", "anh_sang": "3 màu", "nhiet_do_mau": "3500K/6500K", "kich_thuoc": "ø120x38mm", "lo_khoet": "ø90mm", "chip_led": "OSRAM", "hieu_suat_quang": "110-120 Lm/w", "chi_so_hoan_mau": "CRI≥85", "dien_ap": "85-265V", "thuong_hieu": "TLC LIGHTING", "tuoi_tho": "40.000h", "bao_hanh": "24 tháng", "dien_ap_ac": "85-265V", "do_hoan_mau": "&gt;85Ra", "che_do_anh_sang": "Chống chói", "duong_kinh_lo_khoet": "D90mm", "duong_kinh_mat": "D120mm", "chieu_day": "38mm", "chat_lieu": "Hợp kim nhôm"}</t>
+          <t>{"cong_suat": "7W", "anh_sang": "3 màu", "nhiet_do_mau": "3500K/6500K", "kich_thuoc": "ø120x38mm", "lo_khoet": "ø90mm", "chip_led": "OSRAM", "hieu_suat_quang": "110-120 Lm/w", "chi_so_hoan_mau": "CRI≥85", "dien_ap": "85-265V", "thuong_hieu": "TLC LIGHTING", "tuoi_tho": "40.000h", "bao_hanh": "24 tháng", "do_hoan_mau": "&gt;85Ra", "che_do_anh_sang": "Chống chói", "duong_kinh_lo_khoet": "D90mm", "duong_kinh_mat": "D120mm", "chieu_day": "38mm", "chat_lieu": "Hợp kim nhôm"}</t>
         </is>
       </c>
       <c r="J14" t="n">
@@ -45910,7 +47238,7 @@
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>{"cong_suat": "7W", "anh_sang": "Trắng/Vàng", "nhiet_do_mau": "3500K/6500K", "kich_thuoc": "ø120x38mm", "lo_khoet": "ø90mm", "chip_led": "OSRAM", "hieu_suat_quang": "110-120 Lm/w", "chi_so_hoan_mau": "CRI≥85", "dien_ap": "85-265V", "thuong_hieu": "TLC LIGHTING", "tuoi_tho": "40.000h", "bao_hanh": "24 tháng", "dien_ap_ac": "85-265V", "hieu_suat_quang_2": "~110Lm/w", "do_hoan_mau": "&gt;85Ra", "che_do_anh_sang": "Chống chói", "duong_kinh_lo_khoet": "D90mm", "duong_kinh_mat": "D120mm", "chieu_day": "38mm", "chat_lieu": "Hợp kim nhôm"}</t>
+          <t>{"cong_suat": "7W", "anh_sang": "Trắng/Vàng", "nhiet_do_mau": "3500K/6500K", "kich_thuoc": "ø120x38mm", "lo_khoet": "ø90mm", "chip_led": "OSRAM", "hieu_suat_quang": "110-120 Lm/w", "chi_so_hoan_mau": "CRI≥85", "dien_ap": "85-265V", "thuong_hieu": "TLC LIGHTING", "tuoi_tho": "40.000h", "bao_hanh": "24 tháng", "dien_ap_ac": "85-265V", "do_hoan_mau": "&gt;85Ra", "che_do_anh_sang": "Chống chói", "duong_kinh_lo_khoet": "D90mm", "duong_kinh_mat": "D120mm", "chieu_day": "38mm", "chat_lieu": "Hợp kim nhôm"}</t>
         </is>
       </c>
       <c r="J15" t="n">
@@ -46282,7 +47610,7 @@
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>{"cong_suat_tai_toi_da": "100W", "dien_ap_hoat_dong": "220V-250V", "loai_dui": "E27", "cap_bao_ve": "IP67", "chat_lieu_vo": "Nhựa PC", "mau_sac": "Đen/ Trắng", "thuong_hieu": "TLC", "xuat_xu": "Việt Nam"}</t>
+          <t>{"cong_suat_tai_toi_da": "100W", "dien_ap_hoat_dong": "220V-250V", "loai_dui": "E27", "cap_bao_ve": "IP67", "chat_lieu_vo": "Nhựa PC", "mau_sac": "Đen/ Trắng", "thuong_hieu": "TLC", "xuat_xu": "Việt Nam", "cong_suat_chiu_tai_toi_da": "100W", "dien_ap": "220V-250V", "chat_lieu": "Vỏ nhựa PC, 2 cực bằng đồng"}</t>
         </is>
       </c>
       <c r="L4" t="inlineStr">
@@ -46519,7 +47847,7 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>TLC-DXC</t>
+          <t>TLC-DGX</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
